--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -11,6 +11,7 @@
     <sheet name="EPA (Statbotics)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="OPR (TBA)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Rankings (TBA)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2nd Pick List" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +72,11 @@
         <fgColor rgb="00B71C1C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E65100"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -98,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,6 +122,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7461,4 +7470,1224 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Pick Order</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Team #</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>OPR</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>CCWM</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>DNP (x = exclude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>858</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Demons Robotics</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>904</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>D Cubed</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Bedford Express</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2075</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Enigma Robotics</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2771</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Code Red Robotics the Stray Dogs</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>3234</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Red Arrows</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3620</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Average Joes</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>3875</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Red Storm Robotics</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>RoboRangers</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>4967</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>That ONE Team-OurNextEngineers</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>5166</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Fabricators</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>5256</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Atomics</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>5501</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Bobcats</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>5980</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>East Grand Rapids Robotics</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>6081</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Digital Dislocators</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>7220</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Steel Falcons</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7221</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Viking Robotics</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>7256</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Irish Robotics</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7289</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Blue Eagles</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7656</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>MC Hammers</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>7658</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>MagiTech</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7808</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Kalkaska Dragoneers</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7809</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>FROST BYTE  Robotics</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7818</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Williamston High School Vespidae</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>8285</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Bionic Bulldogs</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>8423</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Next Express</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>8767</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Dark Horse Robotics</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>9206</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>GRP Titans</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>9208</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Eddies Circuit</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>9549</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>The Mechadogs</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>9566</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Red Storm Rookies</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>9638</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Tigers, Bro!</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>9671</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Robosnacks</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>9685</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Crystal Oscillators</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>9756</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Robo Panthers</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>10181</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>ProtoWarriors</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>10633</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>BeeBotics</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>10642</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Comstock Colts</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>10664</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Big Reds</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>11399</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Timber Tech</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -737,40 +737,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L3" s="3" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>1367</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="4">
@@ -827,40 +813,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L4" s="2" t="n">
+        <v>68.08</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>109.18</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>109.18</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1655</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>27.16</v>
       </c>
     </row>
     <row r="5">
@@ -917,40 +889,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L5" s="3" t="n">
+        <v>88.79000000000001</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>1653</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>64.63</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>23.17</v>
       </c>
     </row>
     <row r="6">
@@ -1007,40 +965,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L6" s="2" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>56.69</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>56.69</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1545</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>13.54</v>
       </c>
     </row>
     <row r="7">
@@ -1097,40 +1041,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L7" s="3" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>1453</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>6.05</v>
       </c>
     </row>
     <row r="8">
@@ -1187,40 +1117,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L8" s="2" t="n">
+        <v>75.04000000000001</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1608</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>22.01</v>
       </c>
     </row>
     <row r="9">
@@ -1277,40 +1193,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L9" s="3" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>1547</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>17.9</v>
       </c>
     </row>
     <row r="10">
@@ -1367,40 +1269,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L10" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1434</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -3833,1354 +3721,1242 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>10633</v>
+        <v>1023</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45.8</v>
+        <v>68.08</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>104.79</v>
+        <v>109.18</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>104.79</v>
+        <v>109.18</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.65</v>
+        <v>18.87</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>63.81</v>
+        <v>63.16</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>25.33</v>
+        <v>27.16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1648</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>5166</v>
+        <v>2075</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>108.35</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>108.35</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>16.5</v>
+        <v>20.55</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>51.01</v>
+        <v>64.63</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>21.73</v>
+        <v>23.17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1619</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7220</v>
+        <v>10633</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45.04</v>
+        <v>45.8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>89.02</v>
+        <v>104.79</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>89.02</v>
+        <v>104.79</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>20.24</v>
+        <v>15.65</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>54.64</v>
+        <v>63.81</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>14.14</v>
+        <v>25.33</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1619</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4967</v>
+        <v>5166</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>68.89</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>86.59</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>86.59</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>19.61</v>
+        <v>16.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45.87</v>
+        <v>51.01</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>21.1</v>
+        <v>21.73</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1613</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7656</v>
+        <v>7220</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>50.91</v>
+        <v>45.04</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>80.70999999999999</v>
+        <v>89.02</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>80.70999999999999</v>
+        <v>89.02</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>10.28</v>
+        <v>20.24</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>47.29</v>
+        <v>54.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>23.14</v>
+        <v>14.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1600</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>9208</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>44.43</v>
+        <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>60.89</v>
+        <v>86.59</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>60.89</v>
+        <v>86.59</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>15.07</v>
+        <v>19.61</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>34.36</v>
+        <v>45.87</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>11.46</v>
+        <v>21.1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1555</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6081</v>
+        <v>3620</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>59.73</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>58.86</v>
+        <v>84.16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>58.86</v>
+        <v>84.16</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>13.66</v>
+        <v>18.91</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>25.05</v>
+        <v>43.23</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20.14</v>
+        <v>22.01</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1550</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>858</v>
+        <v>7656</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>55.1</v>
+        <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>51.63</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>51.63</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>6.46</v>
+        <v>10.28</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>27.33</v>
+        <v>47.29</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>17.84</v>
+        <v>23.14</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1533</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>28.04</v>
+        <v>44.43</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>39.76</v>
+        <v>60.89</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>39.76</v>
+        <v>60.89</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.47</v>
+        <v>15.07</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>18.9</v>
+        <v>34.36</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.4</v>
+        <v>11.46</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1504</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>9685</v>
+        <v>6081</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>27.75</v>
+        <v>59.73</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>39.35</v>
+        <v>58.86</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>39.35</v>
+        <v>58.86</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>14.16</v>
+        <v>13.66</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.48</v>
+        <v>25.05</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>16.71</v>
+        <v>20.14</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1503</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>9756</v>
+        <v>3875</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>29.21</v>
+        <v>50.66</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>38.47</v>
+        <v>57.35</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>38.47</v>
+        <v>57.35</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3.62</v>
+        <v>6.65</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>21.23</v>
+        <v>32.81</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>13.63</v>
+        <v>17.9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1501</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7808</v>
+        <v>2771</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>24.37</v>
+        <v>53.52</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>34.73</v>
+        <v>56.69</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>34.73</v>
+        <v>56.69</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>6.55</v>
+        <v>7.98</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>18.66</v>
+        <v>35.17</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>9.52</v>
+        <v>13.54</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1490</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9671</v>
+        <v>858</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>27.39</v>
+        <v>55.1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34.06</v>
+        <v>51.63</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>34.06</v>
+        <v>51.63</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>11.03</v>
+        <v>6.46</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>18.98</v>
+        <v>27.33</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4.06</v>
+        <v>17.84</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1489</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>5501</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>31.87</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31.87</v>
+        <v>39.76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>31.87</v>
+        <v>39.76</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>6.95</v>
+        <v>10.47</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>17.02</v>
+        <v>18.9</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>7.9</v>
+        <v>10.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1482</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7809</v>
+        <v>9685</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>23.83</v>
+        <v>27.75</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>31.74</v>
+        <v>39.35</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>31.74</v>
+        <v>39.35</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2.91</v>
+        <v>14.16</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>14.95</v>
+        <v>8.48</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>13.87</v>
+        <v>16.71</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1482</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>8767</v>
+        <v>9756</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.21</v>
+        <v>29.21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>31.51</v>
+        <v>38.47</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>31.51</v>
+        <v>38.47</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>4.86</v>
+        <v>3.62</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>17.87</v>
+        <v>21.23</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>13.63</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1481</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7289</v>
+        <v>7808</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>33.29</v>
+        <v>24.37</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>28.94</v>
+        <v>34.73</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>28.94</v>
+        <v>34.73</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>11.23</v>
+        <v>6.55</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>7.04</v>
+        <v>18.66</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.67</v>
+        <v>9.52</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1473</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9206</v>
+        <v>9671</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>21.07</v>
+        <v>27.39</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27.77</v>
+        <v>34.06</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>27.77</v>
+        <v>34.06</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.14</v>
+        <v>11.03</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10.09</v>
+        <v>18.98</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>12.54</v>
+        <v>4.06</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1470</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9566</v>
+        <v>5501</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>39.97</v>
+        <v>31.87</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>26.12</v>
+        <v>31.87</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>26.12</v>
+        <v>31.87</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3.19</v>
+        <v>6.95</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>14.75</v>
+        <v>17.02</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.18</v>
+        <v>7.9</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1464</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>8285</v>
+        <v>7809</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>39.07</v>
+        <v>23.83</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>24.48</v>
+        <v>31.74</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>24.48</v>
+        <v>31.74</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5.09</v>
+        <v>2.91</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>11.62</v>
+        <v>14.95</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>7.77</v>
+        <v>13.87</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1458</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7221</v>
+        <v>8767</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8.82</v>
+        <v>27.21</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>21.92</v>
+        <v>31.51</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>21.92</v>
+        <v>31.51</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>6.34</v>
+        <v>4.86</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7.07</v>
+        <v>17.87</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8.51</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1449</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>10664</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>21.7</v>
+        <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>21.7</v>
+        <v>28.94</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>21.7</v>
+        <v>28.94</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.73</v>
+        <v>11.23</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>11.59</v>
+        <v>7.04</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5.38</v>
+        <v>10.67</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1448</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7818</v>
+        <v>9206</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>32.45</v>
+        <v>21.07</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>20.47</v>
+        <v>27.77</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>20.47</v>
+        <v>27.77</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6.48</v>
+        <v>5.14</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>5.6</v>
+        <v>12.54</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1443</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>5256</v>
+        <v>9566</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>35.18</v>
+        <v>39.97</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>19.62</v>
+        <v>26.12</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>19.62</v>
+        <v>26.12</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5.27</v>
+        <v>3.19</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.06</v>
+        <v>14.75</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>3.29</v>
+        <v>8.18</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1440</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5980</v>
+        <v>8285</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>38.55</v>
+        <v>39.07</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>18.85</v>
+        <v>24.48</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>18.85</v>
+        <v>24.48</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>7.13</v>
+        <v>5.09</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>7.76</v>
+        <v>11.62</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>3.97</v>
+        <v>7.77</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1437</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9549</v>
+        <v>3234</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>17.6</v>
+        <v>22.62</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>17.48</v>
+        <v>22.9</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>17.48</v>
+        <v>22.9</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.36</v>
+        <v>4.98</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>10.59</v>
+        <v>11.87</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.53</v>
+        <v>6.05</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1431</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10642</v>
+        <v>7221</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>25.63</v>
+        <v>8.82</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>16.51</v>
+        <v>21.92</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>16.51</v>
+        <v>21.92</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.64</v>
+        <v>6.34</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6.37</v>
+        <v>7.07</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.5</v>
+        <v>8.51</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1426</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>11399</v>
+        <v>10664</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>23.74</v>
+        <v>21.7</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>16.22</v>
+        <v>21.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>16.22</v>
+        <v>21.7</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.81</v>
+        <v>4.73</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10.8</v>
+        <v>11.59</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.39</v>
+        <v>5.38</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1425</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>10181</v>
+        <v>7818</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>23.43</v>
+        <v>32.45</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>14.48</v>
+        <v>20.47</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>14.48</v>
+        <v>20.47</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>4.56</v>
+        <v>6.48</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6.45</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>3.47</v>
+        <v>5.6</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1417</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9638</v>
+        <v>5256</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>22.93</v>
+        <v>35.18</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>13.05</v>
+        <v>19.62</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>13.05</v>
+        <v>19.62</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6.04</v>
+        <v>5.27</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>3.26</v>
+        <v>11.06</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1410</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7256</v>
+        <v>5980</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>25.23</v>
+        <v>38.55</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>12.97</v>
+        <v>18.85</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12.97</v>
+        <v>18.85</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>2.57</v>
+        <v>7.13</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4.96</v>
+        <v>7.76</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>5.45</v>
+        <v>3.97</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1409</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7658</v>
+        <v>4325</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>14.34</v>
+        <v>32.52</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>5.84</v>
+        <v>18.16</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>5.84</v>
+        <v>18.16</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3.29</v>
+        <v>7.79</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4.91</v>
+        <v>8.77</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-2.37</v>
+        <v>1.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1370</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>904</v>
+        <v>9549</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>The Mechadogs</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>1431</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>1023</v>
+        <v>10642</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Comstock Colts</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>1426</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>2075</v>
+        <v>11399</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Timber Tech</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>1425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>2771</v>
+        <v>10181</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ProtoWarriors</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>1417</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3234</v>
+        <v>9638</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Tigers, Bro!</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1410</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>3620</v>
+        <v>7256</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Irish Robotics</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>1409</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3875</v>
+        <v>7658</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>MagiTech</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1370</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>4325</v>
+        <v>904</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>D Cubed</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>1367</v>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -1117,40 +1117,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L8" s="2" t="n">
+        <v>75.04000000000001</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1608</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>22.01</v>
       </c>
     </row>
     <row r="9">
@@ -1283,40 +1269,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L10" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1433</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -1525,40 +1497,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L13" s="3" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>1440</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>3.29</v>
       </c>
     </row>
     <row r="14">
@@ -1691,40 +1649,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L15" s="3" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>1436</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>3.97</v>
       </c>
     </row>
     <row r="16">
@@ -1781,40 +1725,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L16" s="2" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>1550</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>20.14</v>
       </c>
     </row>
     <row r="17">
@@ -2175,40 +2105,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L21" s="3" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>80.70999999999999</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>80.70999999999999</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>23.14</v>
       </c>
     </row>
     <row r="22">
@@ -2949,40 +2865,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L31" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>1430</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="32">
@@ -3267,40 +3169,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L35" s="3" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>1503</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>16.71</v>
       </c>
     </row>
     <row r="36">
@@ -3357,40 +3245,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L36" s="2" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>13.63</v>
       </c>
     </row>
     <row r="37">
@@ -4033,1182 +3907,1056 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>9208</v>
+        <v>3620</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>44.43</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>60.89</v>
+        <v>84.16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60.89</v>
+        <v>84.16</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>15.07</v>
+        <v>18.91</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>34.36</v>
+        <v>43.23</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>11.46</v>
+        <v>22.01</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1555</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3875</v>
+        <v>7656</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.66</v>
+        <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>57.35</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>57.35</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>6.65</v>
+        <v>10.28</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>32.81</v>
+        <v>47.29</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>17.9</v>
+        <v>23.14</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1547</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2771</v>
+        <v>9208</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>53.52</v>
+        <v>44.43</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>56.69</v>
+        <v>60.89</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>56.69</v>
+        <v>60.89</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>7.98</v>
+        <v>15.07</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>35.17</v>
+        <v>34.36</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>13.54</v>
+        <v>11.46</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1545</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>858</v>
+        <v>6081</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>55.1</v>
+        <v>59.73</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>51.63</v>
+        <v>58.86</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>51.63</v>
+        <v>58.86</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>6.46</v>
+        <v>13.66</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>27.33</v>
+        <v>25.05</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>17.84</v>
+        <v>20.14</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1533</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8423</v>
+        <v>3875</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>28.04</v>
+        <v>50.66</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>39.76</v>
+        <v>57.35</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>39.76</v>
+        <v>57.35</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>10.47</v>
+        <v>6.65</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>18.9</v>
+        <v>32.81</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.4</v>
+        <v>17.9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1504</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7808</v>
+        <v>2771</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>24.37</v>
+        <v>53.52</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>34.73</v>
+        <v>56.69</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>34.73</v>
+        <v>56.69</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>6.55</v>
+        <v>7.98</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>18.66</v>
+        <v>35.17</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>9.52</v>
+        <v>13.54</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1490</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9671</v>
+        <v>858</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>27.39</v>
+        <v>55.1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34.06</v>
+        <v>51.63</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>34.06</v>
+        <v>51.63</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>11.03</v>
+        <v>6.46</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>18.98</v>
+        <v>27.33</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4.06</v>
+        <v>17.84</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1488</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>5501</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>31.87</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31.87</v>
+        <v>39.76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>31.87</v>
+        <v>39.76</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>6.95</v>
+        <v>10.47</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>17.02</v>
+        <v>18.9</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>7.9</v>
+        <v>10.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1482</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7809</v>
+        <v>9685</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>23.83</v>
+        <v>27.75</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>31.74</v>
+        <v>39.35</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>31.74</v>
+        <v>39.35</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2.91</v>
+        <v>14.16</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>14.95</v>
+        <v>8.48</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>13.87</v>
+        <v>16.71</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1482</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>8767</v>
+        <v>9756</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.21</v>
+        <v>29.21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>31.51</v>
+        <v>38.47</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>31.51</v>
+        <v>38.47</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>4.86</v>
+        <v>3.62</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>17.87</v>
+        <v>21.23</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>13.63</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1481</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7289</v>
+        <v>7808</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>33.29</v>
+        <v>24.37</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>28.94</v>
+        <v>34.73</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>28.94</v>
+        <v>34.73</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>11.23</v>
+        <v>6.55</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>7.04</v>
+        <v>18.66</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.67</v>
+        <v>9.52</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1473</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9206</v>
+        <v>9671</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>21.07</v>
+        <v>27.39</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27.77</v>
+        <v>34.06</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>27.77</v>
+        <v>34.06</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.14</v>
+        <v>11.03</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10.09</v>
+        <v>18.98</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>12.54</v>
+        <v>4.06</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1469</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9566</v>
+        <v>5501</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>39.97</v>
+        <v>31.87</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>26.12</v>
+        <v>31.87</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>26.12</v>
+        <v>31.87</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3.19</v>
+        <v>6.95</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>14.75</v>
+        <v>17.02</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.18</v>
+        <v>7.9</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1464</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>8285</v>
+        <v>7809</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>39.07</v>
+        <v>23.83</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>24.48</v>
+        <v>31.74</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>24.48</v>
+        <v>31.74</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5.09</v>
+        <v>2.91</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>11.62</v>
+        <v>14.95</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>7.77</v>
+        <v>13.87</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1458</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3234</v>
+        <v>8767</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>22.62</v>
+        <v>27.21</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>22.9</v>
+        <v>31.51</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>22.9</v>
+        <v>31.51</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.98</v>
+        <v>4.86</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>11.87</v>
+        <v>17.87</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>6.05</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1453</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7221</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8.82</v>
+        <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>21.92</v>
+        <v>28.94</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>21.92</v>
+        <v>28.94</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6.34</v>
+        <v>11.23</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.07</v>
+        <v>7.04</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.51</v>
+        <v>10.67</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1449</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>10664</v>
+        <v>9206</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>21.7</v>
+        <v>21.07</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>21.7</v>
+        <v>27.77</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>21.7</v>
+        <v>27.77</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>4.73</v>
+        <v>5.14</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11.59</v>
+        <v>10.09</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>5.38</v>
+        <v>12.54</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1448</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>7818</v>
+        <v>9566</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>32.45</v>
+        <v>39.97</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>20.47</v>
+        <v>26.12</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>20.47</v>
+        <v>26.12</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>6.48</v>
+        <v>3.19</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.390000000000001</v>
+        <v>14.75</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>5.6</v>
+        <v>8.18</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1443</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>10642</v>
+        <v>8285</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>25.63</v>
+        <v>39.07</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>16.51</v>
+        <v>24.48</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>16.51</v>
+        <v>24.48</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>4.64</v>
+        <v>5.09</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>6.37</v>
+        <v>11.62</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5.5</v>
+        <v>7.77</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1426</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>11399</v>
+        <v>3234</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>23.74</v>
+        <v>22.62</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>16.22</v>
+        <v>22.9</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>16.22</v>
+        <v>22.9</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.81</v>
+        <v>4.98</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>10.8</v>
+        <v>11.87</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.39</v>
+        <v>6.05</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1425</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10181</v>
+        <v>7221</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>23.43</v>
+        <v>8.82</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>14.48</v>
+        <v>21.92</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>14.48</v>
+        <v>21.92</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.56</v>
+        <v>6.34</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6.45</v>
+        <v>7.07</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>3.47</v>
+        <v>8.51</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1417</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9638</v>
+        <v>10664</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>22.93</v>
+        <v>21.7</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>13.05</v>
+        <v>21.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>13.05</v>
+        <v>21.7</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.04</v>
+        <v>4.73</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.26</v>
+        <v>11.59</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.75</v>
+        <v>5.38</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1410</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7256</v>
+        <v>7818</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>25.23</v>
+        <v>32.45</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>12.97</v>
+        <v>20.47</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.97</v>
+        <v>20.47</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2.57</v>
+        <v>6.48</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>4.96</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5.45</v>
+        <v>5.6</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1409</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7658</v>
+        <v>5256</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>14.34</v>
+        <v>35.18</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>5.84</v>
+        <v>19.62</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5.84</v>
+        <v>19.62</v>
       </c>
       <c r="F31" s="3" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>3.29</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>-2.37</v>
-      </c>
       <c r="I31" s="3" t="n">
-        <v>1370</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>904</v>
+        <v>5980</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>27.91</v>
+        <v>38.55</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5.38</v>
+        <v>18.85</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>5.38</v>
+        <v>18.85</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>4.03</v>
+        <v>7.13</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.89</v>
+        <v>7.76</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.45</v>
+        <v>3.97</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1367</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>3620</v>
+        <v>4325</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>RoboRangers</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>1433</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>4325</v>
+        <v>9549</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>The Mechadogs</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>1430</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>5256</v>
+        <v>10642</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Comstock Colts</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>1426</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5980</v>
+        <v>11399</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Timber Tech</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>1425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>6081</v>
+        <v>10181</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ProtoWarriors</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>1417</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7656</v>
+        <v>9638</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Tigers, Bro!</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1410</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>9549</v>
+        <v>7256</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Irish Robotics</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>1409</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>9685</v>
+        <v>7658</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>MagiTech</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1370</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>9756</v>
+        <v>904</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>D Cubed</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>1367</v>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -2409,26 +2409,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>1443</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>5.6</v>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -3321,26 +3335,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>1417</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="Q37" s="3" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>3.47</v>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3397,26 +3425,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L38" s="2" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>104.79</v>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>104.79</v>
-      </c>
-      <c r="O38" s="2" t="n">
-        <v>1648</v>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="Q38" s="2" t="n">
-        <v>63.81</v>
-      </c>
-      <c r="R38" s="2" t="n">
-        <v>25.33</v>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -3783,61 +3825,61 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>10633</v>
+        <v>5166</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45.8</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>104.79</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>104.79</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15.65</v>
+        <v>16.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.81</v>
+        <v>51.01</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25.33</v>
+        <v>21.73</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1648</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>5166</v>
+        <v>7220</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>89.02</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>89.02</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>16.5</v>
+        <v>20.24</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>51.01</v>
+        <v>54.64</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>21.73</v>
+        <v>14.14</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1619</v>
@@ -3845,464 +3887,464 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7220</v>
+        <v>4967</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45.04</v>
+        <v>68.89</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>89.02</v>
+        <v>86.59</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>89.02</v>
+        <v>86.59</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20.24</v>
+        <v>19.61</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>54.64</v>
+        <v>45.87</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>14.14</v>
+        <v>21.1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1619</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>3620</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>68.89</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>86.59</v>
+        <v>84.16</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>86.59</v>
+        <v>84.16</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>19.61</v>
+        <v>18.91</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>45.87</v>
+        <v>43.23</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>21.1</v>
+        <v>22.01</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1613</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3620</v>
+        <v>7656</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>50.91</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>84.16</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>84.16</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>18.91</v>
+        <v>10.28</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>43.23</v>
+        <v>47.29</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>22.01</v>
+        <v>23.14</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1608</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>9208</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.91</v>
+        <v>44.43</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>60.89</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>60.89</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.28</v>
+        <v>15.07</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>47.29</v>
+        <v>34.36</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23.14</v>
+        <v>11.46</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1600</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9208</v>
+        <v>6081</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>44.43</v>
+        <v>59.73</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>60.89</v>
+        <v>58.86</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>60.89</v>
+        <v>58.86</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>15.07</v>
+        <v>13.66</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>34.36</v>
+        <v>25.05</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11.46</v>
+        <v>20.14</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1555</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>6081</v>
+        <v>3875</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>59.73</v>
+        <v>50.66</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>58.86</v>
+        <v>57.35</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>58.86</v>
+        <v>57.35</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>13.66</v>
+        <v>6.65</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>25.05</v>
+        <v>32.81</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>20.14</v>
+        <v>17.9</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3875</v>
+        <v>2771</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>50.66</v>
+        <v>53.52</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>57.35</v>
+        <v>56.69</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>57.35</v>
+        <v>56.69</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6.65</v>
+        <v>7.98</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>32.81</v>
+        <v>35.17</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17.9</v>
+        <v>13.54</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1547</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>2771</v>
+        <v>858</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>53.52</v>
+        <v>55.1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>56.69</v>
+        <v>51.63</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>56.69</v>
+        <v>51.63</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>7.98</v>
+        <v>6.46</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>35.17</v>
+        <v>27.33</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13.54</v>
+        <v>17.84</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1545</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>858</v>
+        <v>8423</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>55.1</v>
+        <v>28.04</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>51.63</v>
+        <v>39.76</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>51.63</v>
+        <v>39.76</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6.46</v>
+        <v>10.47</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>27.33</v>
+        <v>18.9</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>17.84</v>
+        <v>10.4</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1533</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>9685</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>27.75</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>39.76</v>
+        <v>39.35</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39.76</v>
+        <v>39.35</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10.47</v>
+        <v>14.16</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>18.9</v>
+        <v>8.48</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.4</v>
+        <v>16.71</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>27.75</v>
+        <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39.35</v>
+        <v>38.47</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39.35</v>
+        <v>38.47</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>14.16</v>
+        <v>3.62</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>8.48</v>
+        <v>21.23</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>16.71</v>
+        <v>13.63</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1503</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9756</v>
+        <v>7808</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>29.21</v>
+        <v>24.37</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>38.47</v>
+        <v>34.73</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>38.47</v>
+        <v>34.73</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3.62</v>
+        <v>6.55</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>21.23</v>
+        <v>18.66</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>13.63</v>
+        <v>9.52</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1500</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7808</v>
+        <v>9671</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>24.37</v>
+        <v>27.39</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>34.73</v>
+        <v>34.06</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>34.73</v>
+        <v>34.06</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6.55</v>
+        <v>11.03</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>18.66</v>
+        <v>18.98</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.52</v>
+        <v>4.06</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9671</v>
+        <v>5501</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.39</v>
+        <v>31.87</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>34.06</v>
+        <v>31.87</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>34.06</v>
+        <v>31.87</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>11.03</v>
+        <v>6.95</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.98</v>
+        <v>17.02</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>4.06</v>
+        <v>7.9</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1488</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5501</v>
+        <v>7809</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>31.87</v>
+        <v>23.83</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>31.87</v>
+        <v>31.74</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.87</v>
+        <v>31.74</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6.95</v>
+        <v>2.91</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>17.02</v>
+        <v>14.95</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>7.9</v>
+        <v>13.87</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>1482</v>
@@ -4310,653 +4352,695 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7809</v>
+        <v>8767</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>23.83</v>
+        <v>27.21</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>31.74</v>
+        <v>31.51</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>31.74</v>
+        <v>31.51</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.91</v>
+        <v>4.86</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>14.95</v>
+        <v>17.87</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>13.87</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8767</v>
+        <v>7289</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>27.21</v>
+        <v>33.29</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.51</v>
+        <v>28.94</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>31.51</v>
+        <v>28.94</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.86</v>
+        <v>11.23</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>17.87</v>
+        <v>7.04</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>10.67</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1481</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7289</v>
+        <v>9206</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>33.29</v>
+        <v>21.07</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.94</v>
+        <v>27.77</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>28.94</v>
+        <v>27.77</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.23</v>
+        <v>5.14</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.04</v>
+        <v>10.09</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.67</v>
+        <v>12.54</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9206</v>
+        <v>9566</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>21.07</v>
+        <v>39.97</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>27.77</v>
+        <v>26.12</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>27.77</v>
+        <v>26.12</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.14</v>
+        <v>3.19</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>10.09</v>
+        <v>14.75</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>12.54</v>
+        <v>8.18</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1469</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9566</v>
+        <v>8285</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>39.97</v>
+        <v>39.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.12</v>
+        <v>24.48</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.12</v>
+        <v>24.48</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.19</v>
+        <v>5.09</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14.75</v>
+        <v>11.62</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8.18</v>
+        <v>7.77</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1464</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8285</v>
+        <v>3234</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>39.07</v>
+        <v>22.62</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24.48</v>
+        <v>22.9</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>24.48</v>
+        <v>22.9</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>5.09</v>
+        <v>4.98</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.62</v>
+        <v>11.87</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>7.77</v>
+        <v>6.05</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1458</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>3234</v>
+        <v>7221</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>22.62</v>
+        <v>8.82</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>22.9</v>
+        <v>21.92</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>22.9</v>
+        <v>21.92</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.98</v>
+        <v>6.34</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>11.87</v>
+        <v>7.07</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.05</v>
+        <v>8.51</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1453</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7221</v>
+        <v>10664</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8.82</v>
+        <v>21.7</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>21.92</v>
+        <v>21.7</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.92</v>
+        <v>21.7</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>6.34</v>
+        <v>4.73</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7.07</v>
+        <v>11.59</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8.51</v>
+        <v>5.38</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>10664</v>
+        <v>5256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>21.7</v>
+        <v>35.18</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.7</v>
+        <v>19.62</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.7</v>
+        <v>19.62</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.73</v>
+        <v>5.27</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.59</v>
+        <v>11.06</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.38</v>
+        <v>3.29</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1448</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7818</v>
+        <v>5980</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>32.45</v>
+        <v>38.55</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>20.47</v>
+        <v>18.85</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>20.47</v>
+        <v>18.85</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6.48</v>
+        <v>7.13</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>7.76</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5.6</v>
+        <v>3.97</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1443</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>5256</v>
+        <v>4325</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>35.18</v>
+        <v>32.52</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>19.62</v>
+        <v>18.16</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>19.62</v>
+        <v>18.16</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5.27</v>
+        <v>7.79</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.06</v>
+        <v>8.77</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>3.29</v>
+        <v>1.6</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1440</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5980</v>
+        <v>9549</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>38.55</v>
+        <v>17.6</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>18.85</v>
+        <v>17.48</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18.85</v>
+        <v>17.48</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7.13</v>
+        <v>5.36</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7.76</v>
+        <v>10.59</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3.97</v>
+        <v>1.53</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1436</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>4325</v>
+        <v>10642</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>32.52</v>
+        <v>25.63</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>18.16</v>
+        <v>16.51</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18.16</v>
+        <v>16.51</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7.79</v>
+        <v>4.64</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>8.77</v>
+        <v>6.37</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1433</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9549</v>
+        <v>11399</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>17.6</v>
+        <v>23.74</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>17.48</v>
+        <v>16.22</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>17.48</v>
+        <v>16.22</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5.36</v>
+        <v>5.81</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10.59</v>
+        <v>10.8</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.53</v>
+        <v>-0.39</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1430</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>10642</v>
+        <v>9638</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>25.63</v>
+        <v>22.93</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>16.51</v>
+        <v>13.05</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>16.51</v>
+        <v>13.05</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.64</v>
+        <v>6.04</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6.37</v>
+        <v>3.26</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1426</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>11399</v>
+        <v>7256</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23.74</v>
+        <v>25.23</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16.22</v>
+        <v>12.97</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>16.22</v>
+        <v>12.97</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.81</v>
+        <v>2.57</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>10.8</v>
+        <v>4.96</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>-0.39</v>
+        <v>5.45</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1425</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>7658</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.43</v>
+        <v>14.34</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>14.48</v>
+        <v>5.84</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>14.48</v>
+        <v>5.84</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4.56</v>
+        <v>3.29</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>6.45</v>
+        <v>4.91</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>3.47</v>
+        <v>-2.37</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1417</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9638</v>
+        <v>904</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22.93</v>
+        <v>27.91</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>13.05</v>
+        <v>5.38</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.05</v>
+        <v>5.38</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6.04</v>
+        <v>4.03</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3.26</v>
+        <v>0.89</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3.75</v>
+        <v>0.45</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1410</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7256</v>
+        <v>7818</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>1409</v>
+          <t>Williamston High School Vespidae</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7658</v>
+        <v>10181</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>1370</v>
+          <t>ProtoWarriors</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>904</v>
+        <v>10633</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>1367</v>
+          <t>BeeBotics</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -3553,22 +3553,22 @@
         <v>21.7</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>33.16</v>
+        <v>44.38</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>33.16</v>
+        <v>44.38</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1482</v>
+        <v>1511</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>7.11</v>
+        <v>8.74</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>17.73</v>
+        <v>23.4</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>8.32</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="41">
@@ -4124,188 +4124,188 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>10664</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>21.7</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>39.76</v>
+        <v>44.38</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39.76</v>
+        <v>44.38</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10.47</v>
+        <v>8.74</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>18.9</v>
+        <v>23.4</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.4</v>
+        <v>12.24</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1504</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9685</v>
+        <v>8423</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>27.75</v>
+        <v>28.04</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39.35</v>
+        <v>39.76</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39.35</v>
+        <v>39.76</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>14.16</v>
+        <v>10.47</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>8.48</v>
+        <v>18.9</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>16.71</v>
+        <v>10.4</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9756</v>
+        <v>9685</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>29.21</v>
+        <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>38.47</v>
+        <v>39.35</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>38.47</v>
+        <v>39.35</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3.62</v>
+        <v>14.16</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>21.23</v>
+        <v>8.48</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>13.63</v>
+        <v>16.71</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1500</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7808</v>
+        <v>9756</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>24.37</v>
+        <v>29.21</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>34.73</v>
+        <v>38.47</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>34.73</v>
+        <v>38.47</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6.55</v>
+        <v>3.62</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>18.66</v>
+        <v>21.23</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.52</v>
+        <v>13.63</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1490</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9671</v>
+        <v>7808</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.39</v>
+        <v>24.37</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>34.06</v>
+        <v>34.73</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>34.06</v>
+        <v>34.73</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>11.03</v>
+        <v>6.55</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.98</v>
+        <v>18.66</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>4.06</v>
+        <v>9.52</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>10664</v>
+        <v>9671</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>21.7</v>
+        <v>27.39</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>33.16</v>
+        <v>34.06</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>33.16</v>
+        <v>34.06</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>7.11</v>
+        <v>11.03</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>17.73</v>
+        <v>18.98</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.32</v>
+        <v>4.06</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1482</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="21">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -3553,22 +3553,22 @@
         <v>21.7</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>44.38</v>
+        <v>40.96</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>44.38</v>
+        <v>40.96</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1511</v>
+        <v>1503</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>8.74</v>
+        <v>9.51</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>23.4</v>
+        <v>23.96</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>12.24</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="41">
@@ -4135,22 +4135,22 @@
         <v>21.7</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>44.38</v>
+        <v>40.96</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>44.38</v>
+        <v>40.96</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>8.74</v>
+        <v>9.51</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>23.4</v>
+        <v>23.96</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>12.24</v>
+        <v>7.49</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1511</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="16">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -671,7 +671,7 @@
         <v>51.63</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>6.46</v>
@@ -747,7 +747,7 @@
         <v>5.38</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>4.03</v>
@@ -823,7 +823,7 @@
         <v>109.18</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1655</v>
+        <v>1648</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>18.87</v>
@@ -899,7 +899,7 @@
         <v>108.35</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>20.55</v>
@@ -975,7 +975,7 @@
         <v>56.69</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>7.98</v>
@@ -1051,7 +1051,7 @@
         <v>22.9</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>4.98</v>
@@ -1127,7 +1127,7 @@
         <v>84.16</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>18.91</v>
@@ -1203,7 +1203,7 @@
         <v>57.35</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.65</v>
@@ -1279,7 +1279,7 @@
         <v>18.16</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>7.79</v>
@@ -1355,7 +1355,7 @@
         <v>86.59</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>19.61</v>
@@ -1431,7 +1431,7 @@
         <v>89.23999999999999</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>16.5</v>
@@ -1507,7 +1507,7 @@
         <v>19.62</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>5.27</v>
@@ -1583,7 +1583,7 @@
         <v>31.87</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>6.95</v>
@@ -1659,7 +1659,7 @@
         <v>18.85</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>7.13</v>
@@ -1735,7 +1735,7 @@
         <v>58.86</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>13.66</v>
@@ -1811,7 +1811,7 @@
         <v>89.02</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1619</v>
+        <v>1610</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>20.24</v>
@@ -1887,7 +1887,7 @@
         <v>21.92</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>6.34</v>
@@ -1963,7 +1963,7 @@
         <v>12.97</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.57</v>
@@ -2039,7 +2039,7 @@
         <v>28.94</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>11.23</v>
@@ -2115,7 +2115,7 @@
         <v>80.70999999999999</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.28</v>
@@ -2191,7 +2191,7 @@
         <v>5.84</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>3.29</v>
@@ -2267,7 +2267,7 @@
         <v>34.73</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>6.55</v>
@@ -2343,7 +2343,7 @@
         <v>31.74</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="P24" s="2" t="n">
         <v>2.91</v>
@@ -2419,7 +2419,7 @@
         <v>20.47</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>6.48</v>
@@ -2495,7 +2495,7 @@
         <v>24.48</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="P26" s="2" t="n">
         <v>5.09</v>
@@ -2571,7 +2571,7 @@
         <v>39.76</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>10.47</v>
@@ -2647,7 +2647,7 @@
         <v>31.51</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="P28" s="2" t="n">
         <v>4.86</v>
@@ -2723,7 +2723,7 @@
         <v>27.77</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>5.14</v>
@@ -2799,7 +2799,7 @@
         <v>60.89</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="P30" s="2" t="n">
         <v>15.07</v>
@@ -2875,7 +2875,7 @@
         <v>17.48</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>5.36</v>
@@ -2951,7 +2951,7 @@
         <v>26.12</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>3.19</v>
@@ -3027,7 +3027,7 @@
         <v>13.05</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>6.04</v>
@@ -3103,7 +3103,7 @@
         <v>34.06</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>11.03</v>
@@ -3179,7 +3179,7 @@
         <v>39.35</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>14.16</v>
@@ -3255,7 +3255,7 @@
         <v>38.47</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="P36" s="2" t="n">
         <v>3.62</v>
@@ -3331,7 +3331,7 @@
         <v>14.48</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>4.56</v>
@@ -3407,7 +3407,7 @@
         <v>104.79</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1648</v>
+        <v>1642</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>15.65</v>
@@ -3483,7 +3483,7 @@
         <v>16.51</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>4.64</v>
@@ -3559,7 +3559,7 @@
         <v>40.96</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="P40" s="2" t="n">
         <v>9.51</v>
@@ -3635,7 +3635,7 @@
         <v>16.22</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>5.81</v>
@@ -3747,7 +3747,7 @@
         <v>27.16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1655</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="3">
@@ -3778,7 +3778,7 @@
         <v>23.17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1653</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="4">
@@ -3809,7 +3809,7 @@
         <v>25.33</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1648</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="5">
@@ -3840,7 +3840,7 @@
         <v>21.73</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1619</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="6">
@@ -3871,7 +3871,7 @@
         <v>14.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1619</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="7">
@@ -3902,7 +3902,7 @@
         <v>21.1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1613</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="8">
@@ -3933,7 +3933,7 @@
         <v>22.01</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1608</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="9">
@@ -3964,7 +3964,7 @@
         <v>23.14</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1600</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="10">
@@ -3995,7 +3995,7 @@
         <v>11.46</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="11">
@@ -4026,7 +4026,7 @@
         <v>20.14</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1550</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="12">
@@ -4057,7 +4057,7 @@
         <v>17.9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1547</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="13">
@@ -4088,7 +4088,7 @@
         <v>13.54</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1545</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="14">
@@ -4119,7 +4119,7 @@
         <v>17.84</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1533</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="15">
@@ -4150,7 +4150,7 @@
         <v>7.49</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="16">
@@ -4181,7 +4181,7 @@
         <v>10.4</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1504</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="17">
@@ -4212,7 +4212,7 @@
         <v>16.71</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1503</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="18">
@@ -4243,7 +4243,7 @@
         <v>13.63</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="19">
@@ -4274,7 +4274,7 @@
         <v>9.52</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="20">
@@ -4305,7 +4305,7 @@
         <v>4.06</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1488</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="21">
@@ -4336,7 +4336,7 @@
         <v>7.9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1482</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="22">
@@ -4367,7 +4367,7 @@
         <v>13.87</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1482</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="23">
@@ -4398,7 +4398,7 @@
         <v>8.779999999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="24">
@@ -4429,7 +4429,7 @@
         <v>10.67</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="25">
@@ -4460,7 +4460,7 @@
         <v>12.54</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="26">
@@ -4491,7 +4491,7 @@
         <v>8.18</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1464</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="27">
@@ -4522,7 +4522,7 @@
         <v>7.77</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1458</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="28">
@@ -4553,7 +4553,7 @@
         <v>6.05</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1453</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="29">
@@ -4584,7 +4584,7 @@
         <v>8.51</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1449</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="30">
@@ -4615,7 +4615,7 @@
         <v>5.6</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1443</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="31">
@@ -4646,7 +4646,7 @@
         <v>3.29</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1440</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="32">
@@ -4677,7 +4677,7 @@
         <v>3.97</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1436</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="33">
@@ -4708,7 +4708,7 @@
         <v>1.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="34">
@@ -4739,7 +4739,7 @@
         <v>1.53</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="35">
@@ -4770,7 +4770,7 @@
         <v>5.5</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1426</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="36">
@@ -4801,7 +4801,7 @@
         <v>-0.39</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1425</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="37">
@@ -4832,7 +4832,7 @@
         <v>3.47</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1417</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="38">
@@ -4863,7 +4863,7 @@
         <v>3.75</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1410</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="39">
@@ -4894,7 +4894,7 @@
         <v>5.45</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1409</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="40">
@@ -4925,7 +4925,7 @@
         <v>-2.37</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1370</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="41">
@@ -4956,7 +4956,7 @@
         <v>0.45</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1367</v>
+        <v>1364</v>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -1355,7 +1355,7 @@
         <v>86.59</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>19.61</v>
@@ -3331,7 +3331,7 @@
         <v>14.48</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>4.56</v>
@@ -3902,7 +3902,7 @@
         <v>21.1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="8">
@@ -4832,7 +4832,7 @@
         <v>3.47</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="38">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -634,37 +634,37 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>132.67</v>
+        <v>162.63</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>53.33</v>
+        <v>-27.82</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>79.33</v>
+        <v>190.44</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>68.89</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>110.45</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>110.45</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1626</v>
+        <v>1645</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>22.33</v>
+        <v>23.76</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>53.28</v>
+        <v>60.94</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>23.89</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="3">
@@ -685,7 +685,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -694,58 +694,58 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>132.67</v>
+        <v>108.11</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>53.33</v>
+        <v>20.12</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>79.33</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>22.93</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>25.95</v>
+        <v>30.36</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>25.95</v>
+        <v>30.36</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1457</v>
+        <v>1471</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>8.75</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>10.67</v>
+        <v>13.2</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>6.54</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>10633</v>
+        <v>1023</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -754,51 +754,51 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>132.67</v>
+        <v>162.64</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>53.33</v>
+        <v>-47.26</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>79.33</v>
+        <v>209.9</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>45.8</v>
+        <v>68.08</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>117.69</v>
+        <v>121.55</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>117.69</v>
+        <v>121.55</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>18.36</v>
+        <v>19.89</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>71.20999999999999</v>
+        <v>68.91</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>28.12</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3620</v>
+        <v>5166</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -817,48 +817,48 @@
         <v>4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>101.67</v>
+        <v>87.31</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>52.67</v>
+        <v>69.06</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>49</v>
+        <v>18.25</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>94.23999999999999</v>
+        <v>98.84</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>94.23999999999999</v>
+        <v>98.84</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1615</v>
+        <v>1624</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>20.28</v>
+        <v>16.43</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>49.41</v>
+        <v>57.98</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>24.55</v>
+        <v>24.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -877,55 +877,55 @@
         <v>4</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>101.67</v>
+        <v>87.31</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>52.67</v>
+        <v>69.06</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>49</v>
+        <v>18.25</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>25.23</v>
+        <v>35.18</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>23.05</v>
+        <v>29.22</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>23.05</v>
+        <v>29.22</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1447</v>
+        <v>1467</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>3.94</v>
+        <v>5.2</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>11.13</v>
+        <v>18.03</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>7.98</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>2771</v>
+        <v>3620</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Saint Joseph, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -934,58 +934,58 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>101.67</v>
+        <v>172.38</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>52.67</v>
+        <v>-82.12</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>49</v>
+        <v>254.49</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>53.52</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>66.77</v>
+        <v>103.83</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>66.77</v>
+        <v>103.83</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1557</v>
+        <v>1634</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>9.35</v>
+        <v>20.21</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>41.35</v>
+        <v>56.37</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>16.08</v>
+        <v>27.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>11399</v>
+        <v>7220</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Brighton, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -994,51 +994,51 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>129.26</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>39.61</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>23.74</v>
+        <v>45.04</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16.22</v>
+        <v>95.17</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>16.22</v>
+        <v>95.17</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1419</v>
+        <v>1616</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>5.81</v>
+        <v>21.87</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>10.8</v>
+        <v>57.78</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.39</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7289</v>
+        <v>11399</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1057,55 +1057,55 @@
         <v>4</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>32.99</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>-27.75</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>33.29</v>
+        <v>23.74</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>28.94</v>
+        <v>20.4</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>28.94</v>
+        <v>20.4</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1467</v>
+        <v>1436</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>11.23</v>
+        <v>5.62</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>7.04</v>
+        <v>11.87</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>10.67</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1023</v>
+        <v>9206</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -1114,58 +1114,58 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>88.95</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>34.32</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0</v>
+        <v>54.62</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>68.08</v>
+        <v>21.07</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>109.18</v>
+        <v>35.77</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>109.18</v>
+        <v>35.77</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1644</v>
+        <v>1486</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>18.87</v>
+        <v>5.47</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>63.16</v>
+        <v>15.33</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>27.16</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>9206</v>
+        <v>3875</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -1174,58 +1174,58 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>51.33</v>
+        <v>46.91</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>13.33</v>
+        <v>52.62</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>38</v>
+        <v>-5.7</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>21.07</v>
+        <v>50.66</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>29.71</v>
+        <v>65.38</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>29.71</v>
+        <v>65.38</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1469</v>
+        <v>1554</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>4.2</v>
+        <v>7.28</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>11.51</v>
+        <v>38.03</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>13.99</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>10642</v>
+        <v>7656</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Michigan Center, Michigan</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -1234,58 +1234,58 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>51.33</v>
+        <v>58.15</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13.33</v>
+        <v>-70.14</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>38</v>
+        <v>128.28</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>25.63</v>
+        <v>50.91</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>18.44</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>18.44</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1429</v>
+        <v>1591</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>3.7</v>
+        <v>9.34</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>7.79</v>
+        <v>48.71</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>6.95</v>
+        <v>24.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7656</v>
+        <v>7808</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
@@ -1294,51 +1294,51 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>51.33</v>
+        <v>16.11</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>13.33</v>
+        <v>-51.84</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>38</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>50.91</v>
+        <v>24.37</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>82.65000000000001</v>
+        <v>36.69</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>82.65000000000001</v>
+        <v>36.69</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1591</v>
+        <v>1488</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>9.34</v>
+        <v>5.91</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>48.71</v>
+        <v>20.06</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>24.59</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3875</v>
+        <v>10633</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1348,57 +1348,57 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46.33</v>
+        <v>127.26</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22.67</v>
+        <v>167.7</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>23.67</v>
+        <v>-40.44</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>50.66</v>
+        <v>45.8</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>59.32</v>
+        <v>122.64</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>59.32</v>
+        <v>122.64</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1541</v>
+        <v>1662</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>6.01</v>
+        <v>20.13</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>34.21</v>
+        <v>72.72</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>19.1</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9549</v>
+        <v>4325</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1408,57 +1408,57 @@
         <v>1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>46.33</v>
+        <v>75.11</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>22.67</v>
+        <v>231.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>23.67</v>
+        <v>-156.09</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>17.6</v>
+        <v>32.52</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>19.45</v>
+        <v>29.89</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>19.45</v>
+        <v>29.89</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1433</v>
+        <v>1469</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>4.73</v>
+        <v>10.12</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>11.98</v>
+        <v>15.27</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>2.74</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7808</v>
+        <v>2075</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1468,43 +1468,43 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46.33</v>
+        <v>93.12</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22.67</v>
+        <v>119.53</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>23.67</v>
+        <v>-26.41</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>24.37</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>36.69</v>
+        <v>117.31</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>36.69</v>
+        <v>117.31</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1488</v>
+        <v>1654</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>5.91</v>
+        <v>22.66</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>20.06</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>10.72</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="17">
@@ -1537,13 +1537,13 @@
         <v>3</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>36.33</v>
+        <v>-10.13</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>18.67</v>
+        <v>8.19</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>17.67</v>
+        <v>-18.32</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>21.7</v>
@@ -1597,13 +1597,13 @@
         <v>3</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.33</v>
+        <v>-10.13</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>18.67</v>
+        <v>8.19</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>17.67</v>
+        <v>-18.32</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>27.75</v>
@@ -1629,16 +1629,16 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>7220</v>
+        <v>5980</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Brighton, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1648,64 +1648,64 @@
         <v>1</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>36.33</v>
+        <v>108.24</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>18.67</v>
+        <v>-9.27</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>17.67</v>
+        <v>117.51</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>45.04</v>
+        <v>38.55</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>84.20999999999999</v>
+        <v>26.85</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>84.20999999999999</v>
+        <v>26.85</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1594</v>
+        <v>1459</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>20.44</v>
+        <v>7.78</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>50.11</v>
+        <v>12.71</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>13.66</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7221</v>
+        <v>9549</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
@@ -1714,58 +1714,58 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>53.33</v>
+        <v>75.97</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>132.67</v>
+        <v>67.23</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-79.33</v>
+        <v>8.75</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>8.82</v>
+        <v>17.6</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>22.69</v>
+        <v>24.39</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>22.69</v>
+        <v>24.39</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>7.23</v>
+        <v>6.49</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>5.91</v>
+        <v>13.5</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>9.56</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>2075</v>
+        <v>858</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>1</v>
@@ -1774,58 +1774,58 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>53.33</v>
+        <v>75.27</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>132.67</v>
+        <v>108.38</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-79.33</v>
+        <v>-33.11</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>109.12</v>
+        <v>60.53</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>109.12</v>
+        <v>60.53</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1643</v>
+        <v>1543</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>21.44</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>63.46</v>
+        <v>32.37</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>24.22</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4325</v>
+        <v>904</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
@@ -1834,58 +1834,58 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>53.33</v>
+        <v>41.74</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>132.67</v>
+        <v>192.98</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-79.33</v>
+        <v>-151.24</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>32.52</v>
+        <v>27.91</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>18.94</v>
+        <v>9.08</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>18.94</v>
+        <v>9.08</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1431</v>
+        <v>1384</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>8.68</v>
+        <v>5.24</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>7.61</v>
+        <v>1.91</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>2.65</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>1</v>
@@ -1894,58 +1894,58 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>52.67</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>101.67</v>
+        <v>102.64</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-49</v>
+        <v>-24.65</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>56.12</v>
+        <v>64.52</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>56.12</v>
+        <v>64.52</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1534</v>
+        <v>1552</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>6.92</v>
+        <v>8.6</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>29.84</v>
+        <v>39.09</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>19.37</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>10181</v>
+        <v>7256</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
@@ -1954,58 +1954,58 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>52.67</v>
+        <v>54.64</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>101.67</v>
+        <v>137.48</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-49</v>
+        <v>-82.84</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>23.43</v>
+        <v>25.23</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>18.98</v>
+        <v>22.31</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>18.98</v>
+        <v>22.31</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1431</v>
+        <v>1444</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>5.02</v>
+        <v>3.81</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>10.68</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>5</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>8285</v>
+        <v>9756</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>24</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>1</v>
@@ -2014,58 +2014,58 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>52.67</v>
+        <v>81.14</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>101.67</v>
+        <v>-2.94</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-49</v>
+        <v>84.08</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>39.07</v>
+        <v>29.21</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>28.97</v>
+        <v>43.05</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>28.97</v>
+        <v>43.05</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1467</v>
+        <v>1504</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>5.55</v>
+        <v>5.02</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>14.13</v>
+        <v>23.84</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>9.289999999999999</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9566</v>
+        <v>7289</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
@@ -2074,58 +2074,58 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>49.11</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0</v>
+        <v>165.27</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>-116.16</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>39.97</v>
+        <v>33.29</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>26.12</v>
+        <v>30.65</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>26.12</v>
+        <v>30.65</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1458</v>
+        <v>1471</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>3.19</v>
+        <v>10.83</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>14.75</v>
+        <v>6.75</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>8.18</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>6081</v>
+        <v>9208</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>Edwardsburg, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>1</v>
@@ -2134,58 +2134,58 @@
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0</v>
+        <v>20.62</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0</v>
+        <v>-15.5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0</v>
+        <v>36.12</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>59.73</v>
+        <v>44.43</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>58.86</v>
+        <v>60.26</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>58.86</v>
+        <v>60.26</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>13.66</v>
+        <v>15.72</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>25.05</v>
+        <v>34.07</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>20.14</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>904</v>
+        <v>10642</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
@@ -2194,51 +2194,51 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0</v>
+        <v>75.81</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>-68.91</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>27.91</v>
+        <v>25.63</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5.38</v>
+        <v>16.19</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>5.38</v>
+        <v>16.19</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1363</v>
+        <v>1419</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>4.03</v>
+        <v>2.95</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>0.89</v>
+        <v>5.53</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>0.45</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7818</v>
+        <v>7809</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -2248,57 +2248,57 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>22.67</v>
+        <v>39.77</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>46.33</v>
+        <v>132.08</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-23.67</v>
+        <v>-92.31</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>32.45</v>
+        <v>23.83</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>20.28</v>
+        <v>31.65</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>20.28</v>
+        <v>31.65</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1436</v>
+        <v>1474</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.92</v>
+        <v>4.21</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>8.66</v>
+        <v>13.65</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>5.71</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8767</v>
+        <v>10181</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2308,57 +2308,57 @@
         <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.67</v>
+        <v>48.46</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46.33</v>
+        <v>35.31</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-23.67</v>
+        <v>13.14</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>27.21</v>
+        <v>23.43</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>31.32</v>
+        <v>19.39</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>31.32</v>
+        <v>19.39</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1474</v>
+        <v>1432</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>4.3</v>
+        <v>5.24</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>18.14</v>
+        <v>8.84</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>5980</v>
+        <v>6081</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -2368,57 +2368,57 @@
         <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>22.67</v>
+        <v>55.64</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46.33</v>
+        <v>91.41</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-23.67</v>
+        <v>-35.77</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>38.55</v>
+        <v>59.73</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>18.66</v>
+        <v>62.98</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>18.66</v>
+        <v>62.98</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1430</v>
+        <v>1549</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>6.56</v>
+        <v>15.08</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>25.96</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>4.08</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7658</v>
+        <v>7221</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -2428,57 +2428,57 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18.67</v>
+        <v>-8.23</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>36.33</v>
+        <v>47.27</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-17.67</v>
+        <v>-55.5</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>14.34</v>
+        <v>8.82</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4.34</v>
+        <v>22.69</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>4.34</v>
+        <v>22.69</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1358</v>
+        <v>1445</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>3.43</v>
+        <v>7.23</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>3.71</v>
+        <v>5.91</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>-2.79</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9671</v>
+        <v>9566</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -2488,57 +2488,57 @@
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>18.67</v>
+        <v>53.62</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>36.33</v>
+        <v>-67.39</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-17.67</v>
+        <v>121.02</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>27.39</v>
+        <v>39.97</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>32.57</v>
+        <v>29.83</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>32.57</v>
+        <v>29.83</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1477</v>
+        <v>1469</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>11.17</v>
+        <v>4.4</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>17.77</v>
+        <v>15.77</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>3.64</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9756</v>
+        <v>8285</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -2548,57 +2548,57 @@
         <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18.67</v>
+        <v>34.27</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>36.33</v>
+        <v>161.31</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-17.67</v>
+        <v>-127.04</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>29.21</v>
+        <v>39.07</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>36.98</v>
+        <v>26.51</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>36.98</v>
+        <v>26.51</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1489</v>
+        <v>1458</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>3.75</v>
+        <v>5.35</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>20.02</v>
+        <v>12.78</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>13.21</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9208</v>
+        <v>7818</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Edwardsburg, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -2617,48 +2617,48 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>13.33</v>
+        <v>8.91</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>51.33</v>
+        <v>77.28</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-38</v>
+        <v>-68.37</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>44.43</v>
+        <v>32.45</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>55.86</v>
+        <v>20.69</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>55.86</v>
+        <v>20.69</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1534</v>
+        <v>1438</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>14.61</v>
+        <v>6.13</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>31.54</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7809</v>
+        <v>9671</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
@@ -2677,48 +2677,48 @@
         <v>0</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>13.33</v>
+        <v>-0.9</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>51.33</v>
+        <v>38.55</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-38</v>
+        <v>-39.44</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>23.83</v>
+        <v>27.39</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>26.7</v>
+        <v>30.32</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>26.7</v>
+        <v>30.32</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1459</v>
+        <v>1471</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>2.45</v>
+        <v>10.42</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>12.14</v>
+        <v>15.51</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>12.11</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>3234</v>
+        <v>8767</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2737,264 +2737,228 @@
         <v>0</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>13.33</v>
+        <v>-49.15</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>51.33</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-38</v>
+        <v>-120.14</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>22.62</v>
+        <v>27.21</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>17.86</v>
+        <v>31.32</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>17.86</v>
+        <v>31.32</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1426</v>
+        <v>1474</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>9.050000000000001</v>
+        <v>18.14</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>4.29</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5166</v>
+        <v>8423</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Temperance, Michigan</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>25.61</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0</v>
+        <v>136.13</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>-110.52</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>28.04</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>89.23999999999999</v>
+        <v>39.02</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>89.23999999999999</v>
+        <v>39.02</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1605</v>
+        <v>1494</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>16.5</v>
+        <v>10.34</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>51.01</v>
+        <v>18.45</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>21.73</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>5256</v>
+        <v>7658</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Kalamazoo, Michigan</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0</v>
+        <v>-24.25</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0</v>
+        <v>73.39</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
+        <v>-97.64</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>35.18</v>
+        <v>14.34</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.62</v>
+        <v>3.6</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>19.62</v>
+        <v>3.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1434</v>
+        <v>1353</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>5.27</v>
+        <v>3.31</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>11.06</v>
+        <v>3.26</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>3.29</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5501</v>
+        <v>3234</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Burr Oak, Michigan</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Lowell, Michigan</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>-20.38</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>-57.81</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>31.87</v>
+        <v>22.62</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>31.87</v>
+        <v>15.4</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>31.87</v>
+        <v>15.4</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1476</v>
+        <v>1415</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>6.95</v>
+        <v>4.31</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>17.02</v>
+        <v>7.7</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>7.9</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>8423</v>
+        <v>5501</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Burr Oak, Michigan</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3022,35 +2986,41 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>28.04</v>
+        <v>31.87</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>39.76</v>
+        <v>31.87</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>39.76</v>
+        <v>31.87</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1497</v>
+        <v>1476</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>10.47</v>
+        <v>6.95</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>18.9</v>
+        <v>17.02</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>10.4</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -3138,22 +3108,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>117.69</v>
+        <v>122.64</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>117.69</v>
+        <v>122.64</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18.36</v>
+        <v>20.13</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>71.20999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>28.12</v>
+        <v>29.79</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1656</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="3">
@@ -3169,22 +3139,22 @@
         <v>68.08</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>109.18</v>
+        <v>121.55</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>109.18</v>
+        <v>121.55</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>18.87</v>
+        <v>19.89</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>63.16</v>
+        <v>68.91</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>27.16</v>
+        <v>32.74</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1644</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="4">
@@ -3200,22 +3170,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>109.12</v>
+        <v>117.31</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>109.12</v>
+        <v>117.31</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>21.44</v>
+        <v>22.66</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.46</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>24.22</v>
+        <v>26.5</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1643</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="5">
@@ -3231,22 +3201,22 @@
         <v>68.89</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.48999999999999</v>
+        <v>110.45</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>99.48999999999999</v>
+        <v>110.45</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>22.33</v>
+        <v>23.76</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>53.28</v>
+        <v>60.94</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>23.89</v>
+        <v>25.74</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1626</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="6">
@@ -3262,22 +3232,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>94.23999999999999</v>
+        <v>103.83</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>94.23999999999999</v>
+        <v>103.83</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20.28</v>
+        <v>20.21</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>49.41</v>
+        <v>56.37</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>24.55</v>
+        <v>27.24</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1615</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="7">
@@ -3293,22 +3263,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>98.84</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>98.84</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>16.5</v>
+        <v>16.43</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>51.01</v>
+        <v>57.98</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>21.73</v>
+        <v>24.42</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1605</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="8">
@@ -3324,22 +3294,22 @@
         <v>45.04</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>84.20999999999999</v>
+        <v>95.17</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>84.20999999999999</v>
+        <v>95.17</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>20.44</v>
+        <v>21.87</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>50.11</v>
+        <v>57.78</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>13.66</v>
+        <v>15.52</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1594</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="9">
@@ -3375,64 +3345,64 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2771</v>
+        <v>3875</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>53.52</v>
+        <v>50.66</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>66.77</v>
+        <v>65.38</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>66.77</v>
+        <v>65.38</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>9.35</v>
+        <v>7.28</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>41.35</v>
+        <v>38.03</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>16.08</v>
+        <v>20.08</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1557</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>3875</v>
+        <v>2771</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>50.66</v>
+        <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>59.32</v>
+        <v>64.52</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>59.32</v>
+        <v>64.52</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>6.01</v>
+        <v>8.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>34.21</v>
+        <v>39.09</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>19.1</v>
+        <v>16.83</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1541</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="12">
@@ -3448,22 +3418,22 @@
         <v>59.73</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>58.86</v>
+        <v>62.98</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>58.86</v>
+        <v>62.98</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>13.66</v>
+        <v>15.08</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>25.05</v>
+        <v>25.96</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>20.14</v>
+        <v>21.93</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1541</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="13">
@@ -3479,22 +3449,22 @@
         <v>55.1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>56.12</v>
+        <v>60.53</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>56.12</v>
+        <v>60.53</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>6.92</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>29.84</v>
+        <v>32.37</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>19.37</v>
+        <v>20.13</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1534</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="14">
@@ -3510,84 +3480,84 @@
         <v>44.43</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>55.86</v>
+        <v>60.26</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>55.86</v>
+        <v>60.26</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14.61</v>
+        <v>15.72</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>31.54</v>
+        <v>34.07</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1534</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>9756</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>29.21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>39.76</v>
+        <v>43.05</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39.76</v>
+        <v>43.05</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10.47</v>
+        <v>5.02</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>18.9</v>
+        <v>23.84</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.4</v>
+        <v>14.19</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1497</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>29.21</v>
+        <v>28.04</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>36.98</v>
+        <v>39.02</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>36.98</v>
+        <v>39.02</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3.75</v>
+        <v>10.34</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20.02</v>
+        <v>18.45</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>13.21</v>
+        <v>10.22</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1489</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="17">
@@ -3623,95 +3593,95 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9685</v>
+        <v>9206</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>27.75</v>
+        <v>21.07</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>34.54</v>
+        <v>35.77</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>34.54</v>
+        <v>35.77</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>14.36</v>
+        <v>5.47</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3.95</v>
+        <v>15.33</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>16.23</v>
+        <v>14.97</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1483</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>10664</v>
+        <v>9685</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>21.7</v>
+        <v>27.75</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>33</v>
+        <v>34.54</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>33</v>
+        <v>34.54</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>9.84</v>
+        <v>14.36</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.3</v>
+        <v>3.95</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3.87</v>
+        <v>16.23</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1478</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9671</v>
+        <v>10664</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>27.39</v>
+        <v>21.7</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>32.57</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>32.57</v>
+        <v>33</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>11.17</v>
+        <v>9.84</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>17.77</v>
+        <v>19.3</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3.64</v>
+        <v>3.87</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="21">
@@ -3747,30 +3717,30 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8767</v>
+        <v>7809</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>27.21</v>
+        <v>23.83</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.32</v>
+        <v>31.65</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>31.32</v>
+        <v>31.65</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>18.14</v>
+        <v>13.65</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>13.78</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>1474</v>
@@ -3778,529 +3748,529 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>9206</v>
+        <v>8767</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>21.07</v>
+        <v>27.21</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>29.71</v>
+        <v>31.32</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>29.71</v>
+        <v>31.32</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>11.51</v>
+        <v>18.14</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>13.99</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8285</v>
+        <v>7289</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>39.07</v>
+        <v>33.29</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.97</v>
+        <v>30.65</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.97</v>
+        <v>30.65</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.55</v>
+        <v>10.83</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>14.13</v>
+        <v>6.75</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.289999999999999</v>
+        <v>13.07</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1467</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>7289</v>
+        <v>9638</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>33.29</v>
+        <v>22.93</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>28.94</v>
+        <v>30.36</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>28.94</v>
+        <v>30.36</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>11.23</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>7.04</v>
+        <v>13.2</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.67</v>
+        <v>7.3</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1467</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7809</v>
+        <v>9671</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>23.83</v>
+        <v>27.39</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>26.7</v>
+        <v>30.32</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>26.7</v>
+        <v>30.32</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2.45</v>
+        <v>10.42</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>12.14</v>
+        <v>15.51</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>12.11</v>
+        <v>4.39</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1459</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9566</v>
+        <v>4325</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>39.97</v>
+        <v>32.52</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>26.12</v>
+        <v>29.89</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>26.12</v>
+        <v>29.89</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.19</v>
+        <v>10.12</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14.75</v>
+        <v>15.27</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8.18</v>
+        <v>4.5</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1458</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9638</v>
+        <v>9566</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>22.93</v>
+        <v>39.97</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>25.95</v>
+        <v>29.83</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>25.95</v>
+        <v>29.83</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>8.75</v>
+        <v>4.4</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>10.67</v>
+        <v>15.77</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6.54</v>
+        <v>9.66</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1457</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>25.23</v>
+        <v>35.18</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>23.05</v>
+        <v>29.22</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>23.05</v>
+        <v>29.22</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.94</v>
+        <v>5.2</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.13</v>
+        <v>18.03</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7.98</v>
+        <v>5.98</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1447</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7221</v>
+        <v>5980</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>8.82</v>
+        <v>38.55</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>22.69</v>
+        <v>26.85</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.69</v>
+        <v>26.85</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>7.23</v>
+        <v>7.78</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>5.91</v>
+        <v>12.71</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.56</v>
+        <v>6.36</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1445</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7818</v>
+        <v>8285</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>32.45</v>
+        <v>39.07</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>20.28</v>
+        <v>26.51</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>20.28</v>
+        <v>26.51</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5.92</v>
+        <v>5.35</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.66</v>
+        <v>12.78</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5.71</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1436</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5256</v>
+        <v>9549</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>35.18</v>
+        <v>17.6</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>19.62</v>
+        <v>24.39</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>19.62</v>
+        <v>24.39</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>5.27</v>
+        <v>6.49</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>11.06</v>
+        <v>13.5</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3.29</v>
+        <v>4.41</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1434</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9549</v>
+        <v>7221</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>17.6</v>
+        <v>8.82</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>19.45</v>
+        <v>22.69</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.45</v>
+        <v>22.69</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.73</v>
+        <v>7.23</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>11.98</v>
+        <v>5.91</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.74</v>
+        <v>9.56</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1433</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10181</v>
+        <v>7256</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>23.43</v>
+        <v>25.23</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>18.98</v>
+        <v>22.31</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.98</v>
+        <v>22.31</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5.02</v>
+        <v>3.81</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>10.68</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5</v>
+        <v>7.81</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1431</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>4325</v>
+        <v>7818</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>32.52</v>
+        <v>32.45</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>18.94</v>
+        <v>20.69</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.94</v>
+        <v>20.69</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>8.68</v>
+        <v>6.13</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>7.61</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.65</v>
+        <v>6.02</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1431</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5980</v>
+        <v>11399</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>38.55</v>
+        <v>23.74</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>18.66</v>
+        <v>20.4</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>18.66</v>
+        <v>20.4</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>6.56</v>
+        <v>5.62</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>11.87</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>4.08</v>
+        <v>2.91</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1430</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10642</v>
+        <v>10181</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>25.63</v>
+        <v>23.43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>18.44</v>
+        <v>19.39</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>18.44</v>
+        <v>19.39</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3.7</v>
+        <v>5.24</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>7.79</v>
+        <v>8.84</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>6.95</v>
+        <v>5.31</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1429</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3234</v>
+        <v>10642</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22.62</v>
+        <v>25.63</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17.86</v>
+        <v>16.19</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17.86</v>
+        <v>16.19</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4.52</v>
+        <v>2.95</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>5.53</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>4.29</v>
+        <v>7.71</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1426</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>11399</v>
+        <v>3234</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>23.74</v>
+        <v>22.62</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>16.22</v>
+        <v>15.4</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>16.22</v>
+        <v>15.4</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>5.81</v>
+        <v>4.31</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>10.8</v>
+        <v>7.7</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>-0.39</v>
+        <v>3.39</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1419</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="40">
@@ -4316,22 +4286,22 @@
         <v>27.91</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>5.38</v>
+        <v>9.08</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>5.38</v>
+        <v>9.08</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>4.03</v>
+        <v>5.24</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.89</v>
+        <v>1.91</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.45</v>
+        <v>1.93</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1363</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="41">
@@ -4347,22 +4317,22 @@
         <v>14.34</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>4.34</v>
+        <v>3.6</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>4.34</v>
+        <v>3.6</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>3.43</v>
+        <v>3.31</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3.71</v>
+        <v>3.26</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-2.79</v>
+        <v>-2.96</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1358</v>
+        <v>1353</v>
       </c>
     </row>
   </sheetData>
@@ -4415,743 +4385,743 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4967</v>
+        <v>3620</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>132.67</v>
+        <v>172.38</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>53.33</v>
+        <v>-82.12</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>79.33</v>
+        <v>254.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>9638</v>
+        <v>1023</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>132.67</v>
+        <v>162.64</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>53.33</v>
+        <v>-47.26</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>79.33</v>
+        <v>209.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>10633</v>
+        <v>4967</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>132.67</v>
+        <v>162.63</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>53.33</v>
+        <v>-27.82</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>79.33</v>
+        <v>190.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2771</v>
+        <v>7220</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>101.67</v>
+        <v>129.26</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>52.67</v>
+        <v>39.61</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>49</v>
+        <v>89.65000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3620</v>
+        <v>10633</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>101.67</v>
+        <v>127.26</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>52.67</v>
+        <v>167.7</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>49</v>
+        <v>-40.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>7256</v>
+        <v>5980</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>101.67</v>
+        <v>108.24</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>52.67</v>
+        <v>-9.27</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>49</v>
+        <v>117.51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2075</v>
+        <v>9638</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>53.33</v>
+        <v>108.11</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>132.67</v>
+        <v>20.12</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-79.33</v>
+        <v>87.98999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>4325</v>
+        <v>2075</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>53.33</v>
+        <v>93.12</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>132.67</v>
+        <v>119.53</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-79.33</v>
+        <v>-26.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7221</v>
+        <v>9206</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>53.33</v>
+        <v>88.95</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>132.67</v>
+        <v>34.32</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-79.33</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>858</v>
+        <v>5166</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>52.67</v>
+        <v>87.31</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>101.67</v>
+        <v>69.06</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-49</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8285</v>
+        <v>5256</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>52.67</v>
+        <v>87.31</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>101.67</v>
+        <v>69.06</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-49</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>10181</v>
+        <v>9756</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>52.67</v>
+        <v>81.14</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>101.67</v>
+        <v>-2.94</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-49</v>
+        <v>84.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7656</v>
+        <v>2771</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>51.33</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13.33</v>
+        <v>102.64</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>38</v>
+        <v>-24.65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9206</v>
+        <v>9549</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>51.33</v>
+        <v>75.97</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.33</v>
+        <v>67.23</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>38</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>10642</v>
+        <v>858</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>51.33</v>
+        <v>75.27</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>13.33</v>
+        <v>108.38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>38</v>
+        <v>-33.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>3875</v>
+        <v>4325</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>46.33</v>
+        <v>75.11</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>22.67</v>
+        <v>231.2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>23.67</v>
+        <v>-156.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7808</v>
+        <v>7656</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46.33</v>
+        <v>58.15</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>22.67</v>
+        <v>-70.14</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>23.67</v>
+        <v>128.28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9549</v>
+        <v>6081</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>46.33</v>
+        <v>55.64</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22.67</v>
+        <v>91.41</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>23.67</v>
+        <v>-35.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7220</v>
+        <v>7256</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>36.33</v>
+        <v>54.64</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>18.67</v>
+        <v>137.48</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>17.67</v>
+        <v>-82.84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>9685</v>
+        <v>9566</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>36.33</v>
+        <v>53.62</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>18.67</v>
+        <v>-67.39</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>17.67</v>
+        <v>121.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>10664</v>
+        <v>7289</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>36.33</v>
+        <v>49.11</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>18.67</v>
+        <v>165.27</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>17.67</v>
+        <v>-116.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>5980</v>
+        <v>10181</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>22.67</v>
+        <v>48.46</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46.33</v>
+        <v>35.31</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-23.67</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7818</v>
+        <v>3875</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>22.67</v>
+        <v>46.91</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>46.33</v>
+        <v>52.62</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-23.67</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>8767</v>
+        <v>904</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>22.67</v>
+        <v>41.74</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46.33</v>
+        <v>192.98</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-23.67</v>
+        <v>-151.24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7658</v>
+        <v>7809</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>18.67</v>
+        <v>39.77</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>36.33</v>
+        <v>132.08</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-17.67</v>
+        <v>-92.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>18.67</v>
+        <v>34.27</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>36.33</v>
+        <v>161.31</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-17.67</v>
+        <v>-127.04</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>18.67</v>
+        <v>25.61</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>36.33</v>
+        <v>136.13</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-17.67</v>
+        <v>-110.52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>3234</v>
+        <v>9208</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>13.33</v>
+        <v>20.62</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>51.33</v>
+        <v>-15.5</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-38</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7809</v>
+        <v>7808</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>13.33</v>
+        <v>16.11</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>51.33</v>
+        <v>-51.84</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-38</v>
+        <v>67.95999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9208</v>
+        <v>7818</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>13.33</v>
+        <v>8.91</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>51.33</v>
+        <v>77.28</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-38</v>
+        <v>-68.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>904</v>
+        <v>10642</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0</v>
+        <v>75.81</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0</v>
+        <v>-68.91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>1023</v>
+        <v>11399</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0</v>
+        <v>32.99</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-0</v>
+        <v>-27.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5166</v>
+        <v>9671</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0</v>
+        <v>38.55</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0</v>
+        <v>-39.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>5256</v>
+        <v>7221</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>-8.23</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>47.27</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>-55.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6081</v>
+        <v>9685</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0</v>
+        <v>-10.13</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0</v>
+        <v>8.19</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-0</v>
+        <v>-18.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7289</v>
+        <v>10664</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>-10.13</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>8.19</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>-18.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8423</v>
+        <v>3234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0</v>
+        <v>-20.38</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>37.42</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>-57.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>9566</v>
+        <v>7658</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0</v>
+        <v>-24.25</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0</v>
+        <v>73.39</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0</v>
+        <v>-97.64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>11399</v>
+        <v>8767</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0</v>
+        <v>-49.15</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0</v>
+        <v>-120.14</v>
       </c>
     </row>
     <row r="41">
@@ -5252,7 +5222,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -5261,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -5277,7 +5247,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -5286,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -5294,15 +5264,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10633</v>
+        <v>1023</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -5311,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -5319,11 +5289,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3620</v>
+        <v>5166</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -5344,11 +5314,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -5369,15 +5339,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2771</v>
+        <v>3620</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -5386,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -5394,15 +5364,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11399</v>
+        <v>7220</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
@@ -5411,7 +5381,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -5419,11 +5389,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7289</v>
+        <v>11399</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -5444,15 +5414,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1023</v>
+        <v>9206</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -5461,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -5469,15 +5439,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9206</v>
+        <v>3875</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -5486,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -5494,15 +5464,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10642</v>
+        <v>7656</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -5511,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -5519,15 +5489,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>7656</v>
+        <v>7808</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -5536,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -5544,24 +5514,24 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3875</v>
+        <v>10633</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -5569,24 +5539,24 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9549</v>
+        <v>4325</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -5594,24 +5564,24 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7808</v>
+        <v>2075</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -5669,24 +5639,24 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>7220</v>
+        <v>5980</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -5694,15 +5664,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7221</v>
+        <v>9549</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1</v>
@@ -5711,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -5719,15 +5689,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2075</v>
+        <v>858</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>1</v>
@@ -5736,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -5744,15 +5714,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>4325</v>
+        <v>904</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1</v>
@@ -5761,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -5769,15 +5739,15 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>1</v>
@@ -5786,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -5794,15 +5764,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10181</v>
+        <v>7256</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1</v>
@@ -5811,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -5819,15 +5789,15 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>8285</v>
+        <v>9756</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>1</v>
@@ -5836,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -5844,15 +5814,15 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9566</v>
+        <v>7289</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1</v>
@@ -5861,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -5869,15 +5839,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6081</v>
+        <v>9208</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>1</v>
@@ -5886,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -5894,15 +5864,15 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>904</v>
+        <v>10642</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1</v>
@@ -5911,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -5919,24 +5889,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7818</v>
+        <v>7809</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -5944,24 +5914,24 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>8767</v>
+        <v>10181</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -5969,24 +5939,24 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5980</v>
+        <v>6081</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -5994,24 +5964,24 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7658</v>
+        <v>7221</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -6019,24 +5989,24 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>9671</v>
+        <v>9566</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -6044,24 +6014,24 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9756</v>
+        <v>8285</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -6069,18 +6039,18 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>9208</v>
+        <v>7818</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
@@ -6094,18 +6064,18 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7809</v>
+        <v>9671</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
@@ -6119,129 +6089,99 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
+        <v>8767</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Dark Horse Robotics</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>8423</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Next Express</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>7658</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>MagiTech</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="n">
         <v>3234</v>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Red Arrows</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Fabricators</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>5256</v>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Atomics</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>5501</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Bobcats</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -6251,11 +6191,11 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>8423</v>
+        <v>5501</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -6344,21 +6284,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4967</v>
+        <v>3620</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>132.67</v>
+        <v>172.38</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>53.33</v>
+        <v>-82.12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>79.33</v>
+        <v>254.49</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6367,21 +6307,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9638</v>
+        <v>1023</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>132.67</v>
+        <v>162.64</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>53.33</v>
+        <v>-47.26</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>79.33</v>
+        <v>209.9</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6390,21 +6330,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10633</v>
+        <v>4967</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>132.67</v>
+        <v>162.63</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>53.33</v>
+        <v>-27.82</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>79.33</v>
+        <v>190.44</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6413,21 +6353,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2771</v>
+        <v>7220</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.67</v>
+        <v>129.26</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>52.67</v>
+        <v>39.61</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>49</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6436,21 +6376,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3620</v>
+        <v>10633</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>101.67</v>
+        <v>127.26</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>52.67</v>
+        <v>167.7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>49</v>
+        <v>-40.44</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6459,21 +6399,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7256</v>
+        <v>5980</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>101.67</v>
+        <v>108.24</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>52.67</v>
+        <v>-9.27</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>49</v>
+        <v>117.51</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6482,21 +6422,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2075</v>
+        <v>9638</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>53.33</v>
+        <v>108.11</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>132.67</v>
+        <v>20.12</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-79.33</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6505,21 +6445,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4325</v>
+        <v>2075</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>53.33</v>
+        <v>93.12</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>132.67</v>
+        <v>119.53</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-79.33</v>
+        <v>-26.41</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6528,21 +6468,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7221</v>
+        <v>9206</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>53.33</v>
+        <v>88.95</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>132.67</v>
+        <v>34.32</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-79.33</v>
+        <v>54.62</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6551,21 +6491,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>858</v>
+        <v>5166</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>52.67</v>
+        <v>87.31</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>101.67</v>
+        <v>69.06</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-49</v>
+        <v>18.25</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6574,21 +6514,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>8285</v>
+        <v>5256</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>52.67</v>
+        <v>87.31</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>101.67</v>
+        <v>69.06</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-49</v>
+        <v>18.25</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6597,21 +6537,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>10181</v>
+        <v>9756</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>52.67</v>
+        <v>81.14</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>101.67</v>
+        <v>-2.94</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-49</v>
+        <v>84.08</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6620,21 +6560,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7656</v>
+        <v>2771</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>51.33</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13.33</v>
+        <v>102.64</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>38</v>
+        <v>-24.65</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6643,21 +6583,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9206</v>
+        <v>9549</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>51.33</v>
+        <v>75.97</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>13.33</v>
+        <v>67.23</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>38</v>
+        <v>8.75</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6666,21 +6606,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>10642</v>
+        <v>858</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>51.33</v>
+        <v>75.27</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13.33</v>
+        <v>108.38</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>38</v>
+        <v>-33.11</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6689,21 +6629,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3875</v>
+        <v>4325</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46.33</v>
+        <v>75.11</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>22.67</v>
+        <v>231.2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>23.67</v>
+        <v>-156.09</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6712,21 +6652,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7808</v>
+        <v>7656</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>46.33</v>
+        <v>58.15</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>22.67</v>
+        <v>-70.14</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>23.67</v>
+        <v>128.28</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6735,21 +6675,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9549</v>
+        <v>6081</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46.33</v>
+        <v>55.64</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>22.67</v>
+        <v>91.41</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>23.67</v>
+        <v>-35.77</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6758,21 +6698,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7220</v>
+        <v>7256</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>36.33</v>
+        <v>54.64</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>18.67</v>
+        <v>137.48</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>17.67</v>
+        <v>-82.84</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6781,21 +6721,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>9685</v>
+        <v>9566</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>36.33</v>
+        <v>53.62</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>18.67</v>
+        <v>-67.39</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>17.67</v>
+        <v>121.02</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6804,21 +6744,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>10664</v>
+        <v>7289</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>36.33</v>
+        <v>49.11</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>18.67</v>
+        <v>165.27</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>17.67</v>
+        <v>-116.16</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6827,21 +6767,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5980</v>
+        <v>10181</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>22.67</v>
+        <v>48.46</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46.33</v>
+        <v>35.31</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-23.67</v>
+        <v>13.14</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6850,21 +6790,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7818</v>
+        <v>3875</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>22.67</v>
+        <v>46.91</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46.33</v>
+        <v>52.62</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-23.67</v>
+        <v>-5.7</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6873,21 +6813,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>8767</v>
+        <v>904</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>22.67</v>
+        <v>41.74</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46.33</v>
+        <v>192.98</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-23.67</v>
+        <v>-151.24</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6896,21 +6836,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7658</v>
+        <v>7809</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>18.67</v>
+        <v>39.77</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>36.33</v>
+        <v>132.08</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-17.67</v>
+        <v>-92.31</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6919,21 +6859,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>18.67</v>
+        <v>34.27</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>36.33</v>
+        <v>161.31</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-17.67</v>
+        <v>-127.04</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6942,21 +6882,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>18.67</v>
+        <v>25.61</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>36.33</v>
+        <v>136.13</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-17.67</v>
+        <v>-110.52</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6965,21 +6905,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3234</v>
+        <v>9208</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>13.33</v>
+        <v>20.62</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>51.33</v>
+        <v>-15.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-38</v>
+        <v>36.12</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6988,21 +6928,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7809</v>
+        <v>7808</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13.33</v>
+        <v>16.11</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>51.33</v>
+        <v>-51.84</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-38</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -7011,21 +6951,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9208</v>
+        <v>7818</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>13.33</v>
+        <v>8.91</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>51.33</v>
+        <v>77.28</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-38</v>
+        <v>-68.37</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -7034,21 +6974,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>904</v>
+        <v>10642</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0</v>
+        <v>75.81</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
+        <v>-68.91</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -7057,21 +6997,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>1023</v>
+        <v>11399</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0</v>
+        <v>32.99</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0</v>
+        <v>-27.75</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7080,21 +7020,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5166</v>
+        <v>9671</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0</v>
+        <v>38.55</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>-39.44</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -7103,21 +7043,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>5256</v>
+        <v>7221</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>-8.23</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>47.27</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>-55.5</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -7126,21 +7066,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>6081</v>
+        <v>9685</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0</v>
+        <v>-10.13</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>8.19</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-0</v>
+        <v>-18.32</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7149,21 +7089,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7289</v>
+        <v>10664</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>-10.13</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>8.19</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>-18.32</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -7172,21 +7112,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>8423</v>
+        <v>3234</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>-20.38</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>37.42</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0</v>
+        <v>-57.81</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -7195,21 +7135,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>9566</v>
+        <v>7658</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0</v>
+        <v>-24.25</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0</v>
+        <v>73.39</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0</v>
+        <v>-97.64</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -7218,21 +7158,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>11399</v>
+        <v>8767</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0</v>
+        <v>-49.15</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0</v>
+        <v>-120.14</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -637,13 +637,13 @@
         <v>10</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>162.63</v>
+        <v>174.08</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-27.82</v>
+        <v>-35.96</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>190.44</v>
+        <v>210.04</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>68.89</v>
@@ -697,13 +697,13 @@
         <v>9</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>108.11</v>
+        <v>108.61</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>20.12</v>
+        <v>19.77</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>87.98999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>22.93</v>
@@ -757,13 +757,13 @@
         <v>9</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>162.64</v>
+        <v>162.25</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-47.26</v>
+        <v>-47.22</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>209.9</v>
+        <v>209.47</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>68.08</v>
@@ -789,23 +789,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>5166</v>
+        <v>3620</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>Saint Joseph, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -814,58 +814,58 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>87.31</v>
+        <v>139.79</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>69.06</v>
+        <v>-58.96</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>18.25</v>
+        <v>198.75</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>98.84</v>
+        <v>103.83</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>98.84</v>
+        <v>103.83</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1624</v>
+        <v>1634</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>16.43</v>
+        <v>20.21</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>57.98</v>
+        <v>56.37</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>24.42</v>
+        <v>27.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5256</v>
+        <v>7220</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>Brighton, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -874,51 +874,51 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>87.31</v>
+        <v>112.03</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>69.06</v>
+        <v>51.86</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>18.25</v>
+        <v>60.17</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>35.18</v>
+        <v>45.04</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>29.22</v>
+        <v>95.17</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>29.22</v>
+        <v>95.17</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1467</v>
+        <v>1616</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>5.2</v>
+        <v>21.87</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>18.03</v>
+        <v>57.78</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>5.98</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3620</v>
+        <v>9206</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -937,48 +937,48 @@
         <v>8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>172.38</v>
+        <v>89.59</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-82.12</v>
+        <v>33.87</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>254.49</v>
+        <v>55.71</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>21.07</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>103.83</v>
+        <v>35.77</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>103.83</v>
+        <v>35.77</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1634</v>
+        <v>1486</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>20.21</v>
+        <v>5.47</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>56.37</v>
+        <v>15.33</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>27.24</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7220</v>
+        <v>3875</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Brighton, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -997,55 +997,55 @@
         <v>8</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>129.26</v>
+        <v>25.4</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>39.61</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>89.65000000000001</v>
+        <v>-42.49</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>45.04</v>
+        <v>50.66</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>95.17</v>
+        <v>65.38</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>95.17</v>
+        <v>65.38</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1616</v>
+        <v>1554</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>21.87</v>
+        <v>7.28</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>57.78</v>
+        <v>38.03</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>15.52</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>11399</v>
+        <v>7656</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Michigan Center, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1054,51 +1054,51 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>5.25</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>32.99</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-27.75</v>
+        <v>165.51</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>23.74</v>
+        <v>50.91</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>20.4</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>20.4</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1436</v>
+        <v>1588</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>5.62</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>11.87</v>
+        <v>48.4</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>2.91</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9206</v>
+        <v>7808</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -1117,48 +1117,48 @@
         <v>8</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>88.95</v>
+        <v>15.72</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>34.32</v>
+        <v>-51.58</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>54.62</v>
+        <v>67.3</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>21.07</v>
+        <v>24.37</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>35.77</v>
+        <v>35.86</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>35.77</v>
+        <v>35.86</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>1486</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>5.47</v>
+        <v>5.95</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>15.33</v>
+        <v>19.74</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>14.97</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>3875</v>
+        <v>5256</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1174,171 +1174,171 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>46.91</v>
+        <v>116.19</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>52.62</v>
+        <v>47.95</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-5.7</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>50.66</v>
+        <v>35.18</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>65.38</v>
+        <v>29.88</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>65.38</v>
+        <v>29.88</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1554</v>
+        <v>1469</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>7.28</v>
+        <v>5.88</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>38.03</v>
+        <v>17.89</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>20.08</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7656</v>
+        <v>10633</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>58.15</v>
+        <v>115.31</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-70.14</v>
+        <v>176.19</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>128.28</v>
+        <v>-60.88</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>50.91</v>
+        <v>45.8</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>82.65000000000001</v>
+        <v>122.64</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>82.65000000000001</v>
+        <v>122.64</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1591</v>
+        <v>1662</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>9.34</v>
+        <v>20.13</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>48.71</v>
+        <v>72.72</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>24.59</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7808</v>
+        <v>4325</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>16.11</v>
+        <v>80.89</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-51.84</v>
+        <v>227.11</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>67.95999999999999</v>
+        <v>-146.22</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>24.37</v>
+        <v>32.52</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>36.69</v>
+        <v>29.89</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>36.69</v>
+        <v>29.89</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1488</v>
+        <v>1469</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>5.91</v>
+        <v>10.12</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>20.06</v>
+        <v>15.27</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>10.72</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>10633</v>
+        <v>2075</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1357,58 +1357,58 @@
         <v>6</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>127.26</v>
+        <v>101.96</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>167.7</v>
+        <v>113.25</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-40.44</v>
+        <v>-11.29</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>45.8</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>122.64</v>
+        <v>117.31</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>122.64</v>
+        <v>117.31</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1662</v>
+        <v>1654</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>20.13</v>
+        <v>22.66</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>72.72</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>29.79</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>4325</v>
+        <v>9685</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -1417,43 +1417,43 @@
         <v>6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>75.11</v>
+        <v>11.06</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>231.2</v>
+        <v>-7.46</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-156.09</v>
+        <v>18.52</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>32.52</v>
+        <v>27.75</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>29.89</v>
+        <v>35.2</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>29.89</v>
+        <v>35.2</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1469</v>
+        <v>1484</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.12</v>
+        <v>15.04</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>15.27</v>
+        <v>3.81</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>4.5</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>2075</v>
+        <v>5980</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1474,51 +1474,51 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>93.12</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>119.53</v>
+        <v>-3.03</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-26.41</v>
+        <v>102.82</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>38.55</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>117.31</v>
+        <v>26.85</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>117.31</v>
+        <v>26.85</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1654</v>
+        <v>1459</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>22.66</v>
+        <v>7.78</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>68.15000000000001</v>
+        <v>12.71</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>26.5</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>10664</v>
+        <v>9549</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1528,57 +1528,57 @@
         <v>1</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-10.13</v>
+        <v>97.88</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>8.19</v>
+        <v>51.68</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-18.32</v>
+        <v>46.2</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>21.7</v>
+        <v>17.6</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>33</v>
+        <v>24.39</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>33</v>
+        <v>24.39</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1478</v>
+        <v>1451</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>9.84</v>
+        <v>6.49</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>19.3</v>
+        <v>13.5</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>3.87</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9685</v>
+        <v>858</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1588,52 +1588,52 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-10.13</v>
+        <v>72.28</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8.19</v>
+        <v>110.52</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-18.32</v>
+        <v>-38.25</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>27.75</v>
+        <v>55.1</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>34.54</v>
+        <v>60.53</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>34.54</v>
+        <v>60.53</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1483</v>
+        <v>1543</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>14.36</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>3.95</v>
+        <v>32.37</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>16.23</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>5980</v>
+        <v>904</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1657,48 +1657,48 @@
         <v>5</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>108.24</v>
+        <v>20.38</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-9.27</v>
+        <v>208.18</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>117.51</v>
+        <v>-187.8</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>38.55</v>
+        <v>27.91</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>26.85</v>
+        <v>8.26</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>26.85</v>
+        <v>8.26</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1459</v>
+        <v>1379</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>7.78</v>
+        <v>5.28</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>12.71</v>
+        <v>1.6</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>6.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9549</v>
+        <v>5166</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1714,51 +1714,51 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>75.97</v>
+        <v>91.03</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67.23</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>8.75</v>
+        <v>24.02</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>17.6</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>24.39</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>24.39</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1451</v>
+        <v>1615</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>6.49</v>
+        <v>15.17</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>13.5</v>
+        <v>56.1</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>4.41</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1774,51 +1774,51 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>75.27</v>
+        <v>102.55</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>108.38</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-33.11</v>
+        <v>17.37</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>60.53</v>
+        <v>64.52</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>60.53</v>
+        <v>64.52</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1543</v>
+        <v>1552</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>32.37</v>
+        <v>39.09</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>20.13</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>904</v>
+        <v>7256</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1834,51 +1834,51 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>41.74</v>
+        <v>62.66</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>192.98</v>
+        <v>131.78</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-151.24</v>
+        <v>-69.12</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>27.91</v>
+        <v>25.23</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9.08</v>
+        <v>22.31</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>9.08</v>
+        <v>22.31</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1384</v>
+        <v>1444</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>5.24</v>
+        <v>3.81</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>1.91</v>
+        <v>10.68</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>1.93</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>2771</v>
+        <v>11399</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1897,48 +1897,48 @@
         <v>4</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>77.98999999999999</v>
+        <v>15.06</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>102.64</v>
+        <v>26.38</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-24.65</v>
+        <v>-11.32</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>53.52</v>
+        <v>23.74</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>64.52</v>
+        <v>16.38</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>64.52</v>
+        <v>16.38</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1552</v>
+        <v>1419</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.6</v>
+        <v>4.36</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>39.09</v>
+        <v>9.99</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>16.83</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7256</v>
+        <v>9756</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1957,48 +1957,48 @@
         <v>4</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>54.64</v>
+        <v>102.01</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>137.48</v>
+        <v>-17.77</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-82.84</v>
+        <v>119.78</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>25.23</v>
+        <v>29.21</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>22.31</v>
+        <v>43.05</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>22.31</v>
+        <v>43.05</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1444</v>
+        <v>1504</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>3.81</v>
+        <v>5.02</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>10.68</v>
+        <v>23.84</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>7.81</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9756</v>
+        <v>7289</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -2017,48 +2017,48 @@
         <v>4</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>81.14</v>
+        <v>39.68</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-2.94</v>
+        <v>171.84</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>84.08</v>
+        <v>-132.15</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>29.21</v>
+        <v>33.29</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>43.05</v>
+        <v>30.65</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>43.05</v>
+        <v>30.65</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1504</v>
+        <v>1471</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>5.02</v>
+        <v>10.83</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>23.84</v>
+        <v>6.75</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>14.19</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7289</v>
+        <v>9208</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Edwardsburg, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -2077,48 +2077,48 @@
         <v>4</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>49.11</v>
+        <v>23.11</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>165.27</v>
+        <v>-17.3</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-116.16</v>
+        <v>40.41</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>33.29</v>
+        <v>44.43</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>30.65</v>
+        <v>60.26</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>30.65</v>
+        <v>60.26</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1471</v>
+        <v>1543</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>10.83</v>
+        <v>15.72</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>6.75</v>
+        <v>34.07</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>13.07</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9208</v>
+        <v>10642</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Edwardsburg, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -2137,48 +2137,48 @@
         <v>4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>20.62</v>
+        <v>-15.49</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-15.5</v>
+        <v>91.73</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>36.12</v>
+        <v>-107.22</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>44.43</v>
+        <v>25.63</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>60.26</v>
+        <v>16.19</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>60.26</v>
+        <v>16.19</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1543</v>
+        <v>1419</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>15.72</v>
+        <v>2.95</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>34.07</v>
+        <v>5.53</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>10.46</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -2194,111 +2194,111 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6.91</v>
+        <v>-14.09</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>75.81</v>
+        <v>11.6</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-68.91</v>
+        <v>-25.7</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>25.63</v>
+        <v>21.7</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>16.19</v>
+        <v>28.98</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>16.19</v>
+        <v>28.98</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1419</v>
+        <v>1466</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>2.95</v>
+        <v>8.58</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>5.53</v>
+        <v>17.42</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>7.71</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7809</v>
+        <v>8767</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>39.77</v>
+        <v>-22.25</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>132.08</v>
+        <v>51.51</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-92.31</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>23.83</v>
+        <v>27.21</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>31.65</v>
+        <v>31.98</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>31.65</v>
+        <v>31.98</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>4.21</v>
+        <v>4.97</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>13.65</v>
+        <v>18</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>13.78</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>10181</v>
+        <v>7809</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2317,48 +2317,48 @@
         <v>1</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>48.46</v>
+        <v>29.81</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>35.31</v>
+        <v>139.12</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>13.14</v>
+        <v>-109.31</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>23.43</v>
+        <v>23.83</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>19.39</v>
+        <v>31.65</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>19.39</v>
+        <v>31.65</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1432</v>
+        <v>1474</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>5.24</v>
+        <v>4.21</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>8.84</v>
+        <v>13.65</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>5.31</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>6081</v>
+        <v>10181</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -2377,48 +2377,48 @@
         <v>1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>55.64</v>
+        <v>49.48</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>91.41</v>
+        <v>34.49</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-35.77</v>
+        <v>15</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>59.73</v>
+        <v>23.43</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>62.98</v>
+        <v>19.39</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>62.98</v>
+        <v>19.39</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1549</v>
+        <v>1432</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>15.08</v>
+        <v>5.24</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>25.96</v>
+        <v>8.84</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>21.93</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7221</v>
+        <v>6081</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -2437,48 +2437,48 @@
         <v>1</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-8.23</v>
+        <v>73.05</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>47.27</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-55.5</v>
+        <v>-5.94</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>8.82</v>
+        <v>59.73</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>22.69</v>
+        <v>62.98</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>22.69</v>
+        <v>62.98</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1445</v>
+        <v>1549</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>7.23</v>
+        <v>15.08</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>5.91</v>
+        <v>25.96</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>9.56</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9566</v>
+        <v>7221</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -2497,48 +2497,48 @@
         <v>1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>53.62</v>
+        <v>-22.85</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>-67.39</v>
+        <v>57.64</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>121.02</v>
+        <v>-80.48999999999999</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>39.97</v>
+        <v>8.82</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>29.83</v>
+        <v>21.32</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>29.83</v>
+        <v>21.32</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1469</v>
+        <v>1440</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.4</v>
+        <v>7.1</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>15.77</v>
+        <v>4.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>9.66</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -2557,48 +2557,48 @@
         <v>1</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>34.27</v>
+        <v>57.57</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>161.31</v>
+        <v>-70.18000000000001</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-127.04</v>
+        <v>127.74</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>39.07</v>
+        <v>39.97</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>26.51</v>
+        <v>28.46</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>26.51</v>
+        <v>28.46</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>5.35</v>
+        <v>4.27</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>12.78</v>
+        <v>14.76</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7818</v>
+        <v>8285</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -2614,51 +2614,51 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>8.91</v>
+        <v>36.24</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>77.28</v>
+        <v>159.99</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-68.37</v>
+        <v>-123.75</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>32.45</v>
+        <v>39.07</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>20.69</v>
+        <v>26.51</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20.69</v>
+        <v>26.51</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1438</v>
+        <v>1458</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>6.13</v>
+        <v>5.35</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>8.539999999999999</v>
+        <v>12.78</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>6.02</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>9671</v>
+        <v>7818</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2677,48 +2677,48 @@
         <v>0</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-0.9</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>38.55</v>
+        <v>90.52</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-39.44</v>
+        <v>-100.06</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>27.39</v>
+        <v>32.45</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>30.32</v>
+        <v>20.69</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>30.32</v>
+        <v>20.69</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1471</v>
+        <v>1438</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>10.42</v>
+        <v>6.13</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>15.51</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>4.39</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>8767</v>
+        <v>9671</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
@@ -2737,34 +2737,34 @@
         <v>0</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>-49.15</v>
+        <v>-3.06</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>70.98999999999999</v>
+        <v>40.09</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-120.14</v>
+        <v>-43.15</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>27.21</v>
+        <v>27.39</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>31.32</v>
+        <v>30.32</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>31.32</v>
+        <v>30.32</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>4.3</v>
+        <v>10.42</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>18.14</v>
+        <v>15.51</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="38">
@@ -2797,34 +2797,34 @@
         <v>0</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25.61</v>
+        <v>36.29</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>136.13</v>
+        <v>128.54</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-110.52</v>
+        <v>-92.25</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>28.04</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>39.02</v>
+        <v>37.65</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>39.02</v>
+        <v>37.65</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>10.34</v>
+        <v>10.21</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>18.45</v>
+        <v>17.44</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>10.22</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="39">
@@ -2857,13 +2857,13 @@
         <v>0</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>-24.25</v>
+        <v>-42.95</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>73.39</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-97.64</v>
+        <v>-129.63</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>14.34</v>
@@ -2917,13 +2917,13 @@
         <v>0</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-20.38</v>
+        <v>-12.92</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>37.42</v>
+        <v>32.17</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-57.81</v>
+        <v>-45.09</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>22.62</v>
@@ -3252,64 +3252,64 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>5166</v>
+        <v>7220</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>98.84</v>
+        <v>95.17</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>98.84</v>
+        <v>95.17</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>16.43</v>
+        <v>21.87</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>57.98</v>
+        <v>57.78</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>24.42</v>
+        <v>15.52</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1624</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7220</v>
+        <v>5166</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>45.04</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>95.17</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>95.17</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>21.87</v>
+        <v>15.17</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>57.78</v>
+        <v>56.1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>15.52</v>
+        <v>23.54</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="9">
@@ -3325,22 +3325,22 @@
         <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>82.65000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>82.65000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>9.34</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>48.71</v>
+        <v>48.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>24.59</v>
+        <v>24.04</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1591</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="10">
@@ -3542,22 +3542,22 @@
         <v>28.04</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39.02</v>
+        <v>37.65</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39.02</v>
+        <v>37.65</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>10.34</v>
+        <v>10.21</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>18.45</v>
+        <v>17.44</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.22</v>
+        <v>9.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1494</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="17">
@@ -3573,22 +3573,22 @@
         <v>24.37</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>36.69</v>
+        <v>35.86</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>36.69</v>
+        <v>35.86</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.91</v>
+        <v>5.95</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>20.06</v>
+        <v>19.74</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.72</v>
+        <v>10.17</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="18">
@@ -3635,53 +3635,53 @@
         <v>27.75</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>34.54</v>
+        <v>35.2</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>34.54</v>
+        <v>35.2</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>14.36</v>
+        <v>15.04</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3.95</v>
+        <v>3.81</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.23</v>
+        <v>16.35</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>10664</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>21.7</v>
+        <v>27.21</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>33</v>
+        <v>31.98</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>33</v>
+        <v>31.98</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>9.84</v>
+        <v>4.97</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>19.3</v>
+        <v>18</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3.87</v>
+        <v>9.01</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1478</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="21">
@@ -3748,61 +3748,61 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>8767</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>27.21</v>
+        <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>31.32</v>
+        <v>30.65</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>31.32</v>
+        <v>30.65</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.3</v>
+        <v>10.83</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>18.14</v>
+        <v>6.75</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>13.07</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7289</v>
+        <v>9638</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>33.29</v>
+        <v>22.93</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>30.65</v>
+        <v>30.36</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30.65</v>
+        <v>30.36</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>10.83</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>6.75</v>
+        <v>13.2</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>13.07</v>
+        <v>7.3</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>1471</v>
@@ -3810,30 +3810,30 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9638</v>
+        <v>9671</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>22.93</v>
+        <v>27.39</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>30.36</v>
+        <v>30.32</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>30.36</v>
+        <v>30.32</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>13.2</v>
+        <v>15.51</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>7.3</v>
+        <v>4.39</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1471</v>
@@ -3841,61 +3841,61 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9671</v>
+        <v>4325</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>27.39</v>
+        <v>32.52</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>30.32</v>
+        <v>29.89</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>30.32</v>
+        <v>29.89</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>10.42</v>
+        <v>10.12</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15.51</v>
+        <v>15.27</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4.39</v>
+        <v>4.5</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>4325</v>
+        <v>5256</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>32.52</v>
+        <v>35.18</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>29.89</v>
+        <v>29.88</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>29.89</v>
+        <v>29.88</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>10.12</v>
+        <v>5.88</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>15.27</v>
+        <v>17.89</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>4.5</v>
+        <v>6.11</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1469</v>
@@ -3903,64 +3903,64 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9566</v>
+        <v>10664</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>39.97</v>
+        <v>21.7</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>29.83</v>
+        <v>28.98</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>29.83</v>
+        <v>28.98</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.4</v>
+        <v>8.58</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.77</v>
+        <v>17.42</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.66</v>
+        <v>2.99</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1469</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>5256</v>
+        <v>9566</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>35.18</v>
+        <v>39.97</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>29.22</v>
+        <v>28.46</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>29.22</v>
+        <v>28.46</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.2</v>
+        <v>4.27</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.03</v>
+        <v>14.76</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.98</v>
+        <v>9.43</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1467</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="30">
@@ -4058,64 +4058,64 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7221</v>
+        <v>7256</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>8.82</v>
+        <v>25.23</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>22.69</v>
+        <v>22.31</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>22.69</v>
+        <v>22.31</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7.23</v>
+        <v>3.81</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>5.91</v>
+        <v>10.68</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>9.56</v>
+        <v>7.81</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7256</v>
+        <v>7221</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>25.23</v>
+        <v>8.82</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>22.31</v>
+        <v>21.32</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>22.31</v>
+        <v>21.32</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>3.81</v>
+        <v>7.1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10.68</v>
+        <v>4.9</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>7.81</v>
+        <v>9.33</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1444</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="35">
@@ -4151,64 +4151,64 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>11399</v>
+        <v>10181</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23.74</v>
+        <v>23.43</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>20.4</v>
+        <v>19.39</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>20.4</v>
+        <v>19.39</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.62</v>
+        <v>5.24</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>11.87</v>
+        <v>8.84</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>2.91</v>
+        <v>5.31</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1436</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>11399</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.43</v>
+        <v>23.74</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>19.39</v>
+        <v>16.38</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>19.39</v>
+        <v>16.38</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.24</v>
+        <v>4.36</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>8.84</v>
+        <v>9.99</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>5.31</v>
+        <v>2.03</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1432</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="38">
@@ -4286,22 +4286,22 @@
         <v>27.91</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9.08</v>
+        <v>8.26</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>9.08</v>
+        <v>8.26</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1384</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="41">
@@ -4385,21 +4385,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3620</v>
+        <v>4967</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>172.38</v>
+        <v>174.08</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-82.12</v>
+        <v>-35.96</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>254.49</v>
+        <v>210.04</v>
       </c>
     </row>
     <row r="3">
@@ -4412,51 +4412,51 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>162.64</v>
+        <v>162.25</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-47.26</v>
+        <v>-47.22</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>209.9</v>
+        <v>209.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4967</v>
+        <v>3620</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>162.63</v>
+        <v>139.79</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-27.82</v>
+        <v>-58.96</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>190.44</v>
+        <v>198.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>7220</v>
+        <v>5256</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>129.26</v>
+        <v>116.19</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>39.61</v>
+        <v>47.95</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>89.65000000000001</v>
+        <v>68.23999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4469,32 +4469,32 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>127.26</v>
+        <v>115.31</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>167.7</v>
+        <v>176.19</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-40.44</v>
+        <v>-60.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>5980</v>
+        <v>7220</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>108.24</v>
+        <v>112.03</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-9.27</v>
+        <v>51.86</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>117.51</v>
+        <v>60.17</v>
       </c>
     </row>
     <row r="8">
@@ -4507,222 +4507,222 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>108.11</v>
+        <v>108.61</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>20.12</v>
+        <v>19.77</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>87.98999999999999</v>
+        <v>88.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>2075</v>
+        <v>2771</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>93.12</v>
+        <v>102.55</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>119.53</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-26.41</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9206</v>
+        <v>9756</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>88.95</v>
+        <v>102.01</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34.32</v>
+        <v>-17.77</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>54.62</v>
+        <v>119.78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>5166</v>
+        <v>2075</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>87.31</v>
+        <v>101.96</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>69.06</v>
+        <v>113.25</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>18.25</v>
+        <v>-11.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5256</v>
+        <v>5980</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>87.31</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>69.06</v>
+        <v>-3.03</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>18.25</v>
+        <v>102.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>9756</v>
+        <v>9549</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>81.14</v>
+        <v>97.88</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-2.94</v>
+        <v>51.68</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>84.08</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>91.03</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>102.64</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-24.65</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9549</v>
+        <v>9206</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>75.97</v>
+        <v>89.59</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>67.23</v>
+        <v>33.87</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>8.75</v>
+        <v>55.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>858</v>
+        <v>4325</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>75.27</v>
+        <v>80.89</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>108.38</v>
+        <v>227.11</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-33.11</v>
+        <v>-146.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>4325</v>
+        <v>7656</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>75.11</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>231.2</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-156.09</v>
+        <v>165.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7656</v>
+        <v>6081</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>58.15</v>
+        <v>73.05</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-70.14</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>128.28</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>6081</v>
+        <v>858</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>55.64</v>
+        <v>72.28</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>91.41</v>
+        <v>110.52</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-35.77</v>
+        <v>-38.25</v>
       </c>
     </row>
     <row r="20">
@@ -4735,13 +4735,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>54.64</v>
+        <v>62.66</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>137.48</v>
+        <v>131.78</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-82.84</v>
+        <v>-69.12</v>
       </c>
     </row>
     <row r="21">
@@ -4754,89 +4754,89 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>53.62</v>
+        <v>57.57</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-67.39</v>
+        <v>-70.18000000000001</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>121.02</v>
+        <v>127.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7289</v>
+        <v>10181</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>49.11</v>
+        <v>49.48</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>165.27</v>
+        <v>34.49</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-116.16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>10181</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>48.46</v>
+        <v>39.68</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>35.31</v>
+        <v>171.84</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>13.14</v>
+        <v>-132.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3875</v>
+        <v>8423</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46.91</v>
+        <v>36.29</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>52.62</v>
+        <v>128.54</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-5.7</v>
+        <v>-92.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>904</v>
+        <v>8285</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>41.74</v>
+        <v>36.24</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>192.98</v>
+        <v>159.99</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-151.24</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="26">
@@ -4849,70 +4849,70 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>39.77</v>
+        <v>29.81</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>132.08</v>
+        <v>139.12</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-92.31</v>
+        <v>-109.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>8285</v>
+        <v>3875</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>34.27</v>
+        <v>25.4</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>161.31</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-127.04</v>
+        <v>-42.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>25.61</v>
+        <v>23.11</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>136.13</v>
+        <v>-17.3</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-110.52</v>
+        <v>40.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9208</v>
+        <v>904</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>20.62</v>
+        <v>20.38</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-15.5</v>
+        <v>208.18</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>36.12</v>
+        <v>-187.8</v>
       </c>
     </row>
     <row r="30">
@@ -4925,203 +4925,203 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>16.11</v>
+        <v>15.72</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>-51.84</v>
+        <v>-51.58</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>67.95999999999999</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7818</v>
+        <v>11399</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.91</v>
+        <v>15.06</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>77.28</v>
+        <v>26.38</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-68.37</v>
+        <v>-11.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>10642</v>
+        <v>9685</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6.91</v>
+        <v>11.06</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>75.81</v>
+        <v>-7.46</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-68.91</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>11399</v>
+        <v>9671</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>5.25</v>
+        <v>-3.06</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>32.99</v>
+        <v>40.09</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-27.75</v>
+        <v>-43.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9671</v>
+        <v>7818</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-0.9</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>38.55</v>
+        <v>90.52</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-39.44</v>
+        <v>-100.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-8.23</v>
+        <v>-12.92</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>47.27</v>
+        <v>32.17</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-55.5</v>
+        <v>-45.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>9685</v>
+        <v>10664</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-10.13</v>
+        <v>-14.09</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8.19</v>
+        <v>11.6</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-18.32</v>
+        <v>-25.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10664</v>
+        <v>10642</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-10.13</v>
+        <v>-15.49</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>8.19</v>
+        <v>91.73</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-18.32</v>
+        <v>-107.22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3234</v>
+        <v>8767</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-20.38</v>
+        <v>-22.25</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>37.42</v>
+        <v>51.51</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-57.81</v>
+        <v>-73.76000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7658</v>
+        <v>7221</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-24.25</v>
+        <v>-22.85</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>73.39</v>
+        <v>57.64</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-97.64</v>
+        <v>-80.48999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8767</v>
+        <v>7658</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-49.15</v>
+        <v>-42.95</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>70.98999999999999</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-120.14</v>
+        <v>-129.63</v>
       </c>
     </row>
     <row r="41">
@@ -5289,15 +5289,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5166</v>
+        <v>3620</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -5314,15 +5314,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5256</v>
+        <v>7220</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -5331,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -5339,11 +5339,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3620</v>
+        <v>9206</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -5364,11 +5364,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7220</v>
+        <v>3875</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -5389,15 +5389,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>11399</v>
+        <v>7656</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -5414,11 +5414,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9206</v>
+        <v>7808</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -5439,11 +5439,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3875</v>
+        <v>5256</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -5456,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -5464,24 +5464,24 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7656</v>
+        <v>10633</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -5489,24 +5489,24 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>7808</v>
+        <v>4325</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -5514,11 +5514,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>10633</v>
+        <v>2075</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -5539,18 +5539,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4325</v>
+        <v>9685</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -5564,11 +5564,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2075</v>
+        <v>5980</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -5581,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -5589,24 +5589,24 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>10664</v>
+        <v>9549</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -5614,24 +5614,24 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>9685</v>
+        <v>858</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -5639,11 +5639,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5980</v>
+        <v>904</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -5664,11 +5664,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>9549</v>
+        <v>5166</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -5689,11 +5689,11 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -5714,11 +5714,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>904</v>
+        <v>7256</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -5739,11 +5739,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2771</v>
+        <v>11399</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -5764,11 +5764,11 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7256</v>
+        <v>9756</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -5789,11 +5789,11 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9756</v>
+        <v>7289</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -5814,11 +5814,11 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7289</v>
+        <v>9208</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -5839,11 +5839,11 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9208</v>
+        <v>10642</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -5864,11 +5864,11 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -5881,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -5889,24 +5889,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7809</v>
+        <v>8767</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -5914,11 +5914,11 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>10181</v>
+        <v>7809</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -5939,11 +5939,11 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>6081</v>
+        <v>10181</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -5964,11 +5964,11 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7221</v>
+        <v>6081</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -5989,11 +5989,11 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>9566</v>
+        <v>7221</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -6014,11 +6014,11 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -6039,11 +6039,11 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7818</v>
+        <v>8285</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -6056,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -6064,11 +6064,11 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>9671</v>
+        <v>7818</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -6089,18 +6089,18 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>8767</v>
+        <v>9671</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
@@ -6284,21 +6284,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3620</v>
+        <v>4967</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>172.38</v>
+        <v>174.08</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-82.12</v>
+        <v>-35.96</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>254.49</v>
+        <v>210.04</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>162.64</v>
+        <v>162.25</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-47.26</v>
+        <v>-47.22</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>209.9</v>
+        <v>209.47</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6330,21 +6330,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4967</v>
+        <v>3620</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>162.63</v>
+        <v>139.79</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-27.82</v>
+        <v>-58.96</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>190.44</v>
+        <v>198.75</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6353,21 +6353,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7220</v>
+        <v>5256</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>129.26</v>
+        <v>116.19</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>39.61</v>
+        <v>47.95</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>89.65000000000001</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6384,13 +6384,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>127.26</v>
+        <v>115.31</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>167.7</v>
+        <v>176.19</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-40.44</v>
+        <v>-60.88</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6399,21 +6399,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5980</v>
+        <v>7220</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>108.24</v>
+        <v>112.03</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-9.27</v>
+        <v>51.86</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>117.51</v>
+        <v>60.17</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>108.11</v>
+        <v>108.61</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20.12</v>
+        <v>19.77</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>87.98999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6445,21 +6445,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>2075</v>
+        <v>2771</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>93.12</v>
+        <v>102.55</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>119.53</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-26.41</v>
+        <v>17.37</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6468,21 +6468,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9206</v>
+        <v>9756</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>88.95</v>
+        <v>102.01</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34.32</v>
+        <v>-17.77</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54.62</v>
+        <v>119.78</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6491,21 +6491,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5166</v>
+        <v>2075</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>87.31</v>
+        <v>101.96</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>69.06</v>
+        <v>113.25</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>18.25</v>
+        <v>-11.29</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6514,21 +6514,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>5256</v>
+        <v>5980</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>87.31</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>69.06</v>
+        <v>-3.03</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>18.25</v>
+        <v>102.82</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6537,21 +6537,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9756</v>
+        <v>9549</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>81.14</v>
+        <v>97.88</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-2.94</v>
+        <v>51.68</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>84.08</v>
+        <v>46.2</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6560,21 +6560,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>91.03</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>102.64</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-24.65</v>
+        <v>24.02</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6583,21 +6583,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9549</v>
+        <v>9206</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>75.97</v>
+        <v>89.59</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>67.23</v>
+        <v>33.87</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>8.75</v>
+        <v>55.71</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6606,21 +6606,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>858</v>
+        <v>4325</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>75.27</v>
+        <v>80.89</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>108.38</v>
+        <v>227.11</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-33.11</v>
+        <v>-146.22</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6629,21 +6629,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>4325</v>
+        <v>7656</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>75.11</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>231.2</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-156.09</v>
+        <v>165.51</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6652,21 +6652,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7656</v>
+        <v>6081</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>58.15</v>
+        <v>73.05</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-70.14</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>128.28</v>
+        <v>-5.94</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6675,21 +6675,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>6081</v>
+        <v>858</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>55.64</v>
+        <v>72.28</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>91.41</v>
+        <v>110.52</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-35.77</v>
+        <v>-38.25</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6706,13 +6706,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>54.64</v>
+        <v>62.66</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>137.48</v>
+        <v>131.78</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-82.84</v>
+        <v>-69.12</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6729,13 +6729,13 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>53.62</v>
+        <v>57.57</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-67.39</v>
+        <v>-70.18000000000001</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>121.02</v>
+        <v>127.74</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6744,21 +6744,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>7289</v>
+        <v>10181</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>49.11</v>
+        <v>49.48</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>165.27</v>
+        <v>34.49</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-116.16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6767,21 +6767,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>10181</v>
+        <v>7289</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>48.46</v>
+        <v>39.68</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>35.31</v>
+        <v>171.84</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>13.14</v>
+        <v>-132.15</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6790,21 +6790,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3875</v>
+        <v>8423</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>46.91</v>
+        <v>36.29</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>52.62</v>
+        <v>128.54</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-5.7</v>
+        <v>-92.25</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6813,21 +6813,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>904</v>
+        <v>8285</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>41.74</v>
+        <v>36.24</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>192.98</v>
+        <v>159.99</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-151.24</v>
+        <v>-123.75</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6844,13 +6844,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>39.77</v>
+        <v>29.81</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>132.08</v>
+        <v>139.12</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-92.31</v>
+        <v>-109.31</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6859,21 +6859,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>8285</v>
+        <v>3875</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>34.27</v>
+        <v>25.4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>161.31</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-127.04</v>
+        <v>-42.49</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6882,21 +6882,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>25.61</v>
+        <v>23.11</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>136.13</v>
+        <v>-17.3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-110.52</v>
+        <v>40.41</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6905,21 +6905,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9208</v>
+        <v>904</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>20.62</v>
+        <v>20.38</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-15.5</v>
+        <v>208.18</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>36.12</v>
+        <v>-187.8</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6936,13 +6936,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>16.11</v>
+        <v>15.72</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-51.84</v>
+        <v>-51.58</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>67.95999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6951,21 +6951,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7818</v>
+        <v>11399</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>8.91</v>
+        <v>15.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>77.28</v>
+        <v>26.38</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-68.37</v>
+        <v>-11.32</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6974,21 +6974,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>10642</v>
+        <v>9685</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>6.91</v>
+        <v>11.06</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>75.81</v>
+        <v>-7.46</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-68.91</v>
+        <v>18.52</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6997,21 +6997,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>11399</v>
+        <v>9671</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>5.25</v>
+        <v>-3.06</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>32.99</v>
+        <v>40.09</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-27.75</v>
+        <v>-43.15</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7020,21 +7020,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9671</v>
+        <v>7818</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-0.9</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>38.55</v>
+        <v>90.52</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-39.44</v>
+        <v>-100.06</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -7043,21 +7043,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-8.23</v>
+        <v>-12.92</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>47.27</v>
+        <v>32.17</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-55.5</v>
+        <v>-45.09</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -7066,21 +7066,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>9685</v>
+        <v>10664</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-10.13</v>
+        <v>-14.09</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>8.19</v>
+        <v>11.6</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-18.32</v>
+        <v>-25.7</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7089,21 +7089,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>10664</v>
+        <v>10642</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-10.13</v>
+        <v>-15.49</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>8.19</v>
+        <v>91.73</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-18.32</v>
+        <v>-107.22</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -7112,21 +7112,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>3234</v>
+        <v>8767</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-20.38</v>
+        <v>-22.25</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>37.42</v>
+        <v>51.51</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-57.81</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -7135,21 +7135,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>7658</v>
+        <v>7221</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-24.25</v>
+        <v>-22.85</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>73.39</v>
+        <v>57.64</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-97.64</v>
+        <v>-80.48999999999999</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -7158,21 +7158,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>8767</v>
+        <v>7658</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-49.15</v>
+        <v>-42.95</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>70.98999999999999</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-120.14</v>
+        <v>-129.63</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -634,58 +634,58 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>174.08</v>
+        <v>234.72</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-35.96</v>
+        <v>-219.84</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>210.04</v>
+        <v>454.56</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>68.89</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>110.45</v>
+        <v>111.23</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>110.45</v>
+        <v>111.23</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>1645</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23.76</v>
+        <v>23.68</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>60.94</v>
+        <v>61.58</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>25.74</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>9638</v>
+        <v>1023</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -694,58 +694,58 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>108.61</v>
+        <v>211.07</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>19.77</v>
+        <v>-132.31</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>88.84</v>
+        <v>343.38</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>22.93</v>
+        <v>68.08</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>30.36</v>
+        <v>121.55</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>30.36</v>
+        <v>121.55</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1471</v>
+        <v>1660</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>19.89</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>13.2</v>
+        <v>68.91</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>7.3</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1023</v>
+        <v>3620</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Saint Joseph, Michigan</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -754,51 +754,51 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>162.25</v>
+        <v>189.69</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-47.22</v>
+        <v>-124.15</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>209.47</v>
+        <v>313.85</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>68.08</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>121.55</v>
+        <v>110.92</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>121.55</v>
+        <v>110.92</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1660</v>
+        <v>1644</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>19.89</v>
+        <v>20.27</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>68.91</v>
+        <v>62.37</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>32.74</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph, Michigan</t>
+          <t>Brighton, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -817,55 +817,55 @@
         <v>8</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>139.79</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-58.96</v>
+        <v>281.99</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>198.75</v>
+        <v>-194.28</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>103.83</v>
+        <v>95.17</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>103.83</v>
+        <v>95.17</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1634</v>
+        <v>1616</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>20.21</v>
+        <v>21.87</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>56.37</v>
+        <v>57.78</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>27.24</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7220</v>
+        <v>7808</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Brighton, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -874,58 +874,58 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>112.03</v>
+        <v>-40.65</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.86</v>
+        <v>60.83</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>60.17</v>
+        <v>-101.48</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45.04</v>
+        <v>24.37</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>95.17</v>
+        <v>42.95</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>95.17</v>
+        <v>42.95</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1616</v>
+        <v>1503</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>21.87</v>
+        <v>6.01</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>57.78</v>
+        <v>25.74</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>15.52</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>9206</v>
+        <v>7656</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Michigan Center, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -934,51 +934,51 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>89.59</v>
+        <v>178.02</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>33.87</v>
+        <v>-210.21</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>55.71</v>
+        <v>388.23</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>21.07</v>
+        <v>50.91</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>35.77</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>35.77</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1486</v>
+        <v>1583</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>5.47</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>15.33</v>
+        <v>50.25</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>14.97</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3875</v>
+        <v>10633</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -988,57 +988,57 @@
         <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25.4</v>
+        <v>86.78</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>104.43</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-42.49</v>
+        <v>-17.64</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>50.66</v>
+        <v>45.8</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>65.38</v>
+        <v>121.75</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>65.38</v>
+        <v>121.75</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1554</v>
+        <v>1659</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>7.28</v>
+        <v>21.49</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>38.03</v>
+        <v>72.2</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>20.08</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>9638</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1048,57 +1048,57 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-85.59999999999999</v>
+        <v>275.42</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>165.51</v>
+        <v>-198.92</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>50.91</v>
+        <v>22.93</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>81.81999999999999</v>
+        <v>25.31</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>81.81999999999999</v>
+        <v>25.31</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1588</v>
+        <v>1454</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>48.4</v>
+        <v>10.14</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>24.04</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7808</v>
+        <v>9549</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -1108,57 +1108,57 @@
         <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.72</v>
+        <v>56.12</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-51.58</v>
+        <v>63.88</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>67.3</v>
+        <v>-7.75</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>24.37</v>
+        <v>17.6</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>35.86</v>
+        <v>28.83</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>35.86</v>
+        <v>28.83</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1486</v>
+        <v>1465</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>5.95</v>
+        <v>7.01</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>19.74</v>
+        <v>16.43</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>10.17</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>5256</v>
+        <v>858</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1168,64 +1168,64 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>116.19</v>
+        <v>86</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>47.95</v>
+        <v>15.61</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>68.23999999999999</v>
+        <v>70.38</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>35.18</v>
+        <v>55.1</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>29.88</v>
+        <v>64.97</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>29.88</v>
+        <v>64.97</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1469</v>
+        <v>1552</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>5.88</v>
+        <v>8.56</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>17.89</v>
+        <v>35.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>6.11</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>10633</v>
+        <v>5980</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
@@ -1234,58 +1234,58 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>115.31</v>
+        <v>6.3</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>176.19</v>
+        <v>172.68</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-60.88</v>
+        <v>-166.38</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>45.8</v>
+        <v>38.55</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>122.64</v>
+        <v>27.47</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>122.64</v>
+        <v>27.47</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1662</v>
+        <v>1461</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>20.13</v>
+        <v>7.6</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>72.72</v>
+        <v>13.5</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>29.79</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>4325</v>
+        <v>3875</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>1</v>
@@ -1294,61 +1294,61 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>80.89</v>
+        <v>123.52</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>227.11</v>
+        <v>-56.71</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-146.22</v>
+        <v>180.23</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>32.52</v>
+        <v>50.66</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>29.89</v>
+        <v>69.14</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>29.89</v>
+        <v>69.14</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1469</v>
+        <v>1561</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.12</v>
+        <v>7.49</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>15.27</v>
+        <v>40.3</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>4.5</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>2075</v>
+        <v>9685</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -1357,48 +1357,48 @@
         <v>6</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>101.96</v>
+        <v>55.55</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>113.25</v>
+        <v>-18.77</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-11.29</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>27.75</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>117.31</v>
+        <v>35.2</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>117.31</v>
+        <v>35.2</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1654</v>
+        <v>1484</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>22.66</v>
+        <v>15.04</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>68.15000000000001</v>
+        <v>3.81</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>26.5</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9685</v>
+        <v>2771</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1408,64 +1408,64 @@
         <v>2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>11.06</v>
+        <v>78.88</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-7.46</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>18.52</v>
+        <v>1.37</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>27.75</v>
+        <v>53.52</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>35.2</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>35.2</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1484</v>
+        <v>1560</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>15.04</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>3.81</v>
+        <v>42.02</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>16.35</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5980</v>
+        <v>7289</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
@@ -1474,58 +1474,58 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>99.79000000000001</v>
+        <v>116.48</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-3.03</v>
+        <v>115.79</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>102.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>38.55</v>
+        <v>33.29</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>26.85</v>
+        <v>29.77</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>26.85</v>
+        <v>29.77</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1459</v>
+        <v>1468</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>7.78</v>
+        <v>12.19</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>12.71</v>
+        <v>6.23</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>6.36</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9549</v>
+        <v>9206</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
         <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>1</v>
@@ -1534,58 +1534,58 @@
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>97.88</v>
+        <v>-33.83</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>51.68</v>
+        <v>-28.01</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46.2</v>
+        <v>-5.82</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>17.6</v>
+        <v>21.07</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>24.39</v>
+        <v>28.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>24.39</v>
+        <v>28.9</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1451</v>
+        <v>1465</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>6.49</v>
+        <v>4.54</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>13.5</v>
+        <v>11.98</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.41</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>858</v>
+        <v>9208</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>Edwardsburg, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
@@ -1594,58 +1594,58 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>72.28</v>
+        <v>41.51</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>110.52</v>
+        <v>-178.03</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-38.25</v>
+        <v>219.54</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>55.1</v>
+        <v>44.43</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>60.53</v>
+        <v>60.88</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>60.53</v>
+        <v>60.88</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>1543</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>15.54</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>32.37</v>
+        <v>34.86</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>20.13</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>904</v>
+        <v>5256</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>1</v>
@@ -1654,58 +1654,58 @@
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>20.38</v>
+        <v>-79.5</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>208.18</v>
+        <v>35.45</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-187.8</v>
+        <v>-114.95</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>27.91</v>
+        <v>35.18</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>8.26</v>
+        <v>24.83</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>8.26</v>
+        <v>24.83</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1379</v>
+        <v>1452</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>5.28</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>1.6</v>
+        <v>14.83</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>1.38</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5166</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
@@ -1714,58 +1714,58 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>91.03</v>
+        <v>128.95</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67.01000000000001</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>24.02</v>
+        <v>53.63</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>27.21</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>39.07</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>39.07</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1615</v>
+        <v>1493</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>15.17</v>
+        <v>5.03</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>56.1</v>
+        <v>23.99</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>23.54</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>2771</v>
+        <v>10664</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>1</v>
@@ -1774,51 +1774,51 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>102.55</v>
+        <v>-34.26</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>85.18000000000001</v>
+        <v>-207.22</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>17.37</v>
+        <v>172.96</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>53.52</v>
+        <v>21.7</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>64.52</v>
+        <v>28.1</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>64.52</v>
+        <v>28.1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1552</v>
+        <v>1463</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>8.6</v>
+        <v>9.94</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>39.09</v>
+        <v>16.89</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>16.83</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7256</v>
+        <v>4325</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1828,57 +1828,57 @@
         <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>62.66</v>
+        <v>44.56</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>131.78</v>
+        <v>180.85</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-69.12</v>
+        <v>-136.29</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>25.23</v>
+        <v>32.52</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>22.31</v>
+        <v>29.98</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>22.31</v>
+        <v>29.98</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1444</v>
+        <v>1469</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>3.81</v>
+        <v>9.66</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>10.68</v>
+        <v>16.1</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>7.81</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>11399</v>
+        <v>2075</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1888,57 +1888,57 @@
         <v>1</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>15.06</v>
+        <v>146.63</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>26.38</v>
+        <v>22.63</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-11.32</v>
+        <v>124.01</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>23.74</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>16.38</v>
+        <v>111.43</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>16.38</v>
+        <v>111.43</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1419</v>
+        <v>1645</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>4.36</v>
+        <v>23.32</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>9.99</v>
+        <v>63.86</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>2.03</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9756</v>
+        <v>7256</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1957,48 +1957,48 @@
         <v>4</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>102.01</v>
+        <v>36.43</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-17.77</v>
+        <v>204.64</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>119.78</v>
+        <v>-168.21</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>29.21</v>
+        <v>25.23</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>43.05</v>
+        <v>22.31</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>43.05</v>
+        <v>22.31</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1504</v>
+        <v>1444</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>5.02</v>
+        <v>3.81</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>23.84</v>
+        <v>10.68</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>14.19</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>7289</v>
+        <v>5166</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -2008,57 +2008,57 @@
         <v>1</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>39.68</v>
+        <v>236.81</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>171.84</v>
+        <v>144.7</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-132.15</v>
+        <v>92.11</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>33.29</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>30.65</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>30.65</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1471</v>
+        <v>1615</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.83</v>
+        <v>15.17</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>6.75</v>
+        <v>56.1</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>13.07</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9208</v>
+        <v>7221</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Edwardsburg, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -2068,57 +2068,57 @@
         <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>23.11</v>
+        <v>-31.2</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-17.3</v>
+        <v>194.52</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>40.41</v>
+        <v>-225.72</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>44.43</v>
+        <v>8.82</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>60.26</v>
+        <v>19.74</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>60.26</v>
+        <v>19.74</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1543</v>
+        <v>1433</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>15.72</v>
+        <v>7.34</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>34.07</v>
+        <v>6.75</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>10.46</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>10642</v>
+        <v>9756</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -2128,57 +2128,57 @@
         <v>1</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-15.49</v>
+        <v>127.3</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>91.73</v>
+        <v>168.72</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-107.22</v>
+        <v>-41.41</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>25.63</v>
+        <v>29.21</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>16.19</v>
+        <v>43.04</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>16.19</v>
+        <v>43.04</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1419</v>
+        <v>1503</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.95</v>
+        <v>5.75</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>5.53</v>
+        <v>23.07</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>7.71</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10664</v>
+        <v>10181</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -2188,57 +2188,57 @@
         <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-14.09</v>
+        <v>23.88</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11.6</v>
+        <v>174.51</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-25.7</v>
+        <v>-150.63</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>21.7</v>
+        <v>23.43</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>28.98</v>
+        <v>20.17</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>28.98</v>
+        <v>20.17</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1466</v>
+        <v>1435</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>8.58</v>
+        <v>5.15</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>17.42</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>2.99</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>8767</v>
+        <v>10642</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -2248,64 +2248,64 @@
         <v>1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-22.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>51.51</v>
+        <v>278.22</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-73.76000000000001</v>
+        <v>-268.41</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>27.21</v>
+        <v>25.63</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>31.98</v>
+        <v>16.18</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>31.98</v>
+        <v>16.18</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1475</v>
+        <v>1418</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>4.97</v>
+        <v>3.68</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>18</v>
+        <v>4.77</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>9.01</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7809</v>
+        <v>904</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>2</v>
@@ -2314,58 +2314,58 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>29.81</v>
+        <v>-21.38</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>139.12</v>
+        <v>220.38</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-109.31</v>
+        <v>-241.75</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>23.83</v>
+        <v>27.91</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>31.65</v>
+        <v>2.37</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>31.65</v>
+        <v>2.37</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1474</v>
+        <v>1346</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>4.21</v>
+        <v>5.94</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>13.65</v>
+        <v>-2.69</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>13.78</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>10181</v>
+        <v>11399</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>2</v>
@@ -2374,58 +2374,58 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>49.48</v>
+        <v>-110.55</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>34.49</v>
+        <v>167.52</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>15</v>
+        <v>-278.06</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>23.43</v>
+        <v>23.74</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>19.39</v>
+        <v>9.51</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>19.39</v>
+        <v>9.51</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1432</v>
+        <v>1386</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>5.24</v>
+        <v>3.43</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>8.84</v>
+        <v>6.64</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>5.31</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6081</v>
+        <v>8423</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>2</v>
@@ -2434,58 +2434,58 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>73.05</v>
+        <v>86.19</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>78.98999999999999</v>
+        <v>63.35</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-5.94</v>
+        <v>22.85</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>59.73</v>
+        <v>28.04</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>62.98</v>
+        <v>38.26</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>62.98</v>
+        <v>38.26</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1549</v>
+        <v>1491</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>15.08</v>
+        <v>10.03</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>25.96</v>
+        <v>18.23</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>21.93</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>2</v>
@@ -2494,51 +2494,51 @@
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>-22.85</v>
+        <v>-101.6</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>57.64</v>
+        <v>133.33</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-80.48999999999999</v>
+        <v>-234.93</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>8.82</v>
+        <v>22.62</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>21.32</v>
+        <v>16.18</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>21.32</v>
+        <v>16.18</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1440</v>
+        <v>1418</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>7.1</v>
+        <v>4.22</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>4.9</v>
+        <v>8.34</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>9.33</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9566</v>
+        <v>7809</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -2548,43 +2548,43 @@
         <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="I34" s="2" t="n">
-        <v>57.57</v>
+        <v>100.1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>-70.18000000000001</v>
+        <v>198.7</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>127.74</v>
+        <v>-98.59999999999999</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>39.97</v>
+        <v>23.83</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>28.46</v>
+        <v>35.4</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>28.46</v>
+        <v>35.4</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1464</v>
+        <v>1484</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>14.76</v>
+        <v>15.92</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>9.43</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="35">
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -2617,48 +2617,48 @@
         <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>36.24</v>
+        <v>48.12</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>159.99</v>
+        <v>114.88</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-123.75</v>
+        <v>-66.75</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>39.07</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>26.51</v>
+        <v>26.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>26.51</v>
+        <v>26.6</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>1458</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>5.35</v>
+        <v>4.89</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>12.78</v>
+        <v>13.6</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>8.390000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7818</v>
+        <v>7658</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2668,57 +2668,57 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-9.539999999999999</v>
+        <v>-66.62</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>90.52</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-100.06</v>
+        <v>-145.63</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>32.45</v>
+        <v>14.34</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>20.69</v>
+        <v>7.36</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>20.69</v>
+        <v>7.36</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1438</v>
+        <v>1374</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>6.13</v>
+        <v>3.52</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>5.53</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>6.02</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>9671</v>
+        <v>6081</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2728,57 +2728,57 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>-3.06</v>
+        <v>156.37</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>40.09</v>
+        <v>138.49</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-43.15</v>
+        <v>17.88</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>27.39</v>
+        <v>59.73</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>30.32</v>
+        <v>56.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>30.32</v>
+        <v>56.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1471</v>
+        <v>1533</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>10.42</v>
+        <v>14.16</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>15.51</v>
+        <v>22.61</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>4.39</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8423</v>
+        <v>9566</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2788,57 +2788,57 @@
         <v>0</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>36.29</v>
+        <v>16</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>128.54</v>
+        <v>-141.87</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-92.25</v>
+        <v>157.87</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>28.04</v>
+        <v>39.97</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>37.65</v>
+        <v>23.42</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>37.65</v>
+        <v>23.42</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1490</v>
+        <v>1447</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>10.21</v>
+        <v>3.67</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>17.44</v>
+        <v>11.71</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>9.99</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7658</v>
+        <v>7818</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -2857,48 +2857,48 @@
         <v>0</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>-42.95</v>
+        <v>-67.25</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>86.68000000000001</v>
+        <v>-109</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-129.63</v>
+        <v>41.75</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>14.34</v>
+        <v>32.45</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>3.6</v>
+        <v>14.81</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>3.6</v>
+        <v>14.81</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1353</v>
+        <v>1412</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>3.31</v>
+        <v>6.79</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>3.26</v>
+        <v>4.26</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>-2.96</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3234</v>
+        <v>9671</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         <v>0</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-12.92</v>
+        <v>-4.69</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>32.17</v>
+        <v>-138.73</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-45.09</v>
+        <v>134.04</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>22.62</v>
+        <v>27.39</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>15.4</v>
+        <v>30.41</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>15.4</v>
+        <v>30.41</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1415</v>
+        <v>1470</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>4.31</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>7.7</v>
+        <v>16.34</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>3.39</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="41">
@@ -3108,22 +3108,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>122.64</v>
+        <v>121.75</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>122.64</v>
+        <v>121.75</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>20.13</v>
+        <v>21.49</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>72.72</v>
+        <v>72.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>29.79</v>
+        <v>28.06</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="3">
@@ -3170,22 +3170,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>117.31</v>
+        <v>111.43</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>117.31</v>
+        <v>111.43</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>22.66</v>
+        <v>23.32</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>68.15000000000001</v>
+        <v>63.86</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>26.5</v>
+        <v>24.24</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1654</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="5">
@@ -3201,19 +3201,19 @@
         <v>68.89</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>110.45</v>
+        <v>111.23</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>110.45</v>
+        <v>111.23</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.76</v>
+        <v>23.68</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>60.94</v>
+        <v>61.58</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>25.74</v>
+        <v>25.98</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1645</v>
@@ -3232,22 +3232,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>103.83</v>
+        <v>110.92</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>103.83</v>
+        <v>110.92</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20.21</v>
+        <v>20.27</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>56.37</v>
+        <v>62.37</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>27.24</v>
+        <v>28.28</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1634</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="7">
@@ -3325,22 +3325,22 @@
         <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>81.81999999999999</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>81.81999999999999</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>48.4</v>
+        <v>50.25</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>24.04</v>
+        <v>20.37</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1588</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="10">
@@ -3356,22 +3356,22 @@
         <v>50.66</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>65.38</v>
+        <v>69.14</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>65.38</v>
+        <v>69.14</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>7.28</v>
+        <v>7.49</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>38.03</v>
+        <v>40.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>20.08</v>
+        <v>21.35</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1554</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="11">
@@ -3387,81 +3387,81 @@
         <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>64.52</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>64.52</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>8.6</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>39.09</v>
+        <v>42.02</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>16.83</v>
+        <v>17.81</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1552</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6081</v>
+        <v>858</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>59.73</v>
+        <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>62.98</v>
+        <v>64.97</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>62.98</v>
+        <v>64.97</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>15.08</v>
+        <v>8.56</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>25.96</v>
+        <v>35.3</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>21.93</v>
+        <v>21.1</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1549</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>858</v>
+        <v>9208</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>55.1</v>
+        <v>44.43</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>60.53</v>
+        <v>60.88</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>60.53</v>
+        <v>60.88</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>15.54</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>32.37</v>
+        <v>34.86</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>20.13</v>
+        <v>10.48</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1543</v>
@@ -3469,33 +3469,33 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9208</v>
+        <v>6081</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>44.43</v>
+        <v>59.73</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>60.26</v>
+        <v>56.1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>60.26</v>
+        <v>56.1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>15.72</v>
+        <v>14.16</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>34.07</v>
+        <v>22.61</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.46</v>
+        <v>19.34</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1543</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="15">
@@ -3511,143 +3511,143 @@
         <v>29.21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>43.05</v>
+        <v>43.04</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>43.05</v>
+        <v>43.04</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.02</v>
+        <v>5.75</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>23.84</v>
+        <v>23.07</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>14.19</v>
+        <v>14.23</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8423</v>
+        <v>7808</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>28.04</v>
+        <v>24.37</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>37.65</v>
+        <v>42.95</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>37.65</v>
+        <v>42.95</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>10.21</v>
+        <v>6.01</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>17.44</v>
+        <v>25.74</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.99</v>
+        <v>11.21</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1490</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>7808</v>
+        <v>8767</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>24.37</v>
+        <v>27.21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>35.86</v>
+        <v>39.07</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>35.86</v>
+        <v>39.07</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.95</v>
+        <v>5.03</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>19.74</v>
+        <v>23.99</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.17</v>
+        <v>10.05</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1486</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9206</v>
+        <v>8423</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>21.07</v>
+        <v>28.04</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>35.77</v>
+        <v>38.26</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>35.77</v>
+        <v>38.26</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5.47</v>
+        <v>10.03</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15.33</v>
+        <v>18.23</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>14.97</v>
+        <v>10.01</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1486</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9685</v>
+        <v>7809</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.75</v>
+        <v>23.83</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>15.04</v>
+        <v>4.43</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3.81</v>
+        <v>15.92</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.35</v>
+        <v>15.06</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1484</v>
@@ -3655,33 +3655,33 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8767</v>
+        <v>9685</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>27.21</v>
+        <v>27.75</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>31.98</v>
+        <v>35.2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.98</v>
+        <v>35.2</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4.97</v>
+        <v>15.04</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18</v>
+        <v>3.81</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.01</v>
+        <v>16.35</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1475</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="21">
@@ -3717,343 +3717,343 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7809</v>
+        <v>9671</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>23.83</v>
+        <v>27.39</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.65</v>
+        <v>30.41</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>31.65</v>
+        <v>30.41</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.21</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13.65</v>
+        <v>16.34</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>13.78</v>
+        <v>4.11</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1474</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7289</v>
+        <v>4325</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>33.29</v>
+        <v>32.52</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>30.65</v>
+        <v>29.98</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>30.65</v>
+        <v>29.98</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>10.83</v>
+        <v>9.66</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>6.75</v>
+        <v>16.1</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>13.07</v>
+        <v>4.22</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9638</v>
+        <v>7289</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>22.93</v>
+        <v>33.29</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>30.36</v>
+        <v>29.77</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30.36</v>
+        <v>29.77</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>12.19</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>13.2</v>
+        <v>6.23</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>7.3</v>
+        <v>11.35</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1471</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>27.39</v>
+        <v>21.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>30.32</v>
+        <v>28.9</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>30.32</v>
+        <v>28.9</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10.42</v>
+        <v>4.54</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>15.51</v>
+        <v>11.98</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.39</v>
+        <v>12.38</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1471</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4325</v>
+        <v>9549</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>32.52</v>
+        <v>17.6</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>29.89</v>
+        <v>28.83</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>29.89</v>
+        <v>28.83</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>10.12</v>
+        <v>7.01</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15.27</v>
+        <v>16.43</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4.5</v>
+        <v>5.38</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>5256</v>
+        <v>10664</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>35.18</v>
+        <v>21.7</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>29.88</v>
+        <v>28.1</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>29.88</v>
+        <v>28.1</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.88</v>
+        <v>9.94</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>17.89</v>
+        <v>16.89</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.11</v>
+        <v>1.26</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1469</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10664</v>
+        <v>5980</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>21.7</v>
+        <v>38.55</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>28.98</v>
+        <v>27.47</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>28.98</v>
+        <v>27.47</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>8.58</v>
+        <v>7.6</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>17.42</v>
+        <v>13.5</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>2.99</v>
+        <v>6.37</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1466</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9566</v>
+        <v>8285</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>39.97</v>
+        <v>39.07</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>28.46</v>
+        <v>26.6</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>28.46</v>
+        <v>26.6</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.27</v>
+        <v>4.89</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14.76</v>
+        <v>13.6</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>9.43</v>
+        <v>8.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1464</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5980</v>
+        <v>9638</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>38.55</v>
+        <v>22.93</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>26.85</v>
+        <v>25.31</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>26.85</v>
+        <v>25.31</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>7.78</v>
+        <v>9.26</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>12.71</v>
+        <v>10.14</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>6.36</v>
+        <v>5.91</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1459</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>8285</v>
+        <v>5256</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>39.07</v>
+        <v>35.18</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>26.51</v>
+        <v>24.83</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>26.51</v>
+        <v>24.83</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>12.78</v>
+        <v>14.83</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>8.390000000000001</v>
+        <v>4.72</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1458</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9549</v>
+        <v>9566</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>17.6</v>
+        <v>39.97</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>24.39</v>
+        <v>23.42</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>24.39</v>
+        <v>23.42</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>6.49</v>
+        <v>3.67</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>13.5</v>
+        <v>11.71</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>4.41</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="33">
@@ -4089,250 +4089,250 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7221</v>
+        <v>10181</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>8.82</v>
+        <v>23.43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>21.32</v>
+        <v>20.17</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>21.32</v>
+        <v>20.17</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7.1</v>
+        <v>5.15</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>4.9</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9.33</v>
+        <v>5.55</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1440</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7818</v>
+        <v>7221</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>32.45</v>
+        <v>8.82</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>20.69</v>
+        <v>19.74</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>20.69</v>
+        <v>19.74</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>6.13</v>
+        <v>7.34</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8.539999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>6.02</v>
+        <v>5.65</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1438</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10181</v>
+        <v>3234</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23.43</v>
+        <v>22.62</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>19.39</v>
+        <v>16.18</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>19.39</v>
+        <v>16.18</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.24</v>
+        <v>4.22</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.84</v>
+        <v>8.34</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>5.31</v>
+        <v>3.62</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1432</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>11399</v>
+        <v>10642</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.74</v>
+        <v>25.63</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>16.38</v>
+        <v>16.18</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>16.38</v>
+        <v>16.18</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4.36</v>
+        <v>3.68</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>9.99</v>
+        <v>4.77</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.03</v>
+        <v>7.74</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10642</v>
+        <v>7818</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25.63</v>
+        <v>32.45</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>16.19</v>
+        <v>14.81</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>16.19</v>
+        <v>14.81</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>2.95</v>
+        <v>6.79</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5.53</v>
+        <v>4.26</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>7.71</v>
+        <v>3.76</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1419</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>3234</v>
+        <v>11399</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>22.62</v>
+        <v>23.74</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>15.4</v>
+        <v>9.51</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>15.4</v>
+        <v>9.51</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4.31</v>
+        <v>3.43</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>7.7</v>
+        <v>6.64</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>3.39</v>
+        <v>-0.57</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1415</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>904</v>
+        <v>7658</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>27.91</v>
+        <v>14.34</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8.26</v>
+        <v>7.36</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>8.26</v>
+        <v>7.36</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>5.28</v>
+        <v>3.52</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1.6</v>
+        <v>5.53</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1.38</v>
+        <v>-1.69</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1379</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>7658</v>
+        <v>904</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>14.34</v>
+        <v>27.91</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>3.31</v>
+        <v>5.94</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3.26</v>
+        <v>-2.69</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-2.96</v>
+        <v>-0.88</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1353</v>
+        <v>1346</v>
       </c>
     </row>
   </sheetData>
@@ -4385,154 +4385,154 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4967</v>
+        <v>5166</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>174.08</v>
+        <v>236.81</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-35.96</v>
+        <v>144.7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>210.04</v>
+        <v>92.11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>1023</v>
+        <v>4967</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>162.25</v>
+        <v>234.72</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-47.22</v>
+        <v>-219.84</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>209.47</v>
+        <v>454.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3620</v>
+        <v>1023</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>139.79</v>
+        <v>211.07</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-58.96</v>
+        <v>-132.31</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>198.75</v>
+        <v>343.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>5256</v>
+        <v>3620</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>116.19</v>
+        <v>189.69</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>47.95</v>
+        <v>-124.15</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>68.23999999999999</v>
+        <v>313.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>10633</v>
+        <v>7656</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>115.31</v>
+        <v>178.02</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>176.19</v>
+        <v>-210.21</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-60.88</v>
+        <v>388.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>7220</v>
+        <v>6081</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>112.03</v>
+        <v>156.37</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>51.86</v>
+        <v>138.49</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>60.17</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>9638</v>
+        <v>2075</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>108.61</v>
+        <v>146.63</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>19.77</v>
+        <v>22.63</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>88.84</v>
+        <v>124.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>2771</v>
+        <v>8767</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>102.55</v>
+        <v>128.95</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.18000000000001</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>17.37</v>
+        <v>53.63</v>
       </c>
     </row>
     <row r="10">
@@ -4545,583 +4545,583 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>102.01</v>
+        <v>127.3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-17.77</v>
+        <v>168.72</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>119.78</v>
+        <v>-41.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2075</v>
+        <v>3875</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>101.96</v>
+        <v>123.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>113.25</v>
+        <v>-56.71</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-11.29</v>
+        <v>180.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5980</v>
+        <v>7289</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>99.79000000000001</v>
+        <v>116.48</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-3.03</v>
+        <v>115.79</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>102.82</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>9549</v>
+        <v>7809</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>97.88</v>
+        <v>100.1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>51.68</v>
+        <v>198.7</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46.2</v>
+        <v>-98.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5166</v>
+        <v>7220</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>91.03</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>67.01000000000001</v>
+        <v>281.99</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>24.02</v>
+        <v>-194.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9206</v>
+        <v>10633</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>89.59</v>
+        <v>86.78</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>33.87</v>
+        <v>104.43</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>55.71</v>
+        <v>-17.64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4325</v>
+        <v>8423</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>80.89</v>
+        <v>86.19</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>227.11</v>
+        <v>63.35</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-146.22</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>7656</v>
+        <v>858</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-85.59999999999999</v>
+        <v>15.61</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>165.51</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6081</v>
+        <v>2771</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>73.05</v>
+        <v>78.88</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>78.98999999999999</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-5.94</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>858</v>
+        <v>9638</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>72.28</v>
+        <v>76.5</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>110.52</v>
+        <v>275.42</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-38.25</v>
+        <v>-198.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7256</v>
+        <v>9549</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>62.66</v>
+        <v>56.12</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>131.78</v>
+        <v>63.88</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-69.12</v>
+        <v>-7.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>9566</v>
+        <v>9685</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>57.57</v>
+        <v>55.55</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-70.18000000000001</v>
+        <v>-18.77</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>127.74</v>
+        <v>74.31999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>10181</v>
+        <v>8285</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>49.48</v>
+        <v>48.12</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>34.49</v>
+        <v>114.88</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>15</v>
+        <v>-66.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7289</v>
+        <v>4325</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>39.68</v>
+        <v>44.56</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>171.84</v>
+        <v>180.85</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-132.15</v>
+        <v>-136.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>36.29</v>
+        <v>41.51</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>128.54</v>
+        <v>-178.03</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-92.25</v>
+        <v>219.54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>8285</v>
+        <v>7256</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>36.24</v>
+        <v>36.43</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>159.99</v>
+        <v>204.64</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-123.75</v>
+        <v>-168.21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7809</v>
+        <v>10181</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>29.81</v>
+        <v>23.88</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>139.12</v>
+        <v>174.51</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-109.31</v>
+        <v>-150.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>3875</v>
+        <v>9566</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>25.4</v>
+        <v>16</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>-141.87</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-42.49</v>
+        <v>157.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9208</v>
+        <v>10642</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>23.11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-17.3</v>
+        <v>278.22</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>40.41</v>
+        <v>-268.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>904</v>
+        <v>5980</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>20.38</v>
+        <v>6.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>208.18</v>
+        <v>172.68</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-187.8</v>
+        <v>-166.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7808</v>
+        <v>9671</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>15.72</v>
+        <v>-4.69</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>-51.58</v>
+        <v>-138.73</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>67.3</v>
+        <v>134.04</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>11399</v>
+        <v>904</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>15.06</v>
+        <v>-21.38</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>26.38</v>
+        <v>220.38</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-11.32</v>
+        <v>-241.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9685</v>
+        <v>7221</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>11.06</v>
+        <v>-31.2</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>-7.46</v>
+        <v>194.52</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18.52</v>
+        <v>-225.72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-3.06</v>
+        <v>-33.83</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>40.09</v>
+        <v>-28.01</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-43.15</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7818</v>
+        <v>10664</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-9.539999999999999</v>
+        <v>-34.26</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>90.52</v>
+        <v>-207.22</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-100.06</v>
+        <v>172.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>3234</v>
+        <v>7808</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-12.92</v>
+        <v>-40.65</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>32.17</v>
+        <v>60.83</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-45.09</v>
+        <v>-101.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10664</v>
+        <v>7658</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-14.09</v>
+        <v>-66.62</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>11.6</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-25.7</v>
+        <v>-145.63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10642</v>
+        <v>7818</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-15.49</v>
+        <v>-67.25</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>91.73</v>
+        <v>-109</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-107.22</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8767</v>
+        <v>5256</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-22.25</v>
+        <v>-79.5</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>51.51</v>
+        <v>35.45</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-73.76000000000001</v>
+        <v>-114.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-22.85</v>
+        <v>-101.6</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>57.64</v>
+        <v>133.33</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-80.48999999999999</v>
+        <v>-234.93</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7658</v>
+        <v>11399</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-42.95</v>
+        <v>-110.55</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>86.68000000000001</v>
+        <v>167.52</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-129.63</v>
+        <v>-278.06</v>
       </c>
     </row>
     <row r="41">
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -5239,15 +5239,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9638</v>
+        <v>1023</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -5256,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -5264,15 +5264,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1023</v>
+        <v>3620</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -5289,11 +5289,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -5314,15 +5314,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7220</v>
+        <v>7808</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -5331,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -5339,15 +5339,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>9206</v>
+        <v>7656</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -5356,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -5364,24 +5364,24 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3875</v>
+        <v>10633</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -5389,24 +5389,24 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7656</v>
+        <v>9638</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -5414,24 +5414,24 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7808</v>
+        <v>9549</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -5439,24 +5439,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5256</v>
+        <v>858</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -5464,15 +5464,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10633</v>
+        <v>5980</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -5489,15 +5489,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>4325</v>
+        <v>3875</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -5514,18 +5514,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2075</v>
+        <v>9685</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -5539,24 +5539,24 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9685</v>
+        <v>2771</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -5564,15 +5564,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5980</v>
+        <v>7289</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1</v>
@@ -5581,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -5589,15 +5589,15 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9549</v>
+        <v>9206</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>1</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -5614,15 +5614,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>858</v>
+        <v>9208</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -5639,15 +5639,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>904</v>
+        <v>5256</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1</v>
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -5664,15 +5664,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>5166</v>
+        <v>8767</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1</v>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -5689,15 +5689,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2771</v>
+        <v>10664</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>1</v>
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -5714,24 +5714,24 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>7256</v>
+        <v>4325</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -5739,24 +5739,24 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>11399</v>
+        <v>2075</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -5764,11 +5764,11 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>9756</v>
+        <v>7256</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -5789,24 +5789,24 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>7289</v>
+        <v>5166</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -5814,24 +5814,24 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9208</v>
+        <v>7221</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -5839,24 +5839,24 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10642</v>
+        <v>9756</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -5864,24 +5864,24 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10664</v>
+        <v>10181</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -5889,24 +5889,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>8767</v>
+        <v>10642</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -5914,15 +5914,15 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7809</v>
+        <v>904</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -5939,15 +5939,15 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10181</v>
+        <v>11399</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>2</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -5964,15 +5964,15 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>6081</v>
+        <v>8423</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>2</v>
@@ -5981,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -5989,15 +5989,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>2</v>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -6014,24 +6014,24 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9566</v>
+        <v>7809</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -6050,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
@@ -6064,24 +6064,24 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7818</v>
+        <v>7658</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -6089,24 +6089,24 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>9671</v>
+        <v>6081</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -6114,24 +6114,24 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>8423</v>
+        <v>9566</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -6139,18 +6139,18 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>7658</v>
+        <v>7818</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -6164,18 +6164,18 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>3234</v>
+        <v>9671</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0</v>
@@ -6284,21 +6284,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4967</v>
+        <v>5166</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>174.08</v>
+        <v>236.81</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-35.96</v>
+        <v>144.7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>210.04</v>
+        <v>92.11</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6307,21 +6307,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1023</v>
+        <v>4967</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>162.25</v>
+        <v>234.72</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-47.22</v>
+        <v>-219.84</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>209.47</v>
+        <v>454.56</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6330,21 +6330,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3620</v>
+        <v>1023</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>139.79</v>
+        <v>211.07</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-58.96</v>
+        <v>-132.31</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>198.75</v>
+        <v>343.38</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6353,21 +6353,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5256</v>
+        <v>3620</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>116.19</v>
+        <v>189.69</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>47.95</v>
+        <v>-124.15</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>68.23999999999999</v>
+        <v>313.85</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6376,21 +6376,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>10633</v>
+        <v>7656</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>115.31</v>
+        <v>178.02</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>176.19</v>
+        <v>-210.21</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-60.88</v>
+        <v>388.23</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6399,21 +6399,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7220</v>
+        <v>6081</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>112.03</v>
+        <v>156.37</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>51.86</v>
+        <v>138.49</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>60.17</v>
+        <v>17.88</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6422,21 +6422,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9638</v>
+        <v>2075</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>108.61</v>
+        <v>146.63</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.77</v>
+        <v>22.63</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>88.84</v>
+        <v>124.01</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6445,21 +6445,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>2771</v>
+        <v>8767</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>102.55</v>
+        <v>128.95</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>85.18000000000001</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>17.37</v>
+        <v>53.63</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>102.01</v>
+        <v>127.3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-17.77</v>
+        <v>168.72</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>119.78</v>
+        <v>-41.41</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6491,21 +6491,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2075</v>
+        <v>3875</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>101.96</v>
+        <v>123.52</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>113.25</v>
+        <v>-56.71</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-11.29</v>
+        <v>180.23</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6514,21 +6514,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>5980</v>
+        <v>7289</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>99.79000000000001</v>
+        <v>116.48</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-3.03</v>
+        <v>115.79</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>102.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6537,21 +6537,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9549</v>
+        <v>7809</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>97.88</v>
+        <v>100.1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>51.68</v>
+        <v>198.7</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46.2</v>
+        <v>-98.59999999999999</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6560,21 +6560,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5166</v>
+        <v>7220</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>91.03</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>67.01000000000001</v>
+        <v>281.99</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>24.02</v>
+        <v>-194.28</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6583,21 +6583,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9206</v>
+        <v>10633</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>89.59</v>
+        <v>86.78</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>33.87</v>
+        <v>104.43</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>55.71</v>
+        <v>-17.64</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6606,21 +6606,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4325</v>
+        <v>8423</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>80.89</v>
+        <v>86.19</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>227.11</v>
+        <v>63.35</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-146.22</v>
+        <v>22.85</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6629,21 +6629,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>7656</v>
+        <v>858</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-85.59999999999999</v>
+        <v>15.61</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>165.51</v>
+        <v>70.38</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6652,21 +6652,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>6081</v>
+        <v>2771</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>73.05</v>
+        <v>78.88</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>78.98999999999999</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-5.94</v>
+        <v>1.37</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6675,21 +6675,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>858</v>
+        <v>9638</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>72.28</v>
+        <v>76.5</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>110.52</v>
+        <v>275.42</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-38.25</v>
+        <v>-198.92</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6698,21 +6698,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7256</v>
+        <v>9549</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>62.66</v>
+        <v>56.12</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>131.78</v>
+        <v>63.88</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-69.12</v>
+        <v>-7.75</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6721,21 +6721,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>9566</v>
+        <v>9685</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>57.57</v>
+        <v>55.55</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-70.18000000000001</v>
+        <v>-18.77</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>127.74</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6744,21 +6744,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>10181</v>
+        <v>8285</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>49.48</v>
+        <v>48.12</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>34.49</v>
+        <v>114.88</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>15</v>
+        <v>-66.75</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6767,21 +6767,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>7289</v>
+        <v>4325</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>39.68</v>
+        <v>44.56</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>171.84</v>
+        <v>180.85</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-132.15</v>
+        <v>-136.29</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6790,21 +6790,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>36.29</v>
+        <v>41.51</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>128.54</v>
+        <v>-178.03</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-92.25</v>
+        <v>219.54</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6813,21 +6813,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>8285</v>
+        <v>7256</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>36.24</v>
+        <v>36.43</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>159.99</v>
+        <v>204.64</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-123.75</v>
+        <v>-168.21</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6836,21 +6836,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7809</v>
+        <v>10181</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>29.81</v>
+        <v>23.88</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>139.12</v>
+        <v>174.51</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-109.31</v>
+        <v>-150.63</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6859,21 +6859,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3875</v>
+        <v>9566</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>25.4</v>
+        <v>16</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>-141.87</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-42.49</v>
+        <v>157.87</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6882,21 +6882,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>9208</v>
+        <v>10642</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>23.11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-17.3</v>
+        <v>278.22</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>40.41</v>
+        <v>-268.41</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6905,21 +6905,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>904</v>
+        <v>5980</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>20.38</v>
+        <v>6.3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>208.18</v>
+        <v>172.68</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-187.8</v>
+        <v>-166.38</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6928,21 +6928,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7808</v>
+        <v>9671</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>15.72</v>
+        <v>-4.69</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-51.58</v>
+        <v>-138.73</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>67.3</v>
+        <v>134.04</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6951,21 +6951,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>11399</v>
+        <v>904</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>15.06</v>
+        <v>-21.38</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>26.38</v>
+        <v>220.38</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-11.32</v>
+        <v>-241.75</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6974,21 +6974,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9685</v>
+        <v>7221</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>11.06</v>
+        <v>-31.2</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-7.46</v>
+        <v>194.52</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>18.52</v>
+        <v>-225.72</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6997,21 +6997,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-3.06</v>
+        <v>-33.83</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>40.09</v>
+        <v>-28.01</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-43.15</v>
+        <v>-5.82</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7020,21 +7020,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7818</v>
+        <v>10664</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-9.539999999999999</v>
+        <v>-34.26</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>90.52</v>
+        <v>-207.22</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-100.06</v>
+        <v>172.96</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -7043,21 +7043,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3234</v>
+        <v>7808</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-12.92</v>
+        <v>-40.65</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>32.17</v>
+        <v>60.83</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-45.09</v>
+        <v>-101.48</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -7066,21 +7066,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>10664</v>
+        <v>7658</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-14.09</v>
+        <v>-66.62</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11.6</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-25.7</v>
+        <v>-145.63</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7089,21 +7089,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>10642</v>
+        <v>7818</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-15.49</v>
+        <v>-67.25</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>91.73</v>
+        <v>-109</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-107.22</v>
+        <v>41.75</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -7112,21 +7112,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>8767</v>
+        <v>5256</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-22.25</v>
+        <v>-79.5</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>51.51</v>
+        <v>35.45</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-73.76000000000001</v>
+        <v>-114.95</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -7135,21 +7135,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-22.85</v>
+        <v>-101.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>57.64</v>
+        <v>133.33</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-80.48999999999999</v>
+        <v>-234.93</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -7158,21 +7158,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>7658</v>
+        <v>11399</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-42.95</v>
+        <v>-110.55</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>86.68000000000001</v>
+        <v>167.52</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-129.63</v>
+        <v>-278.06</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -634,51 +634,51 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>234.72</v>
+        <v>144.03</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-219.84</v>
+        <v>27.3</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>454.56</v>
+        <v>116.73</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>68.89</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>111.23</v>
+        <v>108.58</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>111.23</v>
+        <v>108.58</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23.68</v>
+        <v>23.01</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>61.58</v>
+        <v>60.36</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>25.98</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>1023</v>
+        <v>7220</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Brighton, Michigan</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -697,48 +697,48 @@
         <v>13</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>211.07</v>
+        <v>137.49</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-132.31</v>
+        <v>87.27</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>343.38</v>
+        <v>50.23</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>68.08</v>
+        <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>121.55</v>
+        <v>109.6</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>121.55</v>
+        <v>109.6</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1660</v>
+        <v>1642</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>19.89</v>
+        <v>23.65</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>68.91</v>
+        <v>67.36</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>32.74</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3620</v>
+        <v>1023</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Saint Joseph, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -754,58 +754,58 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>189.69</v>
+        <v>177.49</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-124.15</v>
+        <v>-54.52</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>313.85</v>
+        <v>232.01</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>110.92</v>
+        <v>119.97</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>110.92</v>
+        <v>119.97</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1644</v>
+        <v>1656</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>20.27</v>
+        <v>20.14</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>62.37</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>28.28</v>
+        <v>29.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Brighton, Michigan</t>
+          <t>Saint Joseph, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -814,37 +814,37 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>87.70999999999999</v>
+        <v>251.88</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>281.99</v>
+        <v>-81.13</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-194.28</v>
+        <v>333.01</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>45.04</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>95.17</v>
+        <v>110.92</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>95.17</v>
+        <v>110.92</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1616</v>
+        <v>1644</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>21.87</v>
+        <v>20.27</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>57.78</v>
+        <v>62.37</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>15.52</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>12</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-40.65</v>
+        <v>-43.09</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>60.83</v>
+        <v>70.89</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-101.48</v>
+        <v>-113.98</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>24.37</v>
@@ -925,7 +925,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -934,58 +934,58 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>178.02</v>
+        <v>101.55</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-210.21</v>
+        <v>-22.6</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>388.23</v>
+        <v>124.15</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>50.91</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>77.22</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>77.22</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>50.25</v>
+        <v>47.34</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>20.37</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>10633</v>
+        <v>3875</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -994,51 +994,51 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>86.78</v>
+        <v>161.25</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>104.43</v>
+        <v>-31.18</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-17.64</v>
+        <v>192.43</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>45.8</v>
+        <v>50.66</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>121.75</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>121.75</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1659</v>
+        <v>1590</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>21.49</v>
+        <v>9.26</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>72.2</v>
+        <v>49.88</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>28.06</v>
+        <v>24.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>9638</v>
+        <v>10633</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1054,51 +1054,51 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>76.5</v>
+        <v>172.92</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>275.42</v>
+        <v>36.95</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-198.92</v>
+        <v>135.97</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>22.93</v>
+        <v>45.8</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>25.31</v>
+        <v>121.75</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>25.31</v>
+        <v>121.75</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1454</v>
+        <v>1659</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>9.26</v>
+        <v>21.49</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>10.14</v>
+        <v>72.2</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>5.91</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9549</v>
+        <v>9638</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -1117,48 +1117,48 @@
         <v>9</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>56.12</v>
+        <v>58.43</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>63.88</v>
+        <v>125.38</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-7.75</v>
+        <v>-66.95999999999999</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>17.6</v>
+        <v>22.93</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>28.83</v>
+        <v>25.31</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>28.83</v>
+        <v>25.31</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1465</v>
+        <v>1454</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>7.01</v>
+        <v>9.26</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>16.43</v>
+        <v>10.14</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>5.38</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>858</v>
+        <v>5980</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1177,55 +1177,55 @@
         <v>9</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>86</v>
+        <v>55.62</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>15.61</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>70.38</v>
+        <v>-36.89</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>55.1</v>
+        <v>38.55</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>64.97</v>
+        <v>27.47</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>64.97</v>
+        <v>27.47</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1552</v>
+        <v>1461</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.56</v>
+        <v>7.6</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>35.3</v>
+        <v>13.5</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>21.1</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5980</v>
+        <v>9208</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Edwardsburg, Michigan</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
@@ -1234,58 +1234,58 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6.3</v>
+        <v>-14.38</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>172.68</v>
+        <v>-138.03</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-166.38</v>
+        <v>123.65</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>38.55</v>
+        <v>44.43</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>27.47</v>
+        <v>57.86</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>27.47</v>
+        <v>57.86</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1461</v>
+        <v>1536</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>7.6</v>
+        <v>15.92</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>13.5</v>
+        <v>31.95</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>6.37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>3875</v>
+        <v>10664</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>1</v>
@@ -1294,118 +1294,118 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>123.52</v>
+        <v>-42.73</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-56.71</v>
+        <v>-57.23</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>180.23</v>
+        <v>14.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>50.66</v>
+        <v>21.7</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>69.14</v>
+        <v>25.45</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>69.14</v>
+        <v>25.45</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1561</v>
+        <v>1454</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>7.49</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>40.3</v>
+        <v>15.67</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>21.35</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9685</v>
+        <v>7289</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>55.55</v>
+        <v>59.22</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-18.77</v>
+        <v>100.09</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>74.31999999999999</v>
+        <v>-40.87</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>27.75</v>
+        <v>33.29</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35.2</v>
+        <v>28.96</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>35.2</v>
+        <v>28.96</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1484</v>
+        <v>1465</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>15.04</v>
+        <v>12.1</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>3.81</v>
+        <v>5.43</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>16.35</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>2771</v>
+        <v>9206</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>1</v>
@@ -1414,51 +1414,51 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>78.88</v>
+        <v>3.37</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>77.51000000000001</v>
+        <v>-10.33</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1.37</v>
+        <v>13.7</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>53.52</v>
+        <v>21.07</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>68.95999999999999</v>
+        <v>28.09</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>68.95999999999999</v>
+        <v>28.09</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1560</v>
+        <v>1463</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>9.130000000000001</v>
+        <v>4.45</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>42.02</v>
+        <v>11.18</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>17.81</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7289</v>
+        <v>2771</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1477,43 +1477,43 @@
         <v>8</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>116.48</v>
+        <v>43.22</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>115.79</v>
+        <v>62.74</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>-19.51</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>33.29</v>
+        <v>53.52</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>29.77</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>29.77</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1468</v>
+        <v>1560</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>12.19</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>6.23</v>
+        <v>42.02</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>11.35</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9206</v>
+        <v>2075</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1528,57 +1528,57 @@
         <v>2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-33.83</v>
+        <v>106.4</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-28.01</v>
+        <v>86.64</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-5.82</v>
+        <v>19.76</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>21.07</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>28.9</v>
+        <v>108.78</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>28.9</v>
+        <v>108.78</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1465</v>
+        <v>1640</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>4.54</v>
+        <v>22.66</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>11.98</v>
+        <v>62.64</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>12.38</v>
+        <v>23.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9208</v>
+        <v>858</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Edwardsburg, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1588,57 +1588,57 @@
         <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>41.51</v>
+        <v>150.02</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-178.03</v>
+        <v>141.15</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>219.54</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>44.43</v>
+        <v>55.1</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>60.88</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>60.88</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1543</v>
+        <v>1553</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>15.54</v>
+        <v>8.43</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>34.86</v>
+        <v>35.77</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>10.48</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>5256</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1657,48 +1657,48 @@
         <v>7</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-79.5</v>
+        <v>72.33</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>35.45</v>
+        <v>32.26</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-114.95</v>
+        <v>40.07</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>35.18</v>
+        <v>27.21</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>24.83</v>
+        <v>39.07</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>24.83</v>
+        <v>39.07</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1452</v>
+        <v>1493</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>5.28</v>
+        <v>5.03</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>14.83</v>
+        <v>23.99</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>4.72</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8767</v>
+        <v>8423</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1708,57 +1708,57 @@
         <v>2</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>128.95</v>
+        <v>102.18</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>75.31999999999999</v>
+        <v>47.68</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>53.63</v>
+        <v>54.5</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>27.21</v>
+        <v>28.04</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>39.07</v>
+        <v>52.69</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>39.07</v>
+        <v>52.69</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1493</v>
+        <v>1525</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>5.03</v>
+        <v>11.8</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>23.99</v>
+        <v>27.81</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>10.05</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>10664</v>
+        <v>9549</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1768,43 +1768,43 @@
         <v>2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-34.26</v>
+        <v>36.29</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-207.22</v>
+        <v>-1.78</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>172.96</v>
+        <v>38.07</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>21.7</v>
+        <v>17.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>28.1</v>
+        <v>25.74</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>28.1</v>
+        <v>25.74</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1463</v>
+        <v>1455</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>9.94</v>
+        <v>6.27</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>16.89</v>
+        <v>14.31</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.26</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="22">
@@ -1837,13 +1837,13 @@
         <v>6</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>44.56</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>180.85</v>
+        <v>108.94</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-136.29</v>
+        <v>-24.87</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>32.52</v>
@@ -1869,26 +1869,26 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>2075</v>
+        <v>9685</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="E23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
@@ -1897,94 +1897,94 @@
         <v>6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>146.63</v>
+        <v>33.74</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>22.63</v>
+        <v>7.7</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>124.01</v>
+        <v>26.04</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>27.75</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>111.43</v>
+        <v>33.08</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>111.43</v>
+        <v>33.08</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1645</v>
+        <v>1477</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>23.32</v>
+        <v>15.75</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>63.86</v>
+        <v>2.19</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>24.24</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>36.43</v>
+        <v>-19.26</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>204.64</v>
+        <v>47.8</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-168.21</v>
+        <v>-67.06</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>25.23</v>
+        <v>35.18</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>22.31</v>
+        <v>21.75</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>22.31</v>
+        <v>21.75</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>3.81</v>
+        <v>4.53</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>10.68</v>
+        <v>12.71</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>7.81</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="25">
@@ -2017,13 +2017,13 @@
         <v>5</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>236.81</v>
+        <v>126.23</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>144.7</v>
+        <v>57.28</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>92.11</v>
+        <v>68.95</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>71.68000000000001</v>
@@ -2035,30 +2035,30 @@
         <v>94.81999999999999</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>15.17</v>
+        <v>15.9</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>56.1</v>
+        <v>55.34</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>23.54</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7221</v>
+        <v>9756</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -2077,48 +2077,48 @@
         <v>5</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-31.2</v>
+        <v>39.61</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>194.52</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-225.72</v>
+        <v>-38.64</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>8.82</v>
+        <v>29.21</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>19.74</v>
+        <v>43.04</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>19.74</v>
+        <v>43.04</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1433</v>
+        <v>1503</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>7.34</v>
+        <v>5.75</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>6.75</v>
+        <v>23.07</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>5.65</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9756</v>
+        <v>10642</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -2137,48 +2137,48 @@
         <v>5</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>127.3</v>
+        <v>17.91</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>168.72</v>
+        <v>102.77</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-41.41</v>
+        <v>-84.86</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>29.21</v>
+        <v>25.63</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>43.04</v>
+        <v>16.18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>43.04</v>
+        <v>16.18</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1503</v>
+        <v>1418</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>5.75</v>
+        <v>3.68</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>23.07</v>
+        <v>4.77</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>14.23</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10181</v>
+        <v>904</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -2197,43 +2197,43 @@
         <v>5</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.88</v>
+        <v>38.98</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>174.51</v>
+        <v>42.77</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-150.63</v>
+        <v>-3.79</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>23.43</v>
+        <v>27.91</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>20.17</v>
+        <v>2.37</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>20.17</v>
+        <v>2.37</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1435</v>
+        <v>1346</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>5.15</v>
+        <v>5.94</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>-2.69</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>5.55</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>10642</v>
+        <v>7256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2254,51 +2254,51 @@
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>-5.06</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>278.22</v>
+        <v>198.41</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-268.41</v>
+        <v>-203.48</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>25.63</v>
+        <v>25.23</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>16.18</v>
+        <v>20.18</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.18</v>
+        <v>20.18</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1418</v>
+        <v>1435</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>3.68</v>
+        <v>4.53</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>4.77</v>
+        <v>9.06</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>7.74</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>904</v>
+        <v>11399</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2314,51 +2314,51 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-21.38</v>
+        <v>-28.08</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>220.38</v>
+        <v>99.7</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-241.75</v>
+        <v>-127.78</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>27.91</v>
+        <v>23.74</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2.37</v>
+        <v>9.51</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2.37</v>
+        <v>9.51</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1346</v>
+        <v>1386</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>5.94</v>
+        <v>3.43</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>-2.69</v>
+        <v>6.64</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>-0.88</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>11399</v>
+        <v>3234</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -2377,48 +2377,48 @@
         <v>4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-110.55</v>
+        <v>2.01</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>167.52</v>
+        <v>91</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-278.06</v>
+        <v>-88.98</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>23.74</v>
+        <v>22.62</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>9.51</v>
+        <v>16.18</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>9.51</v>
+        <v>16.18</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1386</v>
+        <v>1418</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>3.43</v>
+        <v>4.22</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>6.64</v>
+        <v>8.34</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.57</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8423</v>
+        <v>7221</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -2428,57 +2428,57 @@
         <v>1</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>86.19</v>
+        <v>-45.17</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>63.35</v>
+        <v>180.24</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>22.85</v>
+        <v>-225.41</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>28.04</v>
+        <v>8.82</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>38.26</v>
+        <v>17.25</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>38.26</v>
+        <v>17.25</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1491</v>
+        <v>1423</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>10.03</v>
+        <v>6.44</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>18.23</v>
+        <v>5.05</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>10.01</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>3234</v>
+        <v>10181</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -2488,64 +2488,64 @@
         <v>1</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>-101.6</v>
+        <v>38.31</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>133.33</v>
+        <v>2.87</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-234.93</v>
+        <v>35.44</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>22.62</v>
+        <v>23.43</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>16.18</v>
+        <v>17.69</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.18</v>
+        <v>17.69</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>8.34</v>
+        <v>7.77</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>3.62</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7809</v>
+        <v>6081</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>3</v>
@@ -2554,58 +2554,58 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>100.1</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>198.7</v>
+        <v>199.62</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-98.59999999999999</v>
+        <v>-117.94</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>23.83</v>
+        <v>59.73</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>35.4</v>
+        <v>53.09</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>35.4</v>
+        <v>53.09</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1484</v>
+        <v>1526</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>4.43</v>
+        <v>14.53</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>15.92</v>
+        <v>19.69</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>15.06</v>
+        <v>18.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
         <v>34</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>3</v>
@@ -2614,51 +2614,51 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>48.12</v>
+        <v>6.39</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>114.88</v>
+        <v>-49.31</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-66.75</v>
+        <v>55.71</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>39.07</v>
+        <v>39.97</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>26.6</v>
+        <v>22.61</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>26.6</v>
+        <v>22.61</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1458</v>
+        <v>1444</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>4.89</v>
+        <v>3.57</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>13.6</v>
+        <v>10.91</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>8.1</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7658</v>
+        <v>7809</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2668,57 +2668,57 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-66.62</v>
+        <v>36.03</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>79.01000000000001</v>
+        <v>235.39</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-145.63</v>
+        <v>-199.37</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>14.34</v>
+        <v>23.83</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7.36</v>
+        <v>33.28</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>7.36</v>
+        <v>33.28</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1374</v>
+        <v>1478</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>3.52</v>
+        <v>5.14</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>5.53</v>
+        <v>14.29</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>-1.69</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>6081</v>
+        <v>7658</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2728,57 +2728,57 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>156.37</v>
+        <v>-24.86</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>138.49</v>
+        <v>56.37</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>17.88</v>
+        <v>-81.23</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>59.73</v>
+        <v>14.34</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>56.1</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>56.1</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1533</v>
+        <v>1379</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>14.16</v>
+        <v>3.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>22.61</v>
+        <v>5.99</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>19.34</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9566</v>
+        <v>7818</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
@@ -2797,48 +2797,48 @@
         <v>1</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16</v>
+        <v>-44.87</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>-141.87</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>157.87</v>
+        <v>-53.32</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>39.97</v>
+        <v>32.45</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>23.42</v>
+        <v>15.67</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>23.42</v>
+        <v>15.67</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1447</v>
+        <v>1416</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>3.67</v>
+        <v>6.67</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>11.71</v>
+        <v>4.72</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7818</v>
+        <v>8285</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -2848,43 +2848,43 @@
         <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>-67.25</v>
+        <v>-9.24</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>-109</v>
+        <v>105.39</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>41.75</v>
+        <v>-114.63</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>32.45</v>
+        <v>39.07</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>14.81</v>
+        <v>23.51</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>14.81</v>
+        <v>23.51</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1412</v>
+        <v>1447</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>6.79</v>
+        <v>4.14</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>4.26</v>
+        <v>11.48</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>3.76</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="40">
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         <v>0</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-4.69</v>
+        <v>29.29</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>-138.73</v>
+        <v>-15.64</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>134.04</v>
+        <v>44.93</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>27.39</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>30.41</v>
+        <v>27.92</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>30.41</v>
+        <v>27.92</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1470</v>
+        <v>1462</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>16.34</v>
+        <v>14.63</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="41">
@@ -3139,146 +3139,146 @@
         <v>68.08</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>121.55</v>
+        <v>119.97</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>121.55</v>
+        <v>119.97</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>19.89</v>
+        <v>20.14</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>68.91</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>32.74</v>
+        <v>29.07</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1660</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2075</v>
+        <v>3620</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>111.43</v>
+        <v>110.92</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>111.43</v>
+        <v>110.92</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>23.32</v>
+        <v>20.27</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.86</v>
+        <v>62.37</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>24.24</v>
+        <v>28.28</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4967</v>
+        <v>7220</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>68.89</v>
+        <v>45.04</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>111.23</v>
+        <v>109.6</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>111.23</v>
+        <v>109.6</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.68</v>
+        <v>23.65</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>61.58</v>
+        <v>67.36</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>25.98</v>
+        <v>18.59</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1645</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3620</v>
+        <v>2075</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>110.92</v>
+        <v>108.78</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>110.92</v>
+        <v>108.78</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20.27</v>
+        <v>22.66</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>62.37</v>
+        <v>62.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>28.28</v>
+        <v>23.47</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1644</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>7220</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>45.04</v>
+        <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>95.17</v>
+        <v>108.58</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>95.17</v>
+        <v>108.58</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>21.87</v>
+        <v>23.01</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>57.78</v>
+        <v>60.36</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>15.52</v>
+        <v>25.22</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1616</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="8">
@@ -3300,78 +3300,78 @@
         <v>94.81999999999999</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>15.17</v>
+        <v>15.9</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>56.1</v>
+        <v>55.34</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>23.54</v>
+        <v>23.58</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1615</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>3875</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.91</v>
+        <v>50.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>50.25</v>
+        <v>49.88</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>20.37</v>
+        <v>24.43</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1583</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3875</v>
+        <v>7656</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50.66</v>
+        <v>50.91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>69.14</v>
+        <v>77.22</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>69.14</v>
+        <v>77.22</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>7.49</v>
+        <v>10</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40.3</v>
+        <v>47.34</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>21.35</v>
+        <v>19.89</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1561</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="11">
@@ -3418,22 +3418,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>64.97</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>64.97</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.56</v>
+        <v>8.43</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>35.3</v>
+        <v>35.77</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>21.1</v>
+        <v>21.62</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="13">
@@ -3449,22 +3449,22 @@
         <v>44.43</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>60.88</v>
+        <v>57.86</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>60.88</v>
+        <v>57.86</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>15.54</v>
+        <v>15.92</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>34.86</v>
+        <v>31.95</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.48</v>
+        <v>10</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1543</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="14">
@@ -3480,81 +3480,81 @@
         <v>59.73</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>56.1</v>
+        <v>53.09</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>56.1</v>
+        <v>53.09</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14.16</v>
+        <v>14.53</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>22.61</v>
+        <v>19.69</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>19.34</v>
+        <v>18.86</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1533</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>29.21</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>43.04</v>
+        <v>52.69</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>43.04</v>
+        <v>52.69</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.75</v>
+        <v>11.8</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>23.07</v>
+        <v>27.81</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>14.23</v>
+        <v>13.08</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1503</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7808</v>
+        <v>9756</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>24.37</v>
+        <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>42.95</v>
+        <v>43.04</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>42.95</v>
+        <v>43.04</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6.01</v>
+        <v>5.75</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>25.74</v>
+        <v>23.07</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>11.21</v>
+        <v>14.23</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1503</v>
@@ -3562,64 +3562,64 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>8767</v>
+        <v>7808</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.21</v>
+        <v>24.37</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>39.07</v>
+        <v>42.95</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>39.07</v>
+        <v>42.95</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.03</v>
+        <v>6.01</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>23.99</v>
+        <v>25.74</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.05</v>
+        <v>11.21</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1493</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8423</v>
+        <v>8767</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>28.04</v>
+        <v>27.21</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>38.26</v>
+        <v>39.07</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>38.26</v>
+        <v>39.07</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>10.03</v>
+        <v>5.03</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>18.23</v>
+        <v>23.99</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.01</v>
+        <v>10.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1491</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="19">
@@ -3635,22 +3635,22 @@
         <v>23.83</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>35.4</v>
+        <v>33.28</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>35.4</v>
+        <v>33.28</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>4.43</v>
+        <v>5.14</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>15.92</v>
+        <v>14.29</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.06</v>
+        <v>13.84</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1484</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="20">
@@ -3666,22 +3666,22 @@
         <v>27.75</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>35.2</v>
+        <v>33.08</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35.2</v>
+        <v>33.08</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>15.04</v>
+        <v>15.75</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3.81</v>
+        <v>2.19</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>16.35</v>
+        <v>15.14</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1484</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="21">
@@ -3717,343 +3717,343 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9671</v>
+        <v>4325</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>27.39</v>
+        <v>32.52</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>30.41</v>
+        <v>29.98</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>30.41</v>
+        <v>29.98</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>16.34</v>
+        <v>16.1</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>4325</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>32.52</v>
+        <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>29.98</v>
+        <v>28.96</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>29.98</v>
+        <v>28.96</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>9.66</v>
+        <v>12.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16.1</v>
+        <v>5.43</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>4.22</v>
+        <v>11.43</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7289</v>
+        <v>9206</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>33.29</v>
+        <v>21.07</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>29.77</v>
+        <v>28.09</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>29.77</v>
+        <v>28.09</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>12.19</v>
+        <v>4.45</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>6.23</v>
+        <v>11.18</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>11.35</v>
+        <v>12.46</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1468</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9206</v>
+        <v>9671</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>21.07</v>
+        <v>27.39</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>28.9</v>
+        <v>27.92</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>28.9</v>
+        <v>27.92</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4.54</v>
+        <v>9.06</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.98</v>
+        <v>14.63</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.38</v>
+        <v>4.22</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1465</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9549</v>
+        <v>5980</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>17.6</v>
+        <v>38.55</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>28.83</v>
+        <v>27.47</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>28.83</v>
+        <v>27.47</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>7.01</v>
+        <v>7.6</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>16.43</v>
+        <v>13.5</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5.38</v>
+        <v>6.37</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1465</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>10664</v>
+        <v>9549</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>21.7</v>
+        <v>17.6</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>28.1</v>
+        <v>25.74</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>28.1</v>
+        <v>25.74</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>9.94</v>
+        <v>6.27</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>16.89</v>
+        <v>14.31</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.26</v>
+        <v>5.17</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1463</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5980</v>
+        <v>10664</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>38.55</v>
+        <v>21.7</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>27.47</v>
+        <v>25.45</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>27.47</v>
+        <v>25.45</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>7.6</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>13.5</v>
+        <v>15.67</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6.37</v>
+        <v>0.5</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1461</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>8285</v>
+        <v>9638</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>39.07</v>
+        <v>22.93</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>26.6</v>
+        <v>25.31</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>26.6</v>
+        <v>25.31</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.89</v>
+        <v>9.26</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>13.6</v>
+        <v>10.14</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8.1</v>
+        <v>5.91</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1458</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9638</v>
+        <v>8285</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>22.93</v>
+        <v>39.07</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>25.31</v>
+        <v>23.51</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>25.31</v>
+        <v>23.51</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>9.26</v>
+        <v>4.14</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.14</v>
+        <v>11.48</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5.91</v>
+        <v>7.89</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1454</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>5256</v>
+        <v>9566</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>35.18</v>
+        <v>39.97</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>24.83</v>
+        <v>22.61</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>24.83</v>
+        <v>22.61</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5.28</v>
+        <v>3.57</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>14.83</v>
+        <v>10.91</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>4.72</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1452</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9566</v>
+        <v>5256</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>39.97</v>
+        <v>35.18</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>23.42</v>
+        <v>21.75</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>23.42</v>
+        <v>21.75</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>3.67</v>
+        <v>4.53</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>11.71</v>
+        <v>12.71</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>4.51</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1447</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="33">
@@ -4069,22 +4069,22 @@
         <v>25.23</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>22.31</v>
+        <v>20.18</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>22.31</v>
+        <v>20.18</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3.81</v>
+        <v>4.53</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>10.68</v>
+        <v>9.06</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.81</v>
+        <v>6.59</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1444</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="34">
@@ -4100,22 +4100,22 @@
         <v>23.43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>20.17</v>
+        <v>17.69</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>20.17</v>
+        <v>17.69</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5.15</v>
+        <v>4.25</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>7.77</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5.55</v>
+        <v>5.66</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1435</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="35">
@@ -4131,22 +4131,22 @@
         <v>8.82</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>19.74</v>
+        <v>17.25</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.74</v>
+        <v>17.25</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>7.34</v>
+        <v>6.44</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6.75</v>
+        <v>5.05</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>5.65</v>
+        <v>5.76</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1433</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="36">
@@ -4224,22 +4224,22 @@
         <v>32.45</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>14.81</v>
+        <v>15.67</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>14.81</v>
+        <v>15.67</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6.79</v>
+        <v>6.67</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4.26</v>
+        <v>4.72</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3.76</v>
+        <v>4.28</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1412</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="39">
@@ -4286,22 +4286,22 @@
         <v>14.34</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7.36</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>7.36</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5.53</v>
+        <v>5.99</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-1.69</v>
+        <v>-1.17</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1374</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="41">
@@ -4385,743 +4385,743 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5166</v>
+        <v>3620</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>236.81</v>
+        <v>251.88</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>144.7</v>
+        <v>-81.13</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>92.11</v>
+        <v>333.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>234.72</v>
+        <v>177.49</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-219.84</v>
+        <v>-54.52</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>454.56</v>
+        <v>232.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>211.07</v>
+        <v>172.92</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-132.31</v>
+        <v>36.95</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>343.38</v>
+        <v>135.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3620</v>
+        <v>3875</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>189.69</v>
+        <v>161.25</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-124.15</v>
+        <v>-31.18</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>313.85</v>
+        <v>192.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7656</v>
+        <v>858</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>178.02</v>
+        <v>150.02</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-210.21</v>
+        <v>141.15</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>388.23</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6081</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>156.37</v>
+        <v>144.03</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>138.49</v>
+        <v>27.3</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>17.88</v>
+        <v>116.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2075</v>
+        <v>7220</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>146.63</v>
+        <v>137.49</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>22.63</v>
+        <v>87.27</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>124.01</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>8767</v>
+        <v>5166</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>128.95</v>
+        <v>126.23</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>75.31999999999999</v>
+        <v>57.28</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>53.63</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9756</v>
+        <v>2075</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>127.3</v>
+        <v>106.4</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>168.72</v>
+        <v>86.64</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-41.41</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>3875</v>
+        <v>8423</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>123.52</v>
+        <v>102.18</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-56.71</v>
+        <v>47.68</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>180.23</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7289</v>
+        <v>7656</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>116.48</v>
+        <v>101.55</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>115.79</v>
+        <v>-22.6</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>124.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7809</v>
+        <v>4325</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>100.1</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>198.7</v>
+        <v>108.94</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-98.59999999999999</v>
+        <v>-24.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7220</v>
+        <v>6081</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>87.70999999999999</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>281.99</v>
+        <v>199.62</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-194.28</v>
+        <v>-117.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>10633</v>
+        <v>8767</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>86.78</v>
+        <v>72.33</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>104.43</v>
+        <v>32.26</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-17.64</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8423</v>
+        <v>7289</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>86.19</v>
+        <v>59.22</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>63.35</v>
+        <v>100.09</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>22.85</v>
+        <v>-40.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>858</v>
+        <v>9638</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>86</v>
+        <v>58.43</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>15.61</v>
+        <v>125.38</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>70.38</v>
+        <v>-66.95999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>2771</v>
+        <v>5980</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>78.88</v>
+        <v>55.62</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.37</v>
+        <v>-36.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9638</v>
+        <v>2771</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>76.5</v>
+        <v>43.22</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>275.42</v>
+        <v>62.74</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-198.92</v>
+        <v>-19.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9549</v>
+        <v>9756</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>56.12</v>
+        <v>39.61</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>63.88</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-7.75</v>
+        <v>-38.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>9685</v>
+        <v>904</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>55.55</v>
+        <v>38.98</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-18.77</v>
+        <v>42.77</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>74.31999999999999</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8285</v>
+        <v>10181</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>48.12</v>
+        <v>38.31</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>114.88</v>
+        <v>2.87</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-66.75</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>4325</v>
+        <v>9549</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>44.56</v>
+        <v>36.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>180.85</v>
+        <v>-1.78</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-136.29</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9208</v>
+        <v>7809</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>41.51</v>
+        <v>36.03</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-178.03</v>
+        <v>235.39</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>219.54</v>
+        <v>-199.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>7256</v>
+        <v>9685</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>36.43</v>
+        <v>33.74</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>204.64</v>
+        <v>7.7</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-168.21</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>10181</v>
+        <v>9671</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>23.88</v>
+        <v>29.29</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>174.51</v>
+        <v>-15.64</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-150.63</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9566</v>
+        <v>10642</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>16</v>
+        <v>17.91</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-141.87</v>
+        <v>102.77</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>157.87</v>
+        <v>-84.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10642</v>
+        <v>9566</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>6.39</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>278.22</v>
+        <v>-49.31</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-268.41</v>
+        <v>55.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>5980</v>
+        <v>9206</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6.3</v>
+        <v>3.37</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>172.68</v>
+        <v>-10.33</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-166.38</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9671</v>
+        <v>3234</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>-4.69</v>
+        <v>2.01</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>-138.73</v>
+        <v>91</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>134.04</v>
+        <v>-88.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>904</v>
+        <v>7256</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-21.38</v>
+        <v>-5.06</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>220.38</v>
+        <v>198.41</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-241.75</v>
+        <v>-203.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7221</v>
+        <v>8285</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>-31.2</v>
+        <v>-9.24</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>194.52</v>
+        <v>105.39</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-225.72</v>
+        <v>-114.63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9206</v>
+        <v>9208</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-33.83</v>
+        <v>-14.38</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-28.01</v>
+        <v>-138.03</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-5.82</v>
+        <v>123.65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10664</v>
+        <v>5256</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-34.26</v>
+        <v>-19.26</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-207.22</v>
+        <v>47.8</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>172.96</v>
+        <v>-67.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7808</v>
+        <v>7658</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-40.65</v>
+        <v>-24.86</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>60.83</v>
+        <v>56.37</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-101.48</v>
+        <v>-81.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7658</v>
+        <v>11399</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-66.62</v>
+        <v>-28.08</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>79.01000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-145.63</v>
+        <v>-127.78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7818</v>
+        <v>10664</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-67.25</v>
+        <v>-42.73</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-109</v>
+        <v>-57.23</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>41.75</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5256</v>
+        <v>7808</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-79.5</v>
+        <v>-43.09</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>35.45</v>
+        <v>70.89</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-114.95</v>
+        <v>-113.98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>3234</v>
+        <v>7818</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-101.6</v>
+        <v>-44.87</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>133.33</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-234.93</v>
+        <v>-53.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>11399</v>
+        <v>7221</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-110.55</v>
+        <v>-45.17</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>167.52</v>
+        <v>180.24</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-278.06</v>
+        <v>-225.41</v>
       </c>
     </row>
     <row r="41">
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -5239,11 +5239,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1023</v>
+        <v>7220</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -5264,11 +5264,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3620</v>
+        <v>1023</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -5289,15 +5289,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -5356,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -5364,15 +5364,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>10633</v>
+        <v>3875</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -5381,7 +5381,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -5389,11 +5389,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9638</v>
+        <v>10633</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -5414,11 +5414,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9549</v>
+        <v>9638</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -5439,11 +5439,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>858</v>
+        <v>5980</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -5464,15 +5464,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>5980</v>
+        <v>9208</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -5489,15 +5489,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3875</v>
+        <v>10664</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -5514,24 +5514,24 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9685</v>
+        <v>7289</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -5539,15 +5539,15 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2771</v>
+        <v>9206</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -5564,11 +5564,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7289</v>
+        <v>2771</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -5589,24 +5589,24 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9206</v>
+        <v>2075</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -5614,24 +5614,24 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>9208</v>
+        <v>858</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -5639,11 +5639,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5256</v>
+        <v>8767</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -5664,24 +5664,24 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>8767</v>
+        <v>8423</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -5689,24 +5689,24 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10664</v>
+        <v>9549</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -5739,18 +5739,18 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2075</v>
+        <v>9685</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0</v>
@@ -5764,24 +5764,24 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -5814,11 +5814,11 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7221</v>
+        <v>9756</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -5839,11 +5839,11 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9756</v>
+        <v>10642</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -5864,11 +5864,11 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10181</v>
+        <v>904</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -5889,11 +5889,11 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>10642</v>
+        <v>7256</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -5906,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -5914,11 +5914,11 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>904</v>
+        <v>11399</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -5931,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -5939,11 +5939,11 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>11399</v>
+        <v>3234</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -5964,24 +5964,24 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>8423</v>
+        <v>7221</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -5989,24 +5989,24 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>3234</v>
+        <v>10181</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -6014,15 +6014,15 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7809</v>
+        <v>6081</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>3</v>
@@ -6031,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -6039,15 +6039,15 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>3</v>
@@ -6056,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -6064,24 +6064,24 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7658</v>
+        <v>7809</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -6089,24 +6089,24 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>6081</v>
+        <v>7658</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -6114,18 +6114,18 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>9566</v>
+        <v>7818</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
@@ -6139,24 +6139,24 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>7818</v>
+        <v>8285</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -6175,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0</v>
@@ -6284,21 +6284,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5166</v>
+        <v>3620</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>236.81</v>
+        <v>251.88</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>144.7</v>
+        <v>-81.13</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>92.11</v>
+        <v>333.01</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6307,21 +6307,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>234.72</v>
+        <v>177.49</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-219.84</v>
+        <v>-54.52</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>454.56</v>
+        <v>232.01</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6330,21 +6330,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>211.07</v>
+        <v>172.92</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-132.31</v>
+        <v>36.95</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>343.38</v>
+        <v>135.97</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6353,21 +6353,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3620</v>
+        <v>3875</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>189.69</v>
+        <v>161.25</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-124.15</v>
+        <v>-31.18</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>313.85</v>
+        <v>192.43</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6376,21 +6376,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7656</v>
+        <v>858</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>178.02</v>
+        <v>150.02</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-210.21</v>
+        <v>141.15</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>388.23</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6399,21 +6399,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>6081</v>
+        <v>4967</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>156.37</v>
+        <v>144.03</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>138.49</v>
+        <v>27.3</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>17.88</v>
+        <v>116.73</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6422,21 +6422,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2075</v>
+        <v>7220</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>146.63</v>
+        <v>137.49</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>22.63</v>
+        <v>87.27</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>124.01</v>
+        <v>50.23</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6445,21 +6445,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8767</v>
+        <v>5166</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>128.95</v>
+        <v>126.23</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>75.31999999999999</v>
+        <v>57.28</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>53.63</v>
+        <v>68.95</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6468,21 +6468,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9756</v>
+        <v>2075</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>127.3</v>
+        <v>106.4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>168.72</v>
+        <v>86.64</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-41.41</v>
+        <v>19.76</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6491,21 +6491,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3875</v>
+        <v>8423</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>123.52</v>
+        <v>102.18</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-56.71</v>
+        <v>47.68</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>180.23</v>
+        <v>54.5</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6514,21 +6514,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7289</v>
+        <v>7656</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>116.48</v>
+        <v>101.55</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>115.79</v>
+        <v>-22.6</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>124.15</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6537,21 +6537,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>7809</v>
+        <v>4325</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>100.1</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>198.7</v>
+        <v>108.94</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-98.59999999999999</v>
+        <v>-24.87</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6560,21 +6560,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7220</v>
+        <v>6081</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>87.70999999999999</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>281.99</v>
+        <v>199.62</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-194.28</v>
+        <v>-117.94</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6583,21 +6583,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10633</v>
+        <v>8767</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>86.78</v>
+        <v>72.33</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>104.43</v>
+        <v>32.26</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-17.64</v>
+        <v>40.07</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6606,21 +6606,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>8423</v>
+        <v>7289</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>86.19</v>
+        <v>59.22</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>63.35</v>
+        <v>100.09</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>22.85</v>
+        <v>-40.87</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6629,21 +6629,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>858</v>
+        <v>9638</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>86</v>
+        <v>58.43</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>15.61</v>
+        <v>125.38</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>70.38</v>
+        <v>-66.95999999999999</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6652,21 +6652,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2771</v>
+        <v>5980</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>78.88</v>
+        <v>55.62</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.37</v>
+        <v>-36.89</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6675,21 +6675,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9638</v>
+        <v>2771</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>76.5</v>
+        <v>43.22</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>275.42</v>
+        <v>62.74</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-198.92</v>
+        <v>-19.51</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6698,21 +6698,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>9549</v>
+        <v>9756</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>56.12</v>
+        <v>39.61</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>63.88</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-7.75</v>
+        <v>-38.64</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6721,21 +6721,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>9685</v>
+        <v>904</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>55.55</v>
+        <v>38.98</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-18.77</v>
+        <v>42.77</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>74.31999999999999</v>
+        <v>-3.79</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6744,21 +6744,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>8285</v>
+        <v>10181</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>48.12</v>
+        <v>38.31</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>114.88</v>
+        <v>2.87</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-66.75</v>
+        <v>35.44</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6767,21 +6767,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>4325</v>
+        <v>9549</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>44.56</v>
+        <v>36.29</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>180.85</v>
+        <v>-1.78</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-136.29</v>
+        <v>38.07</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6790,21 +6790,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>9208</v>
+        <v>7809</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>41.51</v>
+        <v>36.03</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-178.03</v>
+        <v>235.39</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>219.54</v>
+        <v>-199.37</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6813,21 +6813,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>7256</v>
+        <v>9685</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>36.43</v>
+        <v>33.74</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>204.64</v>
+        <v>7.7</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-168.21</v>
+        <v>26.04</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6836,21 +6836,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>10181</v>
+        <v>9671</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>23.88</v>
+        <v>29.29</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>174.51</v>
+        <v>-15.64</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-150.63</v>
+        <v>44.93</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6859,21 +6859,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9566</v>
+        <v>10642</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>16</v>
+        <v>17.91</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-141.87</v>
+        <v>102.77</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>157.87</v>
+        <v>-84.86</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6882,21 +6882,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10642</v>
+        <v>9566</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>6.39</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>278.22</v>
+        <v>-49.31</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-268.41</v>
+        <v>55.71</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6905,21 +6905,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5980</v>
+        <v>9206</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6.3</v>
+        <v>3.37</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>172.68</v>
+        <v>-10.33</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-166.38</v>
+        <v>13.7</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6928,21 +6928,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9671</v>
+        <v>3234</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>-4.69</v>
+        <v>2.01</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-138.73</v>
+        <v>91</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>134.04</v>
+        <v>-88.98</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6951,21 +6951,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>904</v>
+        <v>7256</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-21.38</v>
+        <v>-5.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>220.38</v>
+        <v>198.41</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-241.75</v>
+        <v>-203.48</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6974,21 +6974,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7221</v>
+        <v>8285</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>-31.2</v>
+        <v>-9.24</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>194.52</v>
+        <v>105.39</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-225.72</v>
+        <v>-114.63</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6997,21 +6997,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>9206</v>
+        <v>9208</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-33.83</v>
+        <v>-14.38</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-28.01</v>
+        <v>-138.03</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-5.82</v>
+        <v>123.65</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7020,21 +7020,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>10664</v>
+        <v>5256</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-34.26</v>
+        <v>-19.26</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-207.22</v>
+        <v>47.8</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>172.96</v>
+        <v>-67.06</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -7043,21 +7043,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7808</v>
+        <v>7658</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-40.65</v>
+        <v>-24.86</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>60.83</v>
+        <v>56.37</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-101.48</v>
+        <v>-81.23</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -7066,21 +7066,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7658</v>
+        <v>11399</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-66.62</v>
+        <v>-28.08</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>79.01000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-145.63</v>
+        <v>-127.78</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7089,21 +7089,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7818</v>
+        <v>10664</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-67.25</v>
+        <v>-42.73</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-109</v>
+        <v>-57.23</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>41.75</v>
+        <v>14.5</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -7112,21 +7112,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5256</v>
+        <v>7808</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-79.5</v>
+        <v>-43.09</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>35.45</v>
+        <v>70.89</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-114.95</v>
+        <v>-113.98</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -7135,21 +7135,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>3234</v>
+        <v>7818</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-101.6</v>
+        <v>-44.87</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>133.33</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-234.93</v>
+        <v>-53.32</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -7158,21 +7158,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>11399</v>
+        <v>7221</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-110.55</v>
+        <v>-45.17</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>167.52</v>
+        <v>180.24</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-278.06</v>
+        <v>-225.41</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -609,16 +609,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Belmont, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -637,55 +637,55 @@
         <v>18</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>144.03</v>
+        <v>139.06</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>27.3</v>
+        <v>-65.16</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>116.73</v>
+        <v>204.21</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>68.89</v>
+        <v>68.08</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>108.58</v>
+        <v>124.01</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>108.58</v>
+        <v>124.01</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1640</v>
+        <v>1661</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23.01</v>
+        <v>21.09</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>60.36</v>
+        <v>74.2</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>25.22</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Brighton, Michigan</t>
+          <t>Saint Joseph, Michigan</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -694,58 +694,58 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>137.49</v>
+        <v>228.09</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>87.27</v>
+        <v>-58.67</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>50.23</v>
+        <v>286.76</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>45.04</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>109.6</v>
+        <v>117.04</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>109.6</v>
+        <v>117.04</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1642</v>
+        <v>1651</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>23.65</v>
+        <v>20.89</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>67.36</v>
+        <v>67.88</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>18.59</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1023</v>
+        <v>7656</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Michigan Center, Michigan</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -754,171 +754,171 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>177.49</v>
+        <v>101.95</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-54.52</v>
+        <v>31.81</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>232.01</v>
+        <v>70.14</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>68.08</v>
+        <v>50.91</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>119.97</v>
+        <v>77.22</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>119.97</v>
+        <v>77.22</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1656</v>
+        <v>1577</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>20.14</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>70.76000000000001</v>
+        <v>47.34</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>29.07</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph, Michigan</t>
+          <t>Brighton, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>251.88</v>
+        <v>150.17</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-81.13</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>333.01</v>
+        <v>59.43</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>110.92</v>
+        <v>113.64</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>110.92</v>
+        <v>113.64</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>20.27</v>
+        <v>24.6</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>62.37</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>28.28</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7808</v>
+        <v>4967</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Belmont, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-43.09</v>
+        <v>156.68</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>70.89</v>
+        <v>-16.06</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-113.98</v>
+        <v>172.73</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>24.37</v>
+        <v>68.89</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42.95</v>
+        <v>109.99</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>42.95</v>
+        <v>109.99</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1503</v>
+        <v>1641</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>6.01</v>
+        <v>22.97</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>25.74</v>
+        <v>60.13</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>11.21</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>7656</v>
+        <v>3875</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -928,57 +928,57 @@
         <v>4</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>101.55</v>
+        <v>160.16</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-22.6</v>
+        <v>12.26</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>124.15</v>
+        <v>147.91</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>50.91</v>
+        <v>50.66</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>77.22</v>
+        <v>88.5</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>77.22</v>
+        <v>88.5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1577</v>
+        <v>1599</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10</v>
+        <v>10.37</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>47.34</v>
+        <v>52.93</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>19.89</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3875</v>
+        <v>7808</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -994,58 +994,58 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>161.25</v>
+        <v>-11.72</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-31.18</v>
+        <v>-14.83</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>192.43</v>
+        <v>3.11</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>50.66</v>
+        <v>24.37</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>83.56999999999999</v>
+        <v>38.49</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>83.56999999999999</v>
+        <v>38.49</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1590</v>
+        <v>1491</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>9.26</v>
+        <v>4.34</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>49.88</v>
+        <v>21.67</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>24.43</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>10633</v>
+        <v>9208</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Edwardsburg, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>1</v>
@@ -1054,58 +1054,58 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>172.92</v>
+        <v>38.56</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>36.95</v>
+        <v>-137.78</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>135.97</v>
+        <v>176.34</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>45.8</v>
+        <v>44.43</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>121.75</v>
+        <v>59.93</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>121.75</v>
+        <v>59.93</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1659</v>
+        <v>1540</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>21.49</v>
+        <v>16.49</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>72.2</v>
+        <v>33.18</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>28.06</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9638</v>
+        <v>2771</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -1114,58 +1114,58 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>58.43</v>
+        <v>102.47</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>125.38</v>
+        <v>29.37</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-66.95999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>22.93</v>
+        <v>53.52</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>25.31</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>25.31</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1454</v>
+        <v>1564</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>9.26</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>10.14</v>
+        <v>44.46</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>5.91</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>5980</v>
+        <v>7289</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1</v>
@@ -1174,51 +1174,51 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>55.62</v>
+        <v>65.59</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>92.51000000000001</v>
+        <v>88.45</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-36.89</v>
+        <v>-22.85</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>38.55</v>
+        <v>33.29</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>27.47</v>
+        <v>31.02</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>27.47</v>
+        <v>31.02</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1461</v>
+        <v>1471</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>7.6</v>
+        <v>12.67</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>6.37</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>9208</v>
+        <v>2075</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Edwardsburg, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1228,67 +1228,67 @@
         <v>3</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-14.38</v>
+        <v>120.6</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-138.03</v>
+        <v>127.12</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>123.65</v>
+        <v>-6.52</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>44.43</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>57.86</v>
+        <v>113.7</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>57.86</v>
+        <v>113.7</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1536</v>
+        <v>1646</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>15.92</v>
+        <v>23.76</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>31.95</v>
+        <v>65.69</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>10</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>10664</v>
+        <v>10633</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -1297,48 +1297,48 @@
         <v>11</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-42.73</v>
+        <v>197.03</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-57.23</v>
+        <v>35.55</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>14.5</v>
+        <v>161.48</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>21.7</v>
+        <v>45.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>25.45</v>
+        <v>117.29</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>25.45</v>
+        <v>117.29</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1454</v>
+        <v>1652</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>9.279999999999999</v>
+        <v>19.82</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>15.67</v>
+        <v>68.13</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.5</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7289</v>
+        <v>10664</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1357,48 +1357,48 @@
         <v>11</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>59.22</v>
+        <v>-69.44</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>100.09</v>
+        <v>-67.64</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-40.87</v>
+        <v>-1.8</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>33.29</v>
+        <v>21.7</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>28.96</v>
+        <v>25.45</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>28.96</v>
+        <v>25.45</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1465</v>
+        <v>1454</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>12.1</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>5.43</v>
+        <v>15.67</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>11.43</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9206</v>
+        <v>9638</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1408,57 +1408,57 @@
         <v>3</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>3.37</v>
+        <v>11.36</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-10.33</v>
+        <v>138.51</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>13.7</v>
+        <v>-127.16</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>21.07</v>
+        <v>22.93</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>28.09</v>
+        <v>21.93</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>28.09</v>
+        <v>21.93</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1463</v>
+        <v>1441</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>4.45</v>
+        <v>8.25</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>11.18</v>
+        <v>8.24</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>12.46</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1468,52 +1468,52 @@
         <v>2</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>43.22</v>
+        <v>117.92</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>62.74</v>
+        <v>73.97</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-19.51</v>
+        <v>43.95</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>53.52</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>68.95999999999999</v>
+        <v>98.86</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>68.95999999999999</v>
+        <v>98.86</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1560</v>
+        <v>1621</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>16.85</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>42.02</v>
+        <v>58.78</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>17.81</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>2075</v>
+        <v>5980</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1537,34 +1537,34 @@
         <v>10</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>106.4</v>
+        <v>62.71</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>86.64</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>19.76</v>
+        <v>-26</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>38.55</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>108.78</v>
+        <v>31.27</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>108.78</v>
+        <v>31.27</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1640</v>
+        <v>1472</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>22.66</v>
+        <v>7.42</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>62.64</v>
+        <v>16.68</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>23.47</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="18">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>150.02</v>
+        <v>120.58</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>141.15</v>
+        <v>131.94</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>8.869999999999999</v>
+        <v>-11.37</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>55.1</v>
@@ -1629,23 +1629,23 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>9685</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>1</v>
@@ -1654,37 +1654,37 @@
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>72.33</v>
+        <v>47.13</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>32.26</v>
+        <v>11.45</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>40.07</v>
+        <v>35.68</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>27.21</v>
+        <v>27.75</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>39.07</v>
+        <v>39.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>39.07</v>
+        <v>39.2</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>1493</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>5.03</v>
+        <v>16.37</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>23.99</v>
+        <v>7.7</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>10.05</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="20">
@@ -1717,13 +1717,13 @@
         <v>9</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>102.18</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>47.68</v>
+        <v>39.58</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>54.5</v>
+        <v>28.73</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>28.04</v>
@@ -1749,16 +1749,16 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>9549</v>
+        <v>10642</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1777,55 +1777,55 @@
         <v>9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>36.29</v>
+        <v>-0.93</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-1.78</v>
+        <v>91.3</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>38.07</v>
+        <v>-92.23</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>17.6</v>
+        <v>25.63</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>25.74</v>
+        <v>22.31</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.74</v>
+        <v>22.31</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1455</v>
+        <v>1443</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>6.27</v>
+        <v>4.3</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>14.31</v>
+        <v>10.28</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>5.17</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4325</v>
+        <v>9549</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>2</v>
@@ -1834,51 +1834,51 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>84.06999999999999</v>
+        <v>5.65</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>108.94</v>
+        <v>41.35</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-24.87</v>
+        <v>-35.7</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>32.52</v>
+        <v>17.6</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>29.98</v>
+        <v>25.74</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>29.98</v>
+        <v>25.74</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1469</v>
+        <v>1455</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>9.66</v>
+        <v>6.27</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>16.1</v>
+        <v>14.31</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>4.22</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1888,43 +1888,43 @@
         <v>2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>33.74</v>
+        <v>59</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>7.7</v>
+        <v>41.65</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>26.04</v>
+        <v>17.34</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>27.75</v>
+        <v>29.21</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>33.08</v>
+        <v>45.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>33.08</v>
+        <v>45.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1477</v>
+        <v>1508</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>15.75</v>
+        <v>5.74</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>2.19</v>
+        <v>25.51</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>15.14</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="24">
@@ -1945,7 +1945,7 @@
         <v>23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>2</v>
@@ -1954,58 +1954,58 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-19.26</v>
+        <v>1.75</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>47.8</v>
+        <v>24.54</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-67.06</v>
+        <v>-22.79</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>35.18</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>21.75</v>
+        <v>26.68</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>21.75</v>
+        <v>26.68</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1441</v>
+        <v>1458</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>4.53</v>
+        <v>5.63</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>12.71</v>
+        <v>15.76</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>4.51</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>5166</v>
+        <v>9206</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>24</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>2</v>
@@ -2014,58 +2014,58 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>126.23</v>
+        <v>0.55</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>57.28</v>
+        <v>-24.11</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>68.95</v>
+        <v>24.66</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>21.07</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>94.81999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>94.81999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1613</v>
+        <v>1460</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>15.9</v>
+        <v>3.92</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>55.34</v>
+        <v>11.87</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>23.58</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9756</v>
+        <v>3234</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>2</v>
@@ -2074,111 +2074,111 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>39.61</v>
+        <v>-21.83</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>102.66</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-38.64</v>
+        <v>-124.49</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>29.21</v>
+        <v>22.62</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>43.04</v>
+        <v>18.44</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>43.04</v>
+        <v>18.44</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1503</v>
+        <v>1428</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>5.75</v>
+        <v>4.22</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>23.07</v>
+        <v>10.77</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>14.23</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>10642</v>
+        <v>7221</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>17.91</v>
+        <v>-11.81</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>102.77</v>
+        <v>123.48</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-84.86</v>
+        <v>-135.29</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>25.63</v>
+        <v>8.82</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>16.18</v>
+        <v>19.32</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>16.18</v>
+        <v>19.32</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1418</v>
+        <v>1431</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>3.68</v>
+        <v>7.01</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.77</v>
+        <v>6.29</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>7.74</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>904</v>
+        <v>4325</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -2188,64 +2188,64 @@
         <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>38.98</v>
+        <v>59.51</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>42.77</v>
+        <v>137.65</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-3.79</v>
+        <v>-78.14</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>27.91</v>
+        <v>32.52</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2.37</v>
+        <v>33.78</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>2.37</v>
+        <v>33.78</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1346</v>
+        <v>1479</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>5.94</v>
+        <v>9.48</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>-2.69</v>
+        <v>19.29</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>-0.88</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7256</v>
+        <v>8767</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>2</v>
@@ -2254,51 +2254,51 @@
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.06</v>
+        <v>37.08</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>198.41</v>
+        <v>66.92</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-203.48</v>
+        <v>-29.83</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>25.23</v>
+        <v>27.21</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>20.18</v>
+        <v>35.69</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>20.18</v>
+        <v>35.69</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1435</v>
+        <v>1484</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>4.53</v>
+        <v>4.02</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>9.06</v>
+        <v>22.09</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>6.59</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>11399</v>
+        <v>7256</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2308,57 +2308,57 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-28.08</v>
+        <v>-24.04</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>99.7</v>
+        <v>193.97</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-127.78</v>
+        <v>-218.01</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>23.74</v>
+        <v>25.23</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9.51</v>
+        <v>15.72</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>9.51</v>
+        <v>15.72</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1386</v>
+        <v>1416</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>3.43</v>
+        <v>2.86</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>6.64</v>
+        <v>4.99</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>-0.57</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>3234</v>
+        <v>10181</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -2368,57 +2368,57 @@
         <v>1</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.01</v>
+        <v>42.87</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>91</v>
+        <v>44.94</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-88.98</v>
+        <v>-2.07</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>22.62</v>
+        <v>23.43</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>16.18</v>
+        <v>17.69</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>16.18</v>
+        <v>17.69</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>8.34</v>
+        <v>7.77</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>3.62</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7221</v>
+        <v>11399</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -2437,48 +2437,48 @@
         <v>5</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-45.17</v>
+        <v>3.65</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>180.24</v>
+        <v>133.36</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-225.41</v>
+        <v>-129.71</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>8.82</v>
+        <v>23.74</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>17.25</v>
+        <v>13.31</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>17.25</v>
+        <v>13.31</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1423</v>
+        <v>1405</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>6.44</v>
+        <v>3.25</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>5.05</v>
+        <v>9.83</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>5.76</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10181</v>
+        <v>904</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -2497,34 +2497,34 @@
         <v>5</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>38.31</v>
+        <v>6.97</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2.87</v>
+        <v>49.16</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>35.44</v>
+        <v>-42.19</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>23.43</v>
+        <v>27.91</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>17.69</v>
+        <v>-1.01</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>17.69</v>
+        <v>-1.01</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1424</v>
+        <v>1328</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.25</v>
+        <v>4.92</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>7.77</v>
+        <v>-4.59</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>5.66</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="34">
@@ -2548,43 +2548,43 @@
         <v>1</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>81.68000000000001</v>
+        <v>54.52</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>199.62</v>
+        <v>153.69</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-117.94</v>
+        <v>-99.17</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>59.73</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>53.09</v>
+        <v>54.49</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>53.09</v>
+        <v>54.49</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>14.53</v>
+        <v>14.49</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>19.69</v>
+        <v>19.47</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>18.86</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="35">
@@ -2617,13 +2617,13 @@
         <v>4</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>6.39</v>
+        <v>26.94</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-49.31</v>
+        <v>-14.33</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>55.71</v>
+        <v>41.26</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>39.97</v>
@@ -2668,57 +2668,57 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>36.03</v>
+        <v>20.82</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>235.39</v>
+        <v>196.06</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-199.37</v>
+        <v>-175.24</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>23.83</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>33.28</v>
+        <v>34.68</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>33.28</v>
+        <v>34.68</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>14.29</v>
+        <v>14.07</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>13.84</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7658</v>
+        <v>7818</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
@@ -2737,48 +2737,48 @@
         <v>2</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>-24.86</v>
+        <v>-27.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>56.37</v>
+        <v>-11.53</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-81.23</v>
+        <v>-16.07</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>14.34</v>
+        <v>32.45</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>15.67</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>15.67</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1379</v>
+        <v>1416</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>3.4</v>
+        <v>6.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>5.99</v>
+        <v>4.72</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>-1.17</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7818</v>
+        <v>7658</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2788,57 +2788,57 @@
         <v>0</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-44.87</v>
+        <v>4.05</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>71.63</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-53.32</v>
+        <v>-67.58</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>32.45</v>
+        <v>14.34</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>15.67</v>
+        <v>7.43</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>15.67</v>
+        <v>7.43</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1416</v>
+        <v>1376</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>6.67</v>
+        <v>2.86</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>4.72</v>
+        <v>6.68</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>4.28</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>8285</v>
+        <v>9671</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -2857,48 +2857,48 @@
         <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>-9.24</v>
+        <v>-4.37</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>105.39</v>
+        <v>3.31</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-114.63</v>
+        <v>-7.68</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>39.07</v>
+        <v>27.39</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>23.51</v>
+        <v>27.92</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>23.51</v>
+        <v>27.92</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1447</v>
+        <v>1462</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>4.14</v>
+        <v>9.06</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>11.48</v>
+        <v>14.63</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>7.89</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2908,43 +2908,43 @@
         <v>0</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>29.29</v>
+        <v>23.33</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>-15.64</v>
+        <v>81.73</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>44.93</v>
+        <v>-58.4</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>27.39</v>
+        <v>39.07</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>27.92</v>
+        <v>22.72</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>27.92</v>
+        <v>22.72</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1462</v>
+        <v>1444</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>9.06</v>
+        <v>3.61</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>14.63</v>
+        <v>12.17</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>4.22</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="41">
@@ -3097,64 +3097,64 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>10633</v>
+        <v>1023</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45.8</v>
+        <v>68.08</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>121.75</v>
+        <v>124.01</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>121.75</v>
+        <v>124.01</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>21.49</v>
+        <v>21.09</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>72.2</v>
+        <v>74.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>28.06</v>
+        <v>28.72</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1659</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>68.08</v>
+        <v>45.8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>119.97</v>
+        <v>117.29</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>119.97</v>
+        <v>117.29</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>20.14</v>
+        <v>19.82</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>70.76000000000001</v>
+        <v>68.13</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>29.07</v>
+        <v>29.34</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1656</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="4">
@@ -3170,84 +3170,84 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>110.92</v>
+        <v>117.04</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>110.92</v>
+        <v>117.04</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>20.27</v>
+        <v>20.89</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>62.37</v>
+        <v>67.88</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>28.28</v>
+        <v>28.27</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1644</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>7220</v>
+        <v>2075</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>45.04</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>109.6</v>
+        <v>113.7</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>109.6</v>
+        <v>113.7</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.65</v>
+        <v>23.76</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>67.36</v>
+        <v>65.69</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>18.59</v>
+        <v>24.25</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1642</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2075</v>
+        <v>7220</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>108.78</v>
+        <v>113.64</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>108.78</v>
+        <v>113.64</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>22.66</v>
+        <v>24.6</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>62.64</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>23.47</v>
+        <v>18.24</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1640</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="7">
@@ -3263,22 +3263,22 @@
         <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>108.58</v>
+        <v>109.99</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>108.58</v>
+        <v>109.99</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>23.01</v>
+        <v>22.97</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>60.36</v>
+        <v>60.13</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>25.22</v>
+        <v>26.89</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="8">
@@ -3294,22 +3294,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>98.86</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>98.86</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>15.9</v>
+        <v>16.85</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>55.34</v>
+        <v>58.78</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>23.58</v>
+        <v>23.23</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1613</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="9">
@@ -3325,22 +3325,22 @@
         <v>50.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>83.56999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>83.56999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>9.26</v>
+        <v>10.37</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>49.88</v>
+        <v>52.93</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>24.43</v>
+        <v>25.2</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1590</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="10">
@@ -3387,22 +3387,22 @@
         <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>68.95999999999999</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>68.95999999999999</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9.130000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>42.02</v>
+        <v>44.46</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>17.81</v>
+        <v>17.63</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1560</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="12">
@@ -3449,22 +3449,22 @@
         <v>44.43</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>57.86</v>
+        <v>59.93</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>57.86</v>
+        <v>59.93</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>15.92</v>
+        <v>16.49</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>31.95</v>
+        <v>33.18</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1536</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="14">
@@ -3480,22 +3480,22 @@
         <v>59.73</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>53.09</v>
+        <v>54.49</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>53.09</v>
+        <v>54.49</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14.53</v>
+        <v>14.49</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>19.69</v>
+        <v>19.47</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>18.86</v>
+        <v>20.53</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1526</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="15">
@@ -3542,270 +3542,270 @@
         <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>43.04</v>
+        <v>45.3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>43.04</v>
+        <v>45.3</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>5.75</v>
+        <v>5.74</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23.07</v>
+        <v>25.51</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.23</v>
+        <v>14.05</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1503</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>7808</v>
+        <v>9685</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>24.37</v>
+        <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>42.95</v>
+        <v>39.2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>42.95</v>
+        <v>39.2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>6.01</v>
+        <v>16.37</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>25.74</v>
+        <v>7.7</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>11.21</v>
+        <v>15.13</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1503</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8767</v>
+        <v>7808</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>27.21</v>
+        <v>24.37</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>39.07</v>
+        <v>38.49</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>39.07</v>
+        <v>38.49</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5.03</v>
+        <v>4.34</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23.99</v>
+        <v>21.67</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.05</v>
+        <v>12.48</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1493</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>7809</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>23.83</v>
+        <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>33.28</v>
+        <v>35.69</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>33.28</v>
+        <v>35.69</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.14</v>
+        <v>4.02</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14.29</v>
+        <v>22.09</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>13.84</v>
+        <v>9.58</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9685</v>
+        <v>7809</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>27.75</v>
+        <v>23.83</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>33.08</v>
+        <v>34.68</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>33.08</v>
+        <v>34.68</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>15.75</v>
+        <v>5.1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2.19</v>
+        <v>14.07</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>15.14</v>
+        <v>15.51</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1477</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>5501</v>
+        <v>4325</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>31.87</v>
+        <v>32.52</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>31.87</v>
+        <v>33.78</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>31.87</v>
+        <v>33.78</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.95</v>
+        <v>9.48</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>17.02</v>
+        <v>19.29</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>7.9</v>
+        <v>5.02</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1476</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4325</v>
+        <v>5501</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>32.52</v>
+        <v>31.87</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>29.98</v>
+        <v>31.87</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>29.98</v>
+        <v>31.87</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>9.66</v>
+        <v>6.95</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>16.1</v>
+        <v>17.02</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>4.22</v>
+        <v>7.9</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1469</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7289</v>
+        <v>5980</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>33.29</v>
+        <v>38.55</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.96</v>
+        <v>31.27</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>28.96</v>
+        <v>31.27</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.1</v>
+        <v>7.42</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.43</v>
+        <v>16.68</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>11.43</v>
+        <v>7.17</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1465</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9206</v>
+        <v>7289</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>21.07</v>
+        <v>33.29</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.09</v>
+        <v>31.02</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.09</v>
+        <v>31.02</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>4.45</v>
+        <v>12.67</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11.18</v>
+        <v>6.67</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>12.46</v>
+        <v>11.68</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1463</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="25">
@@ -3841,123 +3841,123 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5980</v>
+        <v>9206</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>38.55</v>
+        <v>21.07</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>27.47</v>
+        <v>27.3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>27.47</v>
+        <v>27.3</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>7.6</v>
+        <v>3.92</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>13.5</v>
+        <v>11.87</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>6.37</v>
+        <v>11.51</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9549</v>
+        <v>5256</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>17.6</v>
+        <v>35.18</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>25.74</v>
+        <v>26.68</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>25.74</v>
+        <v>26.68</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6.27</v>
+        <v>5.63</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14.31</v>
+        <v>15.76</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.17</v>
+        <v>5.28</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1455</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10664</v>
+        <v>9549</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>21.7</v>
+        <v>17.6</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>25.45</v>
+        <v>25.74</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>25.45</v>
+        <v>25.74</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>9.279999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.67</v>
+        <v>14.31</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.5</v>
+        <v>5.17</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9638</v>
+        <v>10664</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>22.93</v>
+        <v>21.7</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>25.31</v>
+        <v>25.45</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>25.31</v>
+        <v>25.45</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.26</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10.14</v>
+        <v>15.67</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.91</v>
+        <v>0.5</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1454</v>
@@ -3976,22 +3976,22 @@
         <v>39.07</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>23.51</v>
+        <v>22.72</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>23.51</v>
+        <v>22.72</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>4.14</v>
+        <v>3.61</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.48</v>
+        <v>12.17</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>7.89</v>
+        <v>6.94</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="31">
@@ -4027,188 +4027,188 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5256</v>
+        <v>10642</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>35.18</v>
+        <v>25.63</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>21.75</v>
+        <v>22.31</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21.75</v>
+        <v>22.31</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>4.53</v>
+        <v>4.3</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>12.71</v>
+        <v>10.28</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>4.51</v>
+        <v>7.73</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1441</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7256</v>
+        <v>9638</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>25.23</v>
+        <v>22.93</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>20.18</v>
+        <v>21.93</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>20.18</v>
+        <v>21.93</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.53</v>
+        <v>8.25</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>9.06</v>
+        <v>8.24</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>6.59</v>
+        <v>5.43</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1435</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10181</v>
+        <v>7221</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>23.43</v>
+        <v>8.82</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>17.69</v>
+        <v>19.32</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>17.69</v>
+        <v>19.32</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4.25</v>
+        <v>7.01</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.77</v>
+        <v>6.29</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5.66</v>
+        <v>6.02</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1424</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>8.82</v>
+        <v>22.62</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>17.25</v>
+        <v>18.44</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.25</v>
+        <v>18.44</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>6.44</v>
+        <v>4.22</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>5.05</v>
+        <v>10.77</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>5.76</v>
+        <v>3.45</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1423</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3234</v>
+        <v>10181</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>22.62</v>
+        <v>23.43</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16.18</v>
+        <v>17.69</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>16.18</v>
+        <v>17.69</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.34</v>
+        <v>7.77</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3.62</v>
+        <v>5.66</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1418</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10642</v>
+        <v>7256</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>25.63</v>
+        <v>25.23</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>16.18</v>
+        <v>15.72</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>16.18</v>
+        <v>15.72</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3.68</v>
+        <v>2.86</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>4.77</v>
+        <v>4.99</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>7.74</v>
+        <v>7.87</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="38">
@@ -4255,22 +4255,22 @@
         <v>23.74</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>9.51</v>
+        <v>13.31</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>9.51</v>
+        <v>13.31</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>6.64</v>
+        <v>9.83</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>-0.57</v>
+        <v>0.23</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1386</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="40">
@@ -4286,22 +4286,22 @@
         <v>14.34</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8.220000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>8.220000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5.99</v>
+        <v>6.68</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-1.17</v>
+        <v>-2.11</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="41">
@@ -4317,22 +4317,22 @@
         <v>27.91</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2.37</v>
+        <v>-1.01</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2.37</v>
+        <v>-1.01</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>5.94</v>
+        <v>4.92</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-2.69</v>
+        <v>-4.59</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.88</v>
+        <v>-1.35</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1346</v>
+        <v>1328</v>
       </c>
     </row>
   </sheetData>
@@ -4393,184 +4393,184 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>251.88</v>
+        <v>228.09</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-81.13</v>
+        <v>-58.67</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>333.01</v>
+        <v>286.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>177.49</v>
+        <v>197.03</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-54.52</v>
+        <v>35.55</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>232.01</v>
+        <v>161.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>10633</v>
+        <v>3875</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>172.92</v>
+        <v>160.16</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>36.95</v>
+        <v>12.26</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>135.97</v>
+        <v>147.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>161.25</v>
+        <v>156.68</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-31.18</v>
+        <v>-16.06</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>192.43</v>
+        <v>172.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>858</v>
+        <v>7220</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>150.02</v>
+        <v>150.17</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>141.15</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8.869999999999999</v>
+        <v>59.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>144.03</v>
+        <v>139.06</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>27.3</v>
+        <v>-65.16</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>116.73</v>
+        <v>204.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7220</v>
+        <v>2075</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>137.49</v>
+        <v>120.6</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>87.27</v>
+        <v>127.12</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>50.23</v>
+        <v>-6.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5166</v>
+        <v>858</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>126.23</v>
+        <v>120.58</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>57.28</v>
+        <v>131.94</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>68.95</v>
+        <v>-11.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2075</v>
+        <v>5166</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>106.4</v>
+        <v>117.92</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>86.64</v>
+        <v>73.97</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.76</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>8423</v>
+        <v>2771</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>102.18</v>
+        <v>102.47</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>47.68</v>
+        <v>29.37</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>54.5</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -4583,507 +4583,507 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>101.55</v>
+        <v>101.95</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-22.6</v>
+        <v>31.81</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>124.15</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>4325</v>
+        <v>8423</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>84.06999999999999</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>108.94</v>
+        <v>39.58</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-24.87</v>
+        <v>28.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6081</v>
+        <v>7289</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>81.68000000000001</v>
+        <v>65.59</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>199.62</v>
+        <v>88.45</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-117.94</v>
+        <v>-22.85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8767</v>
+        <v>5980</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>72.33</v>
+        <v>62.71</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>32.26</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>40.07</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7289</v>
+        <v>4325</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>59.22</v>
+        <v>59.51</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>100.09</v>
+        <v>137.65</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-40.87</v>
+        <v>-78.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9638</v>
+        <v>9756</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>58.43</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>125.38</v>
+        <v>41.65</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-66.95999999999999</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5980</v>
+        <v>6081</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>55.62</v>
+        <v>54.52</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>92.51000000000001</v>
+        <v>153.69</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-36.89</v>
+        <v>-99.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>2771</v>
+        <v>9685</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>43.22</v>
+        <v>47.13</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>62.74</v>
+        <v>11.45</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-19.51</v>
+        <v>35.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9756</v>
+        <v>10181</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>39.61</v>
+        <v>42.87</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>44.94</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-38.64</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>904</v>
+        <v>9208</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>38.98</v>
+        <v>38.56</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>42.77</v>
+        <v>-137.78</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-3.79</v>
+        <v>176.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>10181</v>
+        <v>8767</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>38.31</v>
+        <v>37.08</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.87</v>
+        <v>66.92</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>35.44</v>
+        <v>-29.83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>9549</v>
+        <v>9566</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>36.29</v>
+        <v>26.94</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-1.78</v>
+        <v>-14.33</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>38.07</v>
+        <v>41.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7809</v>
+        <v>8285</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>36.03</v>
+        <v>23.33</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>235.39</v>
+        <v>81.73</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-199.37</v>
+        <v>-58.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9685</v>
+        <v>7809</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>33.74</v>
+        <v>20.82</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>7.7</v>
+        <v>196.06</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.04</v>
+        <v>-175.24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9671</v>
+        <v>9638</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>29.29</v>
+        <v>11.36</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-15.64</v>
+        <v>138.51</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>44.93</v>
+        <v>-127.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>10642</v>
+        <v>904</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>17.91</v>
+        <v>6.97</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>102.77</v>
+        <v>49.16</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-84.86</v>
+        <v>-42.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9566</v>
+        <v>9549</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6.39</v>
+        <v>5.65</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-49.31</v>
+        <v>41.35</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>55.71</v>
+        <v>-35.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9206</v>
+        <v>7658</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.37</v>
+        <v>4.05</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-10.33</v>
+        <v>71.63</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>13.7</v>
+        <v>-67.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3234</v>
+        <v>11399</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2.01</v>
+        <v>3.65</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>91</v>
+        <v>133.36</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-88.98</v>
+        <v>-129.71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-5.06</v>
+        <v>1.75</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>198.41</v>
+        <v>24.54</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-203.48</v>
+        <v>-22.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8285</v>
+        <v>9206</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>-9.24</v>
+        <v>0.55</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>105.39</v>
+        <v>-24.11</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-114.63</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9208</v>
+        <v>10642</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-14.38</v>
+        <v>-0.93</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-138.03</v>
+        <v>91.3</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>123.65</v>
+        <v>-92.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5256</v>
+        <v>9671</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-19.26</v>
+        <v>-4.37</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>47.8</v>
+        <v>3.31</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-67.06</v>
+        <v>-7.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7658</v>
+        <v>7808</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-24.86</v>
+        <v>-11.72</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>56.37</v>
+        <v>-14.83</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-81.23</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>11399</v>
+        <v>7221</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-28.08</v>
+        <v>-11.81</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>99.7</v>
+        <v>123.48</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-127.78</v>
+        <v>-135.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10664</v>
+        <v>3234</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-42.73</v>
+        <v>-21.83</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-57.23</v>
+        <v>102.66</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>14.5</v>
+        <v>-124.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7808</v>
+        <v>7256</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-43.09</v>
+        <v>-24.04</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>70.89</v>
+        <v>193.97</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-113.98</v>
+        <v>-218.01</v>
       </c>
     </row>
     <row r="39">
@@ -5096,32 +5096,32 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-44.87</v>
+        <v>-27.6</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>8.449999999999999</v>
+        <v>-11.53</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-53.32</v>
+        <v>-16.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7221</v>
+        <v>10664</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-45.17</v>
+        <v>-69.44</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>180.24</v>
+        <v>-67.64</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-225.41</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="41">
@@ -5214,11 +5214,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -5239,15 +5239,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -5256,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -5264,15 +5264,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1023</v>
+        <v>7656</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -5289,24 +5289,24 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -5314,24 +5314,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7808</v>
+        <v>4967</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -5339,24 +5339,24 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7656</v>
+        <v>3875</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -5364,11 +5364,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3875</v>
+        <v>7808</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -5381,7 +5381,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -5389,15 +5389,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10633</v>
+        <v>9208</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -5414,15 +5414,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9638</v>
+        <v>2771</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
@@ -5431,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -5439,15 +5439,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5980</v>
+        <v>7289</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
@@ -5456,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -5464,24 +5464,24 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>9208</v>
+        <v>2075</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -5489,18 +5489,18 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>10664</v>
+        <v>10633</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
@@ -5514,11 +5514,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7289</v>
+        <v>10664</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -5539,24 +5539,24 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9206</v>
+        <v>9638</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -5564,24 +5564,24 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -5589,11 +5589,11 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2075</v>
+        <v>5980</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -5639,15 +5639,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>8767</v>
+        <v>9685</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1</v>
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -5689,11 +5689,11 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>9549</v>
+        <v>10642</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -5714,15 +5714,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>4325</v>
+        <v>9549</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>2</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -5739,24 +5739,24 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>2</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -5789,15 +5789,15 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5166</v>
+        <v>9206</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>2</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -5814,15 +5814,15 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9756</v>
+        <v>3234</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>2</v>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -5839,24 +5839,24 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10642</v>
+        <v>7221</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -5864,24 +5864,24 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>904</v>
+        <v>4325</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -5889,15 +5889,15 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7256</v>
+        <v>8767</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>2</v>
@@ -5906,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -5914,24 +5914,24 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>11399</v>
+        <v>7256</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -5939,24 +5939,24 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3234</v>
+        <v>10181</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -5964,11 +5964,11 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7221</v>
+        <v>11399</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -5989,11 +5989,11 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>10181</v>
+        <v>904</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -6025,13 +6025,13 @@
         <v>1</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -6075,13 +6075,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -6089,18 +6089,18 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7658</v>
+        <v>7818</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
@@ -6114,24 +6114,24 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7818</v>
+        <v>7658</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -6139,18 +6139,18 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>8285</v>
+        <v>9671</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -6164,24 +6164,24 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>251.88</v>
+        <v>228.09</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-81.13</v>
+        <v>-58.67</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>333.01</v>
+        <v>286.76</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6307,21 +6307,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>177.49</v>
+        <v>197.03</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-54.52</v>
+        <v>35.55</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>232.01</v>
+        <v>161.48</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6330,21 +6330,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10633</v>
+        <v>3875</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>172.92</v>
+        <v>160.16</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>36.95</v>
+        <v>12.26</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>135.97</v>
+        <v>147.91</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6353,21 +6353,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>161.25</v>
+        <v>156.68</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-31.18</v>
+        <v>-16.06</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>192.43</v>
+        <v>172.73</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6376,21 +6376,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>858</v>
+        <v>7220</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>150.02</v>
+        <v>150.17</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>141.15</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8.869999999999999</v>
+        <v>59.43</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6399,21 +6399,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>144.03</v>
+        <v>139.06</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>27.3</v>
+        <v>-65.16</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>116.73</v>
+        <v>204.21</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6422,21 +6422,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7220</v>
+        <v>2075</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>137.49</v>
+        <v>120.6</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>87.27</v>
+        <v>127.12</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>50.23</v>
+        <v>-6.52</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6445,21 +6445,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5166</v>
+        <v>858</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>126.23</v>
+        <v>120.58</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>57.28</v>
+        <v>131.94</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>68.95</v>
+        <v>-11.37</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6468,21 +6468,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2075</v>
+        <v>5166</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>106.4</v>
+        <v>117.92</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>86.64</v>
+        <v>73.97</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>19.76</v>
+        <v>43.95</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6491,21 +6491,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>8423</v>
+        <v>2771</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>102.18</v>
+        <v>102.47</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>47.68</v>
+        <v>29.37</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>54.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6522,13 +6522,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>101.55</v>
+        <v>101.95</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-22.6</v>
+        <v>31.81</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>124.15</v>
+        <v>70.14</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6537,21 +6537,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>4325</v>
+        <v>8423</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>84.06999999999999</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>108.94</v>
+        <v>39.58</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-24.87</v>
+        <v>28.73</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6560,21 +6560,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>6081</v>
+        <v>7289</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>81.68000000000001</v>
+        <v>65.59</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>199.62</v>
+        <v>88.45</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-117.94</v>
+        <v>-22.85</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6583,21 +6583,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>8767</v>
+        <v>5980</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>72.33</v>
+        <v>62.71</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>32.26</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>40.07</v>
+        <v>-26</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6606,21 +6606,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7289</v>
+        <v>4325</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>59.22</v>
+        <v>59.51</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>100.09</v>
+        <v>137.65</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-40.87</v>
+        <v>-78.14</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6629,21 +6629,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9638</v>
+        <v>9756</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>58.43</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>125.38</v>
+        <v>41.65</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-66.95999999999999</v>
+        <v>17.34</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6652,21 +6652,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>5980</v>
+        <v>6081</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>55.62</v>
+        <v>54.52</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>92.51000000000001</v>
+        <v>153.69</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-36.89</v>
+        <v>-99.17</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6675,21 +6675,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2771</v>
+        <v>9685</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>43.22</v>
+        <v>47.13</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>62.74</v>
+        <v>11.45</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-19.51</v>
+        <v>35.68</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6698,21 +6698,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>9756</v>
+        <v>10181</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>39.61</v>
+        <v>42.87</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>44.94</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-38.64</v>
+        <v>-2.07</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6721,21 +6721,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>904</v>
+        <v>9208</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>38.98</v>
+        <v>38.56</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>42.77</v>
+        <v>-137.78</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-3.79</v>
+        <v>176.34</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6744,21 +6744,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>10181</v>
+        <v>8767</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>38.31</v>
+        <v>37.08</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2.87</v>
+        <v>66.92</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>35.44</v>
+        <v>-29.83</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6767,21 +6767,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>9549</v>
+        <v>9566</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>36.29</v>
+        <v>26.94</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-1.78</v>
+        <v>-14.33</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>38.07</v>
+        <v>41.26</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6790,21 +6790,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7809</v>
+        <v>8285</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>36.03</v>
+        <v>23.33</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>235.39</v>
+        <v>81.73</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-199.37</v>
+        <v>-58.4</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6813,21 +6813,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9685</v>
+        <v>7809</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>33.74</v>
+        <v>20.82</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>7.7</v>
+        <v>196.06</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>26.04</v>
+        <v>-175.24</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6836,21 +6836,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9671</v>
+        <v>9638</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>29.29</v>
+        <v>11.36</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-15.64</v>
+        <v>138.51</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>44.93</v>
+        <v>-127.16</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6859,21 +6859,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10642</v>
+        <v>904</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>17.91</v>
+        <v>6.97</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>102.77</v>
+        <v>49.16</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-84.86</v>
+        <v>-42.19</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6882,21 +6882,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>9566</v>
+        <v>9549</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6.39</v>
+        <v>5.65</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-49.31</v>
+        <v>41.35</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>55.71</v>
+        <v>-35.7</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6905,21 +6905,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9206</v>
+        <v>7658</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.37</v>
+        <v>4.05</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-10.33</v>
+        <v>71.63</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>13.7</v>
+        <v>-67.58</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6928,21 +6928,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>3234</v>
+        <v>11399</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2.01</v>
+        <v>3.65</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>91</v>
+        <v>133.36</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-88.98</v>
+        <v>-129.71</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6951,21 +6951,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-5.06</v>
+        <v>1.75</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>198.41</v>
+        <v>24.54</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-203.48</v>
+        <v>-22.79</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6974,21 +6974,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>8285</v>
+        <v>9206</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>-9.24</v>
+        <v>0.55</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>105.39</v>
+        <v>-24.11</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-114.63</v>
+        <v>24.66</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6997,21 +6997,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>9208</v>
+        <v>10642</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-14.38</v>
+        <v>-0.93</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-138.03</v>
+        <v>91.3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>123.65</v>
+        <v>-92.23</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7020,21 +7020,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5256</v>
+        <v>9671</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-19.26</v>
+        <v>-4.37</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>47.8</v>
+        <v>3.31</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-67.06</v>
+        <v>-7.68</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -7043,21 +7043,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7658</v>
+        <v>7808</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-24.86</v>
+        <v>-11.72</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>56.37</v>
+        <v>-14.83</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-81.23</v>
+        <v>3.11</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -7066,21 +7066,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>11399</v>
+        <v>7221</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-28.08</v>
+        <v>-11.81</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>99.7</v>
+        <v>123.48</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-127.78</v>
+        <v>-135.29</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7089,21 +7089,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>10664</v>
+        <v>3234</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-42.73</v>
+        <v>-21.83</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-57.23</v>
+        <v>102.66</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>14.5</v>
+        <v>-124.49</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -7112,21 +7112,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7808</v>
+        <v>7256</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-43.09</v>
+        <v>-24.04</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>70.89</v>
+        <v>193.97</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-113.98</v>
+        <v>-218.01</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -7143,13 +7143,13 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-44.87</v>
+        <v>-27.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>8.449999999999999</v>
+        <v>-11.53</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-53.32</v>
+        <v>-16.07</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -7158,21 +7158,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>7221</v>
+        <v>10664</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-45.17</v>
+        <v>-69.44</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>180.24</v>
+        <v>-67.64</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-225.41</v>
+        <v>-1.8</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -609,23 +609,23 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1023</v>
+        <v>3620</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Saint Joseph, Michigan</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -634,51 +634,51 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>139.06</v>
+        <v>212.62</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-65.16</v>
+        <v>-15.86</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>204.21</v>
+        <v>228.49</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>68.08</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>124.01</v>
+        <v>126.18</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>124.01</v>
+        <v>126.18</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>21.09</v>
+        <v>25.21</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>74.2</v>
+        <v>69.73</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>28.72</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph, Michigan</t>
+          <t>Brighton, Michigan</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -688,43 +688,43 @@
         <v>5</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>228.09</v>
+        <v>125.36</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-58.67</v>
+        <v>101.91</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>286.76</v>
+        <v>23.46</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>117.04</v>
+        <v>113.57</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>117.04</v>
+        <v>113.57</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>20.89</v>
+        <v>27.31</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>67.88</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>28.27</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="4">
@@ -745,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -754,51 +754,51 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>101.95</v>
+        <v>102.42</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>31.81</v>
+        <v>35.78</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>70.14</v>
+        <v>66.64</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>50.91</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>77.22</v>
+        <v>88.72</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>77.22</v>
+        <v>88.72</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1577</v>
+        <v>1599</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>10</v>
+        <v>10.89</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>47.34</v>
+        <v>53.14</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>19.89</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>7220</v>
+        <v>7808</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Brighton, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -814,51 +814,51 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>150.17</v>
+        <v>10.17</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>90.73999999999999</v>
+        <v>-47.3</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>59.43</v>
+        <v>57.47</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>45.04</v>
+        <v>24.37</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>113.64</v>
+        <v>39.89</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>113.64</v>
+        <v>39.89</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1646</v>
+        <v>1494</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>24.6</v>
+        <v>5.37</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>70.79000000000001</v>
+        <v>22.68</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>18.24</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Belmont, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -868,64 +868,64 @@
         <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>156.68</v>
+        <v>142.25</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-16.06</v>
+        <v>28.04</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>172.73</v>
+        <v>114.21</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>68.89</v>
+        <v>68.08</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>109.99</v>
+        <v>124.83</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>109.99</v>
+        <v>124.83</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1641</v>
+        <v>1661</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>22.97</v>
+        <v>21.41</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>60.13</v>
+        <v>73.97</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>26.89</v>
+        <v>29.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3875</v>
+        <v>2771</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>1</v>
@@ -934,111 +934,111 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>160.16</v>
+        <v>100.52</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>12.26</v>
+        <v>34.01</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>147.91</v>
+        <v>66.52</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>50.66</v>
+        <v>53.52</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>88.5</v>
+        <v>70.09</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>88.5</v>
+        <v>70.09</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1599</v>
+        <v>1561</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10.37</v>
+        <v>8.99</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>52.93</v>
+        <v>44.97</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.2</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7808</v>
+        <v>2075</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-11.72</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-14.83</v>
+        <v>82.86</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3.11</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>24.37</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38.49</v>
+        <v>115.05</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>38.49</v>
+        <v>115.05</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1491</v>
+        <v>1648</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>4.34</v>
+        <v>25.89</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>21.67</v>
+        <v>63.31</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>12.48</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>9208</v>
+        <v>4967</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Edwardsburg, Michigan</t>
+          <t>Belmont, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1048,103 +1048,103 @@
         <v>4</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>38.56</v>
+        <v>150.58</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-137.78</v>
+        <v>-23.63</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>176.34</v>
+        <v>174.21</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>44.43</v>
+        <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>59.93</v>
+        <v>105.05</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>59.93</v>
+        <v>105.05</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1540</v>
+        <v>1632</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>16.49</v>
+        <v>24.29</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>33.18</v>
+        <v>55.97</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>10.25</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2771</v>
+        <v>3875</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>102.47</v>
+        <v>160.41</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29.37</v>
+        <v>78.5</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>81.91</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>53.52</v>
+        <v>50.66</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>71.20999999999999</v>
+        <v>87.52</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>71.20999999999999</v>
+        <v>87.52</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1564</v>
+        <v>1596</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>10.56</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>44.46</v>
+        <v>51.15</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>17.63</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="11">
@@ -1165,7 +1165,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1</v>
@@ -1174,51 +1174,51 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>65.59</v>
+        <v>63.37</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>88.45</v>
+        <v>22.67</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-22.85</v>
+        <v>40.7</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>33.29</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>31.02</v>
+        <v>32.42</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>31.02</v>
+        <v>32.42</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>12.67</v>
+        <v>13.7</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6.67</v>
+        <v>7.68</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>11.68</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2075</v>
+        <v>10633</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1234,58 +1234,58 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>120.6</v>
+        <v>176.96</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>127.12</v>
+        <v>52.41</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-6.52</v>
+        <v>124.55</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>113.7</v>
+        <v>122.17</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>113.7</v>
+        <v>122.17</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1646</v>
+        <v>1657</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>23.76</v>
+        <v>21.02</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>65.69</v>
+        <v>69.78</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>24.25</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>10633</v>
+        <v>9208</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Edwardsburg, Michigan</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>2</v>
@@ -1294,51 +1294,51 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>197.03</v>
+        <v>10.97</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>35.55</v>
+        <v>-5.91</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>161.48</v>
+        <v>16.88</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>45.8</v>
+        <v>44.43</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>117.29</v>
+        <v>58.95</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>117.29</v>
+        <v>58.95</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1652</v>
+        <v>1537</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19.82</v>
+        <v>16.68</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>68.13</v>
+        <v>31.41</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>29.34</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>10664</v>
+        <v>5166</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1348,57 +1348,57 @@
         <v>3</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-69.44</v>
+        <v>116.97</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-67.64</v>
+        <v>13</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-1.8</v>
+        <v>103.97</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>21.7</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>25.45</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>25.45</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1454</v>
+        <v>1617</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>9.279999999999999</v>
+        <v>16.72</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>15.67</v>
+        <v>59.29</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>0.5</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9638</v>
+        <v>858</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1414,118 +1414,118 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>11.36</v>
+        <v>132.21</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>138.51</v>
+        <v>48.32</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-127.16</v>
+        <v>83.89</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>22.93</v>
+        <v>55.1</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>21.93</v>
+        <v>70.34</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>21.93</v>
+        <v>70.34</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1441</v>
+        <v>1561</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8.25</v>
+        <v>10.16</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>8.24</v>
+        <v>37.01</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>5.43</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5166</v>
+        <v>9685</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>117.92</v>
+        <v>58</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>73.97</v>
+        <v>-13.94</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>43.95</v>
+        <v>71.94</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>27.75</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>98.86</v>
+        <v>43.71</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>98.86</v>
+        <v>43.71</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1621</v>
+        <v>1504</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>16.85</v>
+        <v>18.1</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>58.78</v>
+        <v>8.94</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>23.23</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>5980</v>
+        <v>9638</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
         <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>2</v>
@@ -1534,58 +1534,58 @@
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>62.71</v>
+        <v>27.34</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>88.70999999999999</v>
+        <v>97.95</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-26</v>
+        <v>-70.59999999999999</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>38.55</v>
+        <v>22.93</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>31.27</v>
+        <v>29.72</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>31.27</v>
+        <v>29.72</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.42</v>
+        <v>10.44</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>16.68</v>
+        <v>12.48</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>7.17</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>858</v>
+        <v>8423</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>2</v>
@@ -1594,118 +1594,118 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>120.58</v>
+        <v>73.98</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>131.94</v>
+        <v>-24.99</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-11.37</v>
+        <v>98.97</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>55.1</v>
+        <v>28.04</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>65.81999999999999</v>
+        <v>57.57</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>65.81999999999999</v>
+        <v>57.57</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1553</v>
+        <v>1535</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>8.43</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>35.77</v>
+        <v>29.46</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>21.62</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9685</v>
+        <v>5980</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>47.13</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>11.45</v>
+        <v>39.17</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>35.68</v>
+        <v>38.28</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>27.75</v>
+        <v>38.55</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>39.2</v>
+        <v>31.92</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>39.2</v>
+        <v>31.92</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1493</v>
+        <v>1474</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>16.37</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>7.7</v>
+        <v>16.91</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>15.13</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8423</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>2</v>
@@ -1714,58 +1714,58 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>68.31999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>39.58</v>
+        <v>55.06</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>28.73</v>
+        <v>-45.6</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>28.04</v>
+        <v>27.21</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>52.69</v>
+        <v>34.57</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>52.69</v>
+        <v>34.57</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1525</v>
+        <v>1481</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>11.8</v>
+        <v>3.88</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>27.81</v>
+        <v>22.6</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>13.08</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>2</v>
@@ -1774,58 +1774,58 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0.93</v>
+        <v>-34.32</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>91.3</v>
+        <v>-20.18</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-92.23</v>
+        <v>-14.14</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>25.63</v>
+        <v>21.7</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>22.31</v>
+        <v>24.08</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22.31</v>
+        <v>24.08</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>4.3</v>
+        <v>8.94</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>10.28</v>
+        <v>14.25</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>7.73</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9549</v>
+        <v>9206</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>2</v>
@@ -1834,51 +1834,51 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5.65</v>
+        <v>10.98</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>41.35</v>
+        <v>-39.63</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-35.7</v>
+        <v>50.62</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>17.6</v>
+        <v>21.07</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>25.74</v>
+        <v>27.3</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>25.74</v>
+        <v>27.3</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1455</v>
+        <v>1460</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>6.27</v>
+        <v>3.92</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>14.31</v>
+        <v>11.87</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>5.17</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>9756</v>
+        <v>4325</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1888,43 +1888,43 @@
         <v>2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>59</v>
+        <v>57.27</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>41.65</v>
+        <v>160.05</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>17.34</v>
+        <v>-102.78</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>29.21</v>
+        <v>32.52</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>45.3</v>
+        <v>38.66</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>45.3</v>
+        <v>38.66</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1508</v>
+        <v>1491</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>5.74</v>
+        <v>10.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>25.51</v>
+        <v>20.94</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>14.05</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="24">
@@ -1948,22 +1948,22 @@
         <v>3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1.75</v>
+        <v>11.51</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24.54</v>
+        <v>12.02</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-22.79</v>
+        <v>-0.52</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>35.18</v>
@@ -1989,76 +1989,76 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9206</v>
+        <v>9549</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>24</v>
       </c>
       <c r="E25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.55</v>
+        <v>-2.07</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-24.11</v>
+        <v>58.53</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>24.66</v>
+        <v>-60.6</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>21.07</v>
+        <v>17.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>27.3</v>
+        <v>26.39</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>27.3</v>
+        <v>26.39</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>3.92</v>
+        <v>6.97</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>11.87</v>
+        <v>14.54</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>11.51</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3234</v>
+        <v>9756</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -2068,57 +2068,57 @@
         <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-21.83</v>
+        <v>47.45</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>102.66</v>
+        <v>58.42</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-124.49</v>
+        <v>-10.97</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>22.62</v>
+        <v>29.21</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>18.44</v>
+        <v>45.94</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>18.44</v>
+        <v>45.94</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1428</v>
+        <v>1509</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>4.22</v>
+        <v>6.44</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>10.77</v>
+        <v>25.74</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>3.45</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>7221</v>
+        <v>10642</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -2137,55 +2137,55 @@
         <v>9</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-11.81</v>
+        <v>-10.95</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>123.48</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-135.29</v>
+        <v>-81.56</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>8.82</v>
+        <v>25.63</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>19.32</v>
+        <v>17.37</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>19.32</v>
+        <v>17.37</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1431</v>
+        <v>1423</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>7.01</v>
+        <v>5.62</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>6.02</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>4325</v>
+        <v>11399</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>3</v>
@@ -2194,51 +2194,51 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>59.51</v>
+        <v>-11.75</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>137.65</v>
+        <v>142.98</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-78.14</v>
+        <v>-154.73</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>32.52</v>
+        <v>23.74</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>33.78</v>
+        <v>17.82</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>33.78</v>
+        <v>17.82</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1479</v>
+        <v>1425</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>9.48</v>
+        <v>4.98</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>19.29</v>
+        <v>11.07</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>5.02</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>8767</v>
+        <v>7221</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -2248,124 +2248,124 @@
         <v>2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>37.08</v>
+        <v>2.89</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>66.92</v>
+        <v>67.16</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-29.83</v>
+        <v>-64.27</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>27.21</v>
+        <v>8.82</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>35.69</v>
+        <v>19.32</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>35.69</v>
+        <v>19.32</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1484</v>
+        <v>1431</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>4.02</v>
+        <v>7.01</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>22.09</v>
+        <v>6.29</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>9.58</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7256</v>
+        <v>6081</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-24.04</v>
+        <v>65.56</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>193.97</v>
+        <v>78.61</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-218.01</v>
+        <v>-13.05</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>25.23</v>
+        <v>59.73</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15.72</v>
+        <v>55.89</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>15.72</v>
+        <v>55.89</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1416</v>
+        <v>1531</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>2.86</v>
+        <v>15.52</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>4.99</v>
+        <v>20.48</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>7.87</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>10181</v>
+        <v>3234</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>3</v>
@@ -2374,51 +2374,51 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>42.87</v>
+        <v>10.51</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>44.94</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-2.07</v>
+        <v>-64.64</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>23.43</v>
+        <v>22.62</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>17.69</v>
+        <v>17.07</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>17.69</v>
+        <v>17.07</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>7.77</v>
+        <v>9.35</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>5.66</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>11399</v>
+        <v>10181</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -2428,43 +2428,43 @@
         <v>1</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3.65</v>
+        <v>16.78</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>133.36</v>
+        <v>96.58</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-129.71</v>
+        <v>-79.81</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>23.74</v>
+        <v>23.43</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>13.31</v>
+        <v>18.51</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>13.31</v>
+        <v>18.51</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1405</v>
+        <v>1428</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>3.25</v>
+        <v>4.57</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>9.83</v>
+        <v>7.54</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>0.23</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="33">
@@ -2488,57 +2488,57 @@
         <v>1</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>6.97</v>
+        <v>3.08</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>49.16</v>
+        <v>66.56</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-42.19</v>
+        <v>-63.48</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>27.91</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.19</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.19</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.92</v>
+        <v>5.24</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>-4.59</v>
+        <v>-4.81</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>-1.35</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6081</v>
+        <v>7256</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -2554,51 +2554,51 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>54.52</v>
+        <v>-31.69</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>153.69</v>
+        <v>191.23</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-99.17</v>
+        <v>-222.92</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>59.73</v>
+        <v>25.23</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>54.49</v>
+        <v>10.79</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>54.49</v>
+        <v>10.79</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1528</v>
+        <v>1393</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>14.49</v>
+        <v>4.19</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>19.47</v>
+        <v>0.83</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>20.53</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9566</v>
+        <v>7818</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -2608,64 +2608,64 @@
         <v>1</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>26.94</v>
+        <v>-3.99</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-14.33</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>41.26</v>
+        <v>-84.09</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>39.97</v>
+        <v>32.45</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>22.61</v>
+        <v>17.96</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>22.61</v>
+        <v>17.96</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1444</v>
+        <v>1426</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>3.57</v>
+        <v>5.95</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>10.91</v>
+        <v>4.48</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>8.119999999999999</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7809</v>
+        <v>9566</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>5</v>
@@ -2674,51 +2674,51 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.82</v>
+        <v>17.45</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>196.06</v>
+        <v>115.52</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-175.24</v>
+        <v>-98.06999999999999</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>23.83</v>
+        <v>39.97</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>34.68</v>
+        <v>20.27</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>34.68</v>
+        <v>20.27</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1481</v>
+        <v>1435</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>5.1</v>
+        <v>3.43</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>14.07</v>
+        <v>7.72</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>15.51</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7818</v>
+        <v>7809</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2734,37 +2734,37 @@
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>-27.6</v>
+        <v>25.55</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>-11.53</v>
+        <v>178.62</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-16.07</v>
+        <v>-153.07</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>32.45</v>
+        <v>23.83</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>15.67</v>
+        <v>34.68</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>15.67</v>
+        <v>34.68</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1416</v>
+        <v>1481</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>6.67</v>
+        <v>5.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>4.72</v>
+        <v>14.07</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>4.28</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="38">
@@ -2797,13 +2797,13 @@
         <v>2</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4.05</v>
+        <v>-4.98</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>71.63</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-67.58</v>
+        <v>-69.92</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>14.34</v>
@@ -2857,34 +2857,34 @@
         <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>-4.37</v>
+        <v>9.91</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.31</v>
+        <v>26.62</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-7.68</v>
+        <v>-16.71</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>27.39</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>27.92</v>
+        <v>26.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>27.92</v>
+        <v>26.5</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>9.06</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>14.63</v>
+        <v>12.82</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>4.22</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="40">
@@ -2917,13 +2917,13 @@
         <v>1</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.33</v>
+        <v>17.1</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>81.73</v>
+        <v>101.15</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-58.4</v>
+        <v>-84.05</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>39.07</v>
@@ -3097,95 +3097,95 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1023</v>
+        <v>3620</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>68.08</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>124.01</v>
+        <v>126.18</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>124.01</v>
+        <v>126.18</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>21.09</v>
+        <v>25.21</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>74.2</v>
+        <v>69.73</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>28.72</v>
+        <v>31.24</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1661</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>10633</v>
+        <v>1023</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>45.8</v>
+        <v>68.08</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>117.29</v>
+        <v>124.83</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>117.29</v>
+        <v>124.83</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>19.82</v>
+        <v>21.41</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>68.13</v>
+        <v>73.97</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>29.34</v>
+        <v>29.45</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1652</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3620</v>
+        <v>10633</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>117.04</v>
+        <v>122.17</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>117.04</v>
+        <v>122.17</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>20.89</v>
+        <v>21.02</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>67.88</v>
+        <v>69.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>28.27</v>
+        <v>31.38</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1651</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="5">
@@ -3201,22 +3201,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>113.7</v>
+        <v>115.05</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>113.7</v>
+        <v>115.05</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.76</v>
+        <v>25.89</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>65.69</v>
+        <v>63.31</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>24.25</v>
+        <v>25.85</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1646</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="6">
@@ -3232,19 +3232,19 @@
         <v>45.04</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>113.64</v>
+        <v>113.57</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>113.64</v>
+        <v>113.57</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>24.6</v>
+        <v>27.31</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>70.79000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>18.24</v>
+        <v>19.66</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1646</v>
@@ -3263,22 +3263,22 @@
         <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>109.99</v>
+        <v>105.05</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>109.99</v>
+        <v>105.05</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>22.97</v>
+        <v>24.29</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>60.13</v>
+        <v>55.97</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>26.89</v>
+        <v>24.79</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1641</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="8">
@@ -3294,50 +3294,50 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>98.86</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>98.86</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>16.85</v>
+        <v>16.72</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>58.78</v>
+        <v>59.29</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>23.23</v>
+        <v>21.74</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1621</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3875</v>
+        <v>7656</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.66</v>
+        <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>88.5</v>
+        <v>88.72</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>88.5</v>
+        <v>88.72</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.37</v>
+        <v>10.89</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>52.93</v>
+        <v>53.14</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>25.2</v>
+        <v>24.69</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>1599</v>
@@ -3345,95 +3345,95 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7656</v>
+        <v>3875</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50.91</v>
+        <v>50.66</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>77.22</v>
+        <v>87.52</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>77.22</v>
+        <v>87.52</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10</v>
+        <v>10.56</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>47.34</v>
+        <v>51.15</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19.89</v>
+        <v>25.8</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1577</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2771</v>
+        <v>858</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>53.52</v>
+        <v>55.1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>71.20999999999999</v>
+        <v>70.34</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>71.20999999999999</v>
+        <v>70.34</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9.119999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>44.46</v>
+        <v>37.01</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>17.63</v>
+        <v>23.16</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1564</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>65.81999999999999</v>
+        <v>70.09</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>65.81999999999999</v>
+        <v>70.09</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.43</v>
+        <v>8.99</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>35.77</v>
+        <v>44.97</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>21.62</v>
+        <v>16.13</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1553</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="13">
@@ -3449,84 +3449,84 @@
         <v>44.43</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>59.93</v>
+        <v>58.95</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>59.93</v>
+        <v>58.95</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>16.49</v>
+        <v>16.68</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>33.18</v>
+        <v>31.41</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.25</v>
+        <v>10.85</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1540</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6081</v>
+        <v>8423</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>59.73</v>
+        <v>28.04</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>54.49</v>
+        <v>57.57</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>54.49</v>
+        <v>57.57</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>19.47</v>
+        <v>29.46</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20.53</v>
+        <v>15.12</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1528</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>6081</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>59.73</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>52.69</v>
+        <v>55.89</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>52.69</v>
+        <v>55.89</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>11.8</v>
+        <v>15.52</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>27.81</v>
+        <v>20.48</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.08</v>
+        <v>19.89</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1525</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="16">
@@ -3542,22 +3542,22 @@
         <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45.3</v>
+        <v>45.94</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45.3</v>
+        <v>45.94</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>5.74</v>
+        <v>6.44</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>25.51</v>
+        <v>25.74</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.05</v>
+        <v>13.76</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="17">
@@ -3573,22 +3573,22 @@
         <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>39.2</v>
+        <v>43.71</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>39.2</v>
+        <v>43.71</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>16.37</v>
+        <v>18.1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>7.7</v>
+        <v>8.94</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>15.13</v>
+        <v>16.66</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1493</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="18">
@@ -3604,53 +3604,53 @@
         <v>24.37</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>38.49</v>
+        <v>39.89</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>38.49</v>
+        <v>39.89</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>4.34</v>
+        <v>5.37</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>21.67</v>
+        <v>22.68</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>12.48</v>
+        <v>11.84</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1491</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>4325</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.21</v>
+        <v>32.52</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>35.69</v>
+        <v>38.66</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>35.69</v>
+        <v>38.66</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>4.02</v>
+        <v>10.67</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>22.09</v>
+        <v>20.94</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>9.58</v>
+        <v>7.05</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1484</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="20">
@@ -3686,64 +3686,64 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>4325</v>
+        <v>8767</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>32.52</v>
+        <v>27.21</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>33.78</v>
+        <v>34.57</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>33.78</v>
+        <v>34.57</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>9.48</v>
+        <v>3.88</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>19.29</v>
+        <v>22.6</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>5.02</v>
+        <v>8.08</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1479</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5501</v>
+        <v>7289</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>31.87</v>
+        <v>33.29</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.87</v>
+        <v>32.42</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>31.87</v>
+        <v>32.42</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>6.95</v>
+        <v>13.7</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>17.02</v>
+        <v>7.68</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>7.9</v>
+        <v>11.04</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="23">
@@ -3759,84 +3759,84 @@
         <v>38.55</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>31.27</v>
+        <v>31.92</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>31.27</v>
+        <v>31.92</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7.42</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16.68</v>
+        <v>16.91</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>7.17</v>
+        <v>6.88</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1472</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7289</v>
+        <v>5501</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>33.29</v>
+        <v>31.87</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>31.02</v>
+        <v>31.87</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>31.02</v>
+        <v>31.87</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>12.67</v>
+        <v>6.95</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>6.67</v>
+        <v>17.02</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>11.68</v>
+        <v>7.9</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1471</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9671</v>
+        <v>9638</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>27.39</v>
+        <v>22.93</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>27.92</v>
+        <v>29.72</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>27.92</v>
+        <v>29.72</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>9.06</v>
+        <v>10.44</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14.63</v>
+        <v>12.48</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.22</v>
+        <v>6.79</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1462</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="26">
@@ -3903,123 +3903,123 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9549</v>
+        <v>9671</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>17.6</v>
+        <v>27.39</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>25.74</v>
+        <v>26.5</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>25.74</v>
+        <v>26.5</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>6.27</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>14.31</v>
+        <v>12.82</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.17</v>
+        <v>4.04</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1455</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>10664</v>
+        <v>9549</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>21.7</v>
+        <v>17.6</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>25.45</v>
+        <v>26.39</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>25.45</v>
+        <v>26.39</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.279999999999999</v>
+        <v>6.97</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>15.67</v>
+        <v>14.54</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.5</v>
+        <v>4.87</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1454</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8285</v>
+        <v>10664</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>39.07</v>
+        <v>21.7</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>22.72</v>
+        <v>24.08</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.72</v>
+        <v>24.08</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>3.61</v>
+        <v>8.94</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>12.17</v>
+        <v>14.25</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>6.94</v>
+        <v>0.89</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1444</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9566</v>
+        <v>8285</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>39.97</v>
+        <v>39.07</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>22.61</v>
+        <v>22.72</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22.61</v>
+        <v>22.72</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>10.91</v>
+        <v>12.17</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>8.119999999999999</v>
+        <v>6.94</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1444</v>
@@ -4027,250 +4027,250 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>10642</v>
+        <v>9566</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>25.63</v>
+        <v>39.97</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>22.31</v>
+        <v>20.27</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>22.31</v>
+        <v>20.27</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>4.3</v>
+        <v>3.43</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10.28</v>
+        <v>7.72</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>7.73</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1443</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9638</v>
+        <v>7221</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>22.93</v>
+        <v>8.82</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>21.93</v>
+        <v>19.32</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>21.93</v>
+        <v>19.32</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>8.25</v>
+        <v>7.01</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>8.24</v>
+        <v>6.29</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>5.43</v>
+        <v>6.02</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1441</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7221</v>
+        <v>10181</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>8.82</v>
+        <v>23.43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.32</v>
+        <v>18.51</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.32</v>
+        <v>18.51</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7.01</v>
+        <v>4.57</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6.29</v>
+        <v>7.54</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.02</v>
+        <v>6.39</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>3234</v>
+        <v>7818</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>22.62</v>
+        <v>32.45</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>18.44</v>
+        <v>17.96</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.44</v>
+        <v>17.96</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.22</v>
+        <v>5.95</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.77</v>
+        <v>4.48</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>3.45</v>
+        <v>7.53</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10181</v>
+        <v>11399</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23.43</v>
+        <v>23.74</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17.69</v>
+        <v>17.82</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.69</v>
+        <v>17.82</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4.25</v>
+        <v>4.98</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>7.77</v>
+        <v>11.07</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>5.66</v>
+        <v>1.77</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7256</v>
+        <v>10642</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>25.23</v>
+        <v>25.63</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>15.72</v>
+        <v>17.37</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>15.72</v>
+        <v>17.37</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2.86</v>
+        <v>5.62</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>4.99</v>
+        <v>6.12</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>7.87</v>
+        <v>5.63</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1416</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7818</v>
+        <v>3234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>32.45</v>
+        <v>22.62</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>15.67</v>
+        <v>17.07</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>15.67</v>
+        <v>17.07</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6.67</v>
+        <v>3.88</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4.72</v>
+        <v>9.35</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>4.28</v>
+        <v>3.84</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1416</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>11399</v>
+        <v>7256</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>23.74</v>
+        <v>25.23</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>13.31</v>
+        <v>10.79</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.31</v>
+        <v>10.79</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3.25</v>
+        <v>4.19</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>9.83</v>
+        <v>0.83</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.23</v>
+        <v>5.77</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1405</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="40">
@@ -4317,22 +4317,22 @@
         <v>27.91</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.19</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.19</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>4.92</v>
+        <v>5.24</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-4.59</v>
+        <v>-4.81</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-1.35</v>
+        <v>-0.62</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1328</v>
+        <v>1333</v>
       </c>
     </row>
   </sheetData>
@@ -4393,13 +4393,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>228.09</v>
+        <v>212.62</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-58.67</v>
+        <v>-15.86</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>286.76</v>
+        <v>228.49</v>
       </c>
     </row>
     <row r="3">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>197.03</v>
+        <v>176.96</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>35.55</v>
+        <v>52.41</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>161.48</v>
+        <v>124.55</v>
       </c>
     </row>
     <row r="4">
@@ -4431,13 +4431,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>160.16</v>
+        <v>160.41</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12.26</v>
+        <v>78.5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>147.91</v>
+        <v>81.91</v>
       </c>
     </row>
     <row r="5">
@@ -4450,108 +4450,108 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>156.68</v>
+        <v>150.58</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-16.06</v>
+        <v>-23.63</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>172.73</v>
+        <v>174.21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7220</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>150.17</v>
+        <v>142.25</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>28.04</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>59.43</v>
+        <v>114.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>1023</v>
+        <v>858</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>139.06</v>
+        <v>132.21</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-65.16</v>
+        <v>48.32</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>204.21</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2075</v>
+        <v>7220</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>120.6</v>
+        <v>125.36</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>127.12</v>
+        <v>101.91</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-6.52</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>858</v>
+        <v>5166</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>120.58</v>
+        <v>116.97</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>131.94</v>
+        <v>13</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-11.37</v>
+        <v>103.97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5166</v>
+        <v>7656</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>117.92</v>
+        <v>102.42</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>73.97</v>
+        <v>35.78</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>43.95</v>
+        <v>66.64</v>
       </c>
     </row>
     <row r="11">
@@ -4564,545 +4564,545 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>102.47</v>
+        <v>100.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>29.37</v>
+        <v>34.01</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>66.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7656</v>
+        <v>2075</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>101.95</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>31.81</v>
+        <v>82.86</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>70.14</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>8423</v>
+        <v>5980</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>68.31999999999999</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>39.58</v>
+        <v>39.17</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>28.73</v>
+        <v>38.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7289</v>
+        <v>8423</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>65.59</v>
+        <v>73.98</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>88.45</v>
+        <v>-24.99</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-22.85</v>
+        <v>98.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>5980</v>
+        <v>6081</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>62.71</v>
+        <v>65.56</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>88.70999999999999</v>
+        <v>78.61</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-26</v>
+        <v>-13.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4325</v>
+        <v>7289</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>59.51</v>
+        <v>63.37</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>137.65</v>
+        <v>22.67</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-78.14</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9756</v>
+        <v>9685</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>41.65</v>
+        <v>-13.94</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>17.34</v>
+        <v>71.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6081</v>
+        <v>4325</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>54.52</v>
+        <v>57.27</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>153.69</v>
+        <v>160.05</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-99.17</v>
+        <v>-102.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>47.13</v>
+        <v>47.45</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.45</v>
+        <v>58.42</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>35.68</v>
+        <v>-10.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>10181</v>
+        <v>9638</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>42.87</v>
+        <v>27.34</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>44.94</v>
+        <v>97.95</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-2.07</v>
+        <v>-70.59999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>9208</v>
+        <v>7809</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>38.56</v>
+        <v>25.55</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-137.78</v>
+        <v>178.62</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>176.34</v>
+        <v>-153.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8767</v>
+        <v>9566</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>37.08</v>
+        <v>17.45</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>66.92</v>
+        <v>115.52</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-29.83</v>
+        <v>-98.06999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>9566</v>
+        <v>8285</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>26.94</v>
+        <v>17.1</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-14.33</v>
+        <v>101.15</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>41.26</v>
+        <v>-84.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8285</v>
+        <v>10181</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>23.33</v>
+        <v>16.78</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>81.73</v>
+        <v>96.58</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-58.4</v>
+        <v>-79.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>7809</v>
+        <v>5256</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>20.82</v>
+        <v>11.51</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>196.06</v>
+        <v>12.02</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-175.24</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9638</v>
+        <v>9206</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>11.36</v>
+        <v>10.98</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>138.51</v>
+        <v>-39.63</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-127.16</v>
+        <v>50.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>904</v>
+        <v>9208</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>6.97</v>
+        <v>10.97</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>49.16</v>
+        <v>-5.91</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-42.19</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9549</v>
+        <v>3234</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>5.65</v>
+        <v>10.51</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>41.35</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-35.7</v>
+        <v>-64.64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7658</v>
+        <v>7808</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.05</v>
+        <v>10.17</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>71.63</v>
+        <v>-47.3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-67.58</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>11399</v>
+        <v>9671</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3.65</v>
+        <v>9.91</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>133.36</v>
+        <v>26.62</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-129.71</v>
+        <v>-16.71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>5256</v>
+        <v>8767</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.75</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>24.54</v>
+        <v>55.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-22.79</v>
+        <v>-45.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9206</v>
+        <v>904</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.55</v>
+        <v>3.08</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>-24.11</v>
+        <v>66.56</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>24.66</v>
+        <v>-63.48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10642</v>
+        <v>7221</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-0.93</v>
+        <v>2.89</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>91.3</v>
+        <v>67.16</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-92.23</v>
+        <v>-64.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9671</v>
+        <v>9549</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-4.37</v>
+        <v>-2.07</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3.31</v>
+        <v>58.53</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-7.68</v>
+        <v>-60.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7808</v>
+        <v>7818</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-11.72</v>
+        <v>-3.99</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-14.83</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>3.11</v>
+        <v>-84.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7221</v>
+        <v>7658</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-11.81</v>
+        <v>-4.98</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>123.48</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-135.29</v>
+        <v>-69.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>3234</v>
+        <v>10642</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-21.83</v>
+        <v>-10.95</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>102.66</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-124.49</v>
+        <v>-81.56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7256</v>
+        <v>11399</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-24.04</v>
+        <v>-11.75</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>193.97</v>
+        <v>142.98</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-218.01</v>
+        <v>-154.73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7818</v>
+        <v>7256</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-27.6</v>
+        <v>-31.69</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-11.53</v>
+        <v>191.23</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-16.07</v>
+        <v>-222.92</v>
       </c>
     </row>
     <row r="40">
@@ -5115,13 +5115,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-69.44</v>
+        <v>-34.32</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-67.64</v>
+        <v>-20.18</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-1.8</v>
+        <v>-14.14</v>
       </c>
     </row>
     <row r="41">
@@ -5214,15 +5214,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1023</v>
+        <v>3620</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -5239,24 +5239,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -5289,11 +5289,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7220</v>
+        <v>7808</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -5314,24 +5314,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -5339,15 +5339,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3875</v>
+        <v>2771</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>1</v>
@@ -5356,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -5364,24 +5364,24 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7808</v>
+        <v>2075</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -5389,24 +5389,24 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9208</v>
+        <v>4967</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -5414,24 +5414,24 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2771</v>
+        <v>3875</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
@@ -5456,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -5464,11 +5464,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2075</v>
+        <v>10633</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -5489,15 +5489,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>10633</v>
+        <v>9208</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2</v>
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -5514,24 +5514,24 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>10664</v>
+        <v>5166</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -5539,11 +5539,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9638</v>
+        <v>858</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -5564,24 +5564,24 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5166</v>
+        <v>9685</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -5589,15 +5589,15 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5980</v>
+        <v>9638</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>2</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -5614,15 +5614,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>858</v>
+        <v>8423</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>2</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -5639,24 +5639,24 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9685</v>
+        <v>5980</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="F19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -5664,15 +5664,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>8423</v>
+        <v>8767</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>2</v>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -5689,15 +5689,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>2</v>
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -5714,15 +5714,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>9549</v>
+        <v>9206</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>2</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -5739,24 +5739,24 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>9756</v>
+        <v>4325</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -5775,13 +5775,13 @@
         <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -5789,24 +5789,24 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9206</v>
+        <v>9549</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="F25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -5814,24 +5814,24 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3234</v>
+        <v>9756</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -5839,11 +5839,11 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7221</v>
+        <v>10642</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -5864,15 +5864,15 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>4325</v>
+        <v>11399</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>3</v>
@@ -5881,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -5889,24 +5889,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>8767</v>
+        <v>7221</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -5914,24 +5914,24 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7256</v>
+        <v>6081</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -5939,15 +5939,15 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10181</v>
+        <v>3234</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>3</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -5964,24 +5964,24 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>11399</v>
+        <v>10181</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -6000,13 +6000,13 @@
         <v>1</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -6014,11 +6014,11 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>6081</v>
+        <v>7256</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -6031,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -6039,24 +6039,24 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>9566</v>
+        <v>7818</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -6064,15 +6064,15 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7809</v>
+        <v>9566</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>5</v>
@@ -6081,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -6089,11 +6089,11 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7818</v>
+        <v>7809</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>228.09</v>
+        <v>212.62</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-58.67</v>
+        <v>-15.86</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>286.76</v>
+        <v>228.49</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>197.03</v>
+        <v>176.96</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>35.55</v>
+        <v>52.41</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>161.48</v>
+        <v>124.55</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6338,13 +6338,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>160.16</v>
+        <v>160.41</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12.26</v>
+        <v>78.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>147.91</v>
+        <v>81.91</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6361,13 +6361,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>156.68</v>
+        <v>150.58</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-16.06</v>
+        <v>-23.63</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>172.73</v>
+        <v>174.21</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6376,21 +6376,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7220</v>
+        <v>1023</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>150.17</v>
+        <v>142.25</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>28.04</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>59.43</v>
+        <v>114.21</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6399,21 +6399,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1023</v>
+        <v>858</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>139.06</v>
+        <v>132.21</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-65.16</v>
+        <v>48.32</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>204.21</v>
+        <v>83.89</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6422,21 +6422,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2075</v>
+        <v>7220</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>120.6</v>
+        <v>125.36</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>127.12</v>
+        <v>101.91</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6.52</v>
+        <v>23.46</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6445,21 +6445,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>858</v>
+        <v>5166</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>120.58</v>
+        <v>116.97</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>131.94</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-11.37</v>
+        <v>103.97</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6468,21 +6468,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5166</v>
+        <v>7656</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>117.92</v>
+        <v>102.42</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>73.97</v>
+        <v>35.78</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>43.95</v>
+        <v>66.64</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6499,13 +6499,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>102.47</v>
+        <v>100.52</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>29.37</v>
+        <v>34.01</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>66.52</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6514,21 +6514,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7656</v>
+        <v>2075</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>101.95</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>31.81</v>
+        <v>82.86</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>70.14</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6537,21 +6537,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8423</v>
+        <v>5980</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>68.31999999999999</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>39.58</v>
+        <v>39.17</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>28.73</v>
+        <v>38.28</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6560,21 +6560,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7289</v>
+        <v>8423</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>65.59</v>
+        <v>73.98</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>88.45</v>
+        <v>-24.99</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-22.85</v>
+        <v>98.97</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6583,21 +6583,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5980</v>
+        <v>6081</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>62.71</v>
+        <v>65.56</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>88.70999999999999</v>
+        <v>78.61</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-26</v>
+        <v>-13.05</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6606,21 +6606,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4325</v>
+        <v>7289</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>59.51</v>
+        <v>63.37</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>137.65</v>
+        <v>22.67</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-78.14</v>
+        <v>40.7</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6629,21 +6629,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9756</v>
+        <v>9685</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>41.65</v>
+        <v>-13.94</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>17.34</v>
+        <v>71.94</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6652,21 +6652,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>6081</v>
+        <v>4325</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>54.52</v>
+        <v>57.27</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>153.69</v>
+        <v>160.05</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-99.17</v>
+        <v>-102.78</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6675,21 +6675,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>47.13</v>
+        <v>47.45</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>11.45</v>
+        <v>58.42</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>35.68</v>
+        <v>-10.97</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6698,21 +6698,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>10181</v>
+        <v>9638</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>42.87</v>
+        <v>27.34</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>44.94</v>
+        <v>97.95</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2.07</v>
+        <v>-70.59999999999999</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6721,21 +6721,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>9208</v>
+        <v>7809</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>38.56</v>
+        <v>25.55</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-137.78</v>
+        <v>178.62</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>176.34</v>
+        <v>-153.07</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6744,21 +6744,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>8767</v>
+        <v>9566</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>37.08</v>
+        <v>17.45</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>66.92</v>
+        <v>115.52</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-29.83</v>
+        <v>-98.06999999999999</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6767,21 +6767,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>9566</v>
+        <v>8285</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>26.94</v>
+        <v>17.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-14.33</v>
+        <v>101.15</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>41.26</v>
+        <v>-84.05</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6790,21 +6790,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>8285</v>
+        <v>10181</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>23.33</v>
+        <v>16.78</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>81.73</v>
+        <v>96.58</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-58.4</v>
+        <v>-79.81</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6813,21 +6813,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>7809</v>
+        <v>5256</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>20.82</v>
+        <v>11.51</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>196.06</v>
+        <v>12.02</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-175.24</v>
+        <v>-0.52</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6836,21 +6836,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9638</v>
+        <v>9206</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>11.36</v>
+        <v>10.98</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>138.51</v>
+        <v>-39.63</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-127.16</v>
+        <v>50.62</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6859,21 +6859,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>904</v>
+        <v>9208</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>6.97</v>
+        <v>10.97</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>49.16</v>
+        <v>-5.91</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-42.19</v>
+        <v>16.88</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6882,21 +6882,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>9549</v>
+        <v>3234</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>5.65</v>
+        <v>10.51</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>41.35</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-35.7</v>
+        <v>-64.64</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6905,21 +6905,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7658</v>
+        <v>7808</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.05</v>
+        <v>10.17</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>71.63</v>
+        <v>-47.3</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-67.58</v>
+        <v>57.47</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6928,21 +6928,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>11399</v>
+        <v>9671</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3.65</v>
+        <v>9.91</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>133.36</v>
+        <v>26.62</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-129.71</v>
+        <v>-16.71</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6951,21 +6951,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5256</v>
+        <v>8767</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1.75</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>24.54</v>
+        <v>55.06</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-22.79</v>
+        <v>-45.6</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6974,21 +6974,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9206</v>
+        <v>904</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.55</v>
+        <v>3.08</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-24.11</v>
+        <v>66.56</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>24.66</v>
+        <v>-63.48</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6997,21 +6997,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>10642</v>
+        <v>7221</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-0.93</v>
+        <v>2.89</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>91.3</v>
+        <v>67.16</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-92.23</v>
+        <v>-64.27</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7020,21 +7020,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9671</v>
+        <v>9549</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-4.37</v>
+        <v>-2.07</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3.31</v>
+        <v>58.53</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-7.68</v>
+        <v>-60.6</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -7043,21 +7043,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7808</v>
+        <v>7818</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-11.72</v>
+        <v>-3.99</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-14.83</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3.11</v>
+        <v>-84.09</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -7066,21 +7066,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7221</v>
+        <v>7658</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-11.81</v>
+        <v>-4.98</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>123.48</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-135.29</v>
+        <v>-69.92</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7089,21 +7089,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>3234</v>
+        <v>10642</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-21.83</v>
+        <v>-10.95</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>102.66</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-124.49</v>
+        <v>-81.56</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -7112,21 +7112,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7256</v>
+        <v>11399</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-24.04</v>
+        <v>-11.75</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>193.97</v>
+        <v>142.98</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-218.01</v>
+        <v>-154.73</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -7135,21 +7135,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>7818</v>
+        <v>7256</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-27.6</v>
+        <v>-31.69</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-11.53</v>
+        <v>191.23</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-16.07</v>
+        <v>-222.92</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -7166,13 +7166,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-69.44</v>
+        <v>-34.32</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-67.64</v>
+        <v>-20.18</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1.8</v>
+        <v>-14.14</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -609,16 +609,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Saint Joseph, Michigan</t>
+          <t>Brighton, Michigan</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -628,127 +628,127 @@
         <v>7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>202.64</v>
+        <v>158.02</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-8.789999999999999</v>
+        <v>59.14</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>211.43</v>
+        <v>98.88</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>128.5</v>
+        <v>129.36</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>128.5</v>
+        <v>129.36</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>1665</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>27.16</v>
+        <v>28.97</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>69.26000000000001</v>
+        <v>79.77</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>32.08</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Brighton, Michigan</t>
+          <t>Saint Joseph, Michigan</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>146.62</v>
+        <v>181.7</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>80.87</v>
+        <v>-17.86</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>65.76000000000001</v>
+        <v>199.56</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>45.04</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>120.09</v>
+        <v>130.31</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>120.09</v>
+        <v>130.31</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1654</v>
+        <v>1666</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>27.43</v>
+        <v>24.54</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>71.43000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>21.23</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4967</v>
+        <v>7656</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Belmont, Michigan</t>
+          <t>Michigan Center, Michigan</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -757,94 +757,94 @@
         <v>28</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>133.98</v>
+        <v>90.05</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.87</v>
+        <v>-14.17</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>117.12</v>
+        <v>104.21</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>68.89</v>
+        <v>50.91</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>112.5</v>
+        <v>80.11</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>112.5</v>
+        <v>80.11</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1643</v>
+        <v>1580</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>24.28</v>
+        <v>10.13</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>62.18</v>
+        <v>48.97</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>26.04</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>7656</v>
+        <v>2075</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>89.04000000000001</v>
+        <v>125.06</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>17.32</v>
+        <v>49.06</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>71.72</v>
+        <v>76</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>50.91</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>81.06</v>
+        <v>127.64</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>81.06</v>
+        <v>127.64</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1582</v>
+        <v>1663</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>9.68</v>
+        <v>24.67</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>48.63</v>
+        <v>72.75</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>22.75</v>
+        <v>30.22</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>27</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>115.06</v>
+        <v>115.72</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.46</v>
+        <v>-7.64</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>111.6</v>
+        <v>123.37</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>71.68000000000001</v>
@@ -937,13 +937,13 @@
         <v>27</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>194.35</v>
+        <v>190.62</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>6.46</v>
+        <v>16.27</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>187.9</v>
+        <v>174.35</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>45.8</v>
@@ -969,16 +969,16 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2075</v>
+        <v>3875</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -994,51 +994,51 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>100.21</v>
+        <v>128.02</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>63.13</v>
+        <v>31.83</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37.08</v>
+        <v>96.19</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>50.66</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>116.95</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>116.95</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1649</v>
+        <v>1592</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>24.31</v>
+        <v>10.23</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>65.95999999999999</v>
+        <v>51.87</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>26.67</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Belmont, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1048,43 +1048,43 @@
         <v>6</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>139.06</v>
+        <v>130.02</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>29.74</v>
+        <v>35.69</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>109.32</v>
+        <v>94.33</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>50.66</v>
+        <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>86.15000000000001</v>
+        <v>112.25</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>86.15000000000001</v>
+        <v>112.25</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1592</v>
+        <v>1643</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>10.23</v>
+        <v>23.83</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>51.87</v>
+        <v>61.46</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>24.04</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="10">
@@ -1105,7 +1105,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>3</v>
@@ -1114,37 +1114,37 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>128.47</v>
+        <v>126.2</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>52.69</v>
+        <v>48.5</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>75.78</v>
+        <v>77.7</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>68.08</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>120.13</v>
+        <v>121.94</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>120.13</v>
+        <v>121.94</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>22.95</v>
+        <v>22.35</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>70.84</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>26.34</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="11">
@@ -1177,13 +1177,13 @@
         <v>24</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>103.9</v>
+        <v>100.26</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>57.65</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>46.25</v>
+        <v>27.09</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>53.52</v>
@@ -1209,62 +1209,62 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7808</v>
+        <v>9208</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Edwardsburg, Michigan</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>12.86</v>
+        <v>31.94</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.55</v>
+        <v>33.62</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>9.31</v>
+        <v>-1.68</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>24.37</v>
+        <v>44.43</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>33.43</v>
+        <v>58.78</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>33.43</v>
+        <v>58.78</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1477</v>
+        <v>1536</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>4.63</v>
+        <v>15.53</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>16.35</v>
+        <v>30.88</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>12.45</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="13">
@@ -1297,13 +1297,13 @@
         <v>23</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>53.58</v>
+        <v>44.97</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-2.71</v>
+        <v>-1.26</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>56.29</v>
+        <v>46.22</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>33.29</v>
@@ -1329,16 +1329,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8423</v>
+        <v>858</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1348,57 +1348,57 @@
         <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>60.63</v>
+        <v>122.56</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-17.16</v>
+        <v>69.53</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>77.79000000000001</v>
+        <v>53.03</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>28.04</v>
+        <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>56.76</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>56.76</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1532</v>
+        <v>1581</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>11.18</v>
+        <v>13.02</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>31.44</v>
+        <v>40.37</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>14.14</v>
+        <v>27.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9208</v>
+        <v>7808</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Edwardsburg, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1417,55 +1417,55 @@
         <v>22</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>27.37</v>
+        <v>17.51</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>36.94</v>
+        <v>32.14</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-9.58</v>
+        <v>-14.62</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>44.43</v>
+        <v>24.37</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>59.01</v>
+        <v>35.2</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>59.01</v>
+        <v>35.2</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1537</v>
+        <v>1482</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>15.49</v>
+        <v>4.17</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>30.97</v>
+        <v>16.5</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>12.55</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>858</v>
+        <v>9756</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>4</v>
@@ -1474,37 +1474,37 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>145.77</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>77.73</v>
+        <v>29.82</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>68.04000000000001</v>
+        <v>43.58</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>55.1</v>
+        <v>29.21</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>84.95</v>
+        <v>56.69</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>84.95</v>
+        <v>56.69</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1590</v>
+        <v>1531</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>14.25</v>
+        <v>6.66</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>43.29</v>
+        <v>35.67</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>27.4</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="17">
@@ -1525,7 +1525,7 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>3</v>
@@ -1534,58 +1534,58 @@
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>19.14</v>
+        <v>19.22</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>33.1</v>
+        <v>30.7</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-13.96</v>
+        <v>-11.48</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>21.07</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>29.18</v>
+        <v>30.99</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>29.18</v>
+        <v>30.99</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>15.67</v>
+        <v>19.43</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>12.4</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8767</v>
+        <v>8423</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>3</v>
@@ -1594,51 +1594,51 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.88</v>
+        <v>65.12</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>73.05</v>
+        <v>14.01</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-50.17</v>
+        <v>51.1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>27.21</v>
+        <v>28.04</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>40.7</v>
+        <v>55.16</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>40.7</v>
+        <v>55.16</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1496</v>
+        <v>1528</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>5.76</v>
+        <v>10.29</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>23.05</v>
+        <v>29.95</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>11.89</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>10642</v>
+        <v>6081</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1654,58 +1654,58 @@
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-3.79</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>26.38</v>
+        <v>68.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-30.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>25.63</v>
+        <v>59.73</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>20.22</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>20.22</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1435</v>
+        <v>1554</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>6.27</v>
+        <v>19</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>7.19</v>
+        <v>28.36</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>6.76</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6081</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>4</v>
@@ -1714,58 +1714,58 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>58.35</v>
+        <v>31.65</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>77.06</v>
+        <v>23.33</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-18.71</v>
+        <v>8.33</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>59.73</v>
+        <v>27.21</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>58.22</v>
+        <v>41.12</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>58.22</v>
+        <v>41.12</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1535</v>
+        <v>1497</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>17.47</v>
+        <v>6.03</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>20.02</v>
+        <v>23.96</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>20.73</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>9756</v>
+        <v>11399</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>4</v>
@@ -1774,58 +1774,58 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>65.5</v>
+        <v>11.76</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>58.94</v>
+        <v>76.87</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>6.56</v>
+        <v>-65.11</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>29.21</v>
+        <v>23.74</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>47.65</v>
+        <v>26.07</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>47.65</v>
+        <v>26.07</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1512</v>
+        <v>1455</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>5.09</v>
+        <v>4.82</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>27.41</v>
+        <v>15.23</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>15.14</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5980</v>
+        <v>9685</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>4</v>
@@ -1834,51 +1834,51 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>73.37</v>
+        <v>40.79</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6.71</v>
+        <v>18.67</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>66.66</v>
+        <v>22.12</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>38.55</v>
+        <v>27.75</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>33.08</v>
+        <v>42.36</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>33.08</v>
+        <v>42.36</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1476</v>
+        <v>1500</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>7.21</v>
+        <v>18.27</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>20.33</v>
+        <v>8.91</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>5.54</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>11399</v>
+        <v>10642</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1888,57 +1888,57 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-11.76</v>
+        <v>-3.62</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>79.87</v>
+        <v>45.62</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-91.62</v>
+        <v>-49.25</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>23.74</v>
+        <v>25.63</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>15.38</v>
+        <v>17.14</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>15.38</v>
+        <v>17.14</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1414</v>
+        <v>1422</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>4.46</v>
+        <v>5.54</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>8.44</v>
+        <v>5.84</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>2.48</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>10181</v>
+        <v>5980</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1954,51 +1954,51 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>33.21</v>
+        <v>60.73</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>51.84</v>
+        <v>47.94</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-18.63</v>
+        <v>12.79</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>23.43</v>
+        <v>38.55</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>23.18</v>
+        <v>34.84</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>23.18</v>
+        <v>34.84</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1445</v>
+        <v>1481</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>7</v>
+        <v>6.74</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>9.9</v>
+        <v>20.49</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>6.28</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9685</v>
+        <v>3234</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -2008,124 +2008,124 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>39.94</v>
+        <v>23.23</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.7</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>29.24</v>
+        <v>-45.47</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>27.75</v>
+        <v>22.62</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>40.56</v>
+        <v>23.91</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>40.56</v>
+        <v>23.91</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1495</v>
+        <v>1448</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.86</v>
+        <v>5.22</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>5.15</v>
+        <v>13.58</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>16.54</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5256</v>
+        <v>4325</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>10.11</v>
+        <v>55.81</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21.13</v>
+        <v>164.72</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-11.01</v>
+        <v>-108.91</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>35.18</v>
+        <v>32.52</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>19.01</v>
+        <v>40.01</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>19.01</v>
+        <v>40.01</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1430</v>
+        <v>1494</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>5.17</v>
+        <v>10.85</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>11.01</v>
+        <v>19.89</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>2.83</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>4325</v>
+        <v>10181</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>6</v>
@@ -2134,51 +2134,51 @@
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>58.68</v>
+        <v>28.15</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>196.18</v>
+        <v>52.33</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-137.5</v>
+        <v>-24.18</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>32.52</v>
+        <v>23.43</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>38.63</v>
+        <v>20.1</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>38.63</v>
+        <v>20.1</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1491</v>
+        <v>1434</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>11.03</v>
+        <v>6.27</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>19.32</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9638</v>
+        <v>7221</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -2188,57 +2188,57 @@
         <v>3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.51</v>
+        <v>11.43</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>62.41</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-36.91</v>
+        <v>-83.03</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>22.93</v>
+        <v>8.82</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>24.42</v>
+        <v>22.06</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>24.42</v>
+        <v>22.06</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1450</v>
+        <v>1441</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>7.99</v>
+        <v>6.01</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>10.93</v>
+        <v>7.88</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>5.5</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7221</v>
+        <v>7256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -2248,117 +2248,117 @@
         <v>3</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>14.84</v>
+        <v>-8.81</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>72.08</v>
+        <v>123.5</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-57.23</v>
+        <v>-132.31</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.82</v>
+        <v>25.23</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>22.31</v>
+        <v>12.34</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>22.31</v>
+        <v>12.34</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1442</v>
+        <v>1400</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.46</v>
+        <v>5.35</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>8.59</v>
+        <v>3.53</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>7.26</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9549</v>
+        <v>9638</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-12.68</v>
+        <v>32.65</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>66.18000000000001</v>
+        <v>59.71</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-78.86</v>
+        <v>-27.06</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>17.6</v>
+        <v>22.93</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>19.8</v>
+        <v>23.39</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>19.8</v>
+        <v>23.39</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1433</v>
+        <v>1446</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>8.09</v>
+        <v>7.53</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>9.609999999999999</v>
+        <v>10.51</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>2.1</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>10664</v>
+        <v>5256</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -2368,57 +2368,57 @@
         <v>3</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-27.94</v>
+        <v>10</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>31.11</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-59.05</v>
+        <v>-56.17</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>21.7</v>
+        <v>35.18</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>19.92</v>
+        <v>17.69</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>19.92</v>
+        <v>17.69</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1433</v>
+        <v>1424</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>8.140000000000001</v>
+        <v>3.97</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>2.14</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3234</v>
+        <v>9566</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -2428,57 +2428,57 @@
         <v>3</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1.49</v>
+        <v>4.12</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>80.02</v>
+        <v>64.23</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-78.53</v>
+        <v>-60.11</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>22.62</v>
+        <v>39.97</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>13.21</v>
+        <v>21.25</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>13.21</v>
+        <v>21.25</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1404</v>
+        <v>1438</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>4.86</v>
+        <v>4.16</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>6.79</v>
+        <v>8.57</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>1.57</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>904</v>
+        <v>9549</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -2488,43 +2488,43 @@
         <v>2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.18</v>
+        <v>-3.41</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>48.3</v>
+        <v>46.86</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-48.11</v>
+        <v>-50.27</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>27.91</v>
+        <v>17.6</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>-0.74</v>
+        <v>20.44</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>-0.74</v>
+        <v>20.44</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1328</v>
+        <v>1435</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>5.37</v>
+        <v>7.46</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>-4.61</v>
+        <v>9.99</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>-1.5</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="34">
@@ -2548,64 +2548,64 @@
         <v>2</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3.67</v>
+        <v>-0.19</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>88.09999999999999</v>
+        <v>107.73</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-84.43000000000001</v>
+        <v>-107.92</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>32.45</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22.92</v>
+        <v>22.68</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>22.92</v>
+        <v>22.68</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>7.02</v>
+        <v>6.57</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>6.98</v>
+        <v>6.27</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>8.92</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9566</v>
+        <v>10664</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
         <v>34</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>6</v>
@@ -2614,58 +2614,58 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>21.67</v>
+        <v>-29.97</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>94.14</v>
+        <v>53.62</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-72.45999999999999</v>
+        <v>-83.59</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>39.97</v>
+        <v>21.7</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>25.52</v>
+        <v>17.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>25.52</v>
+        <v>17.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1454</v>
+        <v>1423</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>5.39</v>
+        <v>6.79</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>11.49</v>
+        <v>7.73</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7809</v>
+        <v>904</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>6</v>
@@ -2674,97 +2674,97 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30.51</v>
+        <v>0.23</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>158.88</v>
+        <v>60.46</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-128.36</v>
+        <v>-60.23</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>23.83</v>
+        <v>27.91</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>31.58</v>
+        <v>-0.1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>31.58</v>
+        <v>-0.1</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1472</v>
+        <v>1332</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>4.05</v>
+        <v>4.74</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>13.49</v>
+        <v>-4.23</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>14.03</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7256</v>
+        <v>7809</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
         <v>36</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>-17.66</v>
+        <v>36.95</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>165.6</v>
+        <v>146.99</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-183.27</v>
+        <v>-110.03</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>25.23</v>
+        <v>23.83</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>13.52</v>
+        <v>36.62</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>13.52</v>
+        <v>36.62</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1406</v>
+        <v>1486</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>4.86</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>3.28</v>
+        <v>18.85</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>5.38</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="38">
@@ -2788,57 +2788,57 @@
         <v>1</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-13.53</v>
+        <v>-2.67</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>42.2</v>
+        <v>28.2</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-55.73</v>
+        <v>-30.87</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>14.34</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7.33</v>
+        <v>9.35</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>7.33</v>
+        <v>9.35</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>3.99</v>
+        <v>3.19</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>5.32</v>
+        <v>6.27</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-1.98</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>8285</v>
+        <v>9671</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -2848,64 +2848,64 @@
         <v>1</v>
       </c>
       <c r="F39" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="I39" s="3" t="n">
-        <v>16.23</v>
+        <v>-2.41</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>87.73</v>
+        <v>27.78</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-71.5</v>
+        <v>-30.2</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>39.07</v>
+        <v>27.39</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.3</v>
+        <v>27.88</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>19.3</v>
+        <v>27.88</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1431</v>
+        <v>1461</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>3.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>10.29</v>
+        <v>15.26</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>5.91</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>7</v>
@@ -2914,37 +2914,37 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-10.51</v>
+        <v>18.26</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>31.18</v>
+        <v>122.36</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-41.69</v>
+        <v>-104.1</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>27.39</v>
+        <v>39.07</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>21.81</v>
+        <v>17.71</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>21.81</v>
+        <v>17.71</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1441</v>
+        <v>1424</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>2.21</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>2.64</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="41">
@@ -3139,115 +3139,115 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>128.5</v>
+        <v>130.31</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>128.5</v>
+        <v>130.31</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>27.16</v>
+        <v>24.54</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>69.26000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>32.08</v>
+        <v>33.64</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1023</v>
+        <v>7220</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>68.08</v>
+        <v>45.04</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>120.13</v>
+        <v>129.36</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>120.13</v>
+        <v>129.36</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>22.95</v>
+        <v>28.97</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>70.84</v>
+        <v>79.77</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>26.34</v>
+        <v>20.62</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1653</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>7220</v>
+        <v>2075</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>45.04</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>120.09</v>
+        <v>127.64</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>120.09</v>
+        <v>127.64</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>27.43</v>
+        <v>24.67</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>71.43000000000001</v>
+        <v>72.75</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>21.23</v>
+        <v>30.22</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1654</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2075</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>116.95</v>
+        <v>121.94</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>116.95</v>
+        <v>121.94</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>24.31</v>
+        <v>22.35</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>65.95999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26.67</v>
+        <v>24.99</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1649</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="7">
@@ -3263,19 +3263,19 @@
         <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>112.5</v>
+        <v>112.25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>112.5</v>
+        <v>112.25</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>24.28</v>
+        <v>23.83</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>62.18</v>
+        <v>61.46</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>26.04</v>
+        <v>26.96</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1643</v>
@@ -3356,22 +3356,22 @@
         <v>55.1</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>84.95</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>84.95</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>14.25</v>
+        <v>13.02</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>43.29</v>
+        <v>40.37</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>27.4</v>
+        <v>27.28</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1590</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="11">
@@ -3387,22 +3387,22 @@
         <v>50.91</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>81.06</v>
+        <v>80.11</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>81.06</v>
+        <v>80.11</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9.68</v>
+        <v>10.13</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>48.63</v>
+        <v>48.97</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>22.75</v>
+        <v>21.02</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="12">
@@ -3438,188 +3438,188 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>9208</v>
+        <v>6081</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>44.43</v>
+        <v>59.73</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>59.01</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>59.01</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>15.49</v>
+        <v>19</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>30.97</v>
+        <v>28.36</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.55</v>
+        <v>20.13</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1537</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6081</v>
+        <v>9208</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>59.73</v>
+        <v>44.43</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>58.22</v>
+        <v>58.78</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>58.22</v>
+        <v>58.78</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>17.47</v>
+        <v>15.53</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20.02</v>
+        <v>30.88</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20.73</v>
+        <v>12.36</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>9756</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>29.21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>56.76</v>
+        <v>56.69</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>56.76</v>
+        <v>56.69</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>11.18</v>
+        <v>6.66</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>31.44</v>
+        <v>35.67</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>14.14</v>
+        <v>14.36</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>29.21</v>
+        <v>28.04</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>47.65</v>
+        <v>55.16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>47.65</v>
+        <v>55.16</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>5.09</v>
+        <v>10.29</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>27.41</v>
+        <v>29.95</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>15.14</v>
+        <v>14.92</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1512</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>8767</v>
+        <v>9685</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.21</v>
+        <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>40.7</v>
+        <v>42.36</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>40.7</v>
+        <v>42.36</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.76</v>
+        <v>18.27</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>23.05</v>
+        <v>8.91</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>11.89</v>
+        <v>15.19</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1496</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9685</v>
+        <v>8767</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>27.75</v>
+        <v>27.21</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>40.56</v>
+        <v>41.12</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>40.56</v>
+        <v>41.12</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>18.86</v>
+        <v>6.03</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5.15</v>
+        <v>23.96</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>16.54</v>
+        <v>11.13</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1495</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="19">
@@ -3635,53 +3635,53 @@
         <v>32.52</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>38.63</v>
+        <v>40.01</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>38.63</v>
+        <v>40.01</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>11.03</v>
+        <v>10.85</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.32</v>
+        <v>19.89</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1491</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7289</v>
+        <v>7809</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>33.29</v>
+        <v>23.83</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>34.23</v>
+        <v>36.62</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>34.23</v>
+        <v>36.62</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>12.91</v>
+        <v>2.2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>9.4</v>
+        <v>18.85</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>11.91</v>
+        <v>15.57</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1479</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="21">
@@ -3697,22 +3697,22 @@
         <v>24.37</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>33.43</v>
+        <v>35.2</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>33.43</v>
+        <v>35.2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4.63</v>
+        <v>4.17</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>16.35</v>
+        <v>16.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>12.45</v>
+        <v>14.53</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1477</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="22">
@@ -3728,84 +3728,84 @@
         <v>38.55</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>33.08</v>
+        <v>34.84</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>33.08</v>
+        <v>34.84</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>7.21</v>
+        <v>6.74</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20.33</v>
+        <v>20.49</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>5.54</v>
+        <v>7.62</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1476</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>5501</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>31.87</v>
+        <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>31.87</v>
+        <v>34.23</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>31.87</v>
+        <v>34.23</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6.95</v>
+        <v>12.91</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>17.02</v>
+        <v>9.4</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>7.9</v>
+        <v>11.91</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1476</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7809</v>
+        <v>5501</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>23.83</v>
+        <v>31.87</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>31.58</v>
+        <v>31.87</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>31.58</v>
+        <v>31.87</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>4.05</v>
+        <v>6.95</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>13.49</v>
+        <v>17.02</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>14.03</v>
+        <v>7.9</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1472</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="25">
@@ -3821,205 +3821,205 @@
         <v>21.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>29.18</v>
+        <v>30.99</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>29.18</v>
+        <v>30.99</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>15.67</v>
+        <v>19.43</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.4</v>
+        <v>11.05</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1465</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9566</v>
+        <v>9671</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>39.97</v>
+        <v>27.39</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>25.52</v>
+        <v>27.88</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>25.52</v>
+        <v>27.88</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>5.39</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.49</v>
+        <v>15.26</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>4.32</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1454</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9638</v>
+        <v>11399</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>22.93</v>
+        <v>23.74</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>24.42</v>
+        <v>26.07</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>24.42</v>
+        <v>26.07</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7.99</v>
+        <v>4.82</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>10.93</v>
+        <v>15.23</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.5</v>
+        <v>6.03</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1450</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10181</v>
+        <v>3234</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>23.43</v>
+        <v>22.62</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>23.18</v>
+        <v>23.91</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>23.18</v>
+        <v>23.91</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>7</v>
+        <v>5.22</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9.9</v>
+        <v>13.58</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6.28</v>
+        <v>5.12</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1445</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7818</v>
+        <v>9638</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>32.45</v>
+        <v>22.93</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>22.92</v>
+        <v>23.39</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>22.92</v>
+        <v>23.39</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.02</v>
+        <v>7.53</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>6.98</v>
+        <v>10.51</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8.92</v>
+        <v>5.36</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7221</v>
+        <v>7818</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>8.82</v>
+        <v>32.45</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>22.31</v>
+        <v>22.68</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.31</v>
+        <v>22.68</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6.46</v>
+        <v>6.57</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8.59</v>
+        <v>6.27</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>7.26</v>
+        <v>9.84</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1442</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9671</v>
+        <v>7221</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>27.39</v>
+        <v>8.82</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>21.81</v>
+        <v>22.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>21.81</v>
+        <v>22.06</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>6.01</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>9.470000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2.64</v>
+        <v>8.17</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1441</v>
@@ -4027,95 +4027,95 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>10642</v>
+        <v>9566</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>25.63</v>
+        <v>39.97</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>20.22</v>
+        <v>21.25</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>20.22</v>
+        <v>21.25</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>6.27</v>
+        <v>4.16</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7.19</v>
+        <v>8.57</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6.76</v>
+        <v>8.52</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1435</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10664</v>
+        <v>9549</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>21.7</v>
+        <v>17.6</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>19.92</v>
+        <v>20.44</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.92</v>
+        <v>20.44</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>8.140000000000001</v>
+        <v>7.46</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.14</v>
+        <v>2.99</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1433</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9549</v>
+        <v>10181</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>17.6</v>
+        <v>23.43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>8.09</v>
+        <v>6.27</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>9.609999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>2.1</v>
+        <v>5.28</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="35">
@@ -4131,22 +4131,22 @@
         <v>39.07</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>19.3</v>
+        <v>17.71</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.3</v>
+        <v>17.71</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3.1</v>
+        <v>2.21</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>5.91</v>
+        <v>6.7</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1431</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="36">
@@ -4162,115 +4162,115 @@
         <v>35.18</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>19.01</v>
+        <v>17.69</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>19.01</v>
+        <v>17.69</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.17</v>
+        <v>3.97</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>11.01</v>
+        <v>9.81</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>2.83</v>
+        <v>3.91</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1430</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>11399</v>
+        <v>10664</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.74</v>
+        <v>21.7</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>15.38</v>
+        <v>17.3</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>15.38</v>
+        <v>17.3</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4.46</v>
+        <v>6.79</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>8.44</v>
+        <v>7.73</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1414</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7256</v>
+        <v>10642</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25.23</v>
+        <v>25.63</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>13.52</v>
+        <v>17.14</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.52</v>
+        <v>17.14</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4.86</v>
+        <v>5.54</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3.28</v>
+        <v>5.84</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>5.38</v>
+        <v>5.76</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1406</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>3234</v>
+        <v>7256</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>22.62</v>
+        <v>25.23</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>13.21</v>
+        <v>12.34</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.21</v>
+        <v>12.34</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4.86</v>
+        <v>5.35</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>6.79</v>
+        <v>3.53</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.57</v>
+        <v>3.47</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1404</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="40">
@@ -4286,22 +4286,22 @@
         <v>14.34</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7.33</v>
+        <v>9.35</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>7.33</v>
+        <v>9.35</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>3.99</v>
+        <v>3.19</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5.32</v>
+        <v>6.27</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-1.98</v>
+        <v>-0.11</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1375</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="41">
@@ -4317,22 +4317,22 @@
         <v>27.91</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.1</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.1</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>5.37</v>
+        <v>4.74</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-4.61</v>
+        <v>-4.23</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-1.5</v>
+        <v>-0.61</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1328</v>
+        <v>1332</v>
       </c>
     </row>
   </sheetData>
@@ -4385,40 +4385,40 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3620</v>
+        <v>10633</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>202.64</v>
+        <v>190.62</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-8.789999999999999</v>
+        <v>16.27</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>211.43</v>
+        <v>174.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>10633</v>
+        <v>3620</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>194.35</v>
+        <v>181.7</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6.46</v>
+        <v>-17.86</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>187.9</v>
+        <v>199.56</v>
       </c>
     </row>
     <row r="4">
@@ -4431,32 +4431,32 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>146.62</v>
+        <v>158.02</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>80.87</v>
+        <v>59.14</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>65.76000000000001</v>
+        <v>98.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>858</v>
+        <v>4967</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>145.77</v>
+        <v>130.02</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>77.73</v>
+        <v>35.69</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>68.04000000000001</v>
+        <v>94.33</v>
       </c>
     </row>
     <row r="6">
@@ -4469,108 +4469,108 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>139.06</v>
+        <v>128.02</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>29.74</v>
+        <v>31.83</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>109.32</v>
+        <v>96.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>133.98</v>
+        <v>126.2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>16.87</v>
+        <v>48.5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>117.12</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>128.47</v>
+        <v>125.06</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>52.69</v>
+        <v>49.06</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>75.78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5166</v>
+        <v>858</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>115.06</v>
+        <v>122.56</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3.46</v>
+        <v>69.53</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>111.6</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>103.9</v>
+        <v>115.72</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>57.65</v>
+        <v>-7.64</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46.25</v>
+        <v>123.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2075</v>
+        <v>2771</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>100.21</v>
+        <v>100.26</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>63.13</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>37.08</v>
+        <v>27.09</v>
       </c>
     </row>
     <row r="12">
@@ -4583,51 +4583,51 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>89.04000000000001</v>
+        <v>90.05</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>17.32</v>
+        <v>-14.17</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>71.72</v>
+        <v>104.21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>5980</v>
+        <v>9756</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>73.37</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>6.71</v>
+        <v>29.82</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>66.66</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>65.5</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>58.94</v>
+        <v>68.3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6.56</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4640,51 +4640,51 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>60.63</v>
+        <v>65.12</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-17.16</v>
+        <v>14.01</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>77.79000000000001</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4325</v>
+        <v>5980</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>58.68</v>
+        <v>60.73</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>196.18</v>
+        <v>47.94</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-137.5</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>6081</v>
+        <v>4325</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>58.35</v>
+        <v>55.81</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>77.06</v>
+        <v>164.72</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-18.71</v>
+        <v>-108.91</v>
       </c>
     </row>
     <row r="18">
@@ -4697,13 +4697,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>53.58</v>
+        <v>44.97</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-2.71</v>
+        <v>-1.26</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>56.29</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="19">
@@ -4716,51 +4716,51 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>39.94</v>
+        <v>40.79</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>10.7</v>
+        <v>18.67</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>29.24</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>10181</v>
+        <v>7809</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>33.21</v>
+        <v>36.95</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>51.84</v>
+        <v>146.99</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-18.63</v>
+        <v>-110.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7809</v>
+        <v>9638</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>30.51</v>
+        <v>32.65</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>158.88</v>
+        <v>59.71</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-128.36</v>
+        <v>-27.06</v>
       </c>
     </row>
     <row r="22">
@@ -4773,70 +4773,70 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>27.37</v>
+        <v>31.94</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>36.94</v>
+        <v>33.62</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-9.58</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>9638</v>
+        <v>8767</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>25.51</v>
+        <v>31.65</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>62.41</v>
+        <v>23.33</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-36.91</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8767</v>
+        <v>10181</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>22.88</v>
+        <v>28.15</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>73.05</v>
+        <v>52.33</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-50.17</v>
+        <v>-24.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9566</v>
+        <v>3234</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>21.67</v>
+        <v>23.23</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>94.14</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-72.45999999999999</v>
+        <v>-45.47</v>
       </c>
     </row>
     <row r="26">
@@ -4849,13 +4849,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>19.14</v>
+        <v>19.22</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>33.1</v>
+        <v>30.7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-13.96</v>
+        <v>-11.48</v>
       </c>
     </row>
     <row r="27">
@@ -4868,108 +4868,108 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>16.23</v>
+        <v>18.26</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>87.73</v>
+        <v>122.36</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-71.5</v>
+        <v>-104.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7221</v>
+        <v>7808</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>14.84</v>
+        <v>17.51</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>72.08</v>
+        <v>32.14</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-57.23</v>
+        <v>-14.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7808</v>
+        <v>11399</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12.86</v>
+        <v>11.76</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.55</v>
+        <v>76.87</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>9.31</v>
+        <v>-65.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5256</v>
+        <v>7221</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>10.11</v>
+        <v>11.43</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>21.13</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-11.01</v>
+        <v>-83.03</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7818</v>
+        <v>5256</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>3.67</v>
+        <v>10</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-84.43000000000001</v>
+        <v>-56.17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3234</v>
+        <v>9566</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.49</v>
+        <v>4.12</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>80.02</v>
+        <v>64.23</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-78.53</v>
+        <v>-60.11</v>
       </c>
     </row>
     <row r="33">
@@ -4982,32 +4982,32 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>48.3</v>
+        <v>60.46</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-48.11</v>
+        <v>-60.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10642</v>
+        <v>7818</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-3.79</v>
+        <v>-0.19</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>26.38</v>
+        <v>107.73</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-30.18</v>
+        <v>-107.92</v>
       </c>
     </row>
     <row r="35">
@@ -5020,32 +5020,32 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-10.51</v>
+        <v>-2.41</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>31.18</v>
+        <v>27.78</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-41.69</v>
+        <v>-30.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>11399</v>
+        <v>7658</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-11.76</v>
+        <v>-2.67</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>79.87</v>
+        <v>28.2</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-91.62</v>
+        <v>-30.87</v>
       </c>
     </row>
     <row r="37">
@@ -5058,32 +5058,32 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-12.68</v>
+        <v>-3.41</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>66.18000000000001</v>
+        <v>46.86</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-78.86</v>
+        <v>-50.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7658</v>
+        <v>10642</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-13.53</v>
+        <v>-3.62</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>42.2</v>
+        <v>45.62</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-55.73</v>
+        <v>-49.25</v>
       </c>
     </row>
     <row r="39">
@@ -5096,13 +5096,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-17.66</v>
+        <v>-8.81</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>165.6</v>
+        <v>123.5</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-183.27</v>
+        <v>-132.31</v>
       </c>
     </row>
     <row r="40">
@@ -5115,13 +5115,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-27.94</v>
+        <v>-29.97</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>31.11</v>
+        <v>53.62</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-59.05</v>
+        <v>-83.59</v>
       </c>
     </row>
     <row r="41">
@@ -5214,24 +5214,24 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -5239,24 +5239,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -5264,18 +5264,18 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4967</v>
+        <v>7656</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -5289,24 +5289,24 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7656</v>
+        <v>2075</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -5364,11 +5364,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2075</v>
+        <v>3875</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -5381,7 +5381,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -5389,24 +5389,24 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
@@ -5431,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -5464,24 +5464,24 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7808</v>
+        <v>9208</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -5514,24 +5514,24 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>8423</v>
+        <v>858</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -5539,11 +5539,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9208</v>
+        <v>7808</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -5564,15 +5564,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>858</v>
+        <v>9756</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>4</v>
@@ -5581,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>3</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -5614,15 +5614,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>8767</v>
+        <v>8423</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>3</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -5639,11 +5639,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>10642</v>
+        <v>6081</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -5664,15 +5664,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>6081</v>
+        <v>8767</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>4</v>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5689,15 +5689,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>9756</v>
+        <v>11399</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>4</v>
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -5714,15 +5714,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>5980</v>
+        <v>9685</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>4</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -5739,24 +5739,24 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>11399</v>
+        <v>10642</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -5764,11 +5764,11 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10181</v>
+        <v>5980</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -5789,24 +5789,24 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9685</v>
+        <v>3234</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -5814,24 +5814,24 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>5256</v>
+        <v>4325</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -5839,15 +5839,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>4325</v>
+        <v>10181</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>6</v>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -5864,24 +5864,24 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>9638</v>
+        <v>7221</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -5889,24 +5889,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7221</v>
+        <v>7256</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -5914,24 +5914,24 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9549</v>
+        <v>9638</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -5939,24 +5939,24 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10664</v>
+        <v>5256</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -5964,24 +5964,24 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3234</v>
+        <v>9566</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -5989,24 +5989,24 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>904</v>
+        <v>9549</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -6025,13 +6025,13 @@
         <v>2</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
@@ -6039,15 +6039,15 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>9566</v>
+        <v>10664</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>6</v>
@@ -6056,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
@@ -6064,15 +6064,15 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7809</v>
+        <v>904</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>6</v>
@@ -6081,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -6089,24 +6089,24 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7256</v>
+        <v>7809</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -6125,13 +6125,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -6139,24 +6139,24 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>8285</v>
+        <v>9671</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
         <v>6</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -6164,15 +6164,15 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>7</v>
@@ -6181,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -6284,21 +6284,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3620</v>
+        <v>10633</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>202.64</v>
+        <v>190.62</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-8.789999999999999</v>
+        <v>16.27</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>211.43</v>
+        <v>174.35</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6307,21 +6307,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10633</v>
+        <v>3620</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>194.35</v>
+        <v>181.7</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6.46</v>
+        <v>-17.86</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>187.9</v>
+        <v>199.56</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6338,13 +6338,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>146.62</v>
+        <v>158.02</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>80.87</v>
+        <v>59.14</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>65.76000000000001</v>
+        <v>98.88</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6353,21 +6353,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>858</v>
+        <v>4967</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>145.77</v>
+        <v>130.02</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>77.73</v>
+        <v>35.69</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>68.04000000000001</v>
+        <v>94.33</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6384,13 +6384,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>139.06</v>
+        <v>128.02</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29.74</v>
+        <v>31.83</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>109.32</v>
+        <v>96.19</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6399,21 +6399,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>133.98</v>
+        <v>126.2</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>16.87</v>
+        <v>48.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>117.12</v>
+        <v>77.7</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6422,21 +6422,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>128.47</v>
+        <v>125.06</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>52.69</v>
+        <v>49.06</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>75.78</v>
+        <v>76</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6445,21 +6445,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5166</v>
+        <v>858</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>115.06</v>
+        <v>122.56</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3.46</v>
+        <v>69.53</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>111.6</v>
+        <v>53.03</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6468,21 +6468,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>103.9</v>
+        <v>115.72</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>57.65</v>
+        <v>-7.64</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46.25</v>
+        <v>123.37</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6491,21 +6491,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2075</v>
+        <v>2771</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>100.21</v>
+        <v>100.26</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>63.13</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>37.08</v>
+        <v>27.09</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6522,13 +6522,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>89.04000000000001</v>
+        <v>90.05</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>17.32</v>
+        <v>-14.17</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>71.72</v>
+        <v>104.21</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6537,21 +6537,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5980</v>
+        <v>9756</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>73.37</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>6.71</v>
+        <v>29.82</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>66.66</v>
+        <v>43.58</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6560,21 +6560,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>65.5</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>58.94</v>
+        <v>68.3</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6591,13 +6591,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>60.63</v>
+        <v>65.12</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-17.16</v>
+        <v>14.01</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>77.79000000000001</v>
+        <v>51.1</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6606,21 +6606,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4325</v>
+        <v>5980</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>58.68</v>
+        <v>60.73</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>196.18</v>
+        <v>47.94</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-137.5</v>
+        <v>12.79</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6629,21 +6629,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6081</v>
+        <v>4325</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>58.35</v>
+        <v>55.81</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>77.06</v>
+        <v>164.72</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-18.71</v>
+        <v>-108.91</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6660,13 +6660,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>53.58</v>
+        <v>44.97</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-2.71</v>
+        <v>-1.26</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>56.29</v>
+        <v>46.22</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>39.94</v>
+        <v>40.79</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>10.7</v>
+        <v>18.67</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>29.24</v>
+        <v>22.12</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6698,21 +6698,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>10181</v>
+        <v>7809</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>33.21</v>
+        <v>36.95</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>51.84</v>
+        <v>146.99</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-18.63</v>
+        <v>-110.03</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6721,21 +6721,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7809</v>
+        <v>9638</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.51</v>
+        <v>32.65</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>158.88</v>
+        <v>59.71</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-128.36</v>
+        <v>-27.06</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>27.37</v>
+        <v>31.94</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>36.94</v>
+        <v>33.62</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-9.58</v>
+        <v>-1.68</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6767,21 +6767,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>9638</v>
+        <v>8767</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>25.51</v>
+        <v>31.65</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>62.41</v>
+        <v>23.33</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-36.91</v>
+        <v>8.33</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6790,21 +6790,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>8767</v>
+        <v>10181</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>22.88</v>
+        <v>28.15</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>73.05</v>
+        <v>52.33</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-50.17</v>
+        <v>-24.18</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6813,21 +6813,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9566</v>
+        <v>3234</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>21.67</v>
+        <v>23.23</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>94.14</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-72.45999999999999</v>
+        <v>-45.47</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6844,13 +6844,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>19.14</v>
+        <v>19.22</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>33.1</v>
+        <v>30.7</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-13.96</v>
+        <v>-11.48</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6867,13 +6867,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>16.23</v>
+        <v>18.26</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>87.73</v>
+        <v>122.36</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-71.5</v>
+        <v>-104.1</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6882,21 +6882,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7221</v>
+        <v>7808</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>14.84</v>
+        <v>17.51</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>72.08</v>
+        <v>32.14</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-57.23</v>
+        <v>-14.62</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6905,21 +6905,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7808</v>
+        <v>11399</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>12.86</v>
+        <v>11.76</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.55</v>
+        <v>76.87</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.31</v>
+        <v>-65.11</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6928,21 +6928,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5256</v>
+        <v>7221</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>10.11</v>
+        <v>11.43</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.13</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-11.01</v>
+        <v>-83.03</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6951,21 +6951,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7818</v>
+        <v>5256</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.67</v>
+        <v>10</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-84.43000000000001</v>
+        <v>-56.17</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6974,21 +6974,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3234</v>
+        <v>9566</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.49</v>
+        <v>4.12</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>80.02</v>
+        <v>64.23</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-78.53</v>
+        <v>-60.11</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -7005,13 +7005,13 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>48.3</v>
+        <v>60.46</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-48.11</v>
+        <v>-60.23</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7020,21 +7020,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>10642</v>
+        <v>7818</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-3.79</v>
+        <v>-0.19</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>26.38</v>
+        <v>107.73</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-30.18</v>
+        <v>-107.92</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -7051,13 +7051,13 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-10.51</v>
+        <v>-2.41</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>31.18</v>
+        <v>27.78</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-41.69</v>
+        <v>-30.2</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -7066,21 +7066,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>11399</v>
+        <v>7658</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-11.76</v>
+        <v>-2.67</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>79.87</v>
+        <v>28.2</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-91.62</v>
+        <v>-30.87</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7097,13 +7097,13 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-12.68</v>
+        <v>-3.41</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>66.18000000000001</v>
+        <v>46.86</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-78.86</v>
+        <v>-50.27</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -7112,21 +7112,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7658</v>
+        <v>10642</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-13.53</v>
+        <v>-3.62</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>42.2</v>
+        <v>45.62</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-55.73</v>
+        <v>-49.25</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -7143,13 +7143,13 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-17.66</v>
+        <v>-8.81</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>165.6</v>
+        <v>123.5</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-183.27</v>
+        <v>-132.31</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -7166,13 +7166,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-27.94</v>
+        <v>-29.97</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>31.11</v>
+        <v>53.62</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-59.05</v>
+        <v>-83.59</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -655,7 +655,7 @@
         <v>129.36</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>28.97</v>
@@ -775,7 +775,7 @@
         <v>80.11</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>10.13</v>
@@ -835,7 +835,7 @@
         <v>127.64</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>24.67</v>
@@ -895,7 +895,7 @@
         <v>109.88</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>20.41</v>
@@ -955,7 +955,7 @@
         <v>137.46</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>26.22</v>
@@ -1015,7 +1015,7 @@
         <v>86.15000000000001</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>10.23</v>
@@ -1075,7 +1075,7 @@
         <v>112.25</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>23.83</v>
@@ -1135,7 +1135,7 @@
         <v>121.94</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>22.35</v>
@@ -1195,7 +1195,7 @@
         <v>75.88</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>6.92</v>
@@ -1255,7 +1255,7 @@
         <v>58.78</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>15.53</v>
@@ -1375,7 +1375,7 @@
         <v>80.68000000000001</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>13.02</v>
@@ -1675,7 +1675,7 @@
         <v>67.48999999999999</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>19</v>
@@ -1735,7 +1735,7 @@
         <v>41.12</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>6.03</v>
@@ -1855,7 +1855,7 @@
         <v>42.36</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>18.27</v>
@@ -2755,7 +2755,7 @@
         <v>36.62</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>2.2</v>
@@ -3001,26 +3001,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L41" s="3" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>1476</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>17.02</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>7.9</v>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3123,7 +3137,7 @@
         <v>34.66</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="3">
@@ -3185,7 +3199,7 @@
         <v>20.62</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="5">
@@ -3216,7 +3230,7 @@
         <v>30.22</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="6">
@@ -3247,7 +3261,7 @@
         <v>24.99</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="7">
@@ -3278,7 +3292,7 @@
         <v>26.96</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="8">
@@ -3309,7 +3323,7 @@
         <v>24.36</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="9">
@@ -3340,7 +3354,7 @@
         <v>24.04</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="10">
@@ -3371,7 +3385,7 @@
         <v>27.28</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="11">
@@ -3402,7 +3416,7 @@
         <v>21.02</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="12">
@@ -3433,7 +3447,7 @@
         <v>21.85</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="13">
@@ -3464,7 +3478,7 @@
         <v>20.13</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="14">
@@ -3495,7 +3509,7 @@
         <v>12.36</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="15">
@@ -3588,7 +3602,7 @@
         <v>15.19</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="18">
@@ -3619,7 +3633,7 @@
         <v>11.13</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="19">
@@ -3681,7 +3695,7 @@
         <v>15.57</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="21">
@@ -3779,371 +3793,371 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5501</v>
+        <v>9206</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>31.87</v>
+        <v>21.07</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>31.87</v>
+        <v>30.99</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>31.87</v>
+        <v>30.99</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6.95</v>
+        <v>0.51</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>17.02</v>
+        <v>19.43</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>7.9</v>
+        <v>11.05</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1476</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9206</v>
+        <v>9671</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>21.07</v>
+        <v>27.39</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>30.99</v>
+        <v>27.88</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>30.99</v>
+        <v>27.88</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.51</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>19.43</v>
+        <v>15.26</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>11.05</v>
+        <v>4.32</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1470</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9671</v>
+        <v>11399</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>27.39</v>
+        <v>23.74</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>27.88</v>
+        <v>26.07</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>27.88</v>
+        <v>26.07</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>4.82</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15.26</v>
+        <v>15.23</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4.32</v>
+        <v>6.03</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1461</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>11399</v>
+        <v>3234</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>23.74</v>
+        <v>22.62</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>26.07</v>
+        <v>23.91</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>26.07</v>
+        <v>23.91</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.82</v>
+        <v>5.22</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>15.23</v>
+        <v>13.58</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.03</v>
+        <v>5.12</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1455</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3234</v>
+        <v>9638</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>22.62</v>
+        <v>22.93</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>23.91</v>
+        <v>23.39</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>23.91</v>
+        <v>23.39</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>5.22</v>
+        <v>7.53</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>13.58</v>
+        <v>10.51</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.12</v>
+        <v>5.36</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9638</v>
+        <v>7818</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>22.93</v>
+        <v>32.45</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>23.39</v>
+        <v>22.68</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>23.39</v>
+        <v>22.68</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.53</v>
+        <v>6.57</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10.51</v>
+        <v>6.27</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.36</v>
+        <v>9.84</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7818</v>
+        <v>7221</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>32.45</v>
+        <v>8.82</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>22.68</v>
+        <v>22.06</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.68</v>
+        <v>22.06</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6.57</v>
+        <v>6.01</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6.27</v>
+        <v>7.88</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.84</v>
+        <v>8.17</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7221</v>
+        <v>9566</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.82</v>
+        <v>39.97</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>22.06</v>
+        <v>21.25</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22.06</v>
+        <v>21.25</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6.01</v>
+        <v>4.16</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>7.88</v>
+        <v>8.57</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>8.17</v>
+        <v>8.52</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1441</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9566</v>
+        <v>9549</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>39.97</v>
+        <v>17.6</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>21.25</v>
+        <v>20.44</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21.25</v>
+        <v>20.44</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>4.16</v>
+        <v>7.46</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8.57</v>
+        <v>9.99</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>8.52</v>
+        <v>2.99</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9549</v>
+        <v>10181</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>17.6</v>
+        <v>23.43</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>20.44</v>
+        <v>20.1</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>20.44</v>
+        <v>20.1</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7.46</v>
+        <v>6.27</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>9.99</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.99</v>
+        <v>5.28</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10181</v>
+        <v>8285</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>23.43</v>
+        <v>39.07</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>20.1</v>
+        <v>17.71</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>20.1</v>
+        <v>17.71</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>6.27</v>
+        <v>2.21</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5.28</v>
+        <v>6.7</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1434</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>8285</v>
+        <v>5256</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>39.07</v>
+        <v>35.18</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>17.71</v>
+        <v>17.69</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.71</v>
+        <v>17.69</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>2.21</v>
+        <v>3.97</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>6.7</v>
+        <v>3.91</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1424</v>
@@ -4151,188 +4165,202 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5256</v>
+        <v>10664</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>35.18</v>
+        <v>21.7</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17.69</v>
+        <v>17.3</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.69</v>
+        <v>17.3</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>3.97</v>
+        <v>6.79</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>9.81</v>
+        <v>7.73</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3.91</v>
+        <v>2.78</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10664</v>
+        <v>10642</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>21.7</v>
+        <v>25.63</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>17.3</v>
+        <v>17.14</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>17.3</v>
+        <v>17.14</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>6.79</v>
+        <v>5.54</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>7.73</v>
+        <v>5.84</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.78</v>
+        <v>5.76</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10642</v>
+        <v>7256</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25.63</v>
+        <v>25.23</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17.14</v>
+        <v>12.34</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17.14</v>
+        <v>12.34</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5.54</v>
+        <v>5.35</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5.84</v>
+        <v>3.53</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>5.76</v>
+        <v>3.47</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1422</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7256</v>
+        <v>7658</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>25.23</v>
+        <v>14.34</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>12.34</v>
+        <v>9.35</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.34</v>
+        <v>9.35</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>5.35</v>
+        <v>3.19</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3.53</v>
+        <v>6.27</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>3.47</v>
+        <v>-0.11</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1400</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7658</v>
+        <v>904</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>14.34</v>
+        <v>27.91</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9.35</v>
+        <v>-0.1</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>9.35</v>
+        <v>-0.1</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>3.19</v>
+        <v>4.74</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6.27</v>
+        <v>-4.23</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.61</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1385</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>904</v>
+        <v>5501</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>-4.23</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>1332</v>
+          <t>Bobcats</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2947,96 +2947,6 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>5501</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Bobcats</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Burr Oak, Michigan</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3048,7 +2958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4318,51 +4228,6 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>5501</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Bobcats</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4374,7 +4239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5152,31 +5017,6 @@
         <v>-83.59</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>5501</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Bobcats</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5188,7 +5028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6212,41 +6052,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>5501</v>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Bobcats</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6258,7 +6063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7204,35 +7009,6 @@
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>5501</v>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Bobcats</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -634,37 +634,37 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>177.81</v>
+        <v>177.15</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-2.62</v>
+        <v>-2.98</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>180.43</v>
+        <v>180.12</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>132.42</v>
+        <v>136.6</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>132.42</v>
+        <v>136.6</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1667</v>
+        <v>1673</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25.48</v>
+        <v>25.3</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>73.63</v>
+        <v>78.14</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>33.31</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="3">
@@ -697,13 +697,13 @@
         <v>38</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>162.9</v>
+        <v>163.97</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>48.48</v>
+        <v>40.57</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>114.42</v>
+        <v>123.4</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>45.04</v>
@@ -729,62 +729,62 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7656</v>
+        <v>10633</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>185.19</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-7.24</v>
+        <v>43.64</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>101.95</v>
+        <v>141.54</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>50.91</v>
+        <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>88.45</v>
+        <v>150.76</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>88.45</v>
+        <v>150.76</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1595</v>
+        <v>1694</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>12.89</v>
+        <v>31.52</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>51.94</v>
+        <v>83.05</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>23.63</v>
+        <v>36.19</v>
       </c>
     </row>
     <row r="5">
@@ -805,7 +805,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>2</v>
@@ -814,58 +814,58 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>134.03</v>
+        <v>139.05</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>34.99</v>
+        <v>22.19</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>99.04000000000001</v>
+        <v>116.86</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>129.77</v>
+        <v>131.87</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>129.77</v>
+        <v>131.87</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>23.88</v>
+        <v>23.8</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>73.83</v>
+        <v>75.95</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>10633</v>
+        <v>5166</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>2</v>
@@ -874,51 +874,51 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>194.92</v>
+        <v>110.31</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>23.1</v>
+        <v>-15.7</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>171.83</v>
+        <v>126.01</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45.8</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>145.8</v>
+        <v>105.81</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>145.8</v>
+        <v>105.81</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1686</v>
+        <v>1629</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>28.98</v>
+        <v>19.83</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>79.56</v>
+        <v>61.97</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>37.27</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>5166</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>Belmont, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -928,64 +928,64 @@
         <v>7</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>115.71</v>
+        <v>130.49</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-7.68</v>
+        <v>51.58</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>123.39</v>
+        <v>78.91</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>111.29</v>
+        <v>114.36</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>111.29</v>
+        <v>114.36</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>20.41</v>
+        <v>24.77</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>62.97</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>24.98</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3875</v>
+        <v>2771</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2</v>
@@ -994,58 +994,58 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>127.32</v>
+        <v>91.55</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>33.74</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>93.59</v>
+        <v>19.63</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>50.66</v>
+        <v>53.52</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>87.55</v>
+        <v>79.63</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>87.55</v>
+        <v>79.63</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1594</v>
+        <v>1577</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>10.24</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>52.66</v>
+        <v>52.94</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>24.66</v>
+        <v>18.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Belmont, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>3</v>
@@ -1054,51 +1054,51 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>126.87</v>
+        <v>120.78</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>45.02</v>
+        <v>72.89</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>81.84999999999999</v>
+        <v>47.89</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>68.89</v>
+        <v>50.66</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>114.36</v>
+        <v>75.17</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>114.36</v>
+        <v>75.17</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1644</v>
+        <v>1568</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>24.77</v>
+        <v>8.83</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>62.97</v>
+        <v>48.11</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>26.63</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2771</v>
+        <v>1023</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -1108,103 +1108,103 @@
         <v>7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>98.88</v>
+        <v>133.74</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>59.56</v>
+        <v>57.05</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>39.33</v>
+        <v>76.69</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>53.52</v>
+        <v>68.08</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>78.41</v>
+        <v>104.24</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>78.41</v>
+        <v>104.24</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1575</v>
+        <v>1626</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>6.05</v>
+        <v>18.68</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>51.16</v>
+        <v>65.52</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>21.2</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>1023</v>
+        <v>7656</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Michigan Center, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>134.58</v>
+        <v>109.54</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>55.24</v>
+        <v>15.54</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>79.34</v>
+        <v>94</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>68.08</v>
+        <v>50.91</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>123.57</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>123.57</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1656</v>
+        <v>1610</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>22.32</v>
+        <v>11.59</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>76.88</v>
+        <v>57.16</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>24.37</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="12">
@@ -1237,13 +1237,13 @@
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31.52</v>
+        <v>30.74</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41.02</v>
+        <v>39.68</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-9.5</v>
+        <v>-8.94</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>44.43</v>
@@ -1297,13 +1297,13 @@
         <v>26</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>116.35</v>
+        <v>115.09</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>95.01000000000001</v>
+        <v>98.61</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>21.34</v>
+        <v>16.48</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>55.1</v>
@@ -1329,23 +1329,23 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>4</v>
@@ -1354,118 +1354,118 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>74.69</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>52.26</v>
+        <v>11.02</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>22.43</v>
+        <v>61.79</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>59.73</v>
+        <v>29.21</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>70.02</v>
+        <v>55.55</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>70.02</v>
+        <v>55.55</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1558</v>
+        <v>1528</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>18.13</v>
+        <v>6.85</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>32.41</v>
+        <v>34.42</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>19.48</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>71.06999999999999</v>
+        <v>66.61</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>29.4</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>41.67</v>
+        <v>-2.46</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>29.21</v>
+        <v>59.73</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>56.69</v>
+        <v>68.2</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>56.69</v>
+        <v>68.2</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1531</v>
+        <v>1554</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>6.66</v>
+        <v>18.16</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>35.67</v>
+        <v>30.7</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>14.36</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7808</v>
+        <v>8423</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>4</v>
@@ -1474,37 +1474,37 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12.77</v>
+        <v>66.55</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>51.26</v>
+        <v>17.35</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-38.49</v>
+        <v>49.21</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>24.37</v>
+        <v>28.04</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>33.47</v>
+        <v>56.3</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>33.47</v>
+        <v>56.3</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1477</v>
+        <v>1530</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>4.45</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>15.15</v>
+        <v>30.07</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>13.87</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="17">
@@ -1528,7 +1528,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
@@ -1537,94 +1537,94 @@
         <v>23</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>39.41</v>
+        <v>38.01</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>16.34</v>
+        <v>20.06</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>23.07</v>
+        <v>17.96</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>33.29</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>33.24</v>
+        <v>31.88</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>33.24</v>
+        <v>31.88</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>12.54</v>
+        <v>11.95</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>8.449999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>12.26</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8423</v>
+        <v>7808</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>69.47</v>
+        <v>13.02</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23.78</v>
+        <v>28.98</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>45.68</v>
+        <v>-15.96</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>28.04</v>
+        <v>24.37</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>56.3</v>
+        <v>29.86</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>56.3</v>
+        <v>29.86</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1530</v>
+        <v>1467</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>5.02</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>30.07</v>
+        <v>12.93</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>17.11</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="19">
@@ -1648,7 +1648,7 @@
         <v>6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
@@ -1657,34 +1657,34 @@
         <v>24</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>16.64</v>
+        <v>14.27</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>51.48</v>
+        <v>48.94</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-34.84</v>
+        <v>-34.67</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>21.07</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>29.26</v>
+        <v>25.68</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>29.26</v>
+        <v>25.68</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1465</v>
+        <v>1454</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>18.07</v>
+        <v>16.21</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>10.39</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="20">
@@ -1708,7 +1708,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -1717,228 +1717,228 @@
         <v>21</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>33.24</v>
+        <v>30</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18.77</v>
+        <v>15.32</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>14.47</v>
+        <v>14.69</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>27.21</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>41.12</v>
+        <v>39.76</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>41.12</v>
+        <v>39.76</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>6.03</v>
+        <v>5.44</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>23.96</v>
+        <v>23.09</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>11.13</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>11399</v>
+        <v>9685</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="E21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>9.93</v>
+        <v>49.62</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>71.92</v>
+        <v>41.02</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-61.99</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>23.74</v>
+        <v>27.75</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>26.07</v>
+        <v>54.37</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>26.07</v>
+        <v>54.37</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1455</v>
+        <v>1525</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>4.82</v>
+        <v>21.64</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>15.23</v>
+        <v>14.09</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>6.03</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9685</v>
+        <v>11399</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46.59</v>
+        <v>12.37</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>19.84</v>
+        <v>51.87</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>26.75</v>
+        <v>-39.5</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>27.75</v>
+        <v>23.74</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>50.7</v>
+        <v>22.46</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>50.7</v>
+        <v>22.46</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1518</v>
+        <v>1443</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>21.03</v>
+        <v>5.39</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>11.88</v>
+        <v>13.01</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>17.8</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>5980</v>
+        <v>3234</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>52.45</v>
+        <v>11.88</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>49.38</v>
+        <v>57.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.08</v>
+        <v>-45.92</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>38.55</v>
+        <v>22.62</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>35.57</v>
+        <v>18.43</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>35.57</v>
+        <v>18.43</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1483</v>
+        <v>1427</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.58</v>
+        <v>4.63</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>19.82</v>
+        <v>9.65</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>7.18</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3234</v>
+        <v>5980</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1948,57 +1948,57 @@
         <v>4</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.54</v>
+        <v>63.75</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>65.59</v>
+        <v>85.83</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-43.05</v>
+        <v>-22.08</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>22.62</v>
+        <v>38.55</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>23.91</v>
+        <v>46.86</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>23.91</v>
+        <v>46.86</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1448</v>
+        <v>1509</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>5.22</v>
+        <v>7.96</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>13.58</v>
+        <v>29.06</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>5.12</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9638</v>
+        <v>7256</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -2008,57 +2008,57 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>46.57</v>
+        <v>0.82</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>38</v>
+        <v>104.9</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8.57</v>
+        <v>-104.08</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>22.93</v>
+        <v>25.23</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>32</v>
+        <v>16.06</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>32</v>
+        <v>16.06</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1473</v>
+        <v>1417</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>7.7</v>
+        <v>5.24</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>15.2</v>
+        <v>7.92</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>9.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>10642</v>
+        <v>9638</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -2077,55 +2077,55 @@
         <v>17</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-6.64</v>
+        <v>42.71</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>36.99</v>
+        <v>39.46</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-43.63</v>
+        <v>3.25</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>25.63</v>
+        <v>22.93</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>13.71</v>
+        <v>32</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>13.71</v>
+        <v>32</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1407</v>
+        <v>1473</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>3.89</v>
+        <v>15.2</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>4.53</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>10181</v>
+        <v>10642</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>6</v>
@@ -2134,58 +2134,58 @@
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>25.39</v>
+        <v>-6.58</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>50.53</v>
+        <v>37.29</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-25.13</v>
+        <v>-43.87</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>23.43</v>
+        <v>25.63</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>20.1</v>
+        <v>13.71</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>20.1</v>
+        <v>13.71</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1434</v>
+        <v>1407</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>6.27</v>
+        <v>5.3</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>8.550000000000001</v>
+        <v>3.89</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>5.28</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9549</v>
+        <v>7221</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>7</v>
@@ -2194,181 +2194,181 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>9.289999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>47.95</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-38.66</v>
+        <v>-88.11</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>17.6</v>
+        <v>8.82</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>28.06</v>
+        <v>25.32</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>28.06</v>
+        <v>25.32</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1462</v>
+        <v>1453</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>7.25</v>
+        <v>5.84</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>13.73</v>
+        <v>11.6</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>7.08</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.54</v>
+        <v>3.42</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>127.71</v>
+        <v>51.91</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-129.25</v>
+        <v>-48.48</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>25.23</v>
+        <v>35.18</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>13.97</v>
+        <v>16.56</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>13.97</v>
+        <v>16.56</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1408</v>
+        <v>1419</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.31</v>
+        <v>4.16</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>5.8</v>
+        <v>8.56</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.85</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5256</v>
+        <v>9566</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5.75</v>
+        <v>11.89</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>68.89</v>
+        <v>38.88</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-63.14</v>
+        <v>-26.98</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>35.18</v>
+        <v>39.97</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>17.69</v>
+        <v>19.92</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>17.69</v>
+        <v>19.92</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>9.81</v>
+        <v>8.73</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>3.91</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>4325</v>
+        <v>7818</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
@@ -2377,48 +2377,48 @@
         <v>14</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>51.47</v>
+        <v>-1.75</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>161.15</v>
+        <v>91.53</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-109.68</v>
+        <v>-93.29000000000001</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>32.52</v>
+        <v>32.45</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>36.58</v>
+        <v>21.54</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>36.58</v>
+        <v>21.54</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1485</v>
+        <v>1439</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10.62</v>
+        <v>6.76</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>17.94</v>
+        <v>5.02</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9671</v>
+        <v>10181</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -2437,108 +2437,108 @@
         <v>14</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5.84</v>
+        <v>24.75</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>24.98</v>
+        <v>49.48</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-19.15</v>
+        <v>-24.73</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>27.39</v>
+        <v>23.43</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>31.41</v>
+        <v>18.74</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>31.41</v>
+        <v>18.74</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1471</v>
+        <v>1428</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>7.51</v>
+        <v>5.68</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>17.12</v>
+        <v>7.69</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>6.78</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7221</v>
+        <v>4325</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>50.95</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>100.72</v>
+        <v>158.41</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-92.42</v>
+        <v>-107.46</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>8.82</v>
+        <v>32.52</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>21.13</v>
+        <v>37.17</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>21.13</v>
+        <v>37.17</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1438</v>
+        <v>1486</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>6.02</v>
+        <v>9.76</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>7.09</v>
+        <v>18.43</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9566</v>
+        <v>9549</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -2548,103 +2548,103 @@
         <v>3</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2.64</v>
+        <v>11.8</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>55.49</v>
+        <v>47.53</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-52.85</v>
+        <v>-35.73</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>39.97</v>
+        <v>17.6</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>17.83</v>
+        <v>24.48</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>17.83</v>
+        <v>24.48</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>3.92</v>
+        <v>7.15</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>6.62</v>
+        <v>11.87</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>7.29</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7818</v>
+        <v>9671</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
         <v>34</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-1.86</v>
+        <v>5.21</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>110.68</v>
+        <v>34.52</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-112.54</v>
+        <v>-29.31</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>32.45</v>
+        <v>27.39</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>22.68</v>
+        <v>27.83</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>22.68</v>
+        <v>27.83</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1444</v>
+        <v>1460</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>6.57</v>
+        <v>7.41</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>6.27</v>
+        <v>15.26</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>9.84</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="36">
@@ -2668,117 +2668,117 @@
         <v>3</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-23.6</v>
+        <v>-20.06</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>64.54000000000001</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-88.14</v>
+        <v>-94.81999999999999</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>21.7</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>18.93</v>
+        <v>19.52</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>18.93</v>
+        <v>19.52</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>6.75</v>
+        <v>5.9</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>2.17</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7809</v>
+        <v>8285</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
         <v>36</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>30.65</v>
+        <v>24.03</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>148.07</v>
+        <v>117.69</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-117.42</v>
+        <v>-93.66</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>23.83</v>
+        <v>39.07</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>36.62</v>
+        <v>23.05</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>36.62</v>
+        <v>23.05</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1485</v>
+        <v>1445</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>18.85</v>
+        <v>13.77</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>15.57</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>904</v>
+        <v>7809</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2797,48 +2797,48 @@
         <v>10</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-8.43</v>
+        <v>29.81</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>72.29000000000001</v>
+        <v>127.41</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-80.72</v>
+        <v>-97.59999999999999</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>27.91</v>
+        <v>23.83</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.3</v>
+        <v>33.01</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.3</v>
+        <v>33.01</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1331</v>
+        <v>1476</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>6.58</v>
+        <v>2.77</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>-5.69</v>
+        <v>16.63</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-1.2</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>8285</v>
+        <v>904</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -2854,37 +2854,37 @@
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>21.48</v>
+        <v>-12.63</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>110.2</v>
+        <v>69.06</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-88.70999999999999</v>
+        <v>-81.69</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>39.07</v>
+        <v>27.91</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.31</v>
+        <v>-0.3</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>19.31</v>
+        <v>-0.3</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1431</v>
+        <v>1331</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1.34</v>
+        <v>6.58</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>12.06</v>
+        <v>-5.69</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>5.91</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="40">
@@ -2908,43 +2908,43 @@
         <v>1</v>
       </c>
       <c r="F40" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="I40" s="2" t="n">
-        <v>-4.59</v>
+        <v>6.68</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>23.83</v>
+        <v>47.02</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-28.42</v>
+        <v>-40.33</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>14.34</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>9.35</v>
+        <v>16.45</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>9.35</v>
+        <v>16.45</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1385</v>
+        <v>1419</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>3.19</v>
+        <v>2.74</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>6.27</v>
+        <v>11</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>-0.11</v>
+        <v>2.71</v>
       </c>
     </row>
   </sheetData>
@@ -3032,22 +3032,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>145.8</v>
+        <v>150.76</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>145.8</v>
+        <v>150.76</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>28.98</v>
+        <v>31.52</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>79.56</v>
+        <v>83.05</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>37.27</v>
+        <v>36.19</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1686</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="3">
@@ -3094,22 +3094,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>132.42</v>
+        <v>136.6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>132.42</v>
+        <v>136.6</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25.48</v>
+        <v>25.3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>73.63</v>
+        <v>78.14</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>33.31</v>
+        <v>33.16</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1667</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="5">
@@ -3125,115 +3125,115 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>129.77</v>
+        <v>131.87</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>129.77</v>
+        <v>131.87</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.88</v>
+        <v>23.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>73.83</v>
+        <v>75.95</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1664</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1023</v>
+        <v>4967</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>68.08</v>
+        <v>68.89</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>123.57</v>
+        <v>114.36</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>123.57</v>
+        <v>114.36</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>22.32</v>
+        <v>24.77</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>76.88</v>
+        <v>62.97</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>24.37</v>
+        <v>26.63</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1656</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>5166</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>68.89</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>114.36</v>
+        <v>105.81</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>114.36</v>
+        <v>105.81</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>24.77</v>
+        <v>19.83</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>62.97</v>
+        <v>61.97</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>26.63</v>
+        <v>24.01</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1644</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5166</v>
+        <v>1023</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>111.29</v>
+        <v>104.24</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>111.29</v>
+        <v>104.24</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>20.41</v>
+        <v>18.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>65.52</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>24.98</v>
+        <v>20.04</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1640</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="9">
@@ -3249,53 +3249,53 @@
         <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>88.45</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>88.45</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>12.89</v>
+        <v>11.59</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>51.94</v>
+        <v>57.16</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23.63</v>
+        <v>27.4</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1595</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3875</v>
+        <v>2771</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50.66</v>
+        <v>53.52</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>87.55</v>
+        <v>79.63</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>87.55</v>
+        <v>79.63</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.24</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>52.66</v>
+        <v>52.94</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>24.66</v>
+        <v>18.66</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1594</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="11">
@@ -3331,33 +3331,33 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2771</v>
+        <v>3875</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>53.52</v>
+        <v>50.66</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>78.41</v>
+        <v>75.17</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>78.41</v>
+        <v>75.17</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6.05</v>
+        <v>8.83</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>51.16</v>
+        <v>48.11</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>21.2</v>
+        <v>18.22</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1575</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="13">
@@ -3373,22 +3373,22 @@
         <v>59.73</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>70.02</v>
+        <v>68.2</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>70.02</v>
+        <v>68.2</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>18.13</v>
+        <v>18.16</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>32.41</v>
+        <v>30.7</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>19.48</v>
+        <v>19.35</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1558</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="14">
@@ -3424,64 +3424,64 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>29.21</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>56.69</v>
+        <v>56.3</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>56.69</v>
+        <v>56.3</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>6.66</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>35.67</v>
+        <v>30.07</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>14.36</v>
+        <v>17.11</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8423</v>
+        <v>9756</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>28.04</v>
+        <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>56.3</v>
+        <v>55.55</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>56.3</v>
+        <v>55.55</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30.07</v>
+        <v>34.42</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>17.11</v>
+        <v>14.28</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1530</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="17">
@@ -3497,84 +3497,84 @@
         <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>50.7</v>
+        <v>54.37</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>50.7</v>
+        <v>54.37</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>21.03</v>
+        <v>21.64</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>11.88</v>
+        <v>14.09</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.8</v>
+        <v>18.64</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1518</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8767</v>
+        <v>5980</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>27.21</v>
+        <v>38.55</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>41.12</v>
+        <v>46.86</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>41.12</v>
+        <v>46.86</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6.03</v>
+        <v>7.96</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23.96</v>
+        <v>29.06</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>11.13</v>
+        <v>9.84</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1496</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>7809</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>23.83</v>
+        <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>36.62</v>
+        <v>39.76</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>36.62</v>
+        <v>39.76</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2.2</v>
+        <v>5.44</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.85</v>
+        <v>23.09</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.57</v>
+        <v>11.22</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1485</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="20">
@@ -3590,84 +3590,84 @@
         <v>32.52</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>36.58</v>
+        <v>37.17</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>36.58</v>
+        <v>37.17</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>10.62</v>
+        <v>9.76</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>17.94</v>
+        <v>18.43</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>5980</v>
+        <v>7809</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>38.55</v>
+        <v>23.83</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>35.57</v>
+        <v>33.01</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>35.57</v>
+        <v>33.01</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>8.58</v>
+        <v>2.77</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>19.82</v>
+        <v>16.63</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>7.18</v>
+        <v>13.61</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1483</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7808</v>
+        <v>9638</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>24.37</v>
+        <v>22.93</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>33.47</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>33.47</v>
+        <v>32</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.45</v>
+        <v>7.7</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>15.15</v>
+        <v>15.2</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>13.87</v>
+        <v>9.1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1477</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="23">
@@ -3683,53 +3683,53 @@
         <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>33.24</v>
+        <v>31.88</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>33.24</v>
+        <v>31.88</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.54</v>
+        <v>11.95</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8.449999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>12.26</v>
+        <v>12.35</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9638</v>
+        <v>7808</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>22.93</v>
+        <v>24.37</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>32</v>
+        <v>29.86</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>32</v>
+        <v>29.86</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7.7</v>
+        <v>5.02</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15.2</v>
+        <v>12.93</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.1</v>
+        <v>11.91</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1473</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="25">
@@ -3745,22 +3745,22 @@
         <v>27.39</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>31.41</v>
+        <v>27.83</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>31.41</v>
+        <v>27.83</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>7.51</v>
+        <v>7.41</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>17.12</v>
+        <v>15.26</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>6.78</v>
+        <v>5.16</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1471</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="26">
@@ -3776,301 +3776,301 @@
         <v>21.07</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>29.26</v>
+        <v>25.68</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>29.26</v>
+        <v>25.68</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>18.07</v>
+        <v>16.21</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.39</v>
+        <v>8.77</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1465</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9549</v>
+        <v>7221</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>17.6</v>
+        <v>8.82</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>28.06</v>
+        <v>25.32</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>28.06</v>
+        <v>25.32</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7.25</v>
+        <v>5.84</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>13.73</v>
+        <v>11.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.08</v>
+        <v>7.87</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1462</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>11399</v>
+        <v>9549</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>23.74</v>
+        <v>17.6</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>26.07</v>
+        <v>24.48</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>26.07</v>
+        <v>24.48</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.82</v>
+        <v>7.15</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.23</v>
+        <v>11.87</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6.03</v>
+        <v>5.46</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1455</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>3234</v>
+        <v>8285</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>22.62</v>
+        <v>39.07</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>23.91</v>
+        <v>23.05</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>23.91</v>
+        <v>23.05</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.22</v>
+        <v>1.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>13.58</v>
+        <v>13.77</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.12</v>
+        <v>7.38</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7818</v>
+        <v>11399</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>32.45</v>
+        <v>23.74</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>22.68</v>
+        <v>22.46</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.68</v>
+        <v>22.46</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6.57</v>
+        <v>5.39</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6.27</v>
+        <v>13.01</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.84</v>
+        <v>4.06</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7221</v>
+        <v>7818</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.82</v>
+        <v>32.45</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>21.13</v>
+        <v>21.54</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>21.13</v>
+        <v>21.54</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6.02</v>
+        <v>6.76</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>7.09</v>
+        <v>5.02</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>10181</v>
+        <v>9566</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>23.43</v>
+        <v>39.97</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>20.1</v>
+        <v>19.92</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>20.1</v>
+        <v>19.92</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>6.27</v>
+        <v>3.85</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>5.28</v>
+        <v>7.34</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>8285</v>
+        <v>10664</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>39.07</v>
+        <v>21.7</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>19.31</v>
+        <v>19.52</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.31</v>
+        <v>19.52</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1.34</v>
+        <v>5.9</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>12.06</v>
+        <v>10.5</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>5.91</v>
+        <v>3.12</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10664</v>
+        <v>10181</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>21.7</v>
+        <v>23.43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>18.93</v>
+        <v>18.74</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.93</v>
+        <v>18.74</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>6.75</v>
+        <v>5.68</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10</v>
+        <v>7.69</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>2.17</v>
+        <v>5.37</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9566</v>
+        <v>3234</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>39.97</v>
+        <v>22.62</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>17.83</v>
+        <v>18.43</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.83</v>
+        <v>18.43</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3.92</v>
+        <v>4.63</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6.62</v>
+        <v>9.65</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>7.29</v>
+        <v>4.15</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1425</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="36">
@@ -4086,115 +4086,115 @@
         <v>35.18</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17.69</v>
+        <v>16.56</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.69</v>
+        <v>16.56</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>3.97</v>
+        <v>4.16</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>9.81</v>
+        <v>8.56</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3.91</v>
+        <v>3.84</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1424</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7256</v>
+        <v>7658</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>25.23</v>
+        <v>14.34</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>13.97</v>
+        <v>16.45</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>13.97</v>
+        <v>16.45</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.31</v>
+        <v>2.74</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1408</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10642</v>
+        <v>7256</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25.63</v>
+        <v>25.23</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>13.71</v>
+        <v>16.06</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.71</v>
+        <v>16.06</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5.3</v>
+        <v>5.24</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3.89</v>
+        <v>7.92</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>4.53</v>
+        <v>2.9</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1407</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7658</v>
+        <v>10642</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>14.34</v>
+        <v>25.63</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>9.35</v>
+        <v>13.71</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>9.35</v>
+        <v>13.71</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3.19</v>
+        <v>5.3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>6.27</v>
+        <v>3.89</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>-0.11</v>
+        <v>4.53</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1385</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="40">
@@ -4286,13 +4286,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>194.92</v>
+        <v>185.19</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>23.1</v>
+        <v>43.64</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>171.83</v>
+        <v>141.54</v>
       </c>
     </row>
     <row r="3">
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>177.81</v>
+        <v>177.15</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-2.62</v>
+        <v>-2.98</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>180.43</v>
+        <v>180.12</v>
       </c>
     </row>
     <row r="4">
@@ -4324,89 +4324,89 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>162.9</v>
+        <v>163.97</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>48.48</v>
+        <v>40.57</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>114.42</v>
+        <v>123.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>134.58</v>
+        <v>139.05</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>55.24</v>
+        <v>22.19</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>79.34</v>
+        <v>116.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2075</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>134.03</v>
+        <v>133.74</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34.99</v>
+        <v>57.05</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>99.04000000000001</v>
+        <v>76.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>127.32</v>
+        <v>130.49</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>33.74</v>
+        <v>51.58</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>93.59</v>
+        <v>78.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>126.87</v>
+        <v>120.78</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>45.02</v>
+        <v>72.89</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>81.84999999999999</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="9">
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>116.35</v>
+        <v>115.09</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>95.01000000000001</v>
+        <v>98.61</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>21.34</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="10">
@@ -4438,89 +4438,89 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>115.71</v>
+        <v>110.31</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-7.68</v>
+        <v>-15.7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>123.39</v>
+        <v>126.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2771</v>
+        <v>7656</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>98.88</v>
+        <v>109.54</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>59.56</v>
+        <v>15.54</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>39.33</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7656</v>
+        <v>2771</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>91.55</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-7.24</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>101.95</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>74.69</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>52.26</v>
+        <v>11.02</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>22.43</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>71.06999999999999</v>
+        <v>66.61</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>29.4</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>41.67</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="15">
@@ -4533,13 +4533,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>69.47</v>
+        <v>66.55</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>23.78</v>
+        <v>17.35</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>45.68</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="16">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>52.45</v>
+        <v>63.75</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>49.38</v>
+        <v>85.83</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3.08</v>
+        <v>-22.08</v>
       </c>
     </row>
     <row r="17">
@@ -4571,13 +4571,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>51.47</v>
+        <v>50.95</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>161.15</v>
+        <v>158.41</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-109.68</v>
+        <v>-107.46</v>
       </c>
     </row>
     <row r="18">
@@ -4590,13 +4590,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46.59</v>
+        <v>49.62</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>19.84</v>
+        <v>41.02</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>26.75</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -4609,13 +4609,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>46.57</v>
+        <v>42.71</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>38</v>
+        <v>39.46</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8.57</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="20">
@@ -4628,51 +4628,51 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>39.41</v>
+        <v>38.01</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>16.34</v>
+        <v>20.06</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>23.07</v>
+        <v>17.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>8767</v>
+        <v>9208</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>33.24</v>
+        <v>30.74</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>18.77</v>
+        <v>39.68</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>14.47</v>
+        <v>-8.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9208</v>
+        <v>8767</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>31.52</v>
+        <v>30</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>41.02</v>
+        <v>15.32</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-9.5</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="23">
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>30.65</v>
+        <v>29.81</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>148.07</v>
+        <v>127.41</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-117.42</v>
+        <v>-97.59999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -4704,260 +4704,260 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>25.39</v>
+        <v>24.75</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>50.53</v>
+        <v>49.48</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-25.13</v>
+        <v>-24.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>3234</v>
+        <v>8285</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>22.54</v>
+        <v>24.03</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>65.59</v>
+        <v>117.69</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-43.05</v>
+        <v>-93.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8285</v>
+        <v>9206</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>21.48</v>
+        <v>14.27</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>110.2</v>
+        <v>48.94</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-88.70999999999999</v>
+        <v>-34.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9206</v>
+        <v>7808</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>16.64</v>
+        <v>13.02</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>51.48</v>
+        <v>28.98</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-34.84</v>
+        <v>-15.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7808</v>
+        <v>11399</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>12.77</v>
+        <v>12.37</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>51.26</v>
+        <v>51.87</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-38.49</v>
+        <v>-39.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>11399</v>
+        <v>9566</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.93</v>
+        <v>11.89</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>71.92</v>
+        <v>38.88</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-61.99</v>
+        <v>-26.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9549</v>
+        <v>3234</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9.289999999999999</v>
+        <v>11.88</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>47.95</v>
+        <v>57.8</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-38.66</v>
+        <v>-45.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7221</v>
+        <v>9549</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>100.72</v>
+        <v>47.53</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-92.42</v>
+        <v>-35.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9671</v>
+        <v>7221</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>5.84</v>
+        <v>7.65</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>24.98</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-19.15</v>
+        <v>-88.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>5256</v>
+        <v>7658</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>5.75</v>
+        <v>6.68</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>68.89</v>
+        <v>47.02</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-63.14</v>
+        <v>-40.33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9566</v>
+        <v>9671</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2.64</v>
+        <v>5.21</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>55.49</v>
+        <v>34.52</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-52.85</v>
+        <v>-29.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-1.54</v>
+        <v>3.42</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>127.71</v>
+        <v>51.91</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-129.25</v>
+        <v>-48.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7818</v>
+        <v>7256</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-1.86</v>
+        <v>0.82</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>110.68</v>
+        <v>104.9</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-112.54</v>
+        <v>-104.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7658</v>
+        <v>7818</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-4.59</v>
+        <v>-1.75</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>23.83</v>
+        <v>91.53</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-28.42</v>
+        <v>-93.29000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-6.64</v>
+        <v>-6.58</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>36.99</v>
+        <v>37.29</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-43.63</v>
+        <v>-43.87</v>
       </c>
     </row>
     <row r="39">
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-8.43</v>
+        <v>-12.63</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>72.29000000000001</v>
+        <v>69.06</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-80.72</v>
+        <v>-81.69</v>
       </c>
     </row>
     <row r="40">
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-23.6</v>
+        <v>-20.06</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>64.54000000000001</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-88.14</v>
+        <v>-94.81999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -5132,24 +5132,24 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7656</v>
+        <v>10633</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
@@ -5174,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -5182,15 +5182,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>10633</v>
+        <v>5166</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>2</v>
@@ -5199,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -5207,24 +5207,24 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5166</v>
+        <v>4967</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -5232,15 +5232,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3875</v>
+        <v>2771</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>2</v>
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -5257,15 +5257,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>3</v>
@@ -5274,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -5282,24 +5282,24 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2771</v>
+        <v>1023</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -5307,24 +5307,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1023</v>
+        <v>7656</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -5382,15 +5382,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>4</v>
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -5407,24 +5407,24 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -5432,15 +5432,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7808</v>
+        <v>8423</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>4</v>
@@ -5449,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -5468,7 +5468,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0</v>
@@ -5482,24 +5482,24 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>8423</v>
+        <v>7808</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -5518,7 +5518,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -5557,24 +5557,24 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>11399</v>
+        <v>9685</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -5582,24 +5582,24 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>9685</v>
+        <v>11399</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -5607,24 +5607,24 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5980</v>
+        <v>3234</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -5632,24 +5632,24 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3234</v>
+        <v>5980</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -5657,24 +5657,24 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9638</v>
+        <v>7256</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -5682,11 +5682,11 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>10642</v>
+        <v>9638</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -5707,15 +5707,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10181</v>
+        <v>10642</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>6</v>
@@ -5724,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -5732,15 +5732,15 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>9549</v>
+        <v>7221</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>7</v>
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -5757,24 +5757,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -5782,24 +5782,24 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5256</v>
+        <v>9566</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -5807,18 +5807,18 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>4325</v>
+        <v>7818</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -5832,11 +5832,11 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9671</v>
+        <v>10181</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -5857,24 +5857,24 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>7221</v>
+        <v>4325</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -5882,24 +5882,24 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9566</v>
+        <v>9549</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -5907,24 +5907,24 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7818</v>
+        <v>9671</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -5943,13 +5943,13 @@
         <v>3</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
@@ -5957,24 +5957,24 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7809</v>
+        <v>8285</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
@@ -5982,11 +5982,11 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>904</v>
+        <v>7809</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -6007,11 +6007,11 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>8285</v>
+        <v>904</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -6024,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -6043,13 +6043,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>194.92</v>
+        <v>185.19</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>23.1</v>
+        <v>43.64</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>171.83</v>
+        <v>141.54</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>177.81</v>
+        <v>177.15</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-2.62</v>
+        <v>-2.98</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>180.43</v>
+        <v>180.12</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>162.9</v>
+        <v>163.97</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>48.48</v>
+        <v>40.57</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>114.42</v>
+        <v>123.4</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6186,21 +6186,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>134.58</v>
+        <v>139.05</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>55.24</v>
+        <v>22.19</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>79.34</v>
+        <v>116.86</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6209,21 +6209,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2075</v>
+        <v>1023</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>134.03</v>
+        <v>133.74</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34.99</v>
+        <v>57.05</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>99.04000000000001</v>
+        <v>76.69</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6232,21 +6232,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>127.32</v>
+        <v>130.49</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>33.74</v>
+        <v>51.58</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>93.59</v>
+        <v>78.91</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6255,21 +6255,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>126.87</v>
+        <v>120.78</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45.02</v>
+        <v>72.89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>81.84999999999999</v>
+        <v>47.89</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6286,13 +6286,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>116.35</v>
+        <v>115.09</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>95.01000000000001</v>
+        <v>98.61</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>21.34</v>
+        <v>16.48</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>115.71</v>
+        <v>110.31</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-7.68</v>
+        <v>-15.7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>123.39</v>
+        <v>126.01</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6324,21 +6324,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2771</v>
+        <v>7656</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>98.88</v>
+        <v>109.54</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>59.56</v>
+        <v>15.54</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>39.33</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6347,21 +6347,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7656</v>
+        <v>2771</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>91.55</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-7.24</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>101.95</v>
+        <v>19.63</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6370,21 +6370,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>74.69</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>52.26</v>
+        <v>11.02</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>22.43</v>
+        <v>61.79</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6393,21 +6393,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>71.06999999999999</v>
+        <v>66.61</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29.4</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>41.67</v>
+        <v>-2.46</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6424,13 +6424,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>69.47</v>
+        <v>66.55</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>23.78</v>
+        <v>17.35</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>45.68</v>
+        <v>49.21</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>52.45</v>
+        <v>63.75</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>49.38</v>
+        <v>85.83</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3.08</v>
+        <v>-22.08</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>51.47</v>
+        <v>50.95</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>161.15</v>
+        <v>158.41</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-109.68</v>
+        <v>-107.46</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>46.59</v>
+        <v>49.62</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>19.84</v>
+        <v>41.02</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>26.75</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6516,13 +6516,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46.57</v>
+        <v>42.71</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>38</v>
+        <v>39.46</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>8.57</v>
+        <v>3.25</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6539,13 +6539,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>39.41</v>
+        <v>38.01</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16.34</v>
+        <v>20.06</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>23.07</v>
+        <v>17.96</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6554,21 +6554,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8767</v>
+        <v>9208</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>33.24</v>
+        <v>30.74</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>18.77</v>
+        <v>39.68</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>14.47</v>
+        <v>-8.94</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6577,21 +6577,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>9208</v>
+        <v>8767</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.52</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>41.02</v>
+        <v>15.32</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-9.5</v>
+        <v>14.69</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>30.65</v>
+        <v>29.81</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>148.07</v>
+        <v>127.41</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-117.42</v>
+        <v>-97.59999999999999</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>25.39</v>
+        <v>24.75</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>50.53</v>
+        <v>49.48</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-25.13</v>
+        <v>-24.73</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6646,21 +6646,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>3234</v>
+        <v>8285</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>22.54</v>
+        <v>24.03</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>65.59</v>
+        <v>117.69</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-43.05</v>
+        <v>-93.66</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6669,21 +6669,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>8285</v>
+        <v>9206</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>21.48</v>
+        <v>14.27</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>110.2</v>
+        <v>48.94</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-88.70999999999999</v>
+        <v>-34.67</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6692,21 +6692,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9206</v>
+        <v>7808</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>16.64</v>
+        <v>13.02</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>51.48</v>
+        <v>28.98</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-34.84</v>
+        <v>-15.96</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6715,21 +6715,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7808</v>
+        <v>11399</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12.77</v>
+        <v>12.37</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>51.26</v>
+        <v>51.87</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-38.49</v>
+        <v>-39.5</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6738,21 +6738,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>11399</v>
+        <v>9566</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9.93</v>
+        <v>11.89</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>71.92</v>
+        <v>38.88</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-61.99</v>
+        <v>-26.98</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6761,21 +6761,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9549</v>
+        <v>3234</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9.289999999999999</v>
+        <v>11.88</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>47.95</v>
+        <v>57.8</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-38.66</v>
+        <v>-45.92</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6784,21 +6784,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7221</v>
+        <v>9549</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>100.72</v>
+        <v>47.53</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-92.42</v>
+        <v>-35.73</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6807,21 +6807,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9671</v>
+        <v>7221</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5.84</v>
+        <v>7.65</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>24.98</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-19.15</v>
+        <v>-88.11</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6830,21 +6830,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>5256</v>
+        <v>7658</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>5.75</v>
+        <v>6.68</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>68.89</v>
+        <v>47.02</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-63.14</v>
+        <v>-40.33</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -6853,21 +6853,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9566</v>
+        <v>9671</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2.64</v>
+        <v>5.21</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>55.49</v>
+        <v>34.52</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-52.85</v>
+        <v>-29.31</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -6876,21 +6876,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7256</v>
+        <v>5256</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-1.54</v>
+        <v>3.42</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>127.71</v>
+        <v>51.91</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-129.25</v>
+        <v>-48.48</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -6899,21 +6899,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7818</v>
+        <v>7256</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-1.86</v>
+        <v>0.82</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>110.68</v>
+        <v>104.9</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-112.54</v>
+        <v>-104.08</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -6922,21 +6922,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7658</v>
+        <v>7818</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-4.59</v>
+        <v>-1.75</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>23.83</v>
+        <v>91.53</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-28.42</v>
+        <v>-93.29000000000001</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-6.64</v>
+        <v>-6.58</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>36.99</v>
+        <v>37.29</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-43.63</v>
+        <v>-43.87</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -6976,13 +6976,13 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-8.43</v>
+        <v>-12.63</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>72.29000000000001</v>
+        <v>69.06</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-80.72</v>
+        <v>-81.69</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -6999,13 +6999,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-23.6</v>
+        <v>-20.06</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>64.54000000000001</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-88.14</v>
+        <v>-94.81999999999999</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -637,13 +637,13 @@
         <v>45</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>177.15</v>
+        <v>175.88</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-2.98</v>
+        <v>-5.47</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>180.12</v>
+        <v>181.35</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>75.04000000000001</v>
@@ -685,7 +685,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2</v>
@@ -694,37 +694,37 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>163.97</v>
+        <v>170.14</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>40.57</v>
+        <v>33.12</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>123.4</v>
+        <v>137.02</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>138.69</v>
+        <v>143.64</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>138.69</v>
+        <v>143.64</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.97</v>
+        <v>30.5</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>83.79000000000001</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>23.92</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="4">
@@ -745,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2</v>
@@ -754,37 +754,37 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>185.19</v>
+        <v>187.47</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>43.64</v>
+        <v>44.72</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>141.54</v>
+        <v>142.75</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>150.76</v>
+        <v>151.93</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>150.76</v>
+        <v>151.93</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>31.52</v>
+        <v>31.13</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>83.05</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>36.19</v>
+        <v>36.85</v>
       </c>
     </row>
     <row r="5">
@@ -805,7 +805,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>2</v>
@@ -814,51 +814,51 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>139.05</v>
+        <v>139.14</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>22.19</v>
+        <v>33.39</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>116.86</v>
+        <v>105.75</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>131.87</v>
+        <v>133.04</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>131.87</v>
+        <v>133.04</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>1667</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>23.8</v>
+        <v>23.41</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>75.95</v>
+        <v>76.86</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>32.11</v>
+        <v>32.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5166</v>
+        <v>4967</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>Belmont, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -868,247 +868,247 @@
         <v>8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>110.31</v>
+        <v>124.04</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-15.7</v>
+        <v>42.12</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>126.01</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>105.81</v>
+        <v>112.68</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>105.81</v>
+        <v>112.68</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1629</v>
+        <v>1641</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>19.83</v>
+        <v>23.79</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>61.97</v>
+        <v>60.45</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>24.01</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>2771</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Belmont, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>130.49</v>
+        <v>92.84</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>51.58</v>
+        <v>67.88</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>78.91</v>
+        <v>24.96</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>68.89</v>
+        <v>53.52</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>114.36</v>
+        <v>80.09</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>114.36</v>
+        <v>80.09</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1644</v>
+        <v>1578</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>24.77</v>
+        <v>7.65</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>62.97</v>
+        <v>51.35</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>26.63</v>
+        <v>21.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2771</v>
+        <v>3875</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>91.55</v>
+        <v>119.38</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>71.93000000000001</v>
+        <v>47.13</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>19.63</v>
+        <v>72.25</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>53.52</v>
+        <v>50.66</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>79.63</v>
+        <v>94.66</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>79.63</v>
+        <v>94.66</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1577</v>
+        <v>1607</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>13.11</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>52.94</v>
+        <v>58.71</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>18.66</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3875</v>
+        <v>1023</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>120.78</v>
+        <v>132.96</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>72.89</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>47.89</v>
+        <v>68.77</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>50.66</v>
+        <v>68.08</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>75.17</v>
+        <v>127.31</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>75.17</v>
+        <v>127.31</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1568</v>
+        <v>1661</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>8.83</v>
+        <v>22.88</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>48.11</v>
+        <v>78.59</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>18.22</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1023</v>
+        <v>7656</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Michigan Center, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -1117,48 +1117,48 @@
         <v>34</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>133.74</v>
+        <v>106.93</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>57.05</v>
+        <v>16.69</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>76.69</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>68.08</v>
+        <v>50.91</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>104.24</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>104.24</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1626</v>
+        <v>1610</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>18.68</v>
+        <v>11.59</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>65.52</v>
+        <v>57.16</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>20.04</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>7656</v>
+        <v>5166</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1168,43 +1168,43 @@
         <v>8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>109.54</v>
+        <v>107.89</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>15.54</v>
+        <v>13.28</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>94</v>
+        <v>94.61</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>50.91</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>96.15000000000001</v>
+        <v>102.78</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>96.15000000000001</v>
+        <v>102.78</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1610</v>
+        <v>1622</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>11.59</v>
+        <v>17.95</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>57.16</v>
+        <v>60.68</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>27.4</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="12">
@@ -1225,46 +1225,46 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>30.74</v>
+        <v>34.43</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>39.68</v>
+        <v>63.69</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-8.94</v>
+        <v>-29.26</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>44.43</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>60.89</v>
+        <v>58.59</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>60.89</v>
+        <v>58.59</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>16.47</v>
+        <v>14.44</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>32.38</v>
+        <v>30.34</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>12.03</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="13">
@@ -1285,7 +1285,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>5</v>
@@ -1294,37 +1294,37 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>115.09</v>
+        <v>112.9</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>98.61</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>16.48</v>
+        <v>37.11</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>55.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>78.95</v>
+        <v>77.95</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>78.95</v>
+        <v>77.95</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>13.31</v>
+        <v>12.68</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>39.02</v>
+        <v>38.22</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>26.62</v>
+        <v>27.05</v>
       </c>
     </row>
     <row r="14">
@@ -1348,43 +1348,43 @@
         <v>6</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>72.81999999999999</v>
+        <v>69.56</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>11.02</v>
+        <v>21.67</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>61.79</v>
+        <v>47.89</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>29.21</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>55.55</v>
+        <v>54.67</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>55.55</v>
+        <v>54.67</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>6.85</v>
+        <v>7.24</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>34.42</v>
+        <v>33.67</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>14.28</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="15">
@@ -1408,43 +1408,43 @@
         <v>6</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>66.61</v>
+        <v>70.86</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>69.06999999999999</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-2.46</v>
+        <v>6.54</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>59.73</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>18.16</v>
+        <v>17.1</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>30.7</v>
+        <v>31.64</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>19.35</v>
+        <v>19.06</v>
       </c>
     </row>
     <row r="16">
@@ -1468,7 +1468,7 @@
         <v>6</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -1477,48 +1477,48 @@
         <v>24</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>66.55</v>
+        <v>64.92</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>17.35</v>
+        <v>26.84</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>49.21</v>
+        <v>38.09</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>28.04</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>56.3</v>
+        <v>55.69</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>56.3</v>
+        <v>55.69</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>30.07</v>
+        <v>30.52</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>17.11</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>7289</v>
+        <v>11399</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1528,64 +1528,64 @@
         <v>6</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>38.01</v>
+        <v>12.45</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>20.06</v>
+        <v>58.04</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>17.96</v>
+        <v>-45.59</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>33.29</v>
+        <v>23.74</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>31.88</v>
+        <v>22.47</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>31.88</v>
+        <v>22.47</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1472</v>
+        <v>1443</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>11.95</v>
+        <v>4.61</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>7.58</v>
+        <v>13.43</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>12.35</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7808</v>
+        <v>9206</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>5</v>
@@ -1594,51 +1594,51 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>13.02</v>
+        <v>15.93</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>28.98</v>
+        <v>47.48</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-15.96</v>
+        <v>-31.55</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>24.37</v>
+        <v>21.07</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>29.86</v>
+        <v>25.68</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>29.86</v>
+        <v>25.68</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1467</v>
+        <v>1454</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>5.02</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>12.93</v>
+        <v>16.21</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>11.91</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9206</v>
+        <v>9685</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1654,58 +1654,58 @@
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>14.27</v>
+        <v>47.08</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>48.94</v>
+        <v>51.91</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-34.67</v>
+        <v>-4.83</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>21.07</v>
+        <v>27.75</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>25.68</v>
+        <v>54.37</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>25.68</v>
+        <v>54.37</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1454</v>
+        <v>1525</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>21.64</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>16.21</v>
+        <v>14.09</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>8.77</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8767</v>
+        <v>7289</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>5</v>
@@ -1714,277 +1714,277 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30</v>
+        <v>37.73</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>15.32</v>
+        <v>-2.17</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>14.69</v>
+        <v>39.9</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>27.21</v>
+        <v>33.29</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>39.76</v>
+        <v>30.92</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>39.76</v>
+        <v>30.92</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1493</v>
+        <v>1469</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>5.44</v>
+        <v>12.05</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>23.09</v>
+        <v>7.63</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>11.22</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>9685</v>
+        <v>5980</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>49.62</v>
+        <v>57.96</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>41.02</v>
+        <v>72.03</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>8.609999999999999</v>
+        <v>-14.07</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>27.75</v>
+        <v>38.55</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>54.37</v>
+        <v>45.18</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>54.37</v>
+        <v>45.18</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1525</v>
+        <v>1505</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>21.64</v>
+        <v>6.98</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>14.09</v>
+        <v>26.54</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>18.64</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>11399</v>
+        <v>10642</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>12.37</v>
+        <v>-4.65</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>51.87</v>
+        <v>43.96</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-39.5</v>
+        <v>-48.62</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>23.74</v>
+        <v>25.63</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>22.46</v>
+        <v>14.9</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>22.46</v>
+        <v>14.9</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1443</v>
+        <v>1411</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>5.39</v>
+        <v>4.13</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>13.01</v>
+        <v>5.22</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>4.06</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>3234</v>
+        <v>5256</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>11.88</v>
+        <v>13.48</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>57.8</v>
+        <v>30.77</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-45.92</v>
+        <v>-17.29</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>22.62</v>
+        <v>35.18</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>18.43</v>
+        <v>21.96</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.43</v>
+        <v>21.96</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1427</v>
+        <v>1441</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>4.63</v>
+        <v>4.08</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>9.65</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>4.15</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5980</v>
+        <v>8767</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>63.75</v>
+        <v>29.51</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>85.83</v>
+        <v>25.66</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-22.08</v>
+        <v>3.85</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>38.55</v>
+        <v>27.21</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>46.86</v>
+        <v>38.87</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>46.86</v>
+        <v>38.87</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1509</v>
+        <v>1490</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>7.96</v>
+        <v>5.83</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>29.06</v>
+        <v>22.34</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>9.84</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="25">
@@ -2005,7 +2005,7 @@
         <v>24</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>7</v>
@@ -2014,118 +2014,118 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.82</v>
+        <v>2.36</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>104.9</v>
+        <v>82.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-104.08</v>
+        <v>-80.44</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>25.23</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>16.06</v>
+        <v>18.28</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>16.06</v>
+        <v>18.28</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1417</v>
+        <v>1426</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>5.24</v>
+        <v>5.52</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>7.92</v>
+        <v>9.99</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9638</v>
+        <v>7808</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>42.71</v>
+        <v>14.76</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>39.46</v>
+        <v>50.41</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>3.25</v>
+        <v>-35.65</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>22.93</v>
+        <v>24.37</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>32</v>
+        <v>28.23</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>32</v>
+        <v>28.23</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1473</v>
+        <v>1461</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>7.7</v>
+        <v>5.23</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>15.2</v>
+        <v>12.97</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>9.1</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>10642</v>
+        <v>3234</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>6</v>
@@ -2134,111 +2134,111 @@
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-6.58</v>
+        <v>12.45</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>37.29</v>
+        <v>47.8</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-43.87</v>
+        <v>-35.36</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>25.63</v>
+        <v>22.62</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>13.71</v>
+        <v>16.41</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>13.71</v>
+        <v>16.41</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1407</v>
+        <v>1418</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>5.3</v>
+        <v>4.06</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>3.89</v>
+        <v>8.43</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>4.53</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7221</v>
+        <v>4325</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7.65</v>
+        <v>50.4</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>95.76000000000001</v>
+        <v>141.2</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-88.11</v>
+        <v>-90.8</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>8.82</v>
+        <v>32.52</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>25.32</v>
+        <v>39.4</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>25.32</v>
+        <v>39.4</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1453</v>
+        <v>1492</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>5.84</v>
+        <v>10.04</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>11.6</v>
+        <v>20.5</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>7.87</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>5256</v>
+        <v>7221</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -2248,57 +2248,57 @@
         <v>4</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.42</v>
+        <v>12.71</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>51.91</v>
+        <v>92.14</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-48.48</v>
+        <v>-79.44</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>35.18</v>
+        <v>8.82</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>16.56</v>
+        <v>24.92</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.56</v>
+        <v>24.92</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1419</v>
+        <v>1451</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>4.16</v>
+        <v>4.78</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>8.56</v>
+        <v>12.55</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>3.84</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9566</v>
+        <v>9638</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2317,178 +2317,178 @@
         <v>17</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11.89</v>
+        <v>40.25</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>38.88</v>
+        <v>48.62</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-26.98</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>39.97</v>
+        <v>22.93</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>19.92</v>
+        <v>31.39</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>19.92</v>
+        <v>31.39</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1433</v>
+        <v>1471</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>3.85</v>
+        <v>7.84</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>8.73</v>
+        <v>15.65</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>7.34</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7818</v>
+        <v>9566</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-1.75</v>
+        <v>10.2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>91.53</v>
+        <v>55.98</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-93.29000000000001</v>
+        <v>-45.79</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>32.45</v>
+        <v>39.97</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>21.54</v>
+        <v>19.04</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>21.54</v>
+        <v>19.04</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1439</v>
+        <v>1429</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>6.76</v>
+        <v>4.24</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>5.02</v>
+        <v>7.98</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>9.76</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>10181</v>
+        <v>8285</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24.75</v>
+        <v>18.21</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>49.48</v>
+        <v>108.72</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-24.73</v>
+        <v>-90.51000000000001</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>23.43</v>
+        <v>39.07</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>18.74</v>
+        <v>21.36</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>18.74</v>
+        <v>21.36</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1428</v>
+        <v>1438</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>5.68</v>
+        <v>0.92</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>7.69</v>
+        <v>11.25</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>5.37</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>4325</v>
+        <v>10181</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -2497,34 +2497,34 @@
         <v>15</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>50.95</v>
+        <v>23.51</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>158.41</v>
+        <v>55.33</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-107.46</v>
+        <v>-31.82</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>32.52</v>
+        <v>23.43</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>37.17</v>
+        <v>18.47</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>37.17</v>
+        <v>18.47</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1486</v>
+        <v>1427</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>9.76</v>
+        <v>5.46</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>18.43</v>
+        <v>6.84</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>8.98</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="34">
@@ -2548,43 +2548,43 @@
         <v>3</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11.8</v>
+        <v>11.63</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>47.53</v>
+        <v>71.45</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-35.73</v>
+        <v>-59.82</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>17.6</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>24.48</v>
+        <v>21.72</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>24.48</v>
+        <v>21.72</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1450</v>
+        <v>1439</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>7.15</v>
+        <v>5.49</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>11.87</v>
+        <v>11.41</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>5.46</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="35">
@@ -2617,13 +2617,13 @@
         <v>14</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>5.21</v>
+        <v>3.97</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>34.52</v>
+        <v>39.33</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-29.31</v>
+        <v>-35.36</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>27.39</v>
@@ -2649,16 +2649,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10664</v>
+        <v>904</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2677,48 +2677,48 @@
         <v>13</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-20.06</v>
+        <v>-15.91</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>74.76000000000001</v>
+        <v>52.78</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-94.81999999999999</v>
+        <v>-68.69</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>21.7</v>
+        <v>27.91</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>19.52</v>
+        <v>-1.31</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>19.52</v>
+        <v>-1.31</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1432</v>
+        <v>1324</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>10.5</v>
+        <v>-6.49</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>3.12</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>8285</v>
+        <v>7818</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2728,117 +2728,117 @@
         <v>3</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>24.03</v>
+        <v>0.65</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>117.69</v>
+        <v>86.92</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-93.66</v>
+        <v>-86.27</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>39.07</v>
+        <v>32.45</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>23.05</v>
+        <v>19.56</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>23.05</v>
+        <v>19.56</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.9</v>
+        <v>6.92</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>13.77</v>
+        <v>4.65</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>7.38</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7809</v>
+        <v>10664</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29.81</v>
+        <v>-14.78</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>127.41</v>
+        <v>70.41</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-97.59999999999999</v>
+        <v>-85.19</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>23.83</v>
+        <v>21.7</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>33.01</v>
+        <v>19.12</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>33.01</v>
+        <v>19.12</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1476</v>
+        <v>1430</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>2.77</v>
+        <v>4.84</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>16.63</v>
+        <v>11.44</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>13.61</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>904</v>
+        <v>7658</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -2848,64 +2848,64 @@
         <v>2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>-12.63</v>
+        <v>12.67</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>69.06</v>
+        <v>54.65</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-81.69</v>
+        <v>-41.98</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>27.91</v>
+        <v>14.34</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>-0.3</v>
+        <v>21.13</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>-0.3</v>
+        <v>21.13</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1331</v>
+        <v>1438</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>6.58</v>
+        <v>2.83</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>-5.69</v>
+        <v>12.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>-1.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7658</v>
+        <v>7809</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>9</v>
@@ -2914,37 +2914,37 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>6.68</v>
+        <v>29.91</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>47.02</v>
+        <v>110.62</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-40.33</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>14.34</v>
+        <v>23.83</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>16.45</v>
+        <v>32.05</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>16.45</v>
+        <v>32.05</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1419</v>
+        <v>1473</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>11</v>
+        <v>16.69</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>2.71</v>
+        <v>12.49</v>
       </c>
     </row>
   </sheetData>
@@ -3032,22 +3032,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>150.76</v>
+        <v>151.93</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>150.76</v>
+        <v>151.93</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.52</v>
+        <v>31.13</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>83.05</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>36.19</v>
+        <v>36.85</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="3">
@@ -3063,22 +3063,22 @@
         <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>138.69</v>
+        <v>143.64</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>138.69</v>
+        <v>143.64</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>30.97</v>
+        <v>30.5</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>83.79000000000001</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>23.92</v>
+        <v>26.68</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1676</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="4">
@@ -3125,19 +3125,19 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>131.87</v>
+        <v>133.04</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>131.87</v>
+        <v>133.04</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.8</v>
+        <v>23.41</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>75.95</v>
+        <v>76.86</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>32.11</v>
+        <v>32.77</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1667</v>
@@ -3145,95 +3145,95 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>68.89</v>
+        <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>114.36</v>
+        <v>127.31</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>114.36</v>
+        <v>127.31</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>24.77</v>
+        <v>22.88</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>62.97</v>
+        <v>78.59</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26.63</v>
+        <v>25.84</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1644</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>5166</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>105.81</v>
+        <v>112.68</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>105.81</v>
+        <v>112.68</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>19.83</v>
+        <v>23.79</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>61.97</v>
+        <v>60.45</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>24.01</v>
+        <v>28.44</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1629</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1023</v>
+        <v>5166</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>68.08</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>104.24</v>
+        <v>102.78</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>104.24</v>
+        <v>102.78</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>18.68</v>
+        <v>17.95</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>65.52</v>
+        <v>60.68</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20.04</v>
+        <v>24.15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1626</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="9">
@@ -3269,95 +3269,95 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2771</v>
+        <v>3875</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>53.52</v>
+        <v>50.66</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>79.63</v>
+        <v>94.66</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>79.63</v>
+        <v>94.66</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>13.11</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>52.94</v>
+        <v>58.71</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>18.66</v>
+        <v>22.83</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1577</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>78.95</v>
+        <v>80.09</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>78.95</v>
+        <v>80.09</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>13.31</v>
+        <v>7.65</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>39.02</v>
+        <v>51.35</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>26.62</v>
+        <v>21.09</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1576</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3875</v>
+        <v>858</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>50.66</v>
+        <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>75.17</v>
+        <v>77.95</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>75.17</v>
+        <v>77.95</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.83</v>
+        <v>12.68</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>48.11</v>
+        <v>38.22</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>18.22</v>
+        <v>27.05</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1568</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="13">
@@ -3373,22 +3373,22 @@
         <v>59.73</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>18.16</v>
+        <v>17.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>30.7</v>
+        <v>31.64</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>19.35</v>
+        <v>19.06</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="14">
@@ -3404,22 +3404,22 @@
         <v>44.43</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>60.89</v>
+        <v>58.59</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>60.89</v>
+        <v>58.59</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>16.47</v>
+        <v>14.44</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>32.38</v>
+        <v>30.34</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>12.03</v>
+        <v>13.82</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1540</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="15">
@@ -3435,22 +3435,22 @@
         <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>56.3</v>
+        <v>55.69</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>56.3</v>
+        <v>55.69</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>9.119999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>30.07</v>
+        <v>30.52</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.11</v>
+        <v>15.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1530</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="16">
@@ -3466,22 +3466,22 @@
         <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>55.55</v>
+        <v>54.67</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>55.55</v>
+        <v>54.67</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6.85</v>
+        <v>7.24</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>34.42</v>
+        <v>33.67</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.28</v>
+        <v>13.76</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="17">
@@ -3528,84 +3528,84 @@
         <v>38.55</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>46.86</v>
+        <v>45.18</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46.86</v>
+        <v>45.18</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7.96</v>
+        <v>6.98</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>29.06</v>
+        <v>26.54</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.84</v>
+        <v>11.65</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1509</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>4325</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.21</v>
+        <v>32.52</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>39.76</v>
+        <v>39.4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>39.76</v>
+        <v>39.4</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.44</v>
+        <v>10.04</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>23.09</v>
+        <v>20.5</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.22</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4325</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>32.52</v>
+        <v>27.21</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.17</v>
+        <v>38.87</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.17</v>
+        <v>38.87</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>9.76</v>
+        <v>5.83</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18.43</v>
+        <v>22.34</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.98</v>
+        <v>10.7</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1486</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="21">
@@ -3621,22 +3621,22 @@
         <v>23.83</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>33.01</v>
+        <v>32.05</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>33.01</v>
+        <v>32.05</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>16.63</v>
+        <v>16.69</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>13.61</v>
+        <v>12.49</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1476</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="22">
@@ -3652,22 +3652,22 @@
         <v>22.93</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>32</v>
+        <v>31.39</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>32</v>
+        <v>31.39</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>7.7</v>
+        <v>7.84</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>15.2</v>
+        <v>15.65</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.1</v>
+        <v>7.89</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="23">
@@ -3683,22 +3683,22 @@
         <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>31.88</v>
+        <v>30.92</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>31.88</v>
+        <v>30.92</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.95</v>
+        <v>12.05</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.58</v>
+        <v>7.63</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>12.35</v>
+        <v>11.23</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1472</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="24">
@@ -3714,22 +3714,22 @@
         <v>24.37</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>29.86</v>
+        <v>28.23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>29.86</v>
+        <v>28.23</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.02</v>
+        <v>5.23</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>12.93</v>
+        <v>12.97</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>11.91</v>
+        <v>10.04</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1467</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="25">
@@ -3807,363 +3807,363 @@
         <v>8.82</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>25.32</v>
+        <v>24.92</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>25.32</v>
+        <v>24.92</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.84</v>
+        <v>4.78</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>11.6</v>
+        <v>12.55</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.87</v>
+        <v>7.58</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9549</v>
+        <v>11399</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>17.6</v>
+        <v>23.74</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>24.48</v>
+        <v>22.47</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>24.48</v>
+        <v>22.47</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>7.15</v>
+        <v>4.61</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>11.87</v>
+        <v>13.43</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.46</v>
+        <v>4.43</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1450</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>8285</v>
+        <v>5256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>39.07</v>
+        <v>35.18</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>23.05</v>
+        <v>21.96</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>23.05</v>
+        <v>21.96</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.9</v>
+        <v>4.08</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>13.77</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7.38</v>
+        <v>8.66</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1445</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>11399</v>
+        <v>9549</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>23.74</v>
+        <v>17.6</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>22.46</v>
+        <v>21.72</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.46</v>
+        <v>21.72</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5.39</v>
+        <v>5.49</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>13.01</v>
+        <v>11.41</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4.06</v>
+        <v>4.81</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1443</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7818</v>
+        <v>8285</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>32.45</v>
+        <v>39.07</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>21.54</v>
+        <v>21.36</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>21.54</v>
+        <v>21.36</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6.76</v>
+        <v>0.92</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5.02</v>
+        <v>11.25</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>9.76</v>
+        <v>9.19</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9566</v>
+        <v>7658</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>39.97</v>
+        <v>14.34</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>19.92</v>
+        <v>21.13</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>19.92</v>
+        <v>21.13</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>3.85</v>
+        <v>2.83</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8.73</v>
+        <v>12.4</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>7.34</v>
+        <v>5.9</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1433</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10664</v>
+        <v>7818</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>21.7</v>
+        <v>32.45</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>19.52</v>
+        <v>19.56</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.52</v>
+        <v>19.56</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>5.9</v>
+        <v>6.92</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>10.5</v>
+        <v>4.65</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>3.12</v>
+        <v>7.99</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10181</v>
+        <v>10664</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>23.43</v>
+        <v>21.7</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>18.74</v>
+        <v>19.12</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.74</v>
+        <v>19.12</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5.68</v>
+        <v>4.84</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.69</v>
+        <v>11.44</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5.37</v>
+        <v>2.83</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1428</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>3234</v>
+        <v>9566</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>22.62</v>
+        <v>39.97</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>18.43</v>
+        <v>19.04</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.43</v>
+        <v>19.04</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.63</v>
+        <v>4.24</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>9.65</v>
+        <v>7.98</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4.15</v>
+        <v>6.82</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1427</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5256</v>
+        <v>10181</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>35.18</v>
+        <v>23.43</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16.56</v>
+        <v>18.47</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>16.56</v>
+        <v>18.47</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4.16</v>
+        <v>5.46</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.56</v>
+        <v>6.84</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3.84</v>
+        <v>6.17</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1419</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7658</v>
+        <v>7256</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>14.34</v>
+        <v>25.23</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>16.45</v>
+        <v>18.28</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>16.45</v>
+        <v>18.28</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2.74</v>
+        <v>5.52</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>11</v>
+        <v>9.99</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1419</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7256</v>
+        <v>3234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25.23</v>
+        <v>22.62</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>16.06</v>
+        <v>16.41</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>16.06</v>
+        <v>16.41</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5.24</v>
+        <v>4.06</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>7.92</v>
+        <v>8.43</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>2.9</v>
+        <v>3.91</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="39">
@@ -4179,22 +4179,22 @@
         <v>25.63</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>13.71</v>
+        <v>14.9</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.71</v>
+        <v>14.9</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>5.3</v>
+        <v>4.13</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3.89</v>
+        <v>5.22</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.53</v>
+        <v>5.55</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1407</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="40">
@@ -4210,22 +4210,22 @@
         <v>27.91</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-0.3</v>
+        <v>-1.31</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-0.3</v>
+        <v>-1.31</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>6.58</v>
+        <v>5.95</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-5.69</v>
+        <v>-6.49</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-1.2</v>
+        <v>-0.77</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1331</v>
+        <v>1324</v>
       </c>
     </row>
   </sheetData>
@@ -4286,13 +4286,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>185.19</v>
+        <v>187.47</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43.64</v>
+        <v>44.72</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>141.54</v>
+        <v>142.75</v>
       </c>
     </row>
     <row r="3">
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>177.15</v>
+        <v>175.88</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-2.98</v>
+        <v>-5.47</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>180.12</v>
+        <v>181.35</v>
       </c>
     </row>
     <row r="4">
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>163.97</v>
+        <v>170.14</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>40.57</v>
+        <v>33.12</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>123.4</v>
+        <v>137.02</v>
       </c>
     </row>
     <row r="5">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>139.05</v>
+        <v>139.14</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>22.19</v>
+        <v>33.39</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>116.86</v>
+        <v>105.75</v>
       </c>
     </row>
     <row r="6">
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>133.74</v>
+        <v>132.96</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>57.05</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>76.69</v>
+        <v>68.77</v>
       </c>
     </row>
     <row r="7">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>130.49</v>
+        <v>124.04</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>51.58</v>
+        <v>42.12</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>78.91</v>
+        <v>81.93000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>120.78</v>
+        <v>119.38</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>72.89</v>
+        <v>47.13</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>47.89</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="9">
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>115.09</v>
+        <v>112.9</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>98.61</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>16.48</v>
+        <v>37.11</v>
       </c>
     </row>
     <row r="10">
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>110.31</v>
+        <v>107.89</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-15.7</v>
+        <v>13.28</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>126.01</v>
+        <v>94.61</v>
       </c>
     </row>
     <row r="11">
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>109.54</v>
+        <v>106.93</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>15.54</v>
+        <v>16.69</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>94</v>
+        <v>90.23999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -4476,51 +4476,51 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>91.55</v>
+        <v>92.84</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>71.93000000000001</v>
+        <v>67.88</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>19.63</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>72.81999999999999</v>
+        <v>70.86</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>11.02</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>61.79</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>66.61</v>
+        <v>69.56</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>69.06999999999999</v>
+        <v>21.67</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-2.46</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="15">
@@ -4533,13 +4533,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>66.55</v>
+        <v>64.92</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>17.35</v>
+        <v>26.84</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>49.21</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="16">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>63.75</v>
+        <v>57.96</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>85.83</v>
+        <v>72.03</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-22.08</v>
+        <v>-14.07</v>
       </c>
     </row>
     <row r="17">
@@ -4571,13 +4571,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>50.95</v>
+        <v>50.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>158.41</v>
+        <v>141.2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-107.46</v>
+        <v>-90.8</v>
       </c>
     </row>
     <row r="18">
@@ -4590,13 +4590,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>49.62</v>
+        <v>47.08</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>41.02</v>
+        <v>51.91</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>8.609999999999999</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="19">
@@ -4609,13 +4609,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>42.71</v>
+        <v>40.25</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>39.46</v>
+        <v>48.62</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>3.25</v>
+        <v>-8.380000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -4628,13 +4628,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>38.01</v>
+        <v>37.73</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>20.06</v>
+        <v>-2.17</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>17.96</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="21">
@@ -4647,51 +4647,51 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>30.74</v>
+        <v>34.43</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>39.68</v>
+        <v>63.69</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-8.94</v>
+        <v>-29.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8767</v>
+        <v>7809</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>30</v>
+        <v>29.91</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>15.32</v>
+        <v>110.62</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>14.69</v>
+        <v>-80.70999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7809</v>
+        <v>8767</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>29.81</v>
+        <v>29.51</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>127.41</v>
+        <v>25.66</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-97.59999999999999</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="24">
@@ -4704,13 +4704,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>24.75</v>
+        <v>23.51</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>49.48</v>
+        <v>55.33</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-24.73</v>
+        <v>-31.82</v>
       </c>
     </row>
     <row r="25">
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>24.03</v>
+        <v>18.21</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>117.69</v>
+        <v>108.72</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-93.66</v>
+        <v>-90.51000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -4742,13 +4742,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>14.27</v>
+        <v>15.93</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>48.94</v>
+        <v>47.48</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-34.67</v>
+        <v>-31.55</v>
       </c>
     </row>
     <row r="27">
@@ -4761,165 +4761,165 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>13.02</v>
+        <v>14.76</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>28.98</v>
+        <v>50.41</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-15.96</v>
+        <v>-35.65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>11399</v>
+        <v>5256</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>12.37</v>
+        <v>13.48</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>51.87</v>
+        <v>30.77</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-39.5</v>
+        <v>-17.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9566</v>
+        <v>7221</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>11.89</v>
+        <v>12.71</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>38.88</v>
+        <v>92.14</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-26.98</v>
+        <v>-79.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3234</v>
+        <v>7658</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>11.88</v>
+        <v>12.67</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>57.8</v>
+        <v>54.65</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-45.92</v>
+        <v>-41.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9549</v>
+        <v>3234</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11.8</v>
+        <v>12.45</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>47.53</v>
+        <v>47.8</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-35.73</v>
+        <v>-35.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7221</v>
+        <v>11399</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>7.65</v>
+        <v>12.45</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>95.76000000000001</v>
+        <v>58.04</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-88.11</v>
+        <v>-45.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7658</v>
+        <v>9549</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>6.68</v>
+        <v>11.63</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>47.02</v>
+        <v>71.45</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-40.33</v>
+        <v>-59.82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9671</v>
+        <v>9566</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5.21</v>
+        <v>10.2</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>34.52</v>
+        <v>55.98</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-29.31</v>
+        <v>-45.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>5256</v>
+        <v>9671</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>3.42</v>
+        <v>3.97</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>51.91</v>
+        <v>39.33</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-48.48</v>
+        <v>-35.36</v>
       </c>
     </row>
     <row r="36">
@@ -4932,13 +4932,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.82</v>
+        <v>2.36</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>104.9</v>
+        <v>82.8</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-104.08</v>
+        <v>-80.44</v>
       </c>
     </row>
     <row r="37">
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-1.75</v>
+        <v>0.65</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>91.53</v>
+        <v>86.92</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-93.29000000000001</v>
+        <v>-86.27</v>
       </c>
     </row>
     <row r="38">
@@ -4970,51 +4970,51 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-6.58</v>
+        <v>-4.65</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>37.29</v>
+        <v>43.96</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-43.87</v>
+        <v>-48.62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>904</v>
+        <v>10664</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-12.63</v>
+        <v>-14.78</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>69.06</v>
+        <v>70.41</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-81.69</v>
+        <v>-85.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>10664</v>
+        <v>904</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-20.06</v>
+        <v>-15.91</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>74.76000000000001</v>
+        <v>52.78</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-94.81999999999999</v>
+        <v>-68.69</v>
       </c>
     </row>
   </sheetData>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>2</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
@@ -5174,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -5182,24 +5182,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5166</v>
+        <v>4967</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -5207,24 +5207,24 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4967</v>
+        <v>2771</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -5232,24 +5232,24 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2771</v>
+        <v>3875</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -5257,24 +5257,24 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3875</v>
+        <v>1023</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -5282,18 +5282,18 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1023</v>
+        <v>7656</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -5307,24 +5307,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7656</v>
+        <v>5166</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -5340,16 +5340,16 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>5</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -5393,13 +5393,13 @@
         <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -5418,13 +5418,13 @@
         <v>6</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -5443,7 +5443,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -5457,24 +5457,24 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>7289</v>
+        <v>11399</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -5482,15 +5482,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7808</v>
+        <v>9206</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>5</v>
@@ -5499,7 +5499,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -5507,11 +5507,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9206</v>
+        <v>9685</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -5524,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -5532,15 +5532,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>8767</v>
+        <v>7289</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>5</v>
@@ -5549,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -5557,24 +5557,24 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>9685</v>
+        <v>5980</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -5582,24 +5582,24 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>11399</v>
+        <v>10642</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -5607,24 +5607,24 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3234</v>
+        <v>5256</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -5632,24 +5632,24 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5980</v>
+        <v>8767</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>7</v>
@@ -5674,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -5682,24 +5682,24 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9638</v>
+        <v>7808</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -5707,15 +5707,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10642</v>
+        <v>3234</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>6</v>
@@ -5724,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -5732,24 +5732,24 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7221</v>
+        <v>4325</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
@@ -5757,24 +5757,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5256</v>
+        <v>7221</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -5782,11 +5782,11 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9566</v>
+        <v>9638</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -5807,24 +5807,24 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7818</v>
+        <v>9566</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -5832,24 +5832,24 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>10181</v>
+        <v>8285</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -5857,18 +5857,18 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>4325</v>
+        <v>10181</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0</v>
@@ -5893,13 +5893,13 @@
         <v>3</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -5932,11 +5932,11 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>10664</v>
+        <v>904</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -5957,24 +5957,24 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>8285</v>
+        <v>7818</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
@@ -5982,24 +5982,24 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7809</v>
+        <v>10664</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -6007,24 +6007,24 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>904</v>
+        <v>7658</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -6032,15 +6032,15 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>7658</v>
+        <v>7809</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>9</v>
@@ -6049,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>185.19</v>
+        <v>187.47</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>43.64</v>
+        <v>44.72</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>141.54</v>
+        <v>142.75</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>177.15</v>
+        <v>175.88</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-2.98</v>
+        <v>-5.47</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>180.12</v>
+        <v>181.35</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>163.97</v>
+        <v>170.14</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>40.57</v>
+        <v>33.12</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>123.4</v>
+        <v>137.02</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6194,13 +6194,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>139.05</v>
+        <v>139.14</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>22.19</v>
+        <v>33.39</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>116.86</v>
+        <v>105.75</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>133.74</v>
+        <v>132.96</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>57.05</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>76.69</v>
+        <v>68.77</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6240,13 +6240,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>130.49</v>
+        <v>124.04</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>51.58</v>
+        <v>42.12</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>78.91</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>120.78</v>
+        <v>119.38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>72.89</v>
+        <v>47.13</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>47.89</v>
+        <v>72.25</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6286,13 +6286,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>115.09</v>
+        <v>112.9</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>98.61</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>16.48</v>
+        <v>37.11</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>110.31</v>
+        <v>107.89</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-15.7</v>
+        <v>13.28</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>126.01</v>
+        <v>94.61</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6332,13 +6332,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>109.54</v>
+        <v>106.93</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15.54</v>
+        <v>16.69</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>94</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>91.55</v>
+        <v>92.84</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>71.93000000000001</v>
+        <v>67.88</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>19.63</v>
+        <v>24.96</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6370,21 +6370,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>72.81999999999999</v>
+        <v>70.86</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11.02</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>61.79</v>
+        <v>6.54</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6393,21 +6393,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>66.61</v>
+        <v>69.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>69.06999999999999</v>
+        <v>21.67</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2.46</v>
+        <v>47.89</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6424,13 +6424,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>66.55</v>
+        <v>64.92</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>17.35</v>
+        <v>26.84</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>49.21</v>
+        <v>38.09</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>63.75</v>
+        <v>57.96</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>85.83</v>
+        <v>72.03</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-22.08</v>
+        <v>-14.07</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>50.95</v>
+        <v>50.4</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>158.41</v>
+        <v>141.2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-107.46</v>
+        <v>-90.8</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>49.62</v>
+        <v>47.08</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>41.02</v>
+        <v>51.91</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>8.609999999999999</v>
+        <v>-4.83</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6516,13 +6516,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>42.71</v>
+        <v>40.25</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>39.46</v>
+        <v>48.62</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3.25</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6539,13 +6539,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>38.01</v>
+        <v>37.73</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>20.06</v>
+        <v>-2.17</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>17.96</v>
+        <v>39.9</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6562,13 +6562,13 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.74</v>
+        <v>34.43</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>39.68</v>
+        <v>63.69</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-8.94</v>
+        <v>-29.26</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6577,21 +6577,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>8767</v>
+        <v>7809</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>30</v>
+        <v>29.91</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>15.32</v>
+        <v>110.62</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>14.69</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6600,21 +6600,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>7809</v>
+        <v>8767</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>29.81</v>
+        <v>29.51</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>127.41</v>
+        <v>25.66</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-97.59999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>24.75</v>
+        <v>23.51</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>49.48</v>
+        <v>55.33</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-24.73</v>
+        <v>-31.82</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6654,13 +6654,13 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>24.03</v>
+        <v>18.21</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>117.69</v>
+        <v>108.72</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-93.66</v>
+        <v>-90.51000000000001</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6677,13 +6677,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>14.27</v>
+        <v>15.93</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>48.94</v>
+        <v>47.48</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-34.67</v>
+        <v>-31.55</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6700,13 +6700,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>13.02</v>
+        <v>14.76</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>28.98</v>
+        <v>50.41</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-15.96</v>
+        <v>-35.65</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6715,21 +6715,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>11399</v>
+        <v>5256</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12.37</v>
+        <v>13.48</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>51.87</v>
+        <v>30.77</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-39.5</v>
+        <v>-17.29</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6738,21 +6738,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9566</v>
+        <v>7221</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.89</v>
+        <v>12.71</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>38.88</v>
+        <v>92.14</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-26.98</v>
+        <v>-79.44</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6761,21 +6761,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>3234</v>
+        <v>7658</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>11.88</v>
+        <v>12.67</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>57.8</v>
+        <v>54.65</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-45.92</v>
+        <v>-41.98</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6784,21 +6784,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9549</v>
+        <v>3234</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>11.8</v>
+        <v>12.45</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>47.53</v>
+        <v>47.8</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-35.73</v>
+        <v>-35.36</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6807,21 +6807,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7221</v>
+        <v>11399</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7.65</v>
+        <v>12.45</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>95.76000000000001</v>
+        <v>58.04</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-88.11</v>
+        <v>-45.59</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6830,21 +6830,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>7658</v>
+        <v>9549</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>6.68</v>
+        <v>11.63</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>47.02</v>
+        <v>71.45</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-40.33</v>
+        <v>-59.82</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -6853,21 +6853,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9671</v>
+        <v>9566</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5.21</v>
+        <v>10.2</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>34.52</v>
+        <v>55.98</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-29.31</v>
+        <v>-45.79</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -6876,21 +6876,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>5256</v>
+        <v>9671</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>3.42</v>
+        <v>3.97</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>51.91</v>
+        <v>39.33</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-48.48</v>
+        <v>-35.36</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -6907,13 +6907,13 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.82</v>
+        <v>2.36</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>104.9</v>
+        <v>82.8</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-104.08</v>
+        <v>-80.44</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -6930,13 +6930,13 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-1.75</v>
+        <v>0.65</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>91.53</v>
+        <v>86.92</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-93.29000000000001</v>
+        <v>-86.27</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-6.58</v>
+        <v>-4.65</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>37.29</v>
+        <v>43.96</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-43.87</v>
+        <v>-48.62</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -6968,21 +6968,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>904</v>
+        <v>10664</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-12.63</v>
+        <v>-14.78</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>69.06</v>
+        <v>70.41</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-81.69</v>
+        <v>-85.19</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -6991,21 +6991,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>10664</v>
+        <v>904</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-20.06</v>
+        <v>-15.91</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>74.76000000000001</v>
+        <v>52.78</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-94.81999999999999</v>
+        <v>-68.69</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>139.04</v>
+        <v>137.32</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>139.04</v>
+        <v>137.32</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25.58</v>
+        <v>25.41</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>79.39</v>
+        <v>77.77</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>34.07</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>142.96</v>
+        <v>145.64</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>142.96</v>
+        <v>145.64</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.01</v>
+        <v>30.87</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>86.04000000000001</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>26.9</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>151.26</v>
+        <v>153.94</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>151.26</v>
+        <v>153.94</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1692</v>
+        <v>1697</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>30.65</v>
+        <v>31.51</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>83.55</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>37.07</v>
+        <v>37.69</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>133.04</v>
+        <v>130.28</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>133.04</v>
+        <v>130.28</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>23.41</v>
+        <v>23.86</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>76.86</v>
+        <v>74.84</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>32.77</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>93.98</v>
+        <v>91.77</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>93.98</v>
+        <v>91.77</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>12.86</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>58.83</v>
+        <v>57.18</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>22.29</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>132.67</v>
+        <v>130.94</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>132.67</v>
+        <v>130.94</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>24.28</v>
+        <v>24.12</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>82.52</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.86</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>103.73</v>
+        <v>99.84</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>103.73</v>
+        <v>99.84</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>17.6</v>
+        <v>17.36</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>61.02</v>
+        <v>58.66</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>25.11</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>114.35</v>
+        <v>111.59</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>114.35</v>
+        <v>111.59</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1643</v>
+        <v>1638</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>23.61</v>
+        <v>24.05</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>61.44</v>
+        <v>59.41</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>29.3</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="10">
@@ -1129,22 +1129,22 @@
         <v>53.52</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>77.63</v>
+        <v>76.73</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>77.63</v>
+        <v>76.73</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>7.64</v>
+        <v>7.82</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>49.74</v>
+        <v>49.19</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>20.25</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="11">
@@ -1189,22 +1189,22 @@
         <v>50.91</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>93.68000000000001</v>
+        <v>91.47</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>93.68000000000001</v>
+        <v>91.47</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.72</v>
+        <v>10.71</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>57.61</v>
+        <v>55.97</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.34</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="12">
@@ -1249,22 +1249,22 @@
         <v>44.43</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>57.51</v>
+        <v>58.14</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>57.51</v>
+        <v>58.14</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>14.51</v>
+        <v>14.74</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>29.41</v>
+        <v>30.21</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>13.59</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="13">
@@ -1309,22 +1309,22 @@
         <v>29.21</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>55.36</v>
+        <v>54.22</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>55.36</v>
+        <v>54.22</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>7.43</v>
+        <v>7.1</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>32.99</v>
+        <v>32.25</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>14.94</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="14">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>77.09</v>
+        <v>73.2</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>77.09</v>
+        <v>73.2</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1571</v>
+        <v>1563</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>11.7</v>
+        <v>11.46</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>38.9</v>
+        <v>36.53</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>26.5</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="15">
@@ -1429,22 +1429,22 @@
         <v>59.73</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>67.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>67.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>17.1</v>
+        <v>17.28</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>31.64</v>
+        <v>31.09</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>19.06</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="16">
@@ -1489,22 +1489,22 @@
         <v>28.04</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>59.31</v>
+        <v>58.16</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>59.31</v>
+        <v>58.16</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>10.59</v>
+        <v>10.26</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>32.52</v>
+        <v>31.79</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>16.19</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="17">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>44.36</v>
+        <v>40.47</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>44.36</v>
+        <v>40.47</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1503</v>
+        <v>1493</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>6.61</v>
+        <v>6.37</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>25.53</v>
+        <v>23.16</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>12.23</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="19">
@@ -1669,22 +1669,22 @@
         <v>38.55</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>44.09</v>
+        <v>44.73</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>44.09</v>
+        <v>44.73</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>7.06</v>
+        <v>7.28</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>25.61</v>
+        <v>26.41</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>11.42</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="20">
@@ -1729,22 +1729,22 @@
         <v>25.63</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>14.22</v>
+        <v>16.9</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>14.22</v>
+        <v>16.9</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1408</v>
+        <v>1420</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>3.65</v>
+        <v>4.51</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>4.81</v>
+        <v>6</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>5.77</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="21">
@@ -1789,22 +1789,22 @@
         <v>27.75</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>50.99</v>
+        <v>49.84</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>50.99</v>
+        <v>49.84</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>21.83</v>
+        <v>21.5</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>11.65</v>
+        <v>10.91</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>17.52</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="22">
@@ -2209,22 +2209,22 @@
         <v>32.52</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>38.72</v>
+        <v>36.51</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>38.72</v>
+        <v>36.51</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>20.61</v>
+        <v>18.97</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>8.31</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="29">
@@ -2269,22 +2269,22 @@
         <v>23.43</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>20.91</v>
+        <v>19.18</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>20.91</v>
+        <v>19.18</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1436</v>
+        <v>1429</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.73</v>
+        <v>5.57</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>8.09</v>
+        <v>6.47</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>7.08</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="30">
@@ -2389,22 +2389,22 @@
         <v>22.93</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>28.93</v>
+        <v>28.03</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>28.93</v>
+        <v>28.03</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>7.84</v>
+        <v>8.01</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>14.04</v>
+        <v>13.49</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>7.05</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="32">
@@ -2449,22 +2449,22 @@
         <v>27.39</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>29.5</v>
+        <v>26.74</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>29.5</v>
+        <v>26.74</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1465</v>
+        <v>1456</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>7.22</v>
+        <v>7.67</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>16.25</v>
+        <v>14.23</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>6.03</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="33">
@@ -2509,22 +2509,22 @@
         <v>39.97</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>17.96</v>
+        <v>18.59</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>17.96</v>
+        <v>18.59</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.31</v>
+        <v>4.54</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>7.05</v>
+        <v>7.85</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>6.59</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="34">
@@ -3032,22 +3032,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>151.26</v>
+        <v>153.94</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>151.26</v>
+        <v>153.94</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.65</v>
+        <v>31.51</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>83.55</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>37.07</v>
+        <v>37.69</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1692</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="3">
@@ -3063,22 +3063,22 @@
         <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>142.96</v>
+        <v>145.64</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>142.96</v>
+        <v>145.64</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>30.01</v>
+        <v>30.87</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>86.04000000000001</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>26.9</v>
+        <v>27.53</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1680</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="4">
@@ -3094,84 +3094,84 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>139.04</v>
+        <v>137.32</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>139.04</v>
+        <v>137.32</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25.58</v>
+        <v>25.41</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>79.39</v>
+        <v>77.77</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>34.07</v>
+        <v>34.14</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1675</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2075</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>133.04</v>
+        <v>130.94</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>133.04</v>
+        <v>130.94</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.41</v>
+        <v>24.12</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>76.86</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>32.77</v>
+        <v>25.93</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1667</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>68.08</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>132.67</v>
+        <v>130.28</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>132.67</v>
+        <v>130.28</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>24.28</v>
+        <v>23.86</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>82.52</v>
+        <v>74.84</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.86</v>
+        <v>31.59</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="7">
@@ -3187,22 +3187,22 @@
         <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>114.35</v>
+        <v>111.59</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>114.35</v>
+        <v>111.59</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>23.61</v>
+        <v>24.05</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>61.44</v>
+        <v>59.41</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>29.3</v>
+        <v>28.12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1643</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="8">
@@ -3218,22 +3218,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>103.73</v>
+        <v>99.84</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>103.73</v>
+        <v>99.84</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17.6</v>
+        <v>17.36</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.02</v>
+        <v>58.66</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>25.11</v>
+        <v>23.83</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1623</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="9">
@@ -3249,22 +3249,22 @@
         <v>50.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>93.98</v>
+        <v>91.77</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>93.98</v>
+        <v>91.77</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>12.86</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>58.83</v>
+        <v>57.18</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>22.29</v>
+        <v>21.73</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1604</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="10">
@@ -3280,22 +3280,22 @@
         <v>50.91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>93.68000000000001</v>
+        <v>91.47</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>93.68000000000001</v>
+        <v>91.47</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.72</v>
+        <v>10.71</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>57.61</v>
+        <v>55.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25.34</v>
+        <v>24.79</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1603</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="11">
@@ -3311,22 +3311,22 @@
         <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>77.63</v>
+        <v>76.73</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>77.63</v>
+        <v>76.73</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7.64</v>
+        <v>7.82</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>49.74</v>
+        <v>49.19</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>20.25</v>
+        <v>19.72</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1572</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="12">
@@ -3342,22 +3342,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>77.09</v>
+        <v>73.2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>77.09</v>
+        <v>73.2</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>11.7</v>
+        <v>11.46</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>38.9</v>
+        <v>36.53</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>26.5</v>
+        <v>25.21</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1571</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="13">
@@ -3373,22 +3373,22 @@
         <v>59.73</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>67.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>67.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17.1</v>
+        <v>17.28</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>31.64</v>
+        <v>31.09</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>19.06</v>
+        <v>18.53</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1553</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="14">
@@ -3404,22 +3404,22 @@
         <v>28.04</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>59.31</v>
+        <v>58.16</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>59.31</v>
+        <v>58.16</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10.59</v>
+        <v>10.26</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>32.52</v>
+        <v>31.79</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>16.19</v>
+        <v>16.11</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="15">
@@ -3435,22 +3435,22 @@
         <v>44.43</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>57.51</v>
+        <v>58.14</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>57.51</v>
+        <v>58.14</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>14.51</v>
+        <v>14.74</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>29.41</v>
+        <v>30.21</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.59</v>
+        <v>13.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="16">
@@ -3466,22 +3466,22 @@
         <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>55.36</v>
+        <v>54.22</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>55.36</v>
+        <v>54.22</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.43</v>
+        <v>7.1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>32.99</v>
+        <v>32.25</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.94</v>
+        <v>14.86</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1527</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="17">
@@ -3497,50 +3497,50 @@
         <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>50.99</v>
+        <v>49.84</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>50.99</v>
+        <v>49.84</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>21.83</v>
+        <v>21.5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>11.65</v>
+        <v>10.91</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.52</v>
+        <v>17.44</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8767</v>
+        <v>5980</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>27.21</v>
+        <v>38.55</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>44.36</v>
+        <v>44.73</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44.36</v>
+        <v>44.73</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6.61</v>
+        <v>7.28</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>25.53</v>
+        <v>26.41</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>12.23</v>
+        <v>11.03</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>1503</v>
@@ -3548,33 +3548,33 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>5980</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>38.55</v>
+        <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>44.09</v>
+        <v>40.47</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>44.09</v>
+        <v>40.47</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>7.06</v>
+        <v>6.37</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>25.61</v>
+        <v>23.16</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.42</v>
+        <v>10.94</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1502</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="20">
@@ -3590,22 +3590,22 @@
         <v>32.52</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>38.72</v>
+        <v>36.51</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>38.72</v>
+        <v>36.51</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20.61</v>
+        <v>18.97</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.31</v>
+        <v>7.76</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1489</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="21">
@@ -3641,64 +3641,64 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9671</v>
+        <v>7289</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>27.39</v>
+        <v>33.29</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>29.5</v>
+        <v>29.12</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>29.5</v>
+        <v>29.12</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>7.22</v>
+        <v>11.43</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>16.25</v>
+        <v>7.97</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>6.03</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7289</v>
+        <v>7808</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>33.29</v>
+        <v>24.37</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>29.12</v>
+        <v>28.23</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>29.12</v>
+        <v>28.23</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.43</v>
+        <v>5.23</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.97</v>
+        <v>12.97</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>9.720000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1464</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="24">
@@ -3714,53 +3714,53 @@
         <v>22.93</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.93</v>
+        <v>28.03</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.93</v>
+        <v>28.03</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7.84</v>
+        <v>8.01</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>14.04</v>
+        <v>13.49</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>7.05</v>
+        <v>6.52</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1463</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>7808</v>
+        <v>9671</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>24.37</v>
+        <v>27.39</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>28.23</v>
+        <v>26.74</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>28.23</v>
+        <v>26.74</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5.23</v>
+        <v>7.67</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>12.97</v>
+        <v>14.23</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.04</v>
+        <v>4.84</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1461</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="26">
@@ -3982,64 +3982,64 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10181</v>
+        <v>7818</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>23.43</v>
+        <v>32.45</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>20.91</v>
+        <v>19.56</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>20.91</v>
+        <v>19.56</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>5.73</v>
+        <v>6.92</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>8.09</v>
+        <v>4.65</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.08</v>
+        <v>7.99</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1436</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7818</v>
+        <v>10181</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>32.45</v>
+        <v>23.43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.56</v>
+        <v>19.18</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.56</v>
+        <v>19.18</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>6.92</v>
+        <v>5.57</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>4.65</v>
+        <v>6.47</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>7.99</v>
+        <v>7.15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="35">
@@ -4075,126 +4075,126 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7256</v>
+        <v>9566</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>25.23</v>
+        <v>39.97</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>18.28</v>
+        <v>18.59</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>18.28</v>
+        <v>18.59</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.52</v>
+        <v>4.54</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>9.99</v>
+        <v>7.85</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>2.78</v>
+        <v>6.2</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>9566</v>
+        <v>7256</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>39.97</v>
+        <v>25.23</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>17.96</v>
+        <v>18.28</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>17.96</v>
+        <v>18.28</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4.31</v>
+        <v>5.52</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>7.05</v>
+        <v>9.99</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>6.59</v>
+        <v>2.78</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1424</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3234</v>
+        <v>10642</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22.62</v>
+        <v>25.63</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>16.41</v>
+        <v>16.9</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>16.41</v>
+        <v>16.9</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4.06</v>
+        <v>4.51</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8.43</v>
+        <v>6</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3.91</v>
+        <v>6.4</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1418</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>10642</v>
+        <v>3234</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>25.63</v>
+        <v>22.62</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>14.22</v>
+        <v>16.41</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>14.22</v>
+        <v>16.41</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3.65</v>
+        <v>4.06</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4.81</v>
+        <v>8.43</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>5.77</v>
+        <v>3.91</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1408</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="40">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>137.32</v>
+        <v>137.64</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>137.32</v>
+        <v>137.64</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>1673</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25.41</v>
+        <v>25.54</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>77.77</v>
+        <v>78.03</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>34.14</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>145.64</v>
+        <v>145.74</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>145.64</v>
+        <v>145.74</v>
       </c>
       <c r="O3" s="3" t="n">
         <v>1683</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.87</v>
+        <v>30.72</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>87.23999999999999</v>
+        <v>87.59</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>27.53</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>153.94</v>
+        <v>154.04</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>153.94</v>
+        <v>154.04</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>1697</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>31.51</v>
+        <v>31.35</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>84.73999999999999</v>
+        <v>85.09</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>37.69</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>130.28</v>
+        <v>129.64</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>130.28</v>
+        <v>129.64</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>23.86</v>
+        <v>23.77</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>74.84</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>31.59</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>91.77</v>
+        <v>92.53</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>91.77</v>
+        <v>92.53</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>12.86</v>
+        <v>12.94</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>57.18</v>
+        <v>57.36</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>21.73</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>130.94</v>
+        <v>131.27</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>130.94</v>
+        <v>131.27</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>1665</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>24.12</v>
+        <v>24.25</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>81.16</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.93</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>99.84</v>
+        <v>99.62</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>99.84</v>
+        <v>99.62</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1615</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>17.36</v>
+        <v>17.38</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>58.66</v>
+        <v>57.69</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>23.83</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>111.59</v>
+        <v>110.94</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>111.59</v>
+        <v>110.94</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>24.05</v>
+        <v>23.97</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>28.12</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="10">
@@ -1189,22 +1189,22 @@
         <v>50.91</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>91.47</v>
+        <v>92.23</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>91.47</v>
+        <v>92.23</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.71</v>
+        <v>10.79</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>55.97</v>
+        <v>56.14</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>24.79</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="12">
@@ -1249,22 +1249,22 @@
         <v>44.43</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>58.14</v>
+        <v>58.22</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>58.14</v>
+        <v>58.22</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>1532</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>14.74</v>
+        <v>14.97</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>30.21</v>
+        <v>30.2</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>13.2</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="13">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>73.2</v>
+        <v>72.98</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>73.2</v>
+        <v>72.98</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>11.46</v>
+        <v>11.48</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>36.53</v>
+        <v>35.56</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>25.21</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="15">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>40.47</v>
+        <v>40.25</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>40.47</v>
+        <v>40.25</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>1493</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>23.16</v>
+        <v>22.19</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>10.94</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="19">
@@ -1669,22 +1669,22 @@
         <v>38.55</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>44.73</v>
+        <v>44.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>44.73</v>
+        <v>44.8</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>1503</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>7.28</v>
+        <v>7.51</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>26.41</v>
+        <v>26.4</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>11.03</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="20">
@@ -1729,22 +1729,22 @@
         <v>25.63</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>1420</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>4.51</v>
+        <v>4.36</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>6.4</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="21">
@@ -2209,22 +2209,22 @@
         <v>32.52</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>36.51</v>
+        <v>37.27</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>36.51</v>
+        <v>37.27</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>18.97</v>
+        <v>19.14</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>7.76</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="29">
@@ -2269,22 +2269,22 @@
         <v>23.43</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>19.18</v>
+        <v>19.51</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>19.18</v>
+        <v>19.51</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.57</v>
+        <v>5.7</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>6.47</v>
+        <v>6.74</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>7.15</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="30">
@@ -2449,22 +2449,22 @@
         <v>27.39</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>26.74</v>
+        <v>26.09</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>26.74</v>
+        <v>26.09</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>7.67</v>
+        <v>7.58</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>14.23</v>
+        <v>14.13</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>4.84</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="33">
@@ -2509,22 +2509,22 @@
         <v>39.97</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>18.59</v>
+        <v>18.67</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>18.59</v>
+        <v>18.67</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>1427</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.54</v>
+        <v>4.77</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>7.85</v>
+        <v>7.84</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="34">
@@ -3032,19 +3032,19 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>153.94</v>
+        <v>154.04</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>153.94</v>
+        <v>154.04</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.51</v>
+        <v>31.35</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>84.73999999999999</v>
+        <v>85.09</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>37.69</v>
+        <v>37.59</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1697</v>
@@ -3063,19 +3063,19 @@
         <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>145.64</v>
+        <v>145.74</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>145.64</v>
+        <v>145.74</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>30.87</v>
+        <v>30.72</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>87.23999999999999</v>
+        <v>87.59</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>27.53</v>
+        <v>27.43</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>1683</v>
@@ -3094,19 +3094,19 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>137.32</v>
+        <v>137.64</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>137.32</v>
+        <v>137.64</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25.41</v>
+        <v>25.54</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>77.77</v>
+        <v>78.03</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>34.14</v>
+        <v>34.07</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1673</v>
@@ -3125,19 +3125,19 @@
         <v>68.08</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>130.94</v>
+        <v>131.27</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>130.94</v>
+        <v>131.27</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>24.12</v>
+        <v>24.25</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>81.16</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>25.93</v>
+        <v>25.86</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1665</v>
@@ -3156,22 +3156,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>130.28</v>
+        <v>129.64</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>130.28</v>
+        <v>129.64</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>23.86</v>
+        <v>23.77</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>74.84</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>31.59</v>
+        <v>31.12</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="7">
@@ -3187,22 +3187,22 @@
         <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>111.59</v>
+        <v>110.94</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>111.59</v>
+        <v>110.94</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>24.05</v>
+        <v>23.97</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>28.12</v>
+        <v>27.66</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="8">
@@ -3218,19 +3218,19 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>99.84</v>
+        <v>99.62</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>99.84</v>
+        <v>99.62</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17.36</v>
+        <v>17.38</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>58.66</v>
+        <v>57.69</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>23.83</v>
+        <v>24.55</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1615</v>
@@ -3249,22 +3249,22 @@
         <v>50.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>91.77</v>
+        <v>92.53</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>91.77</v>
+        <v>92.53</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>12.86</v>
+        <v>12.94</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.18</v>
+        <v>57.36</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>21.73</v>
+        <v>22.24</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="10">
@@ -3280,22 +3280,22 @@
         <v>50.91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>91.47</v>
+        <v>92.23</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>91.47</v>
+        <v>92.23</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.71</v>
+        <v>10.79</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>55.97</v>
+        <v>56.14</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>24.79</v>
+        <v>25.3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="11">
@@ -3342,22 +3342,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>73.2</v>
+        <v>72.98</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>73.2</v>
+        <v>72.98</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>11.46</v>
+        <v>11.48</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>36.53</v>
+        <v>35.56</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>25.21</v>
+        <v>25.93</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="13">
@@ -3393,30 +3393,30 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>28.04</v>
+        <v>44.43</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>58.16</v>
+        <v>58.22</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>58.16</v>
+        <v>58.22</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10.26</v>
+        <v>14.97</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>31.79</v>
+        <v>30.2</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>16.11</v>
+        <v>13.05</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1532</v>
@@ -3424,30 +3424,30 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9208</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>44.43</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>58.14</v>
+        <v>58.16</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>58.14</v>
+        <v>58.16</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>14.74</v>
+        <v>10.26</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>30.21</v>
+        <v>31.79</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.2</v>
+        <v>16.11</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1532</v>
@@ -3528,19 +3528,19 @@
         <v>38.55</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>44.73</v>
+        <v>44.8</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44.73</v>
+        <v>44.8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7.28</v>
+        <v>7.51</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>26.41</v>
+        <v>26.4</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>11.03</v>
+        <v>10.89</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>1503</v>
@@ -3559,19 +3559,19 @@
         <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>40.47</v>
+        <v>40.25</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>40.47</v>
+        <v>40.25</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>23.16</v>
+        <v>22.19</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.94</v>
+        <v>11.66</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1493</v>
@@ -3590,22 +3590,22 @@
         <v>32.52</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>36.51</v>
+        <v>37.27</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>36.51</v>
+        <v>37.27</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18.97</v>
+        <v>19.14</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>7.76</v>
+        <v>8.26</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1484</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="21">
@@ -3734,64 +3734,64 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>27.39</v>
+        <v>21.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.74</v>
+        <v>26.39</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.74</v>
+        <v>26.39</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>7.67</v>
+        <v>0.93</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14.23</v>
+        <v>16.79</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.84</v>
+        <v>8.67</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9206</v>
+        <v>9671</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>21.07</v>
+        <v>27.39</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>26.39</v>
+        <v>26.09</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>26.39</v>
+        <v>26.09</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.93</v>
+        <v>7.58</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>16.79</v>
+        <v>14.13</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>8.67</v>
+        <v>4.38</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="27">
@@ -4024,22 +4024,22 @@
         <v>23.43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.18</v>
+        <v>19.51</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.18</v>
+        <v>19.51</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5.57</v>
+        <v>5.7</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6.47</v>
+        <v>6.74</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>7.15</v>
+        <v>7.07</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="35">
@@ -4086,19 +4086,19 @@
         <v>39.97</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>18.59</v>
+        <v>18.67</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>18.59</v>
+        <v>18.67</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4.54</v>
+        <v>4.77</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>7.85</v>
+        <v>7.84</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>1427</v>
@@ -4148,19 +4148,19 @@
         <v>25.63</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4.51</v>
+        <v>4.36</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>6.4</v>
+        <v>6.29</v>
       </c>
       <c r="I38" s="2" t="n">
         <v>1420</v>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -775,7 +775,7 @@
         <v>149.8</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>30.34</v>
@@ -1015,7 +1015,7 @@
         <v>98.01000000000001</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>17.3</v>
@@ -1195,7 +1195,7 @@
         <v>92.23</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>10.79</v>
@@ -2875,7 +2875,7 @@
         <v>-0.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>6.18</v>
@@ -3047,7 +3047,7 @@
         <v>35.66</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="3">
@@ -3233,7 +3233,7 @@
         <v>24.56</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="9">
@@ -3295,7 +3295,7 @@
         <v>25.3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="11">
@@ -4225,7 +4225,7 @@
         <v>-0.87</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>92.53</v>
+        <v>62.61</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>92.53</v>
+        <v>62.61</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1599</v>
+        <v>1539</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>12.94</v>
+        <v>6.67</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>57.36</v>
+        <v>40.45</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>22.24</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>128.61</v>
+        <v>100.5</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>128.61</v>
+        <v>100.5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1659</v>
+        <v>1613</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>24.1</v>
+        <v>18.41</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>79.12</v>
+        <v>62.88</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.39</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="8">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>110.94</v>
+        <v>106.02</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>110.94</v>
+        <v>106.02</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1634</v>
+        <v>1624</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>23.97</v>
+        <v>21.89</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>59.31</v>
+        <v>57.44</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>27.66</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="10">
@@ -3145,64 +3145,64 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1023</v>
+        <v>4967</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>68.08</v>
+        <v>68.89</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>128.61</v>
+        <v>106.02</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>128.61</v>
+        <v>106.02</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>24.1</v>
+        <v>21.89</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>79.12</v>
+        <v>57.44</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.39</v>
+        <v>26.7</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1659</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>68.89</v>
+        <v>68.08</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>110.94</v>
+        <v>100.5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>110.94</v>
+        <v>100.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>23.97</v>
+        <v>18.41</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>59.31</v>
+        <v>62.88</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>27.66</v>
+        <v>19.21</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1634</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="8">
@@ -3238,157 +3238,157 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3875</v>
+        <v>7656</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.66</v>
+        <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92.53</v>
+        <v>92.23</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>92.53</v>
+        <v>92.23</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>12.94</v>
+        <v>10.79</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.36</v>
+        <v>56.14</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>22.24</v>
+        <v>25.3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7656</v>
+        <v>2771</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50.91</v>
+        <v>53.52</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>92.23</v>
+        <v>76.73</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>92.23</v>
+        <v>76.73</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.79</v>
+        <v>7.82</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>56.14</v>
+        <v>49.19</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25.3</v>
+        <v>19.72</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1598</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2771</v>
+        <v>858</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>53.52</v>
+        <v>55.1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>76.73</v>
+        <v>71.37</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>76.73</v>
+        <v>71.37</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7.82</v>
+        <v>11.41</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>49.19</v>
+        <v>34.02</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>19.72</v>
+        <v>25.94</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>858</v>
+        <v>6081</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>55.1</v>
+        <v>59.73</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>71.37</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>71.37</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>11.41</v>
+        <v>17.28</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>34.02</v>
+        <v>31.09</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>25.94</v>
+        <v>18.53</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1557</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>6081</v>
+        <v>3875</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>59.73</v>
+        <v>50.66</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17.28</v>
+        <v>6.67</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>31.09</v>
+        <v>40.45</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>18.53</v>
+        <v>15.49</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1549</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="14">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>134.99</v>
+        <v>135.91</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>134.99</v>
+        <v>135.91</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25.39</v>
+        <v>22.54</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>75.98999999999999</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>33.6</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>141.51</v>
+        <v>150.3</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>141.51</v>
+        <v>150.3</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1675</v>
+        <v>1684</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>29.71</v>
+        <v>33.02</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>86.3</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>25.49</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>149.8</v>
+        <v>153.8</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>149.8</v>
+        <v>153.8</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1686</v>
+        <v>1691</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>30.34</v>
+        <v>28.32</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>83.8</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>35.66</v>
+        <v>40.47</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>129.64</v>
+        <v>133.63</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>129.64</v>
+        <v>133.63</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>23.77</v>
+        <v>21.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>74.73999999999999</v>
+        <v>75.95</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>31.12</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>62.61</v>
+        <v>98.67</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>62.61</v>
+        <v>98.67</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1539</v>
+        <v>1609</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>6.67</v>
+        <v>14</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>40.45</v>
+        <v>61.98</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>15.49</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>100.5</v>
+        <v>127.56</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>100.5</v>
+        <v>127.56</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1613</v>
+        <v>1656</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>18.41</v>
+        <v>26.48</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>62.88</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>19.21</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="8">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>71.37</v>
+        <v>72.73</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>71.37</v>
+        <v>72.73</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>11.41</v>
+        <v>9.27</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>34.02</v>
+        <v>36.09</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>25.94</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="15">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>38.64</v>
+        <v>37.51</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>38.64</v>
+        <v>37.51</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>6.32</v>
+        <v>5.63</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>20.65</v>
+        <v>21.24</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>11.67</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="19">
@@ -3032,22 +3032,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>149.8</v>
+        <v>153.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>149.8</v>
+        <v>153.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.34</v>
+        <v>28.32</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>83.8</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>35.66</v>
+        <v>40.47</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1686</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="3">
@@ -3063,22 +3063,22 @@
         <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>141.51</v>
+        <v>150.3</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>141.51</v>
+        <v>150.3</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>29.71</v>
+        <v>33.02</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>86.3</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>25.49</v>
+        <v>27.13</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1675</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="4">
@@ -3094,22 +3094,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>134.99</v>
+        <v>135.91</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>134.99</v>
+        <v>135.91</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25.39</v>
+        <v>22.54</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>75.98999999999999</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>33.6</v>
+        <v>35.8</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="5">
@@ -3125,112 +3125,112 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>129.64</v>
+        <v>133.63</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>129.64</v>
+        <v>133.63</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.77</v>
+        <v>21.75</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>74.73999999999999</v>
+        <v>75.95</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>31.12</v>
+        <v>35.94</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1660</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>68.89</v>
+        <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>106.02</v>
+        <v>127.56</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>106.02</v>
+        <v>127.56</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>21.89</v>
+        <v>26.48</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>57.44</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26.7</v>
+        <v>25.54</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1624</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>1023</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>68.08</v>
+        <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>100.5</v>
+        <v>106.02</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>100.5</v>
+        <v>106.02</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>18.41</v>
+        <v>21.89</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>62.88</v>
+        <v>57.44</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>19.21</v>
+        <v>26.7</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1613</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5166</v>
+        <v>3875</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>50.66</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>98.01000000000001</v>
+        <v>98.67</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>98.01000000000001</v>
+        <v>98.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17.3</v>
+        <v>14</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>56.14</v>
+        <v>61.98</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>24.56</v>
+        <v>22.69</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1609</v>
@@ -3238,157 +3238,157 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>5166</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.91</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92.23</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>92.23</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.79</v>
+        <v>17.3</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>56.14</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>25.3</v>
+        <v>24.56</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1598</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2771</v>
+        <v>7656</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>53.52</v>
+        <v>50.91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>76.73</v>
+        <v>92.23</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>76.73</v>
+        <v>92.23</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>7.82</v>
+        <v>10.79</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>49.19</v>
+        <v>56.14</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19.72</v>
+        <v>25.3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1568</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>71.37</v>
+        <v>76.73</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>71.37</v>
+        <v>76.73</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>11.41</v>
+        <v>7.82</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>34.02</v>
+        <v>49.19</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>25.94</v>
+        <v>19.72</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1557</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6081</v>
+        <v>858</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>59.73</v>
+        <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>17.28</v>
+        <v>9.27</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>31.09</v>
+        <v>36.09</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>18.53</v>
+        <v>27.37</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1549</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>3875</v>
+        <v>6081</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>50.66</v>
+        <v>59.73</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>62.61</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>62.61</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>6.67</v>
+        <v>17.28</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>40.45</v>
+        <v>31.09</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>15.49</v>
+        <v>18.53</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1539</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="14">
@@ -3559,22 +3559,22 @@
         <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>38.64</v>
+        <v>37.51</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>38.64</v>
+        <v>37.51</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>6.32</v>
+        <v>5.63</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>20.65</v>
+        <v>21.24</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.67</v>
+        <v>10.64</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="20">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>135.91</v>
+        <v>135.5</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>135.91</v>
+        <v>135.5</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>22.54</v>
+        <v>21.36</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>77.56999999999999</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>35.8</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>150.3</v>
+        <v>150.23</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>150.3</v>
+        <v>150.23</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>33.02</v>
+        <v>32.97</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>90.15000000000001</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>27.13</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>153.8</v>
+        <v>147.56</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>153.8</v>
+        <v>147.56</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1691</v>
+        <v>1680</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>28.32</v>
+        <v>28.77</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>85.01000000000001</v>
+        <v>82.66</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>40.47</v>
+        <v>36.13</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>133.63</v>
+        <v>138.16</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>133.63</v>
+        <v>138.16</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1663</v>
+        <v>1668</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>21.75</v>
+        <v>18.92</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>75.95</v>
+        <v>81.31</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>35.94</v>
+        <v>37.93</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>98.67</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>98.67</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>14</v>
+        <v>12.21</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>61.98</v>
+        <v>61.91</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>22.69</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>127.56</v>
+        <v>127.55</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>127.56</v>
+        <v>127.55</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>26.48</v>
+        <v>27.84</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>75.54000000000001</v>
+        <v>74.42</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.54</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>98.01000000000001</v>
+        <v>98.75</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>98.01000000000001</v>
+        <v>98.75</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1609</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>17.3</v>
+        <v>18.54</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>56.14</v>
+        <v>56.8</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>24.56</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>106.02</v>
+        <v>105.1</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>106.02</v>
+        <v>105.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>21.89</v>
+        <v>23.38</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>57.44</v>
+        <v>55.88</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>26.7</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="10">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>72.73</v>
+        <v>74.12</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>72.73</v>
+        <v>74.12</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>9.27</v>
+        <v>11.71</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>36.09</v>
+        <v>35.98</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>27.37</v>
+        <v>26.43</v>
       </c>
     </row>
     <row r="15">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>37.51</v>
+        <v>36.5</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>37.51</v>
+        <v>36.5</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>5.63</v>
+        <v>4.88</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>21.24</v>
+        <v>20.6</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>10.64</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="19">
@@ -3021,126 +3021,126 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>10633</v>
+        <v>7220</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45.8</v>
+        <v>45.04</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>153.8</v>
+        <v>150.23</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>153.8</v>
+        <v>150.23</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>28.32</v>
+        <v>32.97</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>85.01000000000001</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40.47</v>
+        <v>27.25</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1691</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>7220</v>
+        <v>10633</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>45.04</v>
+        <v>45.8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>150.3</v>
+        <v>147.56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>150.3</v>
+        <v>147.56</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>33.02</v>
+        <v>28.77</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>90.15000000000001</v>
+        <v>82.66</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>27.13</v>
+        <v>36.13</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1684</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3620</v>
+        <v>2075</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>135.91</v>
+        <v>138.16</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>135.91</v>
+        <v>138.16</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>22.54</v>
+        <v>18.92</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>77.56999999999999</v>
+        <v>81.31</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>35.8</v>
+        <v>37.93</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1666</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2075</v>
+        <v>3620</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>133.63</v>
+        <v>135.5</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>133.63</v>
+        <v>135.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>21.75</v>
+        <v>21.36</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>75.95</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>35.94</v>
+        <v>35.35</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1663</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="6">
@@ -3156,22 +3156,22 @@
         <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>127.56</v>
+        <v>127.55</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>127.56</v>
+        <v>127.55</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>26.48</v>
+        <v>27.84</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>75.54000000000001</v>
+        <v>74.42</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.54</v>
+        <v>25.29</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="7">
@@ -3187,22 +3187,22 @@
         <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>106.02</v>
+        <v>105.1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>106.02</v>
+        <v>105.1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>21.89</v>
+        <v>23.38</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>57.44</v>
+        <v>55.88</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>26.7</v>
+        <v>25.83</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1624</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="8">
@@ -3218,22 +3218,22 @@
         <v>50.66</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>98.67</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>98.67</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>14</v>
+        <v>12.21</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.98</v>
+        <v>61.91</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>22.69</v>
+        <v>24.8</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="9">
@@ -3249,19 +3249,19 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>98.01000000000001</v>
+        <v>98.75</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>98.01000000000001</v>
+        <v>98.75</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>17.3</v>
+        <v>18.54</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>56.14</v>
+        <v>56.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>24.56</v>
+        <v>23.41</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>1609</v>
@@ -3342,22 +3342,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>72.73</v>
+        <v>74.12</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>72.73</v>
+        <v>74.12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>9.27</v>
+        <v>11.71</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>36.09</v>
+        <v>35.98</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>27.37</v>
+        <v>26.43</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1559</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="13">
@@ -3548,30 +3548,30 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>4325</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.21</v>
+        <v>32.52</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>37.51</v>
+        <v>37.27</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>37.51</v>
+        <v>37.27</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.63</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>21.24</v>
+        <v>19.14</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.64</v>
+        <v>8.26</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1485</v>
@@ -3579,33 +3579,33 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4325</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>32.52</v>
+        <v>27.21</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.27</v>
+        <v>36.5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.27</v>
+        <v>36.5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>4.88</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>19.14</v>
+        <v>20.6</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.26</v>
+        <v>11.02</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1485</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="21">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>147.56</v>
+        <v>147.86</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>147.56</v>
+        <v>147.86</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>28.77</v>
+        <v>28.29</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>82.66</v>
+        <v>82.19</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>36.13</v>
+        <v>37.38</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>138.16</v>
+        <v>136.24</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>138.16</v>
+        <v>136.24</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>18.92</v>
+        <v>20.41</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>81.31</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>37.93</v>
+        <v>34.54</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>98.93000000000001</v>
+        <v>102.8</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>98.93000000000001</v>
+        <v>102.8</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1608</v>
+        <v>1615</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>12.21</v>
+        <v>10.99</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>61.91</v>
+        <v>65.17</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>24.8</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="7">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>98.75</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>98.75</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>18.54</v>
+        <v>16.71</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>56.8</v>
+        <v>55.45</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>23.41</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>105.1</v>
+        <v>100.25</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>105.1</v>
+        <v>100.25</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>23.38</v>
+        <v>22.57</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>55.88</v>
+        <v>50.77</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>25.83</v>
+        <v>26.91</v>
       </c>
     </row>
     <row r="10">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>74.12</v>
+        <v>76.73</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>74.12</v>
+        <v>76.73</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>11.71</v>
+        <v>12.08</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>35.98</v>
+        <v>37.6</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>26.43</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="15">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>36.5</v>
+        <v>37.19</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>36.5</v>
+        <v>37.19</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>4.88</v>
+        <v>4.14</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>11.02</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="19">
@@ -3063,22 +3063,22 @@
         <v>45.8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>147.56</v>
+        <v>147.86</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>147.56</v>
+        <v>147.86</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>28.77</v>
+        <v>28.29</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>82.66</v>
+        <v>82.19</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>36.13</v>
+        <v>37.38</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="4">
@@ -3094,22 +3094,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>138.16</v>
+        <v>136.24</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>138.16</v>
+        <v>136.24</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>18.92</v>
+        <v>20.41</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>81.31</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>37.93</v>
+        <v>34.54</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1668</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="5">
@@ -3176,139 +3176,139 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>68.89</v>
+        <v>50.66</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>105.1</v>
+        <v>102.8</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>105.1</v>
+        <v>102.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>23.38</v>
+        <v>10.99</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>55.88</v>
+        <v>65.17</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>25.83</v>
+        <v>26.65</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1620</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>50.66</v>
+        <v>68.89</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>98.93000000000001</v>
+        <v>100.25</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>98.93000000000001</v>
+        <v>100.25</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>12.21</v>
+        <v>22.57</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.91</v>
+        <v>50.77</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>24.8</v>
+        <v>26.91</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5166</v>
+        <v>7656</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>98.75</v>
+        <v>92.23</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>98.75</v>
+        <v>92.23</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>18.54</v>
+        <v>10.79</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>56.8</v>
+        <v>56.14</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23.41</v>
+        <v>25.3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1609</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7656</v>
+        <v>5166</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50.91</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>92.23</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>92.23</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.79</v>
+        <v>16.71</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>56.14</v>
+        <v>55.45</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25.3</v>
+        <v>19.6</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1598</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2771</v>
+        <v>858</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>53.52</v>
+        <v>55.1</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>76.73</v>
@@ -3317,47 +3317,47 @@
         <v>76.73</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7.82</v>
+        <v>12.08</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>49.19</v>
+        <v>37.6</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>19.72</v>
+        <v>27.04</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>74.12</v>
+        <v>76.73</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>74.12</v>
+        <v>76.73</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>11.71</v>
+        <v>7.82</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>35.98</v>
+        <v>49.19</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>26.43</v>
+        <v>19.72</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1561</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="13">
@@ -3590,22 +3590,22 @@
         <v>27.21</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>36.5</v>
+        <v>37.19</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>36.5</v>
+        <v>37.19</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4.88</v>
+        <v>4.14</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>11.02</v>
+        <v>12.54</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1482</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="21">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>135.5</v>
+        <v>134.26</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>135.5</v>
+        <v>134.26</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>21.36</v>
+        <v>20.62</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>78.79000000000001</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>35.35</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>150.23</v>
+        <v>143.23</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>150.23</v>
+        <v>143.23</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1683</v>
+        <v>1673</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>32.97</v>
+        <v>29.92</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>90.01000000000001</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>27.25</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="4">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>136.24</v>
+        <v>114.87</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>136.24</v>
+        <v>114.87</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1664</v>
+        <v>1638</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>20.41</v>
+        <v>22.12</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>81.29000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>34.54</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>102.8</v>
+        <v>101.16</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>102.8</v>
+        <v>101.16</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>10.99</v>
+        <v>10.84</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>65.17</v>
+        <v>59.85</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>26.65</v>
+        <v>30.47</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>127.55</v>
+        <v>131.23</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>127.55</v>
+        <v>131.23</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>27.84</v>
+        <v>27.67</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>74.42</v>
+        <v>75.59</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.29</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="8">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>100.25</v>
+        <v>104.04</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>100.25</v>
+        <v>104.04</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1610</v>
+        <v>1617</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>22.57</v>
+        <v>21.36</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>50.77</v>
+        <v>52.57</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>26.91</v>
+        <v>30.12</v>
       </c>
     </row>
     <row r="10">
@@ -3021,219 +3021,219 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7220</v>
+        <v>10633</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45.04</v>
+        <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>150.23</v>
+        <v>147.86</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>150.23</v>
+        <v>147.86</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32.97</v>
+        <v>28.29</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>90.01000000000001</v>
+        <v>82.19</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>27.25</v>
+        <v>37.38</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1683</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>10633</v>
+        <v>7220</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>45.8</v>
+        <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>147.86</v>
+        <v>143.23</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>147.86</v>
+        <v>143.23</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>28.29</v>
+        <v>29.92</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>82.19</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>37.38</v>
+        <v>28.34</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1679</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2075</v>
+        <v>3620</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>136.24</v>
+        <v>134.26</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>136.24</v>
+        <v>134.26</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>20.41</v>
+        <v>20.62</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>81.29000000000001</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>34.54</v>
+        <v>34.93</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3620</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>135.5</v>
+        <v>131.23</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>135.5</v>
+        <v>131.23</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>21.36</v>
+        <v>27.67</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>78.79000000000001</v>
+        <v>75.59</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>35.35</v>
+        <v>27.96</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1665</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>68.08</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>127.55</v>
+        <v>114.87</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>127.55</v>
+        <v>114.87</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>27.84</v>
+        <v>22.12</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>74.42</v>
+        <v>67.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.29</v>
+        <v>25.25</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1655</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>50.66</v>
+        <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>102.8</v>
+        <v>104.04</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>102.8</v>
+        <v>104.04</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>10.99</v>
+        <v>21.36</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>65.17</v>
+        <v>52.57</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>26.65</v>
+        <v>30.12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1615</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>68.89</v>
+        <v>50.66</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>100.25</v>
+        <v>101.16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>100.25</v>
+        <v>101.16</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>22.57</v>
+        <v>10.84</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>50.77</v>
+        <v>59.85</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>26.91</v>
+        <v>30.47</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="9">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -1135,7 +1135,7 @@
         <v>76.73</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>7.82</v>
@@ -1195,7 +1195,7 @@
         <v>92.23</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>10.79</v>
@@ -1255,7 +1255,7 @@
         <v>58.22</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>14.97</v>
@@ -1315,7 +1315,7 @@
         <v>54.22</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>7.1</v>
@@ -1375,7 +1375,7 @@
         <v>76.73</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>12.08</v>
@@ -1435,7 +1435,7 @@
         <v>66.90000000000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>17.28</v>
@@ -1495,7 +1495,7 @@
         <v>58.16</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>10.26</v>
@@ -1675,7 +1675,7 @@
         <v>44.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>7.51</v>
@@ -1795,7 +1795,7 @@
         <v>49.84</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>21.5</v>
@@ -1915,7 +1915,7 @@
         <v>29.12</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>11.43</v>
@@ -1975,7 +1975,7 @@
         <v>26.39</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="P24" s="2" t="n">
         <v>0.93</v>
@@ -2215,7 +2215,7 @@
         <v>37.27</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="P28" s="2" t="n">
         <v>9.869999999999999</v>
@@ -2335,7 +2335,7 @@
         <v>24.92</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="P30" s="2" t="n">
         <v>4.78</v>
@@ -2395,7 +2395,7 @@
         <v>28.03</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>8.01</v>
@@ -2455,7 +2455,7 @@
         <v>26.09</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>7.58</v>
@@ -2635,7 +2635,7 @@
         <v>21.72</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>5.49</v>
@@ -2755,7 +2755,7 @@
         <v>19.12</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>4.84</v>
@@ -2935,7 +2935,7 @@
         <v>32.76</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="P40" s="2" t="n">
         <v>3.1</v>
@@ -3264,7 +3264,7 @@
         <v>25.3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1598</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="10">
@@ -3326,7 +3326,7 @@
         <v>27.04</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="12">
@@ -3357,7 +3357,7 @@
         <v>19.72</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1568</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="13">
@@ -3388,7 +3388,7 @@
         <v>18.53</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1549</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="14">
@@ -3419,7 +3419,7 @@
         <v>13.05</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1531</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="15">
@@ -3450,7 +3450,7 @@
         <v>16.11</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1531</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="16">
@@ -3481,7 +3481,7 @@
         <v>14.86</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1523</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="17">
@@ -3512,7 +3512,7 @@
         <v>17.44</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="18">
@@ -3543,7 +3543,7 @@
         <v>10.89</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1503</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="19">
@@ -3574,7 +3574,7 @@
         <v>8.26</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20">
@@ -3636,7 +3636,7 @@
         <v>12.39</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="22">
@@ -3667,7 +3667,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="23">
@@ -3729,7 +3729,7 @@
         <v>6.52</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="25">
@@ -3760,7 +3760,7 @@
         <v>8.67</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="26">
@@ -3791,7 +3791,7 @@
         <v>4.38</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="27">
@@ -3822,7 +3822,7 @@
         <v>7.58</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="28">
@@ -3915,7 +3915,7 @@
         <v>4.81</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="31">
@@ -4039,7 +4039,7 @@
         <v>2.83</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="35">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>134.26</v>
+        <v>128.08</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>134.26</v>
+        <v>128.08</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1662</v>
+        <v>1654</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>20.62</v>
+        <v>22.25</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>78.70999999999999</v>
+        <v>73.08</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>34.93</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="3">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>147.86</v>
+        <v>139.4</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>147.86</v>
+        <v>139.4</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1679</v>
+        <v>1667</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>28.29</v>
+        <v>27.21</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>82.19</v>
+        <v>77.22</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>37.38</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="5">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>101.16</v>
+        <v>102.9</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>101.16</v>
+        <v>102.9</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>10.84</v>
+        <v>11.89</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>59.85</v>
+        <v>60.28</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>30.47</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>131.23</v>
+        <v>135.54</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>131.23</v>
+        <v>135.54</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1658</v>
+        <v>1663</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>27.67</v>
+        <v>28.7</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>75.59</v>
+        <v>78.72</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>27.96</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>98.44</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>98.44</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1594</v>
+        <v>1606</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>16.71</v>
+        <v>19.92</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>55.45</v>
+        <v>57.28</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>19.6</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>104.04</v>
+        <v>102.42</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>104.04</v>
+        <v>102.42</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1617</v>
+        <v>1613</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>21.36</v>
+        <v>21.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>52.57</v>
+        <v>53.68</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>30.12</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="10">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>12.08</v>
+        <v>12.23</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>37.6</v>
+        <v>40.66</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>27.04</v>
+        <v>23.21</v>
       </c>
     </row>
     <row r="15">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>37.19</v>
+        <v>38.68</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>37.19</v>
+        <v>38.68</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>4.14</v>
+        <v>3.82</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>20.5</v>
+        <v>23.17</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>12.54</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="19">
@@ -3021,126 +3021,126 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>10633</v>
+        <v>7220</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45.8</v>
+        <v>45.04</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>147.86</v>
+        <v>143.23</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>147.86</v>
+        <v>143.23</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>28.29</v>
+        <v>29.92</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>82.19</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>37.38</v>
+        <v>28.34</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1679</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>7220</v>
+        <v>10633</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>45.04</v>
+        <v>45.8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>143.23</v>
+        <v>139.4</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>143.23</v>
+        <v>139.4</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>29.92</v>
+        <v>27.21</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>84.95999999999999</v>
+        <v>77.22</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>28.34</v>
+        <v>34.97</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1673</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3620</v>
+        <v>1023</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>134.26</v>
+        <v>135.54</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>134.26</v>
+        <v>135.54</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>20.62</v>
+        <v>28.7</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>78.70999999999999</v>
+        <v>78.72</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>34.93</v>
+        <v>28.12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>1023</v>
+        <v>3620</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>68.08</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>131.23</v>
+        <v>128.08</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>131.23</v>
+        <v>128.08</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>27.67</v>
+        <v>22.25</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>75.59</v>
+        <v>73.08</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>27.96</v>
+        <v>32.75</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1658</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="6">
@@ -3176,139 +3176,139 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>68.89</v>
+        <v>50.66</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>104.04</v>
+        <v>102.9</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>104.04</v>
+        <v>102.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>21.36</v>
+        <v>11.89</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>52.57</v>
+        <v>60.28</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>30.12</v>
+        <v>30.73</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1617</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>50.66</v>
+        <v>68.89</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>101.16</v>
+        <v>102.42</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>101.16</v>
+        <v>102.42</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>10.84</v>
+        <v>21.7</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>59.85</v>
+        <v>53.68</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>30.47</v>
+        <v>27.04</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>5166</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.91</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92.23</v>
+        <v>98.44</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>92.23</v>
+        <v>98.44</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.79</v>
+        <v>19.92</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>56.14</v>
+        <v>57.28</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>25.3</v>
+        <v>21.23</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1595</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5166</v>
+        <v>7656</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>50.91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>92.23</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>92.23</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>16.71</v>
+        <v>10.79</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>55.45</v>
+        <v>56.14</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19.6</v>
+        <v>25.3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>76.73</v>
@@ -3317,13 +3317,13 @@
         <v>76.73</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>12.08</v>
+        <v>7.82</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>37.6</v>
+        <v>49.19</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>27.04</v>
+        <v>19.72</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>1565</v>
@@ -3331,33 +3331,33 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2771</v>
+        <v>858</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>53.52</v>
+        <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>7.82</v>
+        <v>12.23</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>49.19</v>
+        <v>40.66</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>19.72</v>
+        <v>23.21</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="13">
@@ -3548,61 +3548,61 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>4325</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.52</v>
+        <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>37.27</v>
+        <v>38.68</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>37.27</v>
+        <v>38.68</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>3.82</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.14</v>
+        <v>23.17</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>8.26</v>
+        <v>11.69</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1484</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8767</v>
+        <v>4325</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>27.21</v>
+        <v>32.52</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.19</v>
+        <v>37.27</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.19</v>
+        <v>37.27</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4.14</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20.5</v>
+        <v>19.14</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>12.54</v>
+        <v>8.26</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>1484</v>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>128.08</v>
+        <v>138.06</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>128.08</v>
+        <v>138.06</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1654</v>
+        <v>1666</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>22.25</v>
+        <v>22.49</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>73.08</v>
+        <v>80.75</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>32.75</v>
+        <v>34.82</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>143.23</v>
+        <v>135.59</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>143.23</v>
+        <v>135.59</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>29.92</v>
+        <v>29.47</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>84.95999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>28.34</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>139.4</v>
+        <v>147.95</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>139.4</v>
+        <v>147.95</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1667</v>
+        <v>1678</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>27.21</v>
+        <v>27.56</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>77.22</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>34.97</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>114.87</v>
+        <v>123.12</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>114.87</v>
+        <v>123.12</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1638</v>
+        <v>1648</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>22.12</v>
+        <v>21.05</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>67.5</v>
+        <v>70.08</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>25.25</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>102.9</v>
+        <v>104.33</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>102.9</v>
+        <v>104.33</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>11.89</v>
+        <v>11.96</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>60.28</v>
+        <v>61.6</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>30.73</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>135.54</v>
+        <v>136.14</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>135.54</v>
+        <v>136.14</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>28.7</v>
+        <v>29.82</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>78.72</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>28.12</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>98.44</v>
+        <v>99.33</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>98.44</v>
+        <v>99.33</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>19.92</v>
+        <v>20.06</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>57.28</v>
+        <v>59.88</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>21.23</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>102.42</v>
+        <v>105.04</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>102.42</v>
+        <v>105.04</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>21.7</v>
+        <v>22.09</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>53.68</v>
+        <v>53.94</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>27.04</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1564</v>
+        <v>1544</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>12.23</v>
+        <v>12.11</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>40.66</v>
+        <v>33</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>23.21</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="15">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>38.68</v>
+        <v>34.8</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>38.68</v>
+        <v>34.8</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1487</v>
+        <v>1478</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>3.82</v>
+        <v>4.67</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>23.17</v>
+        <v>21</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>11.69</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -3021,64 +3021,64 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7220</v>
+        <v>10633</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45.04</v>
+        <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>143.23</v>
+        <v>147.95</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>143.23</v>
+        <v>147.95</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>29.92</v>
+        <v>27.56</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>84.95999999999999</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>28.34</v>
+        <v>32.68</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1673</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>10633</v>
+        <v>3620</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>45.8</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>139.4</v>
+        <v>138.06</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>139.4</v>
+        <v>138.06</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>27.21</v>
+        <v>22.49</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>77.22</v>
+        <v>80.75</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>34.97</v>
+        <v>34.82</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="4">
@@ -3094,53 +3094,53 @@
         <v>68.08</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>135.54</v>
+        <v>136.14</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>135.54</v>
+        <v>136.14</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.7</v>
+        <v>29.82</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>78.72</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>28.12</v>
+        <v>25.98</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>128.08</v>
+        <v>135.59</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>128.08</v>
+        <v>135.59</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>22.25</v>
+        <v>29.47</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>73.08</v>
+        <v>78.13</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>32.75</v>
+        <v>27.99</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1654</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="6">
@@ -3156,84 +3156,84 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>114.87</v>
+        <v>123.12</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>114.87</v>
+        <v>123.12</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>22.12</v>
+        <v>21.05</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>67.5</v>
+        <v>70.08</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.25</v>
+        <v>31.99</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1638</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3875</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>50.66</v>
+        <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>102.9</v>
+        <v>105.04</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>102.9</v>
+        <v>105.04</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>11.89</v>
+        <v>22.09</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>60.28</v>
+        <v>53.94</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>30.73</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1614</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>68.89</v>
+        <v>50.66</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>102.42</v>
+        <v>104.33</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>102.42</v>
+        <v>104.33</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>21.7</v>
+        <v>11.96</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>53.68</v>
+        <v>61.6</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>27.04</v>
+        <v>30.77</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1613</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="9">
@@ -3249,22 +3249,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>98.44</v>
+        <v>99.33</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>98.44</v>
+        <v>99.33</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>19.92</v>
+        <v>20.06</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.28</v>
+        <v>59.88</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>21.23</v>
+        <v>19.39</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="10">
@@ -3331,64 +3331,64 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>858</v>
+        <v>6081</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>55.1</v>
+        <v>59.73</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12.23</v>
+        <v>17.28</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40.66</v>
+        <v>31.09</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>23.21</v>
+        <v>18.53</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1564</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>6081</v>
+        <v>858</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>59.73</v>
+        <v>55.1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17.28</v>
+        <v>12.11</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>31.09</v>
+        <v>33</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>18.53</v>
+        <v>20.73</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1546</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="14">
@@ -3548,64 +3548,64 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>4325</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.21</v>
+        <v>32.52</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>38.68</v>
+        <v>37.27</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>38.68</v>
+        <v>37.27</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3.82</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>23.17</v>
+        <v>19.14</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.69</v>
+        <v>8.26</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1487</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4325</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>32.52</v>
+        <v>27.21</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.27</v>
+        <v>34.8</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.27</v>
+        <v>34.8</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>4.67</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>19.14</v>
+        <v>21</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.26</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1484</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="21">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -645,26 +645,40 @@
       <c r="K2" s="2" t="n">
         <v>181.12</v>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>75.04000000000001</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>138.06</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>138.06</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>1666</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>34.82</v>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -705,26 +719,40 @@
       <c r="K3" s="3" t="n">
         <v>135.32</v>
       </c>
-      <c r="L3" s="3" t="n">
-        <v>45.04</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>135.59</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>135.59</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>1663</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>29.47</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>78.13</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>27.99</v>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -829,22 +857,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>123.12</v>
+        <v>125.67</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>123.12</v>
+        <v>125.67</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>21.05</v>
+        <v>21.92</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>70.08</v>
+        <v>71.03</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>31.99</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="6">
@@ -885,26 +913,40 @@
       <c r="K6" s="2" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>50.66</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>104.33</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>104.33</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>1617</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>30.77</v>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -945,26 +987,40 @@
       <c r="K7" s="3" t="n">
         <v>70.78</v>
       </c>
-      <c r="L7" s="3" t="n">
-        <v>68.08</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>136.14</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>136.14</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>1664</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>29.82</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>80.34999999999999</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>25.98</v>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1005,26 +1061,40 @@
       <c r="K8" s="2" t="n">
         <v>93.25</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>99.33</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>99.33</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>1607</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>59.88</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>19.39</v>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1139,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>105.04</v>
+        <v>107.95</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>105.04</v>
+        <v>107.95</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>22.09</v>
+        <v>22.4</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>53.94</v>
+        <v>56.06</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="10">
@@ -1185,26 +1255,40 @@
       <c r="K11" s="3" t="n">
         <v>67.28</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>50.91</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>92.23</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>92.23</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>1595</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>25.3</v>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1305,26 +1389,40 @@
       <c r="K13" s="3" t="n">
         <v>44.45</v>
       </c>
-      <c r="L13" s="3" t="n">
-        <v>29.21</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>54.22</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>54.22</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>1521</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>32.25</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>14.86</v>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1425,26 +1523,40 @@
       <c r="K15" s="3" t="n">
         <v>8.26</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>59.73</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>1546</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>17.28</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>31.09</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>18.53</v>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1609,22 +1721,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>34.8</v>
+        <v>34.07</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>34.8</v>
+        <v>34.07</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>4.67</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>21</v>
+        <v>19.51</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1665,26 +1777,40 @@
       <c r="K19" s="3" t="n">
         <v>-15.3</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>38.55</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>1501</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>10.89</v>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1845,26 +1971,40 @@
       <c r="K22" s="2" t="n">
         <v>-16.86</v>
       </c>
-      <c r="L22" s="2" t="n">
-        <v>35.18</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>1439</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>8.66</v>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2025,26 +2165,40 @@
       <c r="K25" s="3" t="n">
         <v>-78.29000000000001</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>1425</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>2.78</v>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2145,26 +2299,40 @@
       <c r="K27" s="3" t="n">
         <v>-34.08</v>
       </c>
-      <c r="L27" s="3" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>1417</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>3.91</v>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2205,26 +2373,40 @@
       <c r="K28" s="2" t="n">
         <v>-90.43000000000001</v>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>32.52</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>37.27</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>37.27</v>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>1484</v>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="R28" s="2" t="n">
-        <v>8.26</v>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2385,26 +2567,40 @@
       <c r="K31" s="3" t="n">
         <v>-12.35</v>
       </c>
-      <c r="L31" s="3" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>28.03</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>28.03</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>1459</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>6.52</v>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2865,26 +3061,40 @@
       <c r="K39" s="3" t="n">
         <v>-65.65000000000001</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>1328</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>-5.92</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>-0.87</v>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -3052,1180 +3262,1390 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>3620</v>
+        <v>2075</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>138.06</v>
+        <v>125.67</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>138.06</v>
+        <v>125.67</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>22.49</v>
+        <v>21.92</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>80.75</v>
+        <v>71.03</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>34.82</v>
+        <v>32.72</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1666</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1023</v>
+        <v>4967</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>68.08</v>
+        <v>68.89</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>136.14</v>
+        <v>107.95</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>136.14</v>
+        <v>107.95</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>29.82</v>
+        <v>22.4</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>80.34999999999999</v>
+        <v>56.06</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25.98</v>
+        <v>29.5</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1664</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>7220</v>
+        <v>2771</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>45.04</v>
+        <v>53.52</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>135.59</v>
+        <v>76.73</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>135.59</v>
+        <v>76.73</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>29.47</v>
+        <v>7.82</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>78.13</v>
+        <v>49.19</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>27.99</v>
+        <v>19.72</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1663</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2075</v>
+        <v>858</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>123.12</v>
+        <v>65.84</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>123.12</v>
+        <v>65.84</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>21.05</v>
+        <v>12.11</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>70.08</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>31.99</v>
+        <v>20.73</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1648</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>9208</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>68.89</v>
+        <v>44.43</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>105.04</v>
+        <v>58.22</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>105.04</v>
+        <v>58.22</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>22.09</v>
+        <v>14.97</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>53.94</v>
+        <v>30.2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>29</v>
+        <v>13.05</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1618</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3875</v>
+        <v>8423</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>50.66</v>
+        <v>28.04</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>104.33</v>
+        <v>58.16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>104.33</v>
+        <v>58.16</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>11.96</v>
+        <v>10.26</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.6</v>
+        <v>31.79</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>30.77</v>
+        <v>16.11</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1617</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5166</v>
+        <v>9685</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>27.75</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>99.33</v>
+        <v>49.84</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>99.33</v>
+        <v>49.84</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>20.06</v>
+        <v>21.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>59.88</v>
+        <v>10.91</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>19.39</v>
+        <v>17.44</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1607</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7656</v>
+        <v>8767</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50.91</v>
+        <v>27.21</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>92.23</v>
+        <v>34.07</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>92.23</v>
+        <v>34.07</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.79</v>
+        <v>5.6</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>56.14</v>
+        <v>19.51</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25.3</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1595</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2771</v>
+        <v>7809</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>53.52</v>
+        <v>23.83</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>76.73</v>
+        <v>32.76</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>76.73</v>
+        <v>32.76</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7.82</v>
+        <v>3.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>49.19</v>
+        <v>17.26</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>19.72</v>
+        <v>12.39</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1565</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6081</v>
+        <v>7289</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>59.73</v>
+        <v>33.29</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>29.12</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>29.12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>17.28</v>
+        <v>11.43</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>31.09</v>
+        <v>7.97</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>18.53</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1546</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>858</v>
+        <v>7808</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>55.1</v>
+        <v>24.37</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>65.84</v>
+        <v>28.23</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>65.84</v>
+        <v>28.23</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>12.11</v>
+        <v>5.23</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>33</v>
+        <v>12.97</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>20.73</v>
+        <v>10.04</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1544</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9208</v>
+        <v>9206</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>44.43</v>
+        <v>21.07</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>58.22</v>
+        <v>26.39</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>58.22</v>
+        <v>26.39</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14.97</v>
+        <v>0.93</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30.2</v>
+        <v>16.79</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>13.05</v>
+        <v>8.67</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1529</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>9671</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>27.39</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>58.16</v>
+        <v>26.09</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>58.16</v>
+        <v>26.09</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10.26</v>
+        <v>7.58</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>31.79</v>
+        <v>14.13</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>16.11</v>
+        <v>4.38</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1529</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9756</v>
+        <v>7221</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>29.21</v>
+        <v>8.82</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>54.22</v>
+        <v>24.92</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>54.22</v>
+        <v>24.92</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.1</v>
+        <v>4.78</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>32.25</v>
+        <v>12.55</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.86</v>
+        <v>7.58</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1521</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9685</v>
+        <v>11399</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.75</v>
+        <v>23.74</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>49.84</v>
+        <v>24.14</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>49.84</v>
+        <v>24.14</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>21.5</v>
+        <v>4.42</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.91</v>
+        <v>14.42</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.44</v>
+        <v>5.29</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1512</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5980</v>
+        <v>9549</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>38.55</v>
+        <v>17.6</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>44.8</v>
+        <v>21.72</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44.8</v>
+        <v>21.72</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7.51</v>
+        <v>5.49</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>26.4</v>
+        <v>11.41</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.89</v>
+        <v>4.81</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1501</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>4325</v>
+        <v>8285</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.52</v>
+        <v>39.07</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>37.27</v>
+        <v>21.36</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>37.27</v>
+        <v>21.36</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.14</v>
+        <v>11.25</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>8.26</v>
+        <v>9.19</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1484</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8767</v>
+        <v>7658</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>27.21</v>
+        <v>14.34</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>34.8</v>
+        <v>21.13</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>34.8</v>
+        <v>21.13</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4.67</v>
+        <v>2.83</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>21</v>
+        <v>12.4</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1478</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7809</v>
+        <v>7818</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>23.83</v>
+        <v>32.45</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>32.76</v>
+        <v>19.56</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>32.76</v>
+        <v>19.56</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3.1</v>
+        <v>6.92</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>17.26</v>
+        <v>4.65</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>12.39</v>
+        <v>7.99</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1472</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7289</v>
+        <v>10664</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>33.29</v>
+        <v>21.7</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>29.12</v>
+        <v>19.12</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>29.12</v>
+        <v>19.12</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>11.43</v>
+        <v>4.84</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7.97</v>
+        <v>11.44</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>2.83</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1462</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7808</v>
+        <v>9566</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>24.37</v>
+        <v>39.97</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.23</v>
+        <v>18.67</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>28.23</v>
+        <v>18.67</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.23</v>
+        <v>4.77</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>12.97</v>
+        <v>7.84</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.04</v>
+        <v>6.05</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1460</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9638</v>
+        <v>10181</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>22.93</v>
+        <v>23.43</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.03</v>
+        <v>16.85</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.03</v>
+        <v>16.85</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>8.01</v>
+        <v>5.55</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>13.49</v>
+        <v>4.69</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>6.52</v>
+        <v>6.61</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1459</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9206</v>
+        <v>10642</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>21.07</v>
+        <v>25.63</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.39</v>
+        <v>12.77</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.39</v>
+        <v>12.77</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.93</v>
+        <v>3.34</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>16.79</v>
+        <v>5.07</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8.67</v>
+        <v>4.36</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1454</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9671</v>
+        <v>904</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>27.39</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>14.13</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>1453</v>
+          <t>D Cubed</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>7221</v>
+        <v>1023</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>1449</v>
+          <t>Bedford Express</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>11399</v>
+        <v>3234</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>23.74</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>1447</v>
+          <t>Red Arrows</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>5256</v>
+        <v>3620</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>35.18</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>1439</v>
+          <t>Average Joes</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9549</v>
+        <v>3875</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>21.72</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>21.72</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>1438</v>
+          <t>Red Storm Robotics</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>8285</v>
+        <v>4325</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>1437</v>
+          <t>RoboRangers</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7658</v>
+        <v>5166</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>1436</v>
+          <t>Fabricators</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7818</v>
+        <v>5256</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>19.56</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>19.56</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>1430</v>
+          <t>Atomics</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10664</v>
+        <v>5980</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>1428</v>
+          <t>East Grand Rapids Robotics</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9566</v>
+        <v>6081</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>39.97</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>1427</v>
+          <t>Digital Dislocators</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7256</v>
+        <v>7220</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>1425</v>
+          <t>Steel Falcons</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>7256</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>1419</v>
+          <t>Irish Robotics</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3234</v>
+        <v>7656</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>1417</v>
+          <t>MC Hammers</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>10642</v>
+        <v>9638</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>25.63</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>1401</v>
+          <t>Tigers, Bro!</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>904</v>
+        <v>9756</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>-5.92</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>1328</v>
+          <t>Robo Panthers</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -645,40 +645,26 @@
       <c r="K2" s="2" t="n">
         <v>181.12</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L2" s="2" t="n">
+        <v>75.04000000000001</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>136.52</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>136.52</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1665</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>30.92</v>
       </c>
     </row>
     <row r="3">
@@ -719,40 +705,26 @@
       <c r="K3" s="3" t="n">
         <v>135.32</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L3" s="3" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>134.04</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>134.04</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>1661</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>25.96</v>
       </c>
     </row>
     <row r="4">
@@ -913,40 +885,26 @@
       <c r="K6" s="2" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L6" s="2" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>116.11</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>116.11</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1638</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>67.43000000000001</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>33.32</v>
       </c>
     </row>
     <row r="7">
@@ -987,40 +945,26 @@
       <c r="K7" s="3" t="n">
         <v>70.78</v>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L7" s="3" t="n">
+        <v>68.08</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>132.69</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>132.69</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>1660</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>82.58</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>21.77</v>
       </c>
     </row>
     <row r="8">
@@ -1061,40 +1005,26 @@
       <c r="K8" s="2" t="n">
         <v>93.25</v>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L8" s="2" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>19.65</v>
       </c>
     </row>
     <row r="9">
@@ -1255,40 +1185,26 @@
       <c r="K11" s="3" t="n">
         <v>67.28</v>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L11" s="3" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>92.23</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>92.23</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>1595</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>25.3</v>
       </c>
     </row>
     <row r="12">
@@ -1389,40 +1305,26 @@
       <c r="K13" s="3" t="n">
         <v>44.45</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L13" s="3" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>1521</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>14.86</v>
       </c>
     </row>
     <row r="14">
@@ -1467,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>65.84</v>
+        <v>71.06</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>65.84</v>
+        <v>71.06</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1544</v>
+        <v>1553</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>12.11</v>
+        <v>12.59</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>33</v>
+        <v>38.71</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>20.73</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="15">
@@ -1523,40 +1425,26 @@
       <c r="K15" s="3" t="n">
         <v>8.26</v>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L15" s="3" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>1546</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>18.53</v>
       </c>
     </row>
     <row r="16">
@@ -1777,40 +1665,26 @@
       <c r="K19" s="3" t="n">
         <v>-15.3</v>
       </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L19" s="3" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>1501</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>10.89</v>
       </c>
     </row>
     <row r="20">
@@ -1971,40 +1845,26 @@
       <c r="K22" s="2" t="n">
         <v>-16.86</v>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L22" s="2" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>8.66</v>
       </c>
     </row>
     <row r="23">
@@ -2165,40 +2025,26 @@
       <c r="K25" s="3" t="n">
         <v>-78.29000000000001</v>
       </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L25" s="3" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>1425</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>2.78</v>
       </c>
     </row>
     <row r="26">
@@ -2299,40 +2145,26 @@
       <c r="K27" s="3" t="n">
         <v>-34.08</v>
       </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L27" s="3" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>1417</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>3.91</v>
       </c>
     </row>
     <row r="28">
@@ -2373,40 +2205,26 @@
       <c r="K28" s="2" t="n">
         <v>-90.43000000000001</v>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L28" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>1484</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>8.26</v>
       </c>
     </row>
     <row r="29">
@@ -2567,40 +2385,26 @@
       <c r="K31" s="3" t="n">
         <v>-12.35</v>
       </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L31" s="3" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>1459</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>6.52</v>
       </c>
     </row>
     <row r="32">
@@ -3061,40 +2865,26 @@
       <c r="K39" s="3" t="n">
         <v>-65.65000000000001</v>
       </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L39" s="3" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>1328</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="40">
@@ -3262,1390 +3052,1180 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2075</v>
+        <v>3620</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>125.67</v>
+        <v>136.52</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>125.67</v>
+        <v>136.52</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>21.92</v>
+        <v>24.38</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>71.03</v>
+        <v>81.22</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>32.72</v>
+        <v>30.92</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1651</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4967</v>
+        <v>7220</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>68.89</v>
+        <v>45.04</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>107.95</v>
+        <v>134.04</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>107.95</v>
+        <v>134.04</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>22.4</v>
+        <v>29.58</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>56.06</v>
+        <v>78.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>29.5</v>
+        <v>25.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1623</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2771</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>53.52</v>
+        <v>68.08</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>76.73</v>
+        <v>132.69</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>76.73</v>
+        <v>132.69</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>7.82</v>
+        <v>28.34</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>49.19</v>
+        <v>82.58</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>19.72</v>
+        <v>21.77</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1565</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>858</v>
+        <v>2075</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>55.1</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>65.84</v>
+        <v>125.67</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>65.84</v>
+        <v>125.67</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>12.11</v>
+        <v>21.92</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>33</v>
+        <v>71.03</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20.73</v>
+        <v>32.72</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1544</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>9208</v>
+        <v>3875</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>44.43</v>
+        <v>50.66</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>58.22</v>
+        <v>116.11</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>58.22</v>
+        <v>116.11</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>14.97</v>
+        <v>15.36</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>30.2</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>13.05</v>
+        <v>33.32</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1529</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8423</v>
+        <v>4967</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>28.04</v>
+        <v>68.89</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>58.16</v>
+        <v>107.95</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>58.16</v>
+        <v>107.95</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>10.26</v>
+        <v>22.4</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>31.79</v>
+        <v>56.06</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>16.11</v>
+        <v>29.5</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1529</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>9685</v>
+        <v>5166</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>27.75</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>49.84</v>
+        <v>95.77</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>49.84</v>
+        <v>95.77</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>21.5</v>
+        <v>19.09</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>10.91</v>
+        <v>57.03</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>17.44</v>
+        <v>19.65</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1512</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8767</v>
+        <v>7656</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>27.21</v>
+        <v>50.91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34.07</v>
+        <v>92.23</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34.07</v>
+        <v>92.23</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5.6</v>
+        <v>10.79</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>19.51</v>
+        <v>56.14</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>8.960000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1475</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>7809</v>
+        <v>2771</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>23.83</v>
+        <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>32.76</v>
+        <v>76.73</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>32.76</v>
+        <v>76.73</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.1</v>
+        <v>7.82</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>17.26</v>
+        <v>49.19</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.39</v>
+        <v>19.72</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1472</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7289</v>
+        <v>858</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>33.29</v>
+        <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>29.12</v>
+        <v>71.06</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>29.12</v>
+        <v>71.06</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>11.43</v>
+        <v>12.59</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>7.97</v>
+        <v>38.71</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>19.76</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1462</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7808</v>
+        <v>6081</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>24.37</v>
+        <v>59.73</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28.23</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>28.23</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5.23</v>
+        <v>17.28</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>12.97</v>
+        <v>31.09</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.04</v>
+        <v>18.53</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1460</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9206</v>
+        <v>9208</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>21.07</v>
+        <v>44.43</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>26.39</v>
+        <v>58.22</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>26.39</v>
+        <v>58.22</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.93</v>
+        <v>14.97</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>16.79</v>
+        <v>30.2</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>8.67</v>
+        <v>13.05</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1454</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9671</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>27.39</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>26.09</v>
+        <v>58.16</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>26.09</v>
+        <v>58.16</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>7.58</v>
+        <v>10.26</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>14.13</v>
+        <v>31.79</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>4.38</v>
+        <v>16.11</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1453</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7221</v>
+        <v>9756</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8.82</v>
+        <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24.92</v>
+        <v>54.22</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>24.92</v>
+        <v>54.22</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4.78</v>
+        <v>7.1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>12.55</v>
+        <v>32.25</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>7.58</v>
+        <v>14.86</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1449</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>11399</v>
+        <v>9685</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>23.74</v>
+        <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>24.14</v>
+        <v>49.84</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>24.14</v>
+        <v>49.84</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>4.42</v>
+        <v>21.5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>14.42</v>
+        <v>10.91</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>5.29</v>
+        <v>17.44</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1447</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9549</v>
+        <v>5980</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>17.6</v>
+        <v>38.55</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>21.72</v>
+        <v>44.8</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>21.72</v>
+        <v>44.8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5.49</v>
+        <v>7.51</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>11.41</v>
+        <v>26.4</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>4.81</v>
+        <v>10.89</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1438</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8285</v>
+        <v>4325</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>39.07</v>
+        <v>32.52</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>21.36</v>
+        <v>37.27</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>21.36</v>
+        <v>37.27</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.92</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>11.25</v>
+        <v>19.14</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>9.19</v>
+        <v>8.26</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1437</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7658</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>14.34</v>
+        <v>27.21</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>21.13</v>
+        <v>34.07</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>21.13</v>
+        <v>34.07</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2.83</v>
+        <v>5.6</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>12.4</v>
+        <v>19.51</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>5.9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1436</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7818</v>
+        <v>7809</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>32.45</v>
+        <v>23.83</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>19.56</v>
+        <v>32.76</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>19.56</v>
+        <v>32.76</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.92</v>
+        <v>3.1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>4.65</v>
+        <v>17.26</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>7.99</v>
+        <v>12.39</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1430</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>10664</v>
+        <v>7289</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>21.7</v>
+        <v>33.29</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>19.12</v>
+        <v>29.12</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>19.12</v>
+        <v>29.12</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.84</v>
+        <v>11.43</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>11.44</v>
+        <v>7.97</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2.83</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1428</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>9566</v>
+        <v>7808</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>39.97</v>
+        <v>24.37</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>18.67</v>
+        <v>28.23</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>18.67</v>
+        <v>28.23</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.77</v>
+        <v>5.23</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.84</v>
+        <v>12.97</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6.05</v>
+        <v>10.04</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1427</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>10181</v>
+        <v>9638</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>23.43</v>
+        <v>22.93</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>16.85</v>
+        <v>28.03</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>16.85</v>
+        <v>28.03</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.55</v>
+        <v>8.01</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4.69</v>
+        <v>13.49</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>6.61</v>
+        <v>6.52</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1419</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>10642</v>
+        <v>9206</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>25.63</v>
+        <v>21.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>12.77</v>
+        <v>26.39</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>12.77</v>
+        <v>26.39</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.34</v>
+        <v>0.93</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>5.07</v>
+        <v>16.79</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.36</v>
+        <v>8.67</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1401</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>904</v>
+        <v>9671</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Robosnacks</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>1453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>1023</v>
+        <v>7221</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Viking Robotics</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>1449</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3234</v>
+        <v>11399</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Timber Tech</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>1447</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>3620</v>
+        <v>5256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Atomics</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>1439</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3875</v>
+        <v>9549</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>The Mechadogs</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>1438</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>4325</v>
+        <v>8285</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Bionic Bulldogs</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>1437</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5166</v>
+        <v>7658</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>MagiTech</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>1436</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>5256</v>
+        <v>7818</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Williamston High School Vespidae</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>1430</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5980</v>
+        <v>10664</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Big Reds</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>1428</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>6081</v>
+        <v>9566</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Red Storm Rookies</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>1427</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7220</v>
+        <v>7256</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Irish Robotics</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>1425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7256</v>
+        <v>10181</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ProtoWarriors</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>1419</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7656</v>
+        <v>3234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Red Arrows</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1417</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>9638</v>
+        <v>10642</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Comstock Colts</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>1401</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>9756</v>
+        <v>904</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>D Cubed</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1328</v>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>136.52</v>
+        <v>135.14</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>136.52</v>
+        <v>135.14</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>24.38</v>
+        <v>24.17</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>81.22</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>30.92</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="3">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>147.95</v>
+        <v>123.5</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>147.95</v>
+        <v>123.5</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1678</v>
+        <v>1647</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>27.56</v>
+        <v>25.63</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>87.70999999999999</v>
+        <v>71.42</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>32.68</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>125.67</v>
+        <v>128.88</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>125.67</v>
+        <v>128.88</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>21.92</v>
+        <v>23.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>71.03</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>32.72</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="6">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>132.69</v>
+        <v>130.79</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>132.69</v>
+        <v>130.79</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1660</v>
+        <v>1656</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>28.34</v>
+        <v>30.76</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>82.58</v>
+        <v>79.16</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>21.77</v>
+        <v>20.87</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>95.77</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>95.77</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1600</v>
+        <v>1568</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>19.09</v>
+        <v>15.96</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>57.03</v>
+        <v>47.86</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>19.65</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>107.95</v>
+        <v>109.83</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>107.95</v>
+        <v>109.83</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>22.4</v>
+        <v>26.28</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>56.06</v>
+        <v>58.16</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>29.5</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="10">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>71.06</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>71.06</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1553</v>
+        <v>1549</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>12.59</v>
+        <v>11.32</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>38.71</v>
+        <v>40.09</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>19.76</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="15">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>34.07</v>
+        <v>37.24</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>34.07</v>
+        <v>37.24</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1475</v>
+        <v>1483</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>5.6</v>
+        <v>6.38</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>19.51</v>
+        <v>19.31</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>8.960000000000001</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="19">
@@ -3021,157 +3021,157 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>10633</v>
+        <v>3620</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45.8</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>147.95</v>
+        <v>135.14</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>147.95</v>
+        <v>135.14</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>27.56</v>
+        <v>24.17</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>87.70999999999999</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>32.68</v>
+        <v>32.93</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1678</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>136.52</v>
+        <v>134.04</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>136.52</v>
+        <v>134.04</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>24.38</v>
+        <v>29.58</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>81.22</v>
+        <v>78.5</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>30.92</v>
+        <v>25.96</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1665</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7220</v>
+        <v>1023</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45.04</v>
+        <v>68.08</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>134.04</v>
+        <v>130.79</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>134.04</v>
+        <v>130.79</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>29.58</v>
+        <v>30.76</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>78.5</v>
+        <v>79.16</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25.96</v>
+        <v>20.87</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1661</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>68.08</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>132.69</v>
+        <v>128.88</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>132.69</v>
+        <v>128.88</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>28.34</v>
+        <v>23.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>82.58</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>21.77</v>
+        <v>31.24</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1660</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2075</v>
+        <v>10633</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>125.67</v>
+        <v>123.5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>125.67</v>
+        <v>123.5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>21.92</v>
+        <v>25.63</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>71.03</v>
+        <v>71.42</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>32.72</v>
+        <v>26.46</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1651</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="7">
@@ -3218,84 +3218,84 @@
         <v>68.89</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>107.95</v>
+        <v>109.83</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>107.95</v>
+        <v>109.83</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>22.4</v>
+        <v>26.28</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>56.06</v>
+        <v>58.16</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>29.5</v>
+        <v>25.4</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1623</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5166</v>
+        <v>7656</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>95.77</v>
+        <v>92.23</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>95.77</v>
+        <v>92.23</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>19.09</v>
+        <v>10.79</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.03</v>
+        <v>56.14</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>19.65</v>
+        <v>25.3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7656</v>
+        <v>5166</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50.91</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>92.23</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>92.23</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.79</v>
+        <v>15.96</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>56.14</v>
+        <v>47.86</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25.3</v>
+        <v>15.39</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1595</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="11">
@@ -3342,22 +3342,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>71.06</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>71.06</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12.59</v>
+        <v>11.32</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>38.71</v>
+        <v>40.09</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>19.76</v>
+        <v>17.59</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1553</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="13">
@@ -3590,22 +3590,22 @@
         <v>27.21</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>34.07</v>
+        <v>37.24</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>34.07</v>
+        <v>37.24</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5.6</v>
+        <v>6.38</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>19.51</v>
+        <v>19.31</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.960000000000001</v>
+        <v>11.55</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1475</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="21">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>135.14</v>
+        <v>142.6</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>135.14</v>
+        <v>142.6</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1663</v>
+        <v>1670</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>24.17</v>
+        <v>24.21</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>78.04000000000001</v>
+        <v>83.38</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>32.93</v>
+        <v>35.01</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>134.04</v>
+        <v>147.54</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>134.04</v>
+        <v>147.54</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1661</v>
+        <v>1676</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>29.58</v>
+        <v>28.13</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>78.5</v>
+        <v>88.78</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>25.96</v>
+        <v>30.64</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>123.5</v>
+        <v>124.89</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>123.5</v>
+        <v>124.89</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>25.63</v>
+        <v>26.64</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>71.42</v>
+        <v>72.09</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>26.46</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>128.88</v>
+        <v>121.99</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>128.88</v>
+        <v>121.99</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1654</v>
+        <v>1645</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>23.1</v>
+        <v>20.86</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>74.54000000000001</v>
+        <v>71.41</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>31.24</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>116.11</v>
+        <v>121.73</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>116.11</v>
+        <v>121.73</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1638</v>
+        <v>1645</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>15.36</v>
+        <v>14.18</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>67.43000000000001</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>33.32</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>130.79</v>
+        <v>139.44</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>130.79</v>
+        <v>139.44</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1656</v>
+        <v>1667</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>30.76</v>
+        <v>31.84</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>79.16</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>20.87</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>79.20999999999999</v>
+        <v>100.46</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>79.20999999999999</v>
+        <v>100.46</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1568</v>
+        <v>1607</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>15.96</v>
+        <v>19.11</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>47.86</v>
+        <v>57.89</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>15.39</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>109.83</v>
+        <v>108.32</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>109.83</v>
+        <v>108.32</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1625</v>
+        <v>1621</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>26.28</v>
+        <v>25.16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>58.16</v>
+        <v>56.99</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>25.4</v>
+        <v>26.17</v>
       </c>
     </row>
     <row r="10">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>68.98999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>68.98999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1549</v>
+        <v>1557</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>11.32</v>
+        <v>12.46</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>40.09</v>
+        <v>45.43</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>17.59</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="15">
@@ -1785,26 +1785,40 @@
       <c r="K21" s="3" t="n">
         <v>-5.32</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>1512</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>17.44</v>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -3021,64 +3035,64 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>135.14</v>
+        <v>147.54</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>135.14</v>
+        <v>147.54</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>24.17</v>
+        <v>28.13</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>78.04000000000001</v>
+        <v>88.78</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>32.93</v>
+        <v>30.64</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1663</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>45.04</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>134.04</v>
+        <v>142.6</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>134.04</v>
+        <v>142.6</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>29.58</v>
+        <v>24.21</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>78.5</v>
+        <v>83.38</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>25.96</v>
+        <v>35.01</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1661</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="4">
@@ -3094,84 +3108,84 @@
         <v>68.08</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>130.79</v>
+        <v>139.44</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>130.79</v>
+        <v>139.44</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>30.76</v>
+        <v>31.84</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>79.16</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20.87</v>
+        <v>21.74</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1656</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2075</v>
+        <v>10633</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>128.88</v>
+        <v>124.89</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>128.88</v>
+        <v>124.89</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.1</v>
+        <v>26.64</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>74.54000000000001</v>
+        <v>72.09</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>31.24</v>
+        <v>26.16</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1654</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>10633</v>
+        <v>2075</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45.8</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>123.5</v>
+        <v>121.99</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>123.5</v>
+        <v>121.99</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>25.63</v>
+        <v>20.86</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>71.42</v>
+        <v>71.41</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26.46</v>
+        <v>29.72</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1647</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="7">
@@ -3187,22 +3201,22 @@
         <v>50.66</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>116.11</v>
+        <v>121.73</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>116.11</v>
+        <v>121.73</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>15.36</v>
+        <v>14.18</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>67.43000000000001</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>33.32</v>
+        <v>36.36</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1638</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="8">
@@ -3218,84 +3232,84 @@
         <v>68.89</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>109.83</v>
+        <v>108.32</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>109.83</v>
+        <v>108.32</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>26.28</v>
+        <v>25.16</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>58.16</v>
+        <v>56.99</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>25.4</v>
+        <v>26.17</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1625</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>5166</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.91</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92.23</v>
+        <v>100.46</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>92.23</v>
+        <v>100.46</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.79</v>
+        <v>19.11</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>56.14</v>
+        <v>57.89</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>25.3</v>
+        <v>23.46</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1595</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5166</v>
+        <v>7656</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>50.91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>79.20999999999999</v>
+        <v>92.23</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>79.20999999999999</v>
+        <v>92.23</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>15.96</v>
+        <v>10.79</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>47.86</v>
+        <v>56.14</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>15.39</v>
+        <v>25.3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1568</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="11">
@@ -3342,22 +3356,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>68.98999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>68.98999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>11.32</v>
+        <v>12.46</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40.09</v>
+        <v>45.43</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17.59</v>
+        <v>15.82</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1549</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="13">
@@ -3486,746 +3500,760 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9685</v>
+        <v>5980</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.75</v>
+        <v>38.55</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>49.84</v>
+        <v>44.8</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>49.84</v>
+        <v>44.8</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>21.5</v>
+        <v>7.51</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.91</v>
+        <v>26.4</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.44</v>
+        <v>10.89</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1512</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5980</v>
+        <v>4325</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>38.55</v>
+        <v>32.52</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>44.8</v>
+        <v>37.27</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44.8</v>
+        <v>37.27</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7.51</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>26.4</v>
+        <v>19.14</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.89</v>
+        <v>8.26</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1501</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>4325</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.52</v>
+        <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>37.27</v>
+        <v>37.24</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>37.27</v>
+        <v>37.24</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>6.38</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.14</v>
+        <v>19.31</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>8.26</v>
+        <v>11.55</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8767</v>
+        <v>7809</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>27.21</v>
+        <v>23.83</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.24</v>
+        <v>32.76</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.24</v>
+        <v>32.76</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6.38</v>
+        <v>3.1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>19.31</v>
+        <v>17.26</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>11.55</v>
+        <v>12.39</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1483</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7809</v>
+        <v>7289</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>23.83</v>
+        <v>33.29</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>32.76</v>
+        <v>29.12</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>32.76</v>
+        <v>29.12</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3.1</v>
+        <v>11.43</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>17.26</v>
+        <v>7.97</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>12.39</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7289</v>
+        <v>7808</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>33.29</v>
+        <v>24.37</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>29.12</v>
+        <v>28.23</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>29.12</v>
+        <v>28.23</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>11.43</v>
+        <v>5.23</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7.97</v>
+        <v>12.97</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7808</v>
+        <v>9638</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>24.37</v>
+        <v>22.93</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.23</v>
+        <v>28.03</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>28.23</v>
+        <v>28.03</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.23</v>
+        <v>8.01</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>12.97</v>
+        <v>13.49</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.04</v>
+        <v>6.52</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9638</v>
+        <v>9206</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>22.93</v>
+        <v>21.07</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.03</v>
+        <v>26.39</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.03</v>
+        <v>26.39</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>8.01</v>
+        <v>0.93</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>13.49</v>
+        <v>16.79</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>6.52</v>
+        <v>8.67</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1459</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9206</v>
+        <v>9671</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>21.07</v>
+        <v>27.39</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.39</v>
+        <v>26.09</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.39</v>
+        <v>26.09</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.93</v>
+        <v>7.58</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>16.79</v>
+        <v>14.13</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8.67</v>
+        <v>4.38</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9671</v>
+        <v>7221</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>27.39</v>
+        <v>8.82</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>26.09</v>
+        <v>24.92</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>26.09</v>
+        <v>24.92</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="H26" s="2" t="n">
         <v>7.58</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>14.13</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>4.38</v>
-      </c>
       <c r="I26" s="2" t="n">
-        <v>1453</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>7221</v>
+        <v>11399</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.82</v>
+        <v>23.74</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>24.92</v>
+        <v>24.14</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>24.92</v>
+        <v>24.14</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.78</v>
+        <v>4.42</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.55</v>
+        <v>14.42</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.58</v>
+        <v>5.29</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>11399</v>
+        <v>5256</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>23.74</v>
+        <v>35.18</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>24.14</v>
+        <v>21.96</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>24.14</v>
+        <v>21.96</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.42</v>
+        <v>4.08</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>14.42</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.29</v>
+        <v>8.66</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1447</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>5256</v>
+        <v>9549</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>35.18</v>
+        <v>17.6</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.96</v>
+        <v>21.72</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.96</v>
+        <v>21.72</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>11.41</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8.66</v>
+        <v>4.81</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9549</v>
+        <v>8285</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>17.6</v>
+        <v>39.07</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>21.72</v>
+        <v>21.36</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.72</v>
+        <v>21.36</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5.49</v>
+        <v>0.92</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.41</v>
+        <v>11.25</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4.81</v>
+        <v>9.19</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>8285</v>
+        <v>7658</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>39.07</v>
+        <v>14.34</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>21.36</v>
+        <v>21.13</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>21.36</v>
+        <v>21.13</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.92</v>
+        <v>2.83</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.25</v>
+        <v>12.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>9.19</v>
+        <v>5.9</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7658</v>
+        <v>7818</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>14.34</v>
+        <v>32.45</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>21.13</v>
+        <v>19.56</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21.13</v>
+        <v>19.56</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>2.83</v>
+        <v>6.92</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>12.4</v>
+        <v>4.65</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>5.9</v>
+        <v>7.99</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1436</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7818</v>
+        <v>10664</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>32.45</v>
+        <v>21.7</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>19.56</v>
+        <v>19.12</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.56</v>
+        <v>19.12</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>6.92</v>
+        <v>4.84</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4.65</v>
+        <v>11.44</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.99</v>
+        <v>2.83</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10664</v>
+        <v>9566</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>21.7</v>
+        <v>39.97</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.12</v>
+        <v>18.67</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.12</v>
+        <v>18.67</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4.84</v>
+        <v>4.77</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>11.44</v>
+        <v>7.84</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>2.83</v>
+        <v>6.05</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9566</v>
+        <v>7256</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>39.97</v>
+        <v>25.23</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>18.67</v>
+        <v>18.28</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.67</v>
+        <v>18.28</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.77</v>
+        <v>5.52</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>7.84</v>
+        <v>9.99</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>6.05</v>
+        <v>2.78</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7256</v>
+        <v>10181</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>25.23</v>
+        <v>23.43</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>18.28</v>
+        <v>16.85</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>18.28</v>
+        <v>16.85</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.52</v>
+        <v>5.55</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>9.99</v>
+        <v>4.69</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>2.78</v>
+        <v>6.61</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1425</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>3234</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.43</v>
+        <v>22.62</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>16.85</v>
+        <v>16.41</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>16.85</v>
+        <v>16.41</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.55</v>
+        <v>4.06</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>4.69</v>
+        <v>8.43</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>6.61</v>
+        <v>3.91</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3234</v>
+        <v>10642</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22.62</v>
+        <v>25.63</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>16.41</v>
+        <v>12.77</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>16.41</v>
+        <v>12.77</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4.06</v>
+        <v>3.34</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8.43</v>
+        <v>5.07</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3.91</v>
+        <v>4.36</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1417</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>10642</v>
+        <v>904</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>25.63</v>
+        <v>27.91</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>12.77</v>
+        <v>-0.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.77</v>
+        <v>-0.6</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3.34</v>
+        <v>6.18</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>5.07</v>
+        <v>-5.92</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.36</v>
+        <v>-0.87</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1401</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>904</v>
+        <v>9685</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>-5.92</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>1328</v>
+          <t>Crystal Oscillators</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>142.6</v>
+        <v>146.75</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>142.6</v>
+        <v>146.75</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>24.21</v>
+        <v>24.67</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>83.38</v>
+        <v>84.92</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>35.01</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="3">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>124.89</v>
+        <v>123.51</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>124.89</v>
+        <v>123.51</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>26.64</v>
+        <v>26.52</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>72.09</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>26.16</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>121.99</v>
+        <v>112.43</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>121.99</v>
+        <v>112.43</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1645</v>
+        <v>1629</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>20.86</v>
+        <v>20.22</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>71.41</v>
+        <v>63.3</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>29.72</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>121.73</v>
+        <v>120.23</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>121.73</v>
+        <v>120.23</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>14.18</v>
+        <v>15.04</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>71.18000000000001</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>36.36</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>139.44</v>
+        <v>127.36</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>139.44</v>
+        <v>127.36</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1667</v>
+        <v>1651</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>31.84</v>
+        <v>32.19</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>85.84999999999999</v>
+        <v>78.08</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>21.74</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>100.46</v>
+        <v>98.41</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>100.46</v>
+        <v>98.41</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1607</v>
+        <v>1603</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>19.11</v>
+        <v>18.79</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>57.89</v>
+        <v>55.74</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>23.46</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>108.32</v>
+        <v>107.94</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>108.32</v>
+        <v>107.94</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>25.16</v>
+        <v>25.98</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>56.99</v>
+        <v>54.37</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>26.17</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="10">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>73.7</v>
+        <v>73.92</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>73.7</v>
+        <v>73.92</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>1557</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>12.46</v>
+        <v>10.58</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>45.43</v>
+        <v>48.83</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>15.82</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="15">
@@ -1485,26 +1485,40 @@
       <c r="K16" s="2" t="n">
         <v>36.76</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>1529</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>16.11</v>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1609,22 +1623,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>37.24</v>
+        <v>42.47</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>37.24</v>
+        <v>42.47</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1483</v>
+        <v>1495</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>6.38</v>
+        <v>8.59</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>19.31</v>
+        <v>20.94</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>11.55</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="19">
@@ -1785,40 +1799,26 @@
       <c r="K21" s="3" t="n">
         <v>-5.32</v>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L21" s="3" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>1512</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>17.44</v>
       </c>
     </row>
     <row r="22">
@@ -1859,26 +1859,40 @@
       <c r="K22" s="2" t="n">
         <v>-16.86</v>
       </c>
-      <c r="L22" s="2" t="n">
-        <v>35.18</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>1439</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>8.66</v>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2759,26 +2773,40 @@
       <c r="K37" s="3" t="n">
         <v>-82.47</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>1428</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="Q37" s="3" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>2.83</v>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3077,22 +3105,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>142.6</v>
+        <v>146.75</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>142.6</v>
+        <v>146.75</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>24.21</v>
+        <v>24.67</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>83.38</v>
+        <v>84.92</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>35.01</v>
+        <v>37.16</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1670</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="4">
@@ -3108,22 +3136,22 @@
         <v>68.08</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>139.44</v>
+        <v>127.36</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>139.44</v>
+        <v>127.36</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>31.84</v>
+        <v>32.19</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>85.84999999999999</v>
+        <v>78.08</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>21.74</v>
+        <v>17.09</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1667</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="5">
@@ -3139,84 +3167,84 @@
         <v>45.8</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>124.89</v>
+        <v>123.51</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>124.89</v>
+        <v>123.51</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>26.64</v>
+        <v>26.52</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>72.09</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>26.16</v>
+        <v>26.07</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1649</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2075</v>
+        <v>3875</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>50.66</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>121.99</v>
+        <v>120.23</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>121.99</v>
+        <v>120.23</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20.86</v>
+        <v>15.04</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>71.41</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>29.72</v>
+        <v>36.68</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1645</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3875</v>
+        <v>2075</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>50.66</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>121.73</v>
+        <v>112.43</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>121.73</v>
+        <v>112.43</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>14.18</v>
+        <v>20.22</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>71.18000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>36.36</v>
+        <v>28.91</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1645</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="8">
@@ -3232,22 +3260,22 @@
         <v>68.89</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>108.32</v>
+        <v>107.94</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>108.32</v>
+        <v>107.94</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>25.16</v>
+        <v>25.98</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>56.99</v>
+        <v>54.37</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>26.17</v>
+        <v>27.59</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="9">
@@ -3263,22 +3291,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>100.46</v>
+        <v>98.41</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>100.46</v>
+        <v>98.41</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>19.11</v>
+        <v>18.79</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.89</v>
+        <v>55.74</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23.46</v>
+        <v>23.88</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1607</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="10">
@@ -3356,19 +3384,19 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>73.7</v>
+        <v>73.92</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>73.7</v>
+        <v>73.92</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12.46</v>
+        <v>10.58</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>45.43</v>
+        <v>48.83</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>15.82</v>
+        <v>14.51</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>1557</v>
@@ -3438,64 +3466,64 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>9756</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>29.21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>58.16</v>
+        <v>54.22</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>58.16</v>
+        <v>54.22</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10.26</v>
+        <v>7.1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>31.79</v>
+        <v>32.25</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>16.11</v>
+        <v>14.86</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1529</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9756</v>
+        <v>9685</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>29.21</v>
+        <v>27.75</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>54.22</v>
+        <v>49.84</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>54.22</v>
+        <v>49.84</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.1</v>
+        <v>21.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>32.25</v>
+        <v>10.91</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.86</v>
+        <v>17.44</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1521</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="17">
@@ -3531,64 +3559,64 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4325</v>
+        <v>8767</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>32.52</v>
+        <v>27.21</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>37.27</v>
+        <v>42.47</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>37.27</v>
+        <v>42.47</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>19.14</v>
+        <v>20.94</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8.26</v>
+        <v>12.93</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1484</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>4325</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.21</v>
+        <v>32.52</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>37.24</v>
+        <v>37.27</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>37.24</v>
+        <v>37.27</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>6.38</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.31</v>
+        <v>19.14</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.55</v>
+        <v>8.26</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20">
@@ -3841,383 +3869,411 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5256</v>
+        <v>9549</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>35.18</v>
+        <v>17.6</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>21.96</v>
+        <v>21.72</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.96</v>
+        <v>21.72</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>11.41</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8.66</v>
+        <v>4.81</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9549</v>
+        <v>8285</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>17.6</v>
+        <v>39.07</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.72</v>
+        <v>21.36</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.72</v>
+        <v>21.36</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.49</v>
+        <v>0.92</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.41</v>
+        <v>11.25</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.81</v>
+        <v>9.19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8285</v>
+        <v>7658</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>39.07</v>
+        <v>14.34</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>21.36</v>
+        <v>21.13</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.36</v>
+        <v>21.13</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.92</v>
+        <v>2.83</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.25</v>
+        <v>12.4</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.19</v>
+        <v>5.9</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7658</v>
+        <v>7818</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>14.34</v>
+        <v>32.45</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>21.13</v>
+        <v>19.56</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>21.13</v>
+        <v>19.56</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2.83</v>
+        <v>6.92</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>12.4</v>
+        <v>4.65</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5.9</v>
+        <v>7.99</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1436</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7818</v>
+        <v>9566</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>32.45</v>
+        <v>39.97</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>19.56</v>
+        <v>18.67</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>19.56</v>
+        <v>18.67</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>6.92</v>
+        <v>4.77</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4.65</v>
+        <v>7.84</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>7.99</v>
+        <v>6.05</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10664</v>
+        <v>7256</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>21.7</v>
+        <v>25.23</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>19.12</v>
+        <v>18.28</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.12</v>
+        <v>18.28</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.84</v>
+        <v>5.52</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>11.44</v>
+        <v>9.99</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9566</v>
+        <v>10181</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>39.97</v>
+        <v>23.43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>18.67</v>
+        <v>16.85</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.67</v>
+        <v>16.85</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4.77</v>
+        <v>5.55</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.84</v>
+        <v>4.69</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.05</v>
+        <v>6.61</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1427</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7256</v>
+        <v>3234</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>25.23</v>
+        <v>22.62</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>18.28</v>
+        <v>16.41</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.28</v>
+        <v>16.41</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>5.52</v>
+        <v>4.06</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>9.99</v>
+        <v>8.43</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.78</v>
+        <v>3.91</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1425</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10181</v>
+        <v>10642</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23.43</v>
+        <v>25.63</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16.85</v>
+        <v>12.77</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>16.85</v>
+        <v>12.77</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.55</v>
+        <v>3.34</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>4.69</v>
+        <v>5.07</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>6.61</v>
+        <v>4.36</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1419</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>3234</v>
+        <v>904</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22.62</v>
+        <v>27.91</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>16.41</v>
+        <v>-0.6</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>16.41</v>
+        <v>-0.6</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4.06</v>
+        <v>6.18</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>8.43</v>
+        <v>-5.92</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>3.91</v>
+        <v>-0.87</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1417</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10642</v>
+        <v>5256</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>25.63</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>1401</v>
+          <t>Atomics</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>904</v>
+        <v>8423</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>-5.92</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>1328</v>
+          <t>Next Express</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>9685</v>
+        <v>10664</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>146.75</v>
+        <v>133.95</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>146.75</v>
+        <v>133.95</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1674</v>
+        <v>1658</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>24.67</v>
+        <v>23.66</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>84.92</v>
+        <v>76.41</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>37.16</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>147.54</v>
+        <v>157.83</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>147.54</v>
+        <v>157.83</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1676</v>
+        <v>1689</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>28.13</v>
+        <v>30.42</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>88.78</v>
+        <v>94.05</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>30.64</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>123.51</v>
+        <v>125.7</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>123.51</v>
+        <v>125.7</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>26.52</v>
+        <v>23.75</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>70.93000000000001</v>
+        <v>74.27</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>26.07</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>112.43</v>
+        <v>114.7</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>112.43</v>
+        <v>114.7</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>20.22</v>
+        <v>19.14</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>63.3</v>
+        <v>64.56</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>28.91</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>120.23</v>
+        <v>122.5</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>120.23</v>
+        <v>122.5</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>15.04</v>
+        <v>13.96</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>68.51000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>36.68</v>
+        <v>38.77</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>127.36</v>
+        <v>122.45</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>127.36</v>
+        <v>122.45</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1651</v>
+        <v>1645</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>32.19</v>
+        <v>31.68</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>78.08</v>
+        <v>71.67</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>17.09</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="8">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>107.94</v>
+        <v>99.5</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>107.94</v>
+        <v>99.5</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1620</v>
+        <v>1604</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>25.98</v>
+        <v>24.37</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>54.37</v>
+        <v>49.66</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>27.59</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="10">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>73.92</v>
+        <v>80.45</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>73.92</v>
+        <v>80.45</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>10.58</v>
+        <v>9.83</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>48.83</v>
+        <v>51.72</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>14.51</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="15">
@@ -1485,40 +1485,26 @@
       <c r="K16" s="2" t="n">
         <v>36.76</v>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L16" s="2" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>16.11</v>
       </c>
     </row>
     <row r="17">
@@ -1623,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>42.47</v>
+        <v>42.92</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>42.47</v>
+        <v>42.92</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>1495</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>8.59</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>20.94</v>
+        <v>21.58</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>12.93</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="19">
@@ -1799,26 +1785,40 @@
       <c r="K21" s="3" t="n">
         <v>-5.32</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>1512</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>17.44</v>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1859,40 +1859,26 @@
       <c r="K22" s="2" t="n">
         <v>-16.86</v>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L22" s="2" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>8.66</v>
       </c>
     </row>
     <row r="23">
@@ -2293,26 +2279,40 @@
       <c r="K29" s="3" t="n">
         <v>-34.09</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>1419</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>6.61</v>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2773,40 +2773,26 @@
       <c r="K37" s="3" t="n">
         <v>-82.47</v>
       </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L37" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>1428</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="38">
@@ -3074,22 +3060,22 @@
         <v>45.04</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>147.54</v>
+        <v>157.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>147.54</v>
+        <v>157.83</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>28.13</v>
+        <v>30.42</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>88.78</v>
+        <v>94.05</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>30.64</v>
+        <v>33.36</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1676</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="3">
@@ -3105,115 +3091,115 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>146.75</v>
+        <v>133.95</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>146.75</v>
+        <v>133.95</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>24.67</v>
+        <v>23.66</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>84.92</v>
+        <v>76.41</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>37.16</v>
+        <v>33.88</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1674</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>68.08</v>
+        <v>45.8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>127.36</v>
+        <v>125.7</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>127.36</v>
+        <v>125.7</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>32.19</v>
+        <v>23.75</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>78.08</v>
+        <v>74.27</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>17.09</v>
+        <v>27.68</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1651</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>10633</v>
+        <v>3875</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>45.8</v>
+        <v>50.66</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>123.51</v>
+        <v>122.5</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>123.51</v>
+        <v>122.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>26.52</v>
+        <v>13.96</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>70.93000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>26.07</v>
+        <v>38.77</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3875</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>50.66</v>
+        <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>120.23</v>
+        <v>122.45</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>120.23</v>
+        <v>122.45</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15.04</v>
+        <v>31.68</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>68.51000000000001</v>
+        <v>71.67</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>36.68</v>
+        <v>19.11</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1642</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="7">
@@ -3229,22 +3215,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>112.43</v>
+        <v>114.7</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>112.43</v>
+        <v>114.7</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>20.22</v>
+        <v>19.14</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>63.3</v>
+        <v>64.56</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>28.91</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1629</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="8">
@@ -3260,22 +3246,22 @@
         <v>68.89</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>107.94</v>
+        <v>99.5</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>107.94</v>
+        <v>99.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>25.98</v>
+        <v>24.37</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>54.37</v>
+        <v>49.66</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>27.59</v>
+        <v>25.46</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1620</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="9">
@@ -3342,64 +3328,64 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2771</v>
+        <v>858</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>53.52</v>
+        <v>55.1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>76.73</v>
+        <v>80.45</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>76.73</v>
+        <v>80.45</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7.82</v>
+        <v>9.83</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>49.19</v>
+        <v>51.72</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>19.72</v>
+        <v>18.9</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>73.92</v>
+        <v>76.73</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>73.92</v>
+        <v>76.73</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>10.58</v>
+        <v>7.82</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>48.83</v>
+        <v>49.19</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>14.51</v>
+        <v>19.72</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1557</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="13">
@@ -3466,64 +3452,64 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>29.21</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>54.22</v>
+        <v>58.16</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>54.22</v>
+        <v>58.16</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>7.1</v>
+        <v>10.26</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>32.25</v>
+        <v>31.79</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>14.86</v>
+        <v>16.11</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1521</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>27.75</v>
+        <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>49.84</v>
+        <v>54.22</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>49.84</v>
+        <v>54.22</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>21.5</v>
+        <v>7.1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>10.91</v>
+        <v>32.25</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>17.44</v>
+        <v>14.86</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1512</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="17">
@@ -3570,19 +3556,19 @@
         <v>27.21</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>42.47</v>
+        <v>42.92</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>42.47</v>
+        <v>42.92</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>8.59</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>20.94</v>
+        <v>21.58</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>12.93</v>
+        <v>11.88</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>1495</v>
@@ -3869,366 +3855,352 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9549</v>
+        <v>5256</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>17.6</v>
+        <v>35.18</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>21.72</v>
+        <v>21.96</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.72</v>
+        <v>21.96</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>11.41</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>4.81</v>
+        <v>8.66</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>8285</v>
+        <v>9549</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>39.07</v>
+        <v>17.6</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.36</v>
+        <v>21.72</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.36</v>
+        <v>21.72</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.92</v>
+        <v>5.49</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.25</v>
+        <v>11.41</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>9.19</v>
+        <v>4.81</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7658</v>
+        <v>8285</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>14.34</v>
+        <v>39.07</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>21.13</v>
+        <v>21.36</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.13</v>
+        <v>21.36</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2.83</v>
+        <v>0.92</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>12.4</v>
+        <v>11.25</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5.9</v>
+        <v>9.19</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7818</v>
+        <v>7658</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>32.45</v>
+        <v>14.34</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>19.56</v>
+        <v>21.13</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>19.56</v>
+        <v>21.13</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6.92</v>
+        <v>2.83</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.65</v>
+        <v>12.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>7.99</v>
+        <v>5.9</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1430</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9566</v>
+        <v>7818</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>39.97</v>
+        <v>32.45</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>18.67</v>
+        <v>19.56</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18.67</v>
+        <v>19.56</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>4.77</v>
+        <v>6.92</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7.84</v>
+        <v>4.65</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6.05</v>
+        <v>7.99</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1427</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7256</v>
+        <v>10664</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>25.23</v>
+        <v>21.7</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>18.28</v>
+        <v>19.12</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18.28</v>
+        <v>19.12</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>5.52</v>
+        <v>4.84</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>9.99</v>
+        <v>11.44</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1425</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10181</v>
+        <v>9566</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>23.43</v>
+        <v>39.97</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>16.85</v>
+        <v>18.67</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>16.85</v>
+        <v>18.67</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5.55</v>
+        <v>4.77</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>4.69</v>
+        <v>7.84</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.61</v>
+        <v>6.05</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1419</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>3234</v>
+        <v>7256</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>22.62</v>
+        <v>25.23</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>16.41</v>
+        <v>18.28</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>16.41</v>
+        <v>18.28</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.06</v>
+        <v>5.52</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8.43</v>
+        <v>9.99</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>3.91</v>
+        <v>2.78</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1417</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10642</v>
+        <v>3234</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>25.63</v>
+        <v>22.62</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>12.77</v>
+        <v>16.41</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>12.77</v>
+        <v>16.41</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>3.34</v>
+        <v>4.06</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5.07</v>
+        <v>8.43</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>4.36</v>
+        <v>3.91</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1401</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>904</v>
+        <v>10642</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>27.91</v>
+        <v>25.63</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-0.6</v>
+        <v>12.77</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.6</v>
+        <v>12.77</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>6.18</v>
+        <v>3.34</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>-5.92</v>
+        <v>5.07</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>-0.87</v>
+        <v>4.36</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1328</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5256</v>
+        <v>904</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>D Cubed</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1328</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>8423</v>
+        <v>9685</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -4269,11 +4241,11 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>10664</v>
+        <v>10181</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>133.95</v>
+        <v>135.93</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>133.95</v>
+        <v>135.93</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23.66</v>
+        <v>22.29</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>76.41</v>
+        <v>79.14</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>33.88</v>
+        <v>34.49</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>157.83</v>
+        <v>155.74</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>157.83</v>
+        <v>155.74</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1689</v>
+        <v>1685</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.42</v>
+        <v>30.45</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>94.05</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>33.36</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>125.7</v>
+        <v>127.67</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>125.7</v>
+        <v>127.67</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>23.75</v>
+        <v>22.38</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>74.27</v>
+        <v>77</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>27.68</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="5">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>122.5</v>
+        <v>126.38</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>122.5</v>
+        <v>126.38</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1645</v>
+        <v>1649</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>13.96</v>
+        <v>14.7</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>69.77</v>
+        <v>69.69</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>38.77</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>122.45</v>
+        <v>116.13</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>122.45</v>
+        <v>116.13</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1645</v>
+        <v>1635</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>31.68</v>
+        <v>31.61</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>71.67</v>
+        <v>67.62</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>19.11</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>98.41</v>
+        <v>98.17</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>98.41</v>
+        <v>98.17</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>18.79</v>
+        <v>18.34</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>55.74</v>
+        <v>56.5</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>23.88</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="9">
@@ -1069,22 +1069,22 @@
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>99.5</v>
+        <v>97.28</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>99.5</v>
+        <v>97.28</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>24.37</v>
+        <v>24.29</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>49.66</v>
+        <v>47.71</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>25.46</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="10">
@@ -1618,13 +1618,13 @@
         <v>1495</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>21.58</v>
+        <v>20.41</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>11.88</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="19">
@@ -1785,40 +1785,26 @@
       <c r="K21" s="3" t="n">
         <v>-5.32</v>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L21" s="3" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>1512</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>17.44</v>
       </c>
     </row>
     <row r="22">
@@ -2279,40 +2265,26 @@
       <c r="K29" s="3" t="n">
         <v>-34.09</v>
       </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L29" s="3" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>1419</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>6.61</v>
       </c>
     </row>
     <row r="30">
@@ -3060,22 +3032,22 @@
         <v>45.04</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>157.83</v>
+        <v>155.74</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>157.83</v>
+        <v>155.74</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.42</v>
+        <v>30.45</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>94.05</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>33.36</v>
+        <v>31.19</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1689</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="3">
@@ -3091,22 +3063,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>133.95</v>
+        <v>135.93</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>133.95</v>
+        <v>135.93</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>23.66</v>
+        <v>22.29</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>76.41</v>
+        <v>79.14</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>33.88</v>
+        <v>34.49</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1658</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="4">
@@ -3122,22 +3094,22 @@
         <v>45.8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>125.7</v>
+        <v>127.67</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>125.7</v>
+        <v>127.67</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>23.75</v>
+        <v>22.38</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>74.27</v>
+        <v>77</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>27.68</v>
+        <v>28.3</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1648</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="5">
@@ -3153,22 +3125,22 @@
         <v>50.66</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>122.5</v>
+        <v>126.38</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>122.5</v>
+        <v>126.38</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>13.96</v>
+        <v>14.7</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>69.77</v>
+        <v>69.69</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>38.77</v>
+        <v>41.99</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1645</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="6">
@@ -3184,22 +3156,22 @@
         <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>122.45</v>
+        <v>116.13</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>122.45</v>
+        <v>116.13</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>31.68</v>
+        <v>31.61</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>71.67</v>
+        <v>67.62</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19.11</v>
+        <v>16.9</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1645</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="7">
@@ -3235,64 +3207,64 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4967</v>
+        <v>5166</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>68.89</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>99.5</v>
+        <v>98.17</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>99.5</v>
+        <v>98.17</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>24.37</v>
+        <v>18.34</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>49.66</v>
+        <v>56.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>25.46</v>
+        <v>23.33</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1604</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5166</v>
+        <v>4967</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>98.41</v>
+        <v>97.28</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>98.41</v>
+        <v>97.28</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>18.79</v>
+        <v>24.29</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55.74</v>
+        <v>47.71</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23.88</v>
+        <v>25.27</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1603</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="10">
@@ -3514,774 +3486,746 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>5980</v>
+        <v>9685</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>38.55</v>
+        <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>44.8</v>
+        <v>49.84</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>44.8</v>
+        <v>49.84</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>7.51</v>
+        <v>21.5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>26.4</v>
+        <v>10.91</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.89</v>
+        <v>17.44</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1501</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8767</v>
+        <v>5980</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>27.21</v>
+        <v>38.55</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>42.92</v>
+        <v>44.8</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>42.92</v>
+        <v>44.8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>7.51</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>21.58</v>
+        <v>26.4</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>11.88</v>
+        <v>10.89</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1495</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>4325</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.52</v>
+        <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>37.27</v>
+        <v>42.92</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>37.27</v>
+        <v>42.92</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.14</v>
+        <v>20.41</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>8.26</v>
+        <v>11.59</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1484</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7809</v>
+        <v>4325</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>23.83</v>
+        <v>32.52</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>32.76</v>
+        <v>37.27</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>32.76</v>
+        <v>37.27</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3.1</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>17.26</v>
+        <v>19.14</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>12.39</v>
+        <v>8.26</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1472</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7289</v>
+        <v>7809</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>33.29</v>
+        <v>23.83</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>29.12</v>
+        <v>32.76</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>29.12</v>
+        <v>32.76</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>11.43</v>
+        <v>3.1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.97</v>
+        <v>17.26</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>9.720000000000001</v>
+        <v>12.39</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1462</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7808</v>
+        <v>7289</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>24.37</v>
+        <v>33.29</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>28.23</v>
+        <v>29.12</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>28.23</v>
+        <v>29.12</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>5.23</v>
+        <v>11.43</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>12.97</v>
+        <v>7.97</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.04</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1460</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>9638</v>
+        <v>7808</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>22.93</v>
+        <v>24.37</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.03</v>
+        <v>28.23</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>28.03</v>
+        <v>28.23</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>8.01</v>
+        <v>5.23</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>13.49</v>
+        <v>12.97</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6.52</v>
+        <v>10.04</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9206</v>
+        <v>9638</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>21.07</v>
+        <v>22.93</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>26.39</v>
+        <v>28.03</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>26.39</v>
+        <v>28.03</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.93</v>
+        <v>8.01</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>16.79</v>
+        <v>13.49</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>8.67</v>
+        <v>6.52</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1454</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>27.39</v>
+        <v>21.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.09</v>
+        <v>26.39</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.09</v>
+        <v>26.39</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>7.58</v>
+        <v>0.93</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14.13</v>
+        <v>16.79</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.38</v>
+        <v>8.67</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7221</v>
+        <v>9671</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>8.82</v>
+        <v>27.39</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24.92</v>
+        <v>26.09</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>24.92</v>
+        <v>26.09</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>4.78</v>
+        <v>7.58</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>12.55</v>
+        <v>14.13</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>7.58</v>
+        <v>4.38</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1449</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>11399</v>
+        <v>7221</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>23.74</v>
+        <v>8.82</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>24.14</v>
+        <v>24.92</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>24.14</v>
+        <v>24.92</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.42</v>
+        <v>4.78</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14.42</v>
+        <v>12.55</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.29</v>
+        <v>7.58</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1447</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5256</v>
+        <v>11399</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>35.18</v>
+        <v>23.74</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>21.96</v>
+        <v>24.14</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.96</v>
+        <v>24.14</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.08</v>
+        <v>4.42</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>14.42</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8.66</v>
+        <v>5.29</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1439</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9549</v>
+        <v>5256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>17.6</v>
+        <v>35.18</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.72</v>
+        <v>21.96</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.72</v>
+        <v>21.96</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.41</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.81</v>
+        <v>8.66</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8285</v>
+        <v>9549</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>39.07</v>
+        <v>17.6</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>21.36</v>
+        <v>21.72</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.36</v>
+        <v>21.72</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.92</v>
+        <v>5.49</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.25</v>
+        <v>11.41</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.19</v>
+        <v>4.81</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7658</v>
+        <v>8285</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>14.34</v>
+        <v>39.07</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>21.13</v>
+        <v>21.36</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>21.13</v>
+        <v>21.36</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2.83</v>
+        <v>0.92</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>12.4</v>
+        <v>11.25</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5.9</v>
+        <v>9.19</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7818</v>
+        <v>7658</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>32.45</v>
+        <v>14.34</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>19.56</v>
+        <v>21.13</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>19.56</v>
+        <v>21.13</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>6.92</v>
+        <v>2.83</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4.65</v>
+        <v>12.4</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>7.99</v>
+        <v>5.9</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1430</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10664</v>
+        <v>7818</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>21.7</v>
+        <v>32.45</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>19.12</v>
+        <v>19.56</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.12</v>
+        <v>19.56</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.84</v>
+        <v>6.92</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>11.44</v>
+        <v>4.65</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.83</v>
+        <v>7.99</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1428</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9566</v>
+        <v>10664</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>39.97</v>
+        <v>21.7</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>18.67</v>
+        <v>19.12</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.67</v>
+        <v>19.12</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4.77</v>
+        <v>4.84</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.84</v>
+        <v>11.44</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.05</v>
+        <v>2.83</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7256</v>
+        <v>9566</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>25.23</v>
+        <v>39.97</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>18.28</v>
+        <v>18.67</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.28</v>
+        <v>18.67</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>5.52</v>
+        <v>4.77</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>9.99</v>
+        <v>7.84</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.78</v>
+        <v>6.05</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1425</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3234</v>
+        <v>7256</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>22.62</v>
+        <v>25.23</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16.41</v>
+        <v>18.28</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>16.41</v>
+        <v>18.28</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4.06</v>
+        <v>5.52</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.43</v>
+        <v>9.99</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3.91</v>
+        <v>2.78</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1417</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10642</v>
+        <v>10181</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>25.63</v>
+        <v>23.43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>12.77</v>
+        <v>16.85</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>12.77</v>
+        <v>16.85</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3.34</v>
+        <v>5.55</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5.07</v>
+        <v>4.69</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4.36</v>
+        <v>6.61</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1401</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>904</v>
+        <v>3234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>27.91</v>
+        <v>22.62</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-0.6</v>
+        <v>16.41</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-0.6</v>
+        <v>16.41</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6.18</v>
+        <v>4.06</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-5.92</v>
+        <v>8.43</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>-0.87</v>
+        <v>3.91</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1328</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>9685</v>
+        <v>10642</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Comstock Colts</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>1401</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>10181</v>
+        <v>904</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>D Cubed</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1328</v>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>135.93</v>
+        <v>135.65</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>135.93</v>
+        <v>135.65</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>22.29</v>
+        <v>22.22</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>79.14</v>
+        <v>78.95</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>34.49</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>155.74</v>
+        <v>161.57</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>155.74</v>
+        <v>161.57</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1685</v>
+        <v>1695</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.45</v>
+        <v>35.26</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>31.19</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>127.67</v>
+        <v>126.75</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>127.67</v>
+        <v>126.75</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>22.38</v>
+        <v>22.15</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>77</v>
+        <v>76.58</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>28.3</v>
+        <v>28.03</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>114.7</v>
+        <v>116.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>114.7</v>
+        <v>116.5</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>19.14</v>
+        <v>21.06</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>64.56</v>
+        <v>63.16</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>31</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>126.38</v>
+        <v>124.9</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>126.38</v>
+        <v>124.9</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>14.7</v>
+        <v>14.33</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>69.69</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>41.99</v>
+        <v>41.36</v>
       </c>
     </row>
     <row r="7">
@@ -3032,22 +3032,22 @@
         <v>45.04</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>155.74</v>
+        <v>161.57</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>155.74</v>
+        <v>161.57</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.45</v>
+        <v>35.26</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>31.19</v>
+        <v>26.9</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1685</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="3">
@@ -3063,22 +3063,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>135.93</v>
+        <v>135.65</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>135.93</v>
+        <v>135.65</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>22.29</v>
+        <v>22.22</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>79.14</v>
+        <v>78.95</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>34.49</v>
+        <v>34.48</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="4">
@@ -3094,22 +3094,22 @@
         <v>45.8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>127.67</v>
+        <v>126.75</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>127.67</v>
+        <v>126.75</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>22.38</v>
+        <v>22.15</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>77</v>
+        <v>76.58</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>28.3</v>
+        <v>28.03</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="5">
@@ -3125,50 +3125,50 @@
         <v>50.66</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>126.38</v>
+        <v>124.9</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>126.38</v>
+        <v>124.9</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>14.7</v>
+        <v>14.33</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>69.69</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>41.99</v>
+        <v>41.36</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1649</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>68.08</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>116.13</v>
+        <v>116.5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>116.13</v>
+        <v>116.5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>31.61</v>
+        <v>21.06</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>67.62</v>
+        <v>63.16</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>16.9</v>
+        <v>32.28</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1635</v>
@@ -3176,33 +3176,33 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>2075</v>
+        <v>1023</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>114.7</v>
+        <v>116.13</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>114.7</v>
+        <v>116.13</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>19.14</v>
+        <v>31.61</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>64.56</v>
+        <v>67.62</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>31</v>
+        <v>16.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1632</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="8">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -1245,26 +1245,40 @@
       <c r="K12" s="2" t="n">
         <v>-23.42</v>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>44.43</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>1529</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>13.05</v>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1545,26 +1559,40 @@
       <c r="K17" s="3" t="n">
         <v>-40.62</v>
       </c>
-      <c r="L17" s="3" t="n">
-        <v>23.74</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>1447</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>5.29</v>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1725,26 +1753,40 @@
       <c r="K20" s="2" t="n">
         <v>-45.92</v>
       </c>
-      <c r="L20" s="2" t="n">
-        <v>25.63</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>1401</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Q20" s="2" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>4.36</v>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1785,26 +1827,40 @@
       <c r="K21" s="3" t="n">
         <v>-5.32</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>1512</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>17.44</v>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1965,26 +2021,40 @@
       <c r="K24" s="2" t="n">
         <v>-27.53</v>
       </c>
-      <c r="L24" s="2" t="n">
-        <v>21.07</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>26.39</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>26.39</v>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>1454</v>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="R24" s="2" t="n">
-        <v>8.67</v>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2265,26 +2335,40 @@
       <c r="K29" s="3" t="n">
         <v>-34.09</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>1419</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>6.61</v>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2385,26 +2469,40 @@
       <c r="K31" s="3" t="n">
         <v>-12.35</v>
       </c>
-      <c r="L31" s="3" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>28.03</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>28.03</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>1459</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>6.52</v>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2505,26 +2603,40 @@
       <c r="K33" s="3" t="n">
         <v>-43.51</v>
       </c>
-      <c r="L33" s="3" t="n">
-        <v>39.97</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>1427</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>6.05</v>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2625,26 +2737,40 @@
       <c r="K35" s="3" t="n">
         <v>-56.86</v>
       </c>
-      <c r="L35" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>21.72</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>21.72</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>1438</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>4.81</v>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2745,26 +2871,40 @@
       <c r="K37" s="3" t="n">
         <v>-82.47</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>1428</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="Q37" s="3" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>2.83</v>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3393,30 +3533,30 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9208</v>
+        <v>8423</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>44.43</v>
+        <v>28.04</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>58.22</v>
+        <v>58.16</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>58.22</v>
+        <v>58.16</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14.97</v>
+        <v>10.26</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30.2</v>
+        <v>31.79</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>13.05</v>
+        <v>16.11</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1529</v>
@@ -3424,684 +3564,768 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>9756</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>29.21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>58.16</v>
+        <v>54.22</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>58.16</v>
+        <v>54.22</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10.26</v>
+        <v>7.1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>31.79</v>
+        <v>32.25</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>16.11</v>
+        <v>14.86</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1529</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9756</v>
+        <v>5980</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>29.21</v>
+        <v>38.55</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>54.22</v>
+        <v>44.8</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>54.22</v>
+        <v>44.8</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.1</v>
+        <v>7.51</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>32.25</v>
+        <v>26.4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.86</v>
+        <v>10.89</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1521</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9685</v>
+        <v>8767</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.75</v>
+        <v>27.21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>49.84</v>
+        <v>42.92</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>49.84</v>
+        <v>42.92</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>21.5</v>
+        <v>10.92</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.91</v>
+        <v>20.41</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.44</v>
+        <v>11.59</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1512</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5980</v>
+        <v>4325</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>38.55</v>
+        <v>32.52</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>44.8</v>
+        <v>37.27</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44.8</v>
+        <v>37.27</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7.51</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>26.4</v>
+        <v>19.14</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.89</v>
+        <v>8.26</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1501</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>7809</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.21</v>
+        <v>23.83</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>42.92</v>
+        <v>32.76</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>42.92</v>
+        <v>32.76</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>10.92</v>
+        <v>3.1</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>20.41</v>
+        <v>17.26</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.59</v>
+        <v>12.39</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1495</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4325</v>
+        <v>7289</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>32.52</v>
+        <v>33.29</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.27</v>
+        <v>29.12</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.27</v>
+        <v>29.12</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>11.43</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>19.14</v>
+        <v>7.97</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.26</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1484</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7809</v>
+        <v>7808</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>23.83</v>
+        <v>24.37</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>32.76</v>
+        <v>28.23</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>32.76</v>
+        <v>28.23</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3.1</v>
+        <v>5.23</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>17.26</v>
+        <v>12.97</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>12.39</v>
+        <v>10.04</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1472</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7289</v>
+        <v>9671</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>33.29</v>
+        <v>27.39</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>29.12</v>
+        <v>26.09</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>29.12</v>
+        <v>26.09</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>11.43</v>
+        <v>7.58</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7.97</v>
+        <v>14.13</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>4.38</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1462</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7808</v>
+        <v>7221</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>24.37</v>
+        <v>8.82</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.23</v>
+        <v>24.92</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>28.23</v>
+        <v>24.92</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.23</v>
+        <v>4.78</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>12.97</v>
+        <v>12.55</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.04</v>
+        <v>7.58</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1460</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9638</v>
+        <v>5256</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>22.93</v>
+        <v>35.18</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.03</v>
+        <v>21.96</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.03</v>
+        <v>21.96</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>8.01</v>
+        <v>4.08</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>13.49</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>6.52</v>
+        <v>8.66</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1459</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9206</v>
+        <v>8285</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>21.07</v>
+        <v>39.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.39</v>
+        <v>21.36</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.39</v>
+        <v>21.36</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>16.79</v>
+        <v>11.25</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8.67</v>
+        <v>9.19</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1454</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9671</v>
+        <v>7658</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>27.39</v>
+        <v>14.34</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>26.09</v>
+        <v>21.13</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>26.09</v>
+        <v>21.13</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>7.58</v>
+        <v>2.83</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>14.13</v>
+        <v>12.4</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4.38</v>
+        <v>5.9</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1453</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>7221</v>
+        <v>7818</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.82</v>
+        <v>32.45</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>24.92</v>
+        <v>19.56</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>24.92</v>
+        <v>19.56</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.78</v>
+        <v>6.92</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.55</v>
+        <v>4.65</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.58</v>
+        <v>7.99</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1449</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>11399</v>
+        <v>7256</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>23.74</v>
+        <v>25.23</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>24.14</v>
+        <v>18.28</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>24.14</v>
+        <v>18.28</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.42</v>
+        <v>5.52</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>14.42</v>
+        <v>9.99</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.29</v>
+        <v>2.78</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1447</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>5256</v>
+        <v>3234</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>35.18</v>
+        <v>22.62</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.96</v>
+        <v>16.41</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.96</v>
+        <v>16.41</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8.66</v>
+        <v>3.91</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1439</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9549</v>
+        <v>904</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>17.6</v>
+        <v>27.91</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>21.72</v>
+        <v>-0.6</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.72</v>
+        <v>-0.6</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5.49</v>
+        <v>6.18</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.41</v>
+        <v>-5.92</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4.81</v>
+        <v>-0.87</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1438</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>8285</v>
+        <v>9206</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>1437</v>
+          <t>GRP Titans</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7658</v>
+        <v>9208</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>1436</v>
+          <t>Eddies Circuit</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7818</v>
+        <v>9549</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>19.56</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>19.56</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>1430</v>
+          <t>The Mechadogs</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10664</v>
+        <v>9566</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>1428</v>
+          <t>Red Storm Rookies</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9566</v>
+        <v>9638</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>39.97</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>1427</v>
+          <t>Tigers, Bro!</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7256</v>
+        <v>9685</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>1425</v>
+          <t>Crystal Oscillators</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -4113,119 +4337,175 @@
           <t>ProtoWarriors</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>1419</v>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3234</v>
+        <v>10642</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>1417</v>
+          <t>Comstock Colts</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>25.63</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>1401</v>
+          <t>Big Reds</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>904</v>
+        <v>11399</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>-5.92</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>1328</v>
+          <t>Timber Tech</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -775,7 +775,7 @@
         <v>126.75</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>22.15</v>
@@ -955,7 +955,7 @@
         <v>116.13</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>31.61</v>
@@ -1135,7 +1135,7 @@
         <v>76.73</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>7.82</v>
@@ -1195,7 +1195,7 @@
         <v>92.23</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>10.79</v>
@@ -1245,40 +1245,26 @@
       <c r="K12" s="2" t="n">
         <v>-23.42</v>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L12" s="2" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>13.05</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1315,7 @@
         <v>54.22</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>7.1</v>
@@ -1449,7 +1435,7 @@
         <v>66.90000000000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>17.28</v>
@@ -1509,7 +1495,7 @@
         <v>58.16</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>10.26</v>
@@ -1559,40 +1545,26 @@
       <c r="K17" s="3" t="n">
         <v>-40.62</v>
       </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L17" s="3" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>1446</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>5.29</v>
       </c>
     </row>
     <row r="18">
@@ -1703,7 +1675,7 @@
         <v>44.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>7.51</v>
@@ -1753,40 +1725,26 @@
       <c r="K20" s="2" t="n">
         <v>-45.92</v>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L20" s="2" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>4.36</v>
       </c>
     </row>
     <row r="21">
@@ -1827,40 +1785,26 @@
       <c r="K21" s="3" t="n">
         <v>-5.32</v>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L21" s="3" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>1510</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>17.44</v>
       </c>
     </row>
     <row r="22">
@@ -1911,7 +1855,7 @@
         <v>21.96</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>4.08</v>
@@ -1971,7 +1915,7 @@
         <v>29.12</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>11.43</v>
@@ -2021,40 +1965,26 @@
       <c r="K24" s="2" t="n">
         <v>-27.53</v>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L24" s="2" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>8.67</v>
       </c>
     </row>
     <row r="25">
@@ -2105,7 +2035,7 @@
         <v>18.28</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>5.52</v>
@@ -2165,7 +2095,7 @@
         <v>28.23</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="P26" s="2" t="n">
         <v>5.23</v>
@@ -2285,7 +2215,7 @@
         <v>37.27</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="P28" s="2" t="n">
         <v>9.869999999999999</v>
@@ -2335,40 +2265,26 @@
       <c r="K29" s="3" t="n">
         <v>-34.09</v>
       </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L29" s="3" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>1419</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>6.61</v>
       </c>
     </row>
     <row r="30">
@@ -2419,7 +2335,7 @@
         <v>24.92</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="P30" s="2" t="n">
         <v>4.78</v>
@@ -2469,40 +2385,26 @@
       <c r="K31" s="3" t="n">
         <v>-12.35</v>
       </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L31" s="3" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>1458</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>6.52</v>
       </c>
     </row>
     <row r="32">
@@ -2553,7 +2455,7 @@
         <v>26.09</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>7.58</v>
@@ -2603,40 +2505,26 @@
       <c r="K33" s="3" t="n">
         <v>-43.51</v>
       </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L33" s="3" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>1426</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>6.05</v>
       </c>
     </row>
     <row r="34">
@@ -2687,7 +2575,7 @@
         <v>21.36</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>0.92</v>
@@ -2737,40 +2625,26 @@
       <c r="K35" s="3" t="n">
         <v>-56.86</v>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>4.81</v>
       </c>
     </row>
     <row r="36">
@@ -2821,7 +2695,7 @@
         <v>19.56</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="P36" s="2" t="n">
         <v>6.92</v>
@@ -2871,40 +2745,26 @@
       <c r="K37" s="3" t="n">
         <v>-82.47</v>
       </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L37" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>1428</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="38">
@@ -2955,7 +2815,7 @@
         <v>21.13</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>2.83</v>
@@ -3015,7 +2875,7 @@
         <v>-0.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>6.18</v>
@@ -3075,7 +2935,7 @@
         <v>32.76</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="P40" s="2" t="n">
         <v>3.1</v>
@@ -3249,7 +3109,7 @@
         <v>28.03</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="5">
@@ -3342,7 +3202,7 @@
         <v>16.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="8">
@@ -3435,7 +3295,7 @@
         <v>25.3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1595</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="11">
@@ -3497,7 +3357,7 @@
         <v>19.72</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1565</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="13">
@@ -3528,804 +3388,720 @@
         <v>18.53</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1546</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>28.04</v>
+        <v>44.43</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>58.16</v>
+        <v>58.22</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>58.16</v>
+        <v>58.22</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10.26</v>
+        <v>14.97</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>31.79</v>
+        <v>30.2</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>16.11</v>
+        <v>13.05</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1529</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>29.21</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>54.22</v>
+        <v>58.16</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>54.22</v>
+        <v>58.16</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>7.1</v>
+        <v>10.26</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>32.25</v>
+        <v>31.79</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>14.86</v>
+        <v>16.11</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1521</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5980</v>
+        <v>9756</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>38.55</v>
+        <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>44.8</v>
+        <v>54.22</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>44.8</v>
+        <v>54.22</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.51</v>
+        <v>7.1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>26.4</v>
+        <v>32.25</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.89</v>
+        <v>14.86</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1501</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>8767</v>
+        <v>9685</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.21</v>
+        <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>42.92</v>
+        <v>49.84</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>42.92</v>
+        <v>49.84</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>10.92</v>
+        <v>21.5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>20.41</v>
+        <v>10.91</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>11.59</v>
+        <v>17.44</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1495</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4325</v>
+        <v>5980</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>32.52</v>
+        <v>38.55</v>
       </c>
       <c r="D18" s="2" t="n